--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -3499,7 +3499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="24" min="1" max="1"/>
@@ -3539,6 +3539,26 @@
       <c r="F1" s="44" t="inlineStr">
         <is>
           <t>Degree</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Foto (arquivo)</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Crédito da foto</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Link da fonte da foto</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Nota da foto (opcional)</t>
         </is>
       </c>
     </row>

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -3541,22 +3541,22 @@
           <t>Degree</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="24" t="inlineStr">
         <is>
           <t>Foto (arquivo)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="24" t="inlineStr">
         <is>
           <t>Crédito da foto</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="24" t="inlineStr">
         <is>
           <t>Link da fonte da foto</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="24" t="inlineStr">
         <is>
           <t>Nota da foto (opcional)</t>
         </is>
@@ -3592,6 +3592,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A2)+COUNTIF(Edges!$B$2:$B$120,A2)</f>
         <v/>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>assoc.jpg</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — não retrata a sede real</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="23.25" customHeight="1" s="25">
       <c r="A3" s="45" t="inlineStr">
@@ -3778,6 +3798,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A8)+COUNTIF(Edges!$B$2:$B$120,A8)</f>
         <v/>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>sala.jpg</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — não retrata a sede real</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="25">
       <c r="A9" s="45" t="inlineStr">
@@ -3809,6 +3849,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A9)+COUNTIF(Edges!$B$2:$B$120,A9)</f>
         <v/>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>bravo.jpg</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Samuel Zeller · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Assembly_Line_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — linha de produção genérica, não retrata a fábrica real</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="25">
       <c r="A10" s="45" t="inlineStr">
@@ -3871,6 +3931,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A11)+COUNTIF(Edges!$B$2:$B$120,A11)</f>
         <v/>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>escw.jpg</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — não retrata a sede real</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="25">
       <c r="A12" s="45" t="inlineStr">
@@ -3902,6 +3982,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A12)+COUNTIF(Edges!$B$2:$B$120,A12)</f>
         <v/>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>bets.jpg</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Maximo Betman · CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Mesa-de-ruleta-casino-ciudad-de-mexico25-04-2023.jpg</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — mesa de cassino genérica, não retrata a empresa real</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="25">
       <c r="A13" s="45" t="inlineStr">
@@ -3964,6 +4064,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A14)+COUNTIF(Edges!$B$2:$B$120,A14)</f>
         <v/>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>wt.jpg</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — não retrata a sede real</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="15" customHeight="1" s="25">
       <c r="A15" s="45" t="inlineStr">
@@ -3995,6 +4115,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A15)+COUNTIF(Edges!$B$2:$B$120,A15)</f>
         <v/>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>alcazar.jpg</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — não retrata a sede real</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="15" customHeight="1" s="25">
       <c r="A16" s="45" t="inlineStr">
@@ -4026,6 +4166,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A16)+COUNTIF(Edges!$B$2:$B$120,A16)</f>
         <v/>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>santander.jpg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Simplus Menegati · CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Agencia_Banco_Santander_de_Telemaco_Borba.jpg</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="25">
       <c r="A17" s="45" t="inlineStr">
@@ -4057,6 +4213,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A17)+COUNTIF(Edges!$B$2:$B$120,A17)</f>
         <v/>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>cpi.jpg</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Agência Senado · CC BY 2.0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:CPIPANDEMIA_-_Comiss%C3%A3o_Parlamentar_de_Inqu%C3%A9rito_da_Pandemia_(1).jpg</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="25">
       <c r="A18" s="45" t="inlineStr">
@@ -4212,6 +4384,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A22)+COUNTIF(Edges!$B$2:$B$120,A22)</f>
         <v/>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>escf.jpg</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — não retrata a sede real</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="15" customHeight="1" s="25">
       <c r="A23" s="45" t="inlineStr">
@@ -4243,6 +4435,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A23)+COUNTIF(Edges!$B$2:$B$120,A23)</f>
         <v/>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>ong.jpg</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — não retrata a sede real</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="15" customHeight="1" s="25">
       <c r="A24" s="45" t="inlineStr">
@@ -4460,6 +4672,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A30)+COUNTIF(Edges!$B$2:$B$120,A30)</f>
         <v/>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>master.jpg</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Anthony Esau · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Farm_Credit_Bank_Building_2016_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — agência bancária genérica, não retrata o Banco Master</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customHeight="1" s="25">
       <c r="A31" s="45" t="inlineStr">
@@ -4553,6 +4785,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A33)+COUNTIF(Edges!$B$2:$B$120,A33)</f>
         <v/>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>primeu.jpg</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — não retrata a sede real</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="15" customHeight="1" s="25">
       <c r="A34" s="45" t="inlineStr">
@@ -4584,6 +4836,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A34)+COUNTIF(Edges!$B$2:$B$120,A34)</f>
         <v/>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>luri.jpg</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — não retrata a sede real</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="23.25" customHeight="1" s="25">
       <c r="A35" s="45" t="inlineStr">
@@ -4708,6 +4980,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A38)+COUNTIF(Edges!$B$2:$B$120,A38)</f>
         <v/>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>angra.jpg</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Tim Gouw · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Drone_pool_and_deck_chairs_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — não retrata o imóvel real</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="25">
       <c r="A39" s="45" t="inlineStr">
@@ -4739,6 +5031,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A39)+COUNTIF(Edges!$B$2:$B$120,A39)</f>
         <v/>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>aptosp.jpg</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Grant Lemons · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Modern_apartment_building_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — não retrata o imóvel real</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="15" customHeight="1" s="25">
       <c r="A40" s="45" t="inlineStr">
@@ -4770,6 +5082,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A40)+COUNTIF(Edges!$B$2:$B$120,A40)</f>
         <v/>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>triplex.jpg</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Grant Lemons · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Modern_apartment_building_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — não retrata o imóvel real</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="23.25" customHeight="1" s="25">
       <c r="A41" s="45" t="inlineStr">
@@ -4801,6 +5133,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A41)+COUNTIF(Edges!$B$2:$B$120,A41)</f>
         <v/>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>jato.jpg</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Checkerberry · CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Flexjet_Embraer_EMB-545_Praetor_500_(N446FX)_Landing_Runway_22_at_KLEX.jpg</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — jato executivo genérico, não retrata a aeronave real</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="15" customHeight="1" s="25">
       <c r="A42" s="45" t="inlineStr">
@@ -4832,6 +5184,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A42)+COUNTIF(Edges!$B$2:$B$120,A42)</f>
         <v/>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>atibaia.jpg</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Ritchie Valens · CC0 (Unsplash via Wikimedia Commons)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Cozy_Cottage_Home_(Unsplash).jpg</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — não retrata o imóvel real</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="15" customHeight="1" s="25">
       <c r="A43" s="45" t="inlineStr">
@@ -5018,6 +5390,26 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A48)+COUNTIF(Edges!$B$2:$B$120,A48)</f>
         <v/>
       </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>coaf.jpg</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>frankieleon · CC BY 2.0</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Scales_of_Justice_(3285348799).jpg</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Imagem ilustrativa — símbolo da justiça, não retrata o caso real</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="15" customHeight="1" s="25">
       <c r="A49" s="45" t="inlineStr">
@@ -5142,6 +5534,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A52)+COUNTIF(Edges!$B$2:$B$120,A52)</f>
         <v/>
       </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>abin.jpg</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Antonio Cruz/Agência Brasil · CC BY 3.0 BR</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Pr%C3%A9dio_da_Abin.jpg</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="25">
       <c r="A53" s="45" t="inlineStr">
@@ -5173,6 +5581,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A53)+COUNTIF(Edges!$B$2:$B$120,A53)</f>
         <v/>
       </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>receita.jpg</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Academia de Letras de Campo Maior · CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Ag%C3%AAncia_da_Receita_Federal_de_Campo_Maior,_Piau%C3%AD,_Brasil.JPG</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="25">
       <c r="A54" s="45" t="inlineStr">
@@ -5204,6 +5628,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A54)+COUNTIF(Edges!$B$2:$B$120,A54)</f>
         <v/>
       </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>pf.jpg</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Agência Senado · CC BY 2.0</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Sede_da_Pol%C3%ADcia_Federal_(52830107256).jpg</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
     </row>
     <row r="55" ht="15" customHeight="1" s="25">
       <c r="A55" s="45" t="inlineStr">
@@ -5235,6 +5675,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A55)+COUNTIF(Edges!$B$2:$B$120,A55)</f>
         <v/>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>pgr.jpg</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Webysther · CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Webysther_20180212174501_-_PGR_-_Procuradoria_Geral_da_Rep%C3%BAblica.jpg</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
     </row>
     <row r="56" ht="23.25" customHeight="1" s="25">
       <c r="A56" s="45" t="inlineStr">
@@ -5297,6 +5753,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A57)+COUNTIF(Edges!$B$2:$B$120,A57)</f>
         <v/>
       </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>stf.jpg</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Daderot · CC0 (domínio público)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Supremo_Tribunal_Federal_building_in_Brasilia_-_DSC00288.JPG</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
     </row>
     <row r="58" ht="15" customHeight="1" s="25">
       <c r="A58" s="45" t="inlineStr">
@@ -5328,6 +5800,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A58)+COUNTIF(Edges!$B$2:$B$120,A58)</f>
         <v/>
       </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>tse.jpg</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Alexandresena · CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Sede_do_Tribunal_Superior_Eleitoral,_em_Bras%C3%ADlia.jpg</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F58"/>

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -3592,26 +3592,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A2)+COUNTIF(Edges!$B$2:$B$120,A2)</f>
         <v/>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>assoc.jpg</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — não retrata a sede real</t>
-        </is>
-      </c>
+      <c r="G2" s="24" t="n"/>
+      <c r="H2" s="24" t="n"/>
+      <c r="I2" s="24" t="n"/>
+      <c r="J2" s="24" t="n"/>
     </row>
     <row r="3" ht="23.25" customHeight="1" s="25">
       <c r="A3" s="45" t="inlineStr">
@@ -3798,26 +3782,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A8)+COUNTIF(Edges!$B$2:$B$120,A8)</f>
         <v/>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>sala.jpg</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — não retrata a sede real</t>
-        </is>
-      </c>
+      <c r="G8" s="24" t="n"/>
+      <c r="H8" s="24" t="n"/>
+      <c r="I8" s="24" t="n"/>
+      <c r="J8" s="24" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="25">
       <c r="A9" s="45" t="inlineStr">
@@ -3849,26 +3817,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A9)+COUNTIF(Edges!$B$2:$B$120,A9)</f>
         <v/>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>bravo.jpg</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Samuel Zeller · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Assembly_Line_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — linha de produção genérica, não retrata a fábrica real</t>
-        </is>
-      </c>
+      <c r="G9" s="24" t="n"/>
+      <c r="H9" s="24" t="n"/>
+      <c r="I9" s="24" t="n"/>
+      <c r="J9" s="24" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="25">
       <c r="A10" s="45" t="inlineStr">
@@ -3931,26 +3883,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A11)+COUNTIF(Edges!$B$2:$B$120,A11)</f>
         <v/>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>escw.jpg</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — não retrata a sede real</t>
-        </is>
-      </c>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
+      <c r="I11" s="24" t="n"/>
+      <c r="J11" s="24" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="25">
       <c r="A12" s="45" t="inlineStr">
@@ -3982,26 +3918,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A12)+COUNTIF(Edges!$B$2:$B$120,A12)</f>
         <v/>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>bets.jpg</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Maximo Betman · CC BY-SA 4.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Mesa-de-ruleta-casino-ciudad-de-mexico25-04-2023.jpg</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — mesa de cassino genérica, não retrata a empresa real</t>
-        </is>
-      </c>
+      <c r="G12" s="24" t="inlineStr">
+        <is>
+          <t>bets.png</t>
+        </is>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
+        <is>
+          <t>blaze.com · domínio público (logo simples, sem direito autoral)</t>
+        </is>
+      </c>
+      <c r="I12" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Blaze_apostas_logo.png</t>
+        </is>
+      </c>
+      <c r="J12" s="24" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1" s="25">
       <c r="A13" s="45" t="inlineStr">
@@ -4064,26 +3996,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A14)+COUNTIF(Edges!$B$2:$B$120,A14)</f>
         <v/>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>wt.jpg</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — não retrata a sede real</t>
-        </is>
-      </c>
+      <c r="G14" s="24" t="n"/>
+      <c r="H14" s="24" t="n"/>
+      <c r="I14" s="24" t="n"/>
+      <c r="J14" s="24" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="25">
       <c r="A15" s="45" t="inlineStr">
@@ -4115,26 +4031,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A15)+COUNTIF(Edges!$B$2:$B$120,A15)</f>
         <v/>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>alcazar.jpg</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — não retrata a sede real</t>
-        </is>
-      </c>
+      <c r="G15" s="24" t="n"/>
+      <c r="H15" s="24" t="n"/>
+      <c r="I15" s="24" t="n"/>
+      <c r="J15" s="24" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="25">
       <c r="A16" s="45" t="inlineStr">
@@ -4166,22 +4066,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A16)+COUNTIF(Edges!$B$2:$B$120,A16)</f>
         <v/>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="24" t="inlineStr">
         <is>
           <t>santander.jpg</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>Simplus Menegati · CC BY-SA 4.0</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Agencia_Banco_Santander_de_Telemaco_Borba.jpg</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" s="24" t="inlineStr"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="25">
       <c r="A17" s="45" t="inlineStr">
@@ -4213,22 +4113,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A17)+COUNTIF(Edges!$B$2:$B$120,A17)</f>
         <v/>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>cpi.jpg</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>Agência Senado · CC BY 2.0</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I17" s="24" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:CPIPANDEMIA_-_Comiss%C3%A3o_Parlamentar_de_Inqu%C3%A9rito_da_Pandemia_(1).jpg</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
+      <c r="J17" s="24" t="inlineStr"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="25">
       <c r="A18" s="45" t="inlineStr">
@@ -4384,26 +4284,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A22)+COUNTIF(Edges!$B$2:$B$120,A22)</f>
         <v/>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>escf.jpg</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — não retrata a sede real</t>
-        </is>
-      </c>
+      <c r="G22" s="24" t="n"/>
+      <c r="H22" s="24" t="n"/>
+      <c r="I22" s="24" t="n"/>
+      <c r="J22" s="24" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1" s="25">
       <c r="A23" s="45" t="inlineStr">
@@ -4435,26 +4319,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A23)+COUNTIF(Edges!$B$2:$B$120,A23)</f>
         <v/>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>ong.jpg</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — não retrata a sede real</t>
-        </is>
-      </c>
+      <c r="G23" s="24" t="n"/>
+      <c r="H23" s="24" t="n"/>
+      <c r="I23" s="24" t="n"/>
+      <c r="J23" s="24" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1" s="25">
       <c r="A24" s="45" t="inlineStr">
@@ -4672,26 +4540,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A30)+COUNTIF(Edges!$B$2:$B$120,A30)</f>
         <v/>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>master.jpg</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Anthony Esau · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Farm_Credit_Bank_Building_2016_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — agência bancária genérica, não retrata o Banco Master</t>
-        </is>
-      </c>
+      <c r="G30" s="24" t="n"/>
+      <c r="H30" s="24" t="n"/>
+      <c r="I30" s="24" t="n"/>
+      <c r="J30" s="24" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="25">
       <c r="A31" s="45" t="inlineStr">
@@ -4785,26 +4637,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A33)+COUNTIF(Edges!$B$2:$B$120,A33)</f>
         <v/>
       </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>primeu.jpg</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — não retrata a sede real</t>
-        </is>
-      </c>
+      <c r="G33" s="24" t="n"/>
+      <c r="H33" s="24" t="n"/>
+      <c r="I33" s="24" t="n"/>
+      <c r="J33" s="24" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1" s="25">
       <c r="A34" s="45" t="inlineStr">
@@ -4836,26 +4672,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A34)+COUNTIF(Edges!$B$2:$B$120,A34)</f>
         <v/>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>luri.jpg</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Riku Lu · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Office_district_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — não retrata a sede real</t>
-        </is>
-      </c>
+      <c r="G34" s="24" t="n"/>
+      <c r="H34" s="24" t="n"/>
+      <c r="I34" s="24" t="n"/>
+      <c r="J34" s="24" t="n"/>
     </row>
     <row r="35" ht="23.25" customHeight="1" s="25">
       <c r="A35" s="45" t="inlineStr">
@@ -4980,26 +4800,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A38)+COUNTIF(Edges!$B$2:$B$120,A38)</f>
         <v/>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>angra.jpg</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Tim Gouw · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Drone_pool_and_deck_chairs_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — não retrata o imóvel real</t>
-        </is>
-      </c>
+      <c r="G38" s="24" t="n"/>
+      <c r="H38" s="24" t="n"/>
+      <c r="I38" s="24" t="n"/>
+      <c r="J38" s="24" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1" s="25">
       <c r="A39" s="45" t="inlineStr">
@@ -5031,26 +4835,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A39)+COUNTIF(Edges!$B$2:$B$120,A39)</f>
         <v/>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>aptosp.jpg</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Grant Lemons · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Modern_apartment_building_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — não retrata o imóvel real</t>
-        </is>
-      </c>
+      <c r="G39" s="24" t="n"/>
+      <c r="H39" s="24" t="n"/>
+      <c r="I39" s="24" t="n"/>
+      <c r="J39" s="24" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1" s="25">
       <c r="A40" s="45" t="inlineStr">
@@ -5082,26 +4870,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A40)+COUNTIF(Edges!$B$2:$B$120,A40)</f>
         <v/>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>triplex.jpg</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Grant Lemons · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Modern_apartment_building_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — não retrata o imóvel real</t>
-        </is>
-      </c>
+      <c r="G40" s="24" t="n"/>
+      <c r="H40" s="24" t="n"/>
+      <c r="I40" s="24" t="n"/>
+      <c r="J40" s="24" t="n"/>
     </row>
     <row r="41" ht="23.25" customHeight="1" s="25">
       <c r="A41" s="45" t="inlineStr">
@@ -5133,26 +4905,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A41)+COUNTIF(Edges!$B$2:$B$120,A41)</f>
         <v/>
       </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>jato.jpg</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Checkerberry · CC BY-SA 4.0</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Flexjet_Embraer_EMB-545_Praetor_500_(N446FX)_Landing_Runway_22_at_KLEX.jpg</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — jato executivo genérico, não retrata a aeronave real</t>
-        </is>
-      </c>
+      <c r="G41" s="24" t="n"/>
+      <c r="H41" s="24" t="n"/>
+      <c r="I41" s="24" t="n"/>
+      <c r="J41" s="24" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1" s="25">
       <c r="A42" s="45" t="inlineStr">
@@ -5184,26 +4940,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A42)+COUNTIF(Edges!$B$2:$B$120,A42)</f>
         <v/>
       </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>atibaia.jpg</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Ritchie Valens · CC0 (Unsplash via Wikimedia Commons)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Cozy_Cottage_Home_(Unsplash).jpg</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — não retrata o imóvel real</t>
-        </is>
-      </c>
+      <c r="G42" s="24" t="n"/>
+      <c r="H42" s="24" t="n"/>
+      <c r="I42" s="24" t="n"/>
+      <c r="J42" s="24" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1" s="25">
       <c r="A43" s="45" t="inlineStr">
@@ -5390,26 +5130,10 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A48)+COUNTIF(Edges!$B$2:$B$120,A48)</f>
         <v/>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>coaf.jpg</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>frankieleon · CC BY 2.0</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>https://commons.wikimedia.org/wiki/File:Scales_of_Justice_(3285348799).jpg</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Imagem ilustrativa — símbolo da justiça, não retrata o caso real</t>
-        </is>
-      </c>
+      <c r="G48" s="24" t="n"/>
+      <c r="H48" s="24" t="n"/>
+      <c r="I48" s="24" t="n"/>
+      <c r="J48" s="24" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1" s="25">
       <c r="A49" s="45" t="inlineStr">
@@ -5534,22 +5258,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A52)+COUNTIF(Edges!$B$2:$B$120,A52)</f>
         <v/>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G52" s="24" t="inlineStr">
         <is>
           <t>abin.jpg</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H52" s="24" t="inlineStr">
         <is>
           <t>Antonio Cruz/Agência Brasil · CC BY 3.0 BR</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I52" s="24" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Pr%C3%A9dio_da_Abin.jpg</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr"/>
+      <c r="J52" s="24" t="inlineStr"/>
     </row>
     <row r="53" ht="15" customHeight="1" s="25">
       <c r="A53" s="45" t="inlineStr">
@@ -5581,22 +5305,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A53)+COUNTIF(Edges!$B$2:$B$120,A53)</f>
         <v/>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="G53" s="24" t="inlineStr">
         <is>
           <t>receita.jpg</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H53" s="24" t="inlineStr">
         <is>
           <t>Academia de Letras de Campo Maior · CC BY-SA 4.0</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="I53" s="24" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Ag%C3%AAncia_da_Receita_Federal_de_Campo_Maior,_Piau%C3%AD,_Brasil.JPG</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" s="24" t="inlineStr"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="25">
       <c r="A54" s="45" t="inlineStr">
@@ -5628,22 +5352,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A54)+COUNTIF(Edges!$B$2:$B$120,A54)</f>
         <v/>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G54" s="24" t="inlineStr">
         <is>
           <t>pf.jpg</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H54" s="24" t="inlineStr">
         <is>
           <t>Agência Senado · CC BY 2.0</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I54" s="24" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Sede_da_Pol%C3%ADcia_Federal_(52830107256).jpg</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
+      <c r="J54" s="24" t="inlineStr"/>
     </row>
     <row r="55" ht="15" customHeight="1" s="25">
       <c r="A55" s="45" t="inlineStr">
@@ -5675,22 +5399,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A55)+COUNTIF(Edges!$B$2:$B$120,A55)</f>
         <v/>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="G55" s="24" t="inlineStr">
         <is>
           <t>pgr.jpg</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="H55" s="24" t="inlineStr">
         <is>
           <t>Webysther · CC BY-SA 4.0</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="I55" s="24" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Webysther_20180212174501_-_PGR_-_Procuradoria_Geral_da_Rep%C3%BAblica.jpg</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr"/>
+      <c r="J55" s="24" t="inlineStr"/>
     </row>
     <row r="56" ht="23.25" customHeight="1" s="25">
       <c r="A56" s="45" t="inlineStr">
@@ -5753,22 +5477,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A57)+COUNTIF(Edges!$B$2:$B$120,A57)</f>
         <v/>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="G57" s="24" t="inlineStr">
         <is>
           <t>stf.jpg</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="H57" s="24" t="inlineStr">
         <is>
           <t>Daderot · CC0 (domínio público)</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="I57" s="24" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Supremo_Tribunal_Federal_building_in_Brasilia_-_DSC00288.JPG</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" s="24" t="inlineStr"/>
     </row>
     <row r="58" ht="15" customHeight="1" s="25">
       <c r="A58" s="45" t="inlineStr">
@@ -5800,22 +5524,22 @@
         <f>COUNTIF(Edges!$A$2:$A$120,A58)+COUNTIF(Edges!$B$2:$B$120,A58)</f>
         <v/>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="G58" s="24" t="inlineStr">
         <is>
           <t>tse.jpg</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="H58" s="24" t="inlineStr">
         <is>
           <t>Alexandresena · CC BY-SA 4.0</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="I58" s="24" t="inlineStr">
         <is>
           <t>https://commons.wikimedia.org/wiki/File:Sede_do_Tribunal_Superior_Eleitoral,_em_Bras%C3%ADlia.jpg</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr"/>
+      <c r="J58" s="24" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F58"/>

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B7" s="38" t="inlineStr">
         <is>
-          <t>Willer Tomaz (planilha: "Tomás")</t>
+          <t>Willer Tomaz</t>
         </is>
       </c>
       <c r="C7" s="37" t="inlineStr">
         <is>
-          <t>Willer Tomás e sua rede</t>
+          <t>Willer Tomaz e sua rede</t>
         </is>
       </c>
       <c r="D7" s="37" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="J7" s="37" t="inlineStr">
         <is>
-          <t>Grafia na imprensa é "Tomaz".</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K7" s="37" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="C8" s="37" t="inlineStr">
         <is>
-          <t>Willer Tomás e sua rede</t>
+          <t>Willer Tomaz e sua rede</t>
         </is>
       </c>
       <c r="D8" s="37" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="C9" s="37" t="inlineStr">
         <is>
-          <t>Willer Tomás e sua rede</t>
+          <t>Willer Tomaz e sua rede</t>
         </is>
       </c>
       <c r="D9" s="37" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B14" s="38" t="inlineStr">
         <is>
-          <t>Frederick Wassef (planilha: "Frederico")</t>
+          <t>Frederick Wassef</t>
         </is>
       </c>
       <c r="C14" s="37" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="J14" s="37" t="inlineStr">
         <is>
-          <t>Grafia correta é "Frederick". Não confirmei a resposta da PGR após julho.</t>
+          <t>Não confirmei a resposta da PGR após julho.</t>
         </is>
       </c>
       <c r="K14" s="37" t="inlineStr">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="B18" s="38" t="inlineStr">
         <is>
-          <t>Fabiano Campos Zettel (planilha: "Zetel")</t>
+          <t>Fabiano Campos Zettel</t>
         </is>
       </c>
       <c r="C18" s="37" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="J18" s="37" t="inlineStr">
         <is>
-          <t>Grafia na imprensa: "Zettel". Não achei a venda do apartamento à WT nas fontes que abri.</t>
+          <t>Não achei a venda do apartamento à WT nas fontes que abri.</t>
         </is>
       </c>
       <c r="K18" s="37" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B26" s="38" t="inlineStr">
         <is>
-          <t>Kassio Nunes Marques</t>
+          <t>Kássio Nunes Marques</t>
         </is>
       </c>
       <c r="C26" s="37" t="inlineStr">
@@ -3329,7 +3329,7 @@
       </c>
       <c r="B30" s="38" t="inlineStr">
         <is>
-          <t>Sergio Fernando Moro</t>
+          <t>Sérgio Fernando Moro</t>
         </is>
       </c>
       <c r="C30" s="37" t="inlineStr">
@@ -3830,7 +3830,7 @@
       </c>
       <c r="B10" s="45" t="inlineStr">
         <is>
-          <t>Willer Tomás</t>
+          <t>Willer Tomaz</t>
         </is>
       </c>
       <c r="C10" s="45" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="D10" s="45" t="inlineStr">
         <is>
-          <t>Willer Tomás e sua rede</t>
+          <t>Willer Tomaz e sua rede</t>
         </is>
       </c>
       <c r="E10" s="45" t="inlineStr">
@@ -3871,7 +3871,7 @@
       </c>
       <c r="D11" s="45" t="inlineStr">
         <is>
-          <t>Willer Tomás e sua rede</t>
+          <t>Willer Tomaz e sua rede</t>
         </is>
       </c>
       <c r="E11" s="45" t="inlineStr">
@@ -3906,7 +3906,7 @@
       </c>
       <c r="D12" s="45" t="inlineStr">
         <is>
-          <t>Willer Tomás e sua rede</t>
+          <t>Willer Tomaz e sua rede</t>
         </is>
       </c>
       <c r="E12" s="45" t="inlineStr">
@@ -3953,7 +3953,7 @@
       </c>
       <c r="D13" s="45" t="inlineStr">
         <is>
-          <t>Willer Tomás e sua rede</t>
+          <t>Willer Tomaz e sua rede</t>
         </is>
       </c>
       <c r="E13" s="45" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="D14" s="45" t="inlineStr">
         <is>
-          <t>Willer Tomás e sua rede</t>
+          <t>Willer Tomaz e sua rede</t>
         </is>
       </c>
       <c r="E14" s="45" t="inlineStr">
@@ -4019,7 +4019,7 @@
       </c>
       <c r="D15" s="45" t="inlineStr">
         <is>
-          <t>Willer Tomás e sua rede</t>
+          <t>Willer Tomaz e sua rede</t>
         </is>
       </c>
       <c r="E15" s="45" t="inlineStr">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
-          <t>Willer Tomás e sua rede</t>
+          <t>Willer Tomaz e sua rede</t>
         </is>
       </c>
       <c r="E16" s="45" t="inlineStr">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
-          <t>Willer Tomás e sua rede</t>
+          <t>Willer Tomaz e sua rede</t>
         </is>
       </c>
       <c r="E17" s="45" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="D18" s="45" t="inlineStr">
         <is>
-          <t>Willer Tomás e sua rede</t>
+          <t>Willer Tomaz e sua rede</t>
         </is>
       </c>
       <c r="E18" s="45" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="B26" s="45" t="inlineStr">
         <is>
-          <t>Frederico Wassef</t>
+          <t>Frederick Wassef</t>
         </is>
       </c>
       <c r="C26" s="45" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="B31" s="45" t="inlineStr">
         <is>
-          <t>Fabiano Zetel</t>
+          <t>Fabiano Zettel</t>
         </is>
       </c>
       <c r="C31" s="45" t="inlineStr">

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Perfis'!$A$1:$M$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Perfis'!$A$1:$P$35</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Nodes'!$A$1:$F$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Edges'!$A$1:$F$120</definedName>
   </definedNames>
@@ -967,10 +967,11 @@
     <row r="2" ht="15" customHeight="1" s="25">
       <c r="A2" s="27" t="inlineStr">
         <is>
-          <t>Pesquisa em fontes públicas, atualizada em 20/10/2026 (revisão 2). Estágio ≠ culpa: só os "Condenado" têm decisão condenatória.</t>
-        </is>
-      </c>
-    </row>
+          <t>Pesquisa em fontes públicas, atualizada em 21/10/2026 (revisão 3, com o acervo a verdade.). Estágio ≠ culpa: só os "Condenado" têm decisão condenatória.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="25">
       <c r="A4" s="28" t="inlineStr">
         <is>
@@ -995,7 +996,7 @@
         </is>
       </c>
       <c r="B5" s="24">
-        <f>COUNTIF(Perfis!$H$2:$H$31,A5)</f>
+        <f>COUNTIF(Perfis!$H$2:$H$35,A5)</f>
         <v/>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -1011,7 +1012,7 @@
         </is>
       </c>
       <c r="B6" s="24">
-        <f>COUNTIF(Perfis!$H$2:$H$31,A6)</f>
+        <f>COUNTIF(Perfis!$H$2:$H$35,A6)</f>
         <v/>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -1027,12 +1028,12 @@
         </is>
       </c>
       <c r="B7" s="24">
-        <f>COUNTIF(Perfis!$H$2:$H$31,A7)</f>
+        <f>COUNTIF(Perfis!$H$2:$H$35,A7)</f>
         <v/>
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>Fábio Luís Lula da Silva; Roberta Moreira Luchsinger; Willer Tomaz; Flávio Bolsonaro; Carlos Bolsonaro; Frederick Wassef; Ciro Nogueira</t>
+          <t>Fábio Luís Lula da Silva; Roberta Moreira Luchsinger; Willer Tomaz; Flávio Bolsonaro; Carlos Bolsonaro; Frederick Wassef; Ciro Nogueira; Mario Frias</t>
         </is>
       </c>
     </row>
@@ -1043,12 +1044,12 @@
         </is>
       </c>
       <c r="B8" s="24">
-        <f>COUNTIF(Perfis!$H$2:$H$31,A8)</f>
+        <f>COUNTIF(Perfis!$H$2:$H$35,A8)</f>
         <v/>
       </c>
       <c r="C8" s="30" t="inlineStr">
         <is>
-          <t>Letícia Caetano dos Reis; Lídia Maria Figueiredo Mazelli; Renan Calheiros; Fabrício José Carlos de Queiroz; Richarlison; Kassio Nunes Marques; Kevin Marques; Sergio Fernando Moro</t>
+          <t>Letícia Caetano dos Reis; Lídia Maria Figueiredo Mazelli; Renan Calheiros; Fabrício José Carlos de Queiroz; Richarlison; Kassio Nunes Marques; Kevin Marques; Sergio Fernando Moro; André Mendonça; Fábio Faria; Alfredo Gaspar</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1060,7 @@
         </is>
       </c>
       <c r="B9" s="24">
-        <f>COUNTIF(Perfis!$H$2:$H$31,A9)</f>
+        <f>COUNTIF(Perfis!$H$2:$H$35,A9)</f>
         <v/>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -1079,6 +1080,23 @@
         <v/>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="25">
       <c r="A28" s="35" t="inlineStr">
         <is>
@@ -1150,7 +1168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="24" min="1" max="1"/>
@@ -1303,7 +1321,7 @@
       </c>
       <c r="K2" s="37" t="inlineStr">
         <is>
-          <t>CNN Brasil 12/09/2025 https://www.cnnbrasil.com.br/politica/quem-e-o-careca-do-inss-preso-em-operacao-da-pf-nesta-sexta-12/ | Delação (fev/2026) https://portaldeprefeitura.com.br/bastidores-da-politica/policia-federal/careca-do-inss-prepara-proposta-de-delacao-premiada-lulinha/615241/ | Gazeta do Povo https://www.gazetadopovo.com.br/republica/mendonca-mantem-prisao-preventiva-do-careca-do-inss/ | Rondônia ao Vivo 09/09/2026 https://www.rondoniaovivo.com/noticia/geral/2026/09/09/stf-mendonca-manda-soltar-filho-do-careca-do-inss.html | Metrópoles https://www.metropoles.com/colunas/manoela-alcantara/careca-do-inss-e-transferido-para-ala-de-vulneraveis-da-papuda</t>
+          <t>CNN Brasil 12/09/2025 https://www.cnnbrasil.com.br/politica/quem-e-o-careca-do-inss-preso-em-operacao-da-pf-nesta-sexta-12/ | Delação (fev/2026) https://portaldeprefeitura.com.br/bastidores-da-politica/policia-federal/careca-do-inss-prepara-proposta-de-delacao-premiada-lulinha/615241/ | Gazeta do Povo https://www.gazetadopovo.com.br/republica/mendonca-mantem-prisao-preventiva-do-careca-do-inss/ | Rondônia ao Vivo 09/09/2026 https://www.rondoniaovivo.com/noticia/geral/2026/09/09/stf-mendonca-manda-soltar-filho-do-careca-do-inss.html | Metrópoles https://www.metropoles.com/colunas/manoela-alcantara/careca-do-inss-e-transferido-para-ala-de-vulneraveis-da-papuda | Revogação da prisão do filho do Careca do INSS (iclnoticias.com.br) https://iclnoticias.com.br/andre-mendonca-revoga-prisao-do-filho-do-careca/ | Endereço e contabilidade compartilhados em Brasília (iclnoticias.com.br) https://iclnoticias.com.br/empresas-de-flavio-bolsonaro-e-careca-do-inss/</t>
         </is>
       </c>
       <c r="L2" s="37" t="inlineStr">
@@ -1313,7 +1331,7 @@
       </c>
       <c r="M2" s="37" t="inlineStr">
         <is>
-          <t>Confirmado preso em 09/09/2026; local, idade e decisão de jan/2026 adicionados.</t>
+          <t>Confirmado preso em 09/09/2026; local, idade e decisão de jan/2026 adicionados. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
       <c r="N2" s="24" t="inlineStr">
@@ -1385,7 +1403,7 @@
       </c>
       <c r="K3" s="37" t="inlineStr">
         <is>
-          <t>Bahia Notícias https://www.bahianoticias.com.br/noticia/321055-empresas-de-flavio-bolsonaro-e-careca-do-inss-dividem-a-mesma-sala-e-possuem-o-mesmo-contador</t>
+          <t>Bahia Notícias https://www.bahianoticias.com.br/noticia/321055-empresas-de-flavio-bolsonaro-e-careca-do-inss-dividem-a-mesma-sala-e-possuem-o-mesmo-contador | Endereço e contabilidade compartilhados em Brasília (iclnoticias.com.br) https://iclnoticias.com.br/empresas-de-flavio-bolsonaro-e-careca-do-inss/</t>
         </is>
       </c>
       <c r="L3" s="37" t="inlineStr">
@@ -1395,7 +1413,7 @@
       </c>
       <c r="M3" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
     </row>
@@ -1653,7 +1671,7 @@
       </c>
       <c r="K7" s="37" t="inlineStr">
         <is>
-          <t>A Tarde https://atarde.com.br/eleicoes/quem-e-willer-tomaz-advogado-suspeito-de-ligacao-com-flavio-bolsonaro-1406358 | Tribuna do Sertão 19/10/2026 https://www.tribunadosertao.com.br/poder-e-governo/2026/10/19/1000284-flavio-bolsonaro-e-investigado-pela-pf-por-suspeita-de-lavagem-de-dinheiro-com-advogado-willer-tomaz | CartaCapital 18/10/2026 https://www.cartacapital.com.br/politica/flavio-bolsonaro-e-alvo-de-segundo-inquerito-no-stf-por-suspeita-de-lavagem-de-dinheiro/ | CNN Brasil https://www.cnnbrasil.com.br/politica/advogado-amigo-de-flavio-movimentou-r-130-milhoes-em-tres-meses-diz-pf/</t>
+          <t>A Tarde https://atarde.com.br/eleicoes/quem-e-willer-tomaz-advogado-suspeito-de-ligacao-com-flavio-bolsonaro-1406358 | Tribuna do Sertão 19/10/2026 https://www.tribunadosertao.com.br/poder-e-governo/2026/10/19/1000284-flavio-bolsonaro-e-investigado-pela-pf-por-suspeita-de-lavagem-de-dinheiro-com-advogado-willer-tomaz | CartaCapital 18/10/2026 https://www.cartacapital.com.br/politica/flavio-bolsonaro-e-alvo-de-segundo-inquerito-no-stf-por-suspeita-de-lavagem-de-dinheiro/ | CNN Brasil https://www.cnnbrasil.com.br/politica/advogado-amigo-de-flavio-movimentou-r-130-milhoes-em-tres-meses-diz-pf/ | O voo no jato de Vorcaro em janeiro de 2025 (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-viajou-em-jato-de-vorcaro/ | E-mails sobre vínculo bancário com Willer Tomaz (noticias.uol.com.br) https://noticias.uol.com.br/colunas/fabio-serapiao/2026/10/10/flavio-dividia-conta-com-suspeito-de-lavar-dinheiro-do-inss-indicam-emails.htm | A disputa pelo imóvel comprado por Richarlison (iclnoticias.com.br) https://iclnoticias.com.br/advogado-defendia-amigo-de-flavio-bolsonaro/ | A disputa pelo imóvel comprado por Richarlison (iclnoticias.com.br) https://iclnoticias.com.br/pf-e-acionada-flavio-bolsonaro-richarlisson/</t>
         </is>
       </c>
       <c r="L7" s="37" t="inlineStr">
@@ -1663,7 +1681,7 @@
       </c>
       <c r="M7" s="37" t="inlineStr">
         <is>
-          <t>Data de entrada no STF (08/10/2026), valores e confirmação da busca de ago/2026.</t>
+          <t>Data de entrada no STF (08/10/2026), valores e confirmação da busca de ago/2026. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
       <c r="N7" s="24" t="inlineStr">
@@ -1879,12 +1897,12 @@
       </c>
       <c r="J10" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Acervo a verdade.: Aos Fatos contou ao menos 43 declarações falsas dele sobre a relação com Vorcaro. Os números do celular variam por fonte (Piauí: 11 meses e 110 registros; Estadão: 3 meses e 6 encontros) e não devem ser somados. Os R$ 134 mi negociados e ≥ R$ 61 mi repassados foram para o filme, o que não comprova recebimento pessoal.</t>
         </is>
       </c>
       <c r="K10" s="37" t="inlineStr">
         <is>
-          <t>Wikipedia pt https://pt.wikipedia.org/wiki/Fl%C3%A1vio_Bolsonaro | Tribuna do Sertão (link acima) | O Povo 23/07/2026 https://www.opovo.com.br/noticias/politica/2026/07/23/amp/andre-mendonca-autoriza-inquerito-sobre-repasses-para-dark-horse-filme-sobre-jair-bolsonaro.html | Resultado do 1º turno https://portaldeprefeitura.com.br/bastidores-da-politica/eleicoes-2026-com-100-das-secoes-totalizadas-flavio-tem-4703-e/633498/ | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal | JB 12/10/2026 https://www.jb.com.br/brasil/justica/2026/10/1061206-moraes-autoriza-flavio-bolsonaro-a-visitar-jair-bolsonaro-em-prisao-domiciliar.html</t>
+          <t>Wikipedia pt https://pt.wikipedia.org/wiki/Fl%C3%A1vio_Bolsonaro | Tribuna do Sertão (link acima) | O Povo 23/07/2026 https://www.opovo.com.br/noticias/politica/2026/07/23/amp/andre-mendonca-autoriza-inquerito-sobre-repasses-para-dark-horse-filme-sobre-jair-bolsonaro.html | Resultado do 1º turno https://portaldeprefeitura.com.br/bastidores-da-politica/eleicoes-2026-com-100-das-secoes-totalizadas-flavio-tem-4703-e/633498/ | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal | JB 12/10/2026 https://www.jb.com.br/brasil/justica/2026/10/1061206-moraes-autoriza-flavio-bolsonaro-a-visitar-jair-bolsonaro-em-prisao-domiciliar.html | A investigação sobre o financiamento de Dark Horse (bbc.com) https://www.bbc.com/portuguese/articles/c4g5ky0r25jo | A investigação sobre o financiamento de Dark Horse (em.com.br) https://www.em.com.br/politica/2026/09/7498387-flavio-bolsonaro-vira-investigado-do-dark-horse-que-segue-sob-sigilo.html | O acordo de R$ 134 milhões para o filme (intercept.com.br) https://www.intercept.com.br/2026/05/13/audio-flavio-negociou-vorcaro-milhoes/ | A checagem de declarações sobre Vorcaro (aosfatos.org) https://www.aosfatos.org/noticias/flavio-mentiu-ao-menos-43-vezes-sobre-envolvimento-com-vorcaro/ | Os registros de contato no celular do banqueiro (piaui.uol.com.br) https://piaui.uol.com.br/web/mensagens-celular-flavio-vorcaro/ | As menções a encontros presenciais (estadao.com.br) https://www.estadao.com.br/politica/celular-de-vorcaro-tinha-tres-meses-de-conversa-com-flavio-bolsonaro-e-mencao-a-seis-encontros/ | O voo no jato de Vorcaro em janeiro de 2025 (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-viajou-em-jato-de-vorcaro/ | O apartamento de Fabiano Zettel e Willer Tomaz (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-zettel-tomaz-imovel-vila-nova-conceicao-sao-paulo/ | O aniversário em uma mansão gerida por empresa de Vorcaro (iclnoticias.com.br) https://iclnoticias.com.br/flavio-bolsonaro-aniversario-da-filha-em-mansao/ | E-mails sobre vínculo bancário com Willer Tomaz (noticias.uol.com.br) https://noticias.uol.com.br/colunas/fabio-serapiao/2026/10/10/flavio-dividia-conta-com-suspeito-de-lavar-dinheiro-do-inss-indicam-emails.htm | Endereço e contabilidade compartilhados em Brasília (iclnoticias.com.br) https://iclnoticias.com.br/empresas-de-flavio-bolsonaro-e-careca-do-inss/ | Cargo na Câmara, faculdade e estágio no Rio (bbc.com) https://www.bbc.com/portuguese/brasil-46828487 | A acusação de rachadinhas na Alerj (valor.globo.com) https://valor.globo.com/politica/eleicoes-2026/noticia/2026/09/01/flavio-bolsonaro-relembre-o-processo-da-rachadinha.ghtml | A acusação de rachadinhas na Alerj (folhadelondrina.com.br) https://www.folhadelondrina.com.br/ultimas-noticias/entenda-quais-provas-da-rachadinha-contra-flavio-bolsonaro-ainda-valem-3131387e.html | A investigação da loja Kopenhagen (oglobo.globo.com) https://oglobo.globo.com/politica/alvo-de-investigacao-das-rachadinhas-loja-de-flavio-bolsonaro-no-rio-vendida-1-24867874 | Imóveis comprados pela família e investigações (g1.globo.com) https://g1.globo.com/jornal-nacional/noticia/2022/08/31/reportagem-do-uol-revela-que-51-imoveis-comprados-pela-familia-bolsonaro-foram-pagos-em-dinheiro-vivo.ghtml | Imóveis comprados pela família e investigações (noticias.uol.com.br) https://noticias.uol.com.br/politica/ultimas-noticias/2022/08/30/imoveis-cla-bolsonaro-objeto-de-investigacao-suspeita-dinheiro-vivo.htm | Imóveis comprados pela família e investigações (estadao.com.br) https://www.estadao.com.br/politica/investigacao-sobre-flaviobolsonaro-alcanca-37-imoveis/ | A compra e a quitação da mansão em Brasília (oglobo.globo.com) https://oglobo.globo.com/politica/eleicoes-2026/noticia/2026/08/14/video-mansao-que-fez-patrimonio-de-flavio-disparar-fica-em-terreno-de-2400-m-e-foi-quitada-27-anos-antes-do-previsto.ghtml | A análise do MPF sobre 37 transações imobiliárias (cnnbrasil.com.br) https://www.cnnbrasil.com.br/politica/o-mpf-ve-fortes-indicios-de-lavagem-de-dinheiro-em-bens-de-flavio-bolsonaro/a | A acusação do MP-RJ sobre organização criminosa (g1.globo.com) https://g1.globo.com/rj/rio-de-janeiro/noticia/2019/12/19/mp-do-rj-detalha-suposto-esquema-de-corrupcao-envolvendo-entao-deputado-flavio-bolsonaro.ghtml?utm_source=twitter&amp;utm_medium=social&amp;utm_campaign=g1 | Destinação de emendas e entidades questionadas (revistaforum.com.br) https://revistaforum.com.br/politica/flavio-bolsonaro-emendas-ong-fantasma-e-instituto-de-miliciano/</t>
         </is>
       </c>
       <c r="L10" s="37" t="inlineStr">
@@ -1894,7 +1912,7 @@
       </c>
       <c r="M10" s="37" t="inlineStr">
         <is>
-          <t>Resultado do 1º turno; 2º inquérito no STF; Operação Make Up; visitas ao pai liberadas.</t>
+          <t>Resultado do 1º turno; 2º inquérito no STF; Operação Make Up; visitas ao pai liberadas. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
       <c r="N10" s="24" t="inlineStr">
@@ -2033,7 +2051,7 @@
       </c>
       <c r="K12" s="37" t="inlineStr">
         <is>
-          <t>Wikipedia https://pt.wikipedia.org/wiki/Carlos_Bolsonaro | HubPolítico https://hubpolitico.com.br/perfil/carlosbolsonaro2/informacoes</t>
+          <t>Wikipedia https://pt.wikipedia.org/wiki/Carlos_Bolsonaro | HubPolítico https://hubpolitico.com.br/perfil/carlosbolsonaro2/informacoes | Condecorações a 16 policiais denunciados (noticias.uol.com.br) https://noticias.uol.com.br/colunas/juliana-dal-piva/2022/09/23/cla-bolsonaro-condecorou-16-pms-denunciados-em-organizacoes-criminosas.htm?cmpid=copiaecola</t>
         </is>
       </c>
       <c r="L12" s="37" t="inlineStr">
@@ -2043,7 +2061,7 @@
       </c>
       <c r="M12" s="37" t="inlineStr">
         <is>
-          <t>Eleito senador por SC; deixou a Câmara de Vereadores.</t>
+          <t>Eleito senador por SC; deixou a Câmara de Vereadores. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
       <c r="N12" s="24" t="inlineStr">
@@ -2115,7 +2133,7 @@
       </c>
       <c r="K13" s="37" t="inlineStr">
         <is>
-          <t>Tribuna do Sertão 03/07/2026 https://tribunadosertao.com.br/poder-e-governo/2026/07/03/933954-moraes-prorroga-prisao-domiciliar-de-bolsonaro | Congresso em Foco https://www.congressoemfoco.com.br/noticia/119918/defesa-de-bolsonaro-pede-ao-stf-prorrogacao-da-prisao-domiciliar | JB 12/10/2026 https://www.jb.com.br/brasil/justica/2026/10/1061206-moraes-autoriza-flavio-bolsonaro-a-visitar-jair-bolsonaro-em-prisao-domiciliar.html | Agência Brasil jul/2026 https://agenciabrasil.ebc.com.br/justica/noticia/2026-07/alexandre-de-moraes-decide-manter-bolsonaro-em-prisao-domiciliar</t>
+          <t>Tribuna do Sertão 03/07/2026 https://tribunadosertao.com.br/poder-e-governo/2026/07/03/933954-moraes-prorroga-prisao-domiciliar-de-bolsonaro | Congresso em Foco https://www.congressoemfoco.com.br/noticia/119918/defesa-de-bolsonaro-pede-ao-stf-prorrogacao-da-prisao-domiciliar | JB 12/10/2026 https://www.jb.com.br/brasil/justica/2026/10/1061206-moraes-autoriza-flavio-bolsonaro-a-visitar-jair-bolsonaro-em-prisao-domiciliar.html | Agência Brasil jul/2026 https://agenciabrasil.ebc.com.br/justica/noticia/2026-07/alexandre-de-moraes-decide-manter-bolsonaro-em-prisao-domiciliar | O áudio de Bolsonaro e Ramagem sobre Flávio (valor.globo.com) https://valor.globo.com/politica/noticia/2024/07/11/audio-mostra-bolsonaro-e-ramagem-discutindo-como-blindar-flavio-no-caso-das-rachadinhas-segundo-pf.ghtml | A fala de Bolsonaro na reunião ministerial (g1.globo.com) https://g1.globo.com/politica/noticia/2020/05/22/em-reuniao-ministerial-bolsonaro-diz-eu-nao-vou-esperar-foder-a-minha-familia-toda-assista.ghtml</t>
         </is>
       </c>
       <c r="L13" s="37" t="inlineStr">
@@ -2125,7 +2143,7 @@
       </c>
       <c r="M13" s="37" t="inlineStr">
         <is>
-          <t>Domiciliar confirmada em 12/10/2026; motivo e visitas de Flávio.</t>
+          <t>Domiciliar confirmada em 12/10/2026; motivo e visitas de Flávio. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
       <c r="N13" s="24" t="inlineStr">
@@ -2279,7 +2297,7 @@
       </c>
       <c r="K15" s="37" t="inlineStr">
         <is>
-          <t>Bahia Notícias https://www.bahianoticias.com.br/noticia/249931-miliciano-adriano-da-nobrega-transferiu-r-400-mil-para-fabricio-queiroz | Mais Goiás https://www.maisgoias.com.br/brasil/gilmar-mendes-da-aval-para-soltar-queiroz-apos-stj-revogar-prisao-domiciliar/ | Portal de Prefeitura https://portaldeprefeitura.com.br/bastidores-da-politica/flavio-bolsonaro-pede-votos-para-fabricio-queiroz-pivo-em-suposto/579564/ | Metrópoles 24/03/2026 https://www.metropoles.com/colunas/igor-gadelha/a-condicao-de-queiroz-para-ser-candidato-em-2026 | JB set/2026 https://www.jb.com.br/brasil/politica/2026/09/1060896-flavio-bolsonaro-e-fabricio-queiroz-se-reuniram-em-brasilia-apos-insistencia.html</t>
+          <t>Bahia Notícias https://www.bahianoticias.com.br/noticia/249931-miliciano-adriano-da-nobrega-transferiu-r-400-mil-para-fabricio-queiroz | Mais Goiás https://www.maisgoias.com.br/brasil/gilmar-mendes-da-aval-para-soltar-queiroz-apos-stj-revogar-prisao-domiciliar/ | Portal de Prefeitura https://portaldeprefeitura.com.br/bastidores-da-politica/flavio-bolsonaro-pede-votos-para-fabricio-queiroz-pivo-em-suposto/579564/ | Metrópoles 24/03/2026 https://www.metropoles.com/colunas/igor-gadelha/a-condicao-de-queiroz-para-ser-candidato-em-2026 | JB set/2026 https://www.jb.com.br/brasil/politica/2026/09/1060896-flavio-bolsonaro-e-fabricio-queiroz-se-reuniram-em-brasilia-apos-insistencia.html | A acusação de rachadinhas na Alerj (valor.globo.com) https://valor.globo.com/politica/eleicoes-2026/noticia/2026/09/01/flavio-bolsonaro-relembre-o-processo-da-rachadinha.ghtml | A acusação de rachadinhas na Alerj (folhadelondrina.com.br) https://www.folhadelondrina.com.br/ultimas-noticias/entenda-quais-provas-da-rachadinha-contra-flavio-bolsonaro-ainda-valem-3131387e.html | Familiares de Adriano da Nóbrega no gabinete (oglobo.globo.com) https://oglobo.globo.com/politica/flavio-bolsonaro-empregou-mae-mulher-de-chefe-do-escritorio-do-crime-em-seu-gabinete-23391490</t>
         </is>
       </c>
       <c r="L15" s="37" t="inlineStr">
@@ -2289,7 +2307,7 @@
       </c>
       <c r="M15" s="37" t="inlineStr">
         <is>
-          <t>Sem candidatura formalizada em 2026 (confirmado pela usuária); cargo público e encontro com Flávio em set/2026.</t>
+          <t>Sem candidatura formalizada em 2026 (confirmado pela usuária); cargo público e encontro com Flávio em set/2026. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
     </row>
@@ -2413,7 +2431,7 @@
       </c>
       <c r="K17" s="37" t="inlineStr">
         <is>
-          <t>Wikipedia en https://en.wikipedia.org/wiki/Daniel_Vorcaro | Times Brasil https://timesbrasil.com.br/brasil/pgr-defende-manutencao-das-prisoes-de-vorcaro-pai-e-investigados-do-caso-master/ | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal | Mateus Oliver 20/10/2026 https://www.mateusoliverreporter.com.br/2026/10/20/pgr-defende-manutencao-de-prisoes-no-caso-banco-master-e-permanencia-de-fachin-a-frente-de-decisoes-no-stf/</t>
+          <t>Wikipedia en https://en.wikipedia.org/wiki/Daniel_Vorcaro | Times Brasil https://timesbrasil.com.br/brasil/pgr-defende-manutencao-das-prisoes-de-vorcaro-pai-e-investigados-do-caso-master/ | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal | Mateus Oliver 20/10/2026 https://www.mateusoliverreporter.com.br/2026/10/20/pgr-defende-manutencao-de-prisoes-no-caso-banco-master-e-permanencia-de-fachin-a-frente-de-decisoes-no-stf/ | O acordo de R$ 134 milhões para o filme (intercept.com.br) https://www.intercept.com.br/2026/05/13/audio-flavio-negociou-vorcaro-milhoes/ | Os registros de contato no celular do banqueiro (piaui.uol.com.br) https://piaui.uol.com.br/web/mensagens-celular-flavio-vorcaro/ | A visita após a soltura do banqueiro (metropoles.com) https://www.metropoles.com/colunas/igor-gadelha/flavio-bolsonaro-visitou-vorcaro-em-casa-apos-prisao | A visita na véspera do anúncio da candidatura (metropoles.com) https://www.metropoles.com/colunas/igor-gadelha/flavio-visitou-vorcaro-na-vespera-de-ser-anunciado-presidenciavel | O voo no jato de Vorcaro em janeiro de 2025 (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-viajou-em-jato-de-vorcaro/ | A viagem à Flórida e os repasses para o filme (piaui.uol.com.br) https://piaui.uol.com.br/web/feriadao-flavio-vorcaro-florida-dark-horse/ | O aniversário em uma mansão gerida por empresa de Vorcaro (iclnoticias.com.br) https://iclnoticias.com.br/flavio-bolsonaro-aniversario-da-filha-em-mansao/</t>
         </is>
       </c>
       <c r="L17" s="37" t="inlineStr">
@@ -2423,7 +2441,7 @@
       </c>
       <c r="M17" s="37" t="inlineStr">
         <is>
-          <t>Preso na Papudinha desde 25/06/2026; delações rejeitadas; situação das provas no STF.</t>
+          <t>Preso na Papudinha desde 25/06/2026; delações rejeitadas; situação das provas no STF. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
       <c r="N17" s="24" t="inlineStr">
@@ -2495,7 +2513,7 @@
       </c>
       <c r="K18" s="37" t="inlineStr">
         <is>
-          <t>Congresso em Foco https://www.congressoemfoco.com.br/noticia/116929/pf-prende-cunhado-de-vorcaro-suspeito-de-operar-esquema-do-master | Mateus Oliver (link na linha do Vorcaro)</t>
+          <t>Congresso em Foco https://www.congressoemfoco.com.br/noticia/116929/pf-prende-cunhado-de-vorcaro-suspeito-de-operar-esquema-do-master | Mateus Oliver (link na linha do Vorcaro) | Doações de Fabiano Zettel nas eleições de 2022 (cnnbrasil.com.br) https://www.cnnbrasil.com.br/politica/alvo-da-pf-doou-r-5-mi-para-campanhas-de-bolsonaro-e-tarcisio-em-2022/ | O apartamento de Fabiano Zettel e Willer Tomaz (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-zettel-tomaz-imovel-vila-nova-conceicao-sao-paulo/</t>
         </is>
       </c>
       <c r="L18" s="37" t="inlineStr">
@@ -2505,7 +2523,7 @@
       </c>
       <c r="M18" s="37" t="inlineStr">
         <is>
-          <t>Segue preso em 20/10/2026 (PGR contra soltura).</t>
+          <t>Segue preso em 20/10/2026 (PGR contra soltura). 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
       <c r="N18" s="24" t="inlineStr">
@@ -2907,12 +2925,12 @@
       </c>
       <c r="J24" s="37" t="inlineStr">
         <is>
-          <t>Em jun/2026 uma advogada publicou e retirou um vídeo sobre o caso, retratando-se por imprecisões.</t>
+          <t>Em jun/2026 uma advogada publicou e retirou um vídeo sobre o caso, retratando-se por imprecisões. Acervo a verdade.: o advogado dele na disputa pela casa foi morto em 2024 no Rio. Nada nas fontes liga Flávio ou Willer ao homicídio. O PDF diz que a mansão é gerida por empresa de Vorcaro; o mapa a registra como da WT.</t>
         </is>
       </c>
       <c r="K24" s="37" t="inlineStr">
         <is>
-          <t>Poder360 https://www.poder360.com.br/justica/richarlison-briga-na-justica-com-amigo-de-flavio-bolsonaro/ | Congresso em Foco https://www.congressoemfoco.com.br/noticia/120171/disputa-por-mansao-de-r-10-mi-envolve-richarlison-e-flavio-bolsonaro</t>
+          <t>Poder360 https://www.poder360.com.br/justica/richarlison-briga-na-justica-com-amigo-de-flavio-bolsonaro/ | Congresso em Foco https://www.congressoemfoco.com.br/noticia/120171/disputa-por-mansao-de-r-10-mi-envolve-richarlison-e-flavio-bolsonaro | A disputa pelo imóvel comprado por Richarlison (iclnoticias.com.br) https://iclnoticias.com.br/advogado-defendia-amigo-de-flavio-bolsonaro/ | A disputa pelo imóvel comprado por Richarlison (iclnoticias.com.br) https://iclnoticias.com.br/pf-e-acionada-flavio-bolsonaro-richarlisson/ | A transferência do imóvel disputado em Angra (iclnoticias.com.br) https://iclnoticias.com.br/governo-bolsonaro-imovel-richarlison/</t>
         </is>
       </c>
       <c r="L24" s="37" t="inlineStr">
@@ -2922,7 +2940,7 @@
       </c>
       <c r="M24" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
       <c r="N24" s="24" t="inlineStr">
@@ -3056,12 +3074,12 @@
       </c>
       <c r="J26" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Acervo a verdade.: o PDF original diz que ele “recebeu R$ 427 mi”. A CNN fala em contrato de advocacia de até R$ 427 mi, condicionado a êxito, o que não comprova recebimento pessoal. Ele nega.</t>
         </is>
       </c>
       <c r="K26" s="37" t="inlineStr">
         <is>
-          <t>Gazeta do Povo https://www.gazetadopovo.com.br/republica/filho-nunes-marques-teria-recebido-500-mil-master-aponta-pf/ | Times Brasil https://timesbrasil.com.br/brasil/deputados-pedem-investigacao-sobre-nunes-marques-e-master/ | Agência Brasil https://agenciabrasil.ebc.com.br/justica/noticia/2026-04/nunes-marques-e-eleito-presidente-do-tse</t>
+          <t>Gazeta do Povo https://www.gazetadopovo.com.br/republica/filho-nunes-marques-teria-recebido-500-mil-master-aponta-pf/ | Times Brasil https://timesbrasil.com.br/brasil/deputados-pedem-investigacao-sobre-nunes-marques-e-master/ | Agência Brasil https://agenciabrasil.ebc.com.br/justica/noticia/2026-04/nunes-marques-e-eleito-presidente-do-tse | O voto de Nunes Marques no caso Alcídia (noticias.uol.com.br) https://noticias.uol.com.br/colunas/a-hora/2026/10/04/kassio-se-declarou-impedido-voltou-atras-e-deu-ganho-bilionario-ao-master.htm | Decisão sobre usinas e mensagens sobre o filho do ministro (noticias.uol.com.br) https://noticias.uol.com.br/colunas/natalia-portinari/2026/09/29/kassio-via-boi-na-linha-em-caso-de-usinas-segundo-mensagens-de-vorcaro.htm?utm_source=chatgpt.com | Contrato de R$ 427 milhões e suspeitas de benefícios (cnnbrasil.com.br) https://www.cnnbrasil.com.br/politica/turma-do-kn-negociou-contrato-de-r-427-mi-com-master-apontam-mensagens/ | Contrato de R$ 427 milhões e suspeitas de benefícios (cnnbrasil.com.br) https://www.cnnbrasil.com.br/politica/dialogos-de-vorcaro-citam-suposta-mesada-de-r-500-mil-para-filho-de-nunes/ | Contrato de R$ 427 milhões e suspeitas de benefícios (almapreta.com.br) https://almapreta.com.br/sessao/politica/apartamento-nunes-marques-prostituta-fabiano-zettel-cunhado-vorcaro/ | Relatos do ex-sócio sobre festas, relógio e lobby (brasildefato.com.br) https://www.brasildefato.com.br/2026/09/29/ex-socio-de-flavio-bolsonaro-cita-festas-com-garotas-de-programa-rolex-de-r-305-mil-e-lobby-com-nunes-marques-diz-site/#google_vignette</t>
         </is>
       </c>
       <c r="L26" s="37" t="inlineStr">
@@ -3071,7 +3089,7 @@
       </c>
       <c r="M26" s="37" t="inlineStr">
         <is>
-          <t>Presidente do TSE confirmado (eleito em 14/04/2026).</t>
+          <t>Presidente do TSE confirmado (eleito em 14/04/2026). 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
       <c r="N26" s="24" t="inlineStr">
@@ -3143,7 +3161,7 @@
       </c>
       <c r="K27" s="37" t="inlineStr">
         <is>
-          <t>Gazeta do Povo (link acima)</t>
+          <t>Gazeta do Povo (link acima) | Decisão sobre usinas e mensagens sobre o filho do ministro (noticias.uol.com.br) https://noticias.uol.com.br/colunas/natalia-portinari/2026/09/29/kassio-via-boi-na-linha-em-caso-de-usinas-segundo-mensagens-de-vorcaro.htm?utm_source=chatgpt.com | Contrato de R$ 427 milhões e suspeitas de benefícios (cnnbrasil.com.br) https://www.cnnbrasil.com.br/politica/turma-do-kn-negociou-contrato-de-r-427-mi-com-master-apontam-mensagens/ | Contrato de R$ 427 milhões e suspeitas de benefícios (cnnbrasil.com.br) https://www.cnnbrasil.com.br/politica/dialogos-de-vorcaro-citam-suposta-mesada-de-r-500-mil-para-filho-de-nunes/ | Contrato de R$ 427 milhões e suspeitas de benefícios (almapreta.com.br) https://almapreta.com.br/sessao/politica/apartamento-nunes-marques-prostituta-fabiano-zettel-cunhado-vorcaro/</t>
         </is>
       </c>
       <c r="L27" s="37" t="inlineStr">
@@ -3153,7 +3171,7 @@
       </c>
       <c r="M27" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3228,7 @@
       </c>
       <c r="K28" s="37" t="inlineStr">
         <is>
-          <t>Agência Pública 29/09/2026 https://apublica.org/2026/09/familia-de-condenado-por-garimpo-na-terra-yanomami-bancou-vida-de-ramagem-nos-eua/ | Wikipedia en https://en.wikipedia.org/wiki/Alexandre_Ramagem | CNN Brasil 05/07/2026 https://www.cnnbrasil.com.br/politica/nos-eua-ramagem-diz-que-extradicao-nao-acontecera-e-cita-volta-ao-brasil/</t>
+          <t>Agência Pública 29/09/2026 https://apublica.org/2026/09/familia-de-condenado-por-garimpo-na-terra-yanomami-bancou-vida-de-ramagem-nos-eua/ | Wikipedia en https://en.wikipedia.org/wiki/Alexandre_Ramagem | CNN Brasil 05/07/2026 https://www.cnnbrasil.com.br/politica/nos-eua-ramagem-diz-que-extradicao-nao-acontecera-e-cita-volta-ao-brasil/ | O áudio de Bolsonaro e Ramagem sobre Flávio (valor.globo.com) https://valor.globo.com/politica/noticia/2024/07/11/audio-mostra-bolsonaro-e-ramagem-discutindo-como-blindar-flavio-no-caso-das-rachadinhas-segundo-pf.ghtml</t>
         </is>
       </c>
       <c r="L28" s="37" t="inlineStr">
@@ -3220,7 +3238,7 @@
       </c>
       <c r="M28" s="37" t="inlineStr">
         <is>
-          <t>Entrevista de 05/07/2026; asilo pendente; processo de extradição em paralelo.</t>
+          <t>Entrevista de 05/07/2026; asilo pendente; processo de extradição em paralelo. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
       <c r="N28" s="24" t="inlineStr">
@@ -3374,7 +3392,7 @@
       </c>
       <c r="K30" s="37" t="inlineStr">
         <is>
-          <t>NSC Total https://www.nsctotal.com.br/politica/eleicoes-2026-quem-e-sergio-moro-candidato-do-pl-ao-governo-do-parana | Congresso em Foco https://www.congressoemfoco.com.br/noticia/122688/sergio-moro-e-eleito-governador-do-parana | Tribuna do Sertão 04/10/2026 https://tribunadosertao.com.br/politica/2026/10/04/990712-sergio-moro-e-eleito-governador-do-parana-no-1o-turno</t>
+          <t>NSC Total https://www.nsctotal.com.br/politica/eleicoes-2026-quem-e-sergio-moro-candidato-do-pl-ao-governo-do-parana | Congresso em Foco https://www.congressoemfoco.com.br/noticia/122688/sergio-moro-e-eleito-governador-do-parana | Tribuna do Sertão 04/10/2026 https://tribunadosertao.com.br/politica/2026/10/04/990712-sergio-moro-e-eleito-governador-do-parana-no-1o-turno | A saída de Moro e a acusação de interferência na PF (g1.globo.com) https://g1.globo.com/politica/noticia/2020/04/24/moro-anuncia-demissao-do-ministerio-da-justica-e-deixa-o-governo-bolsonaro.ghtml</t>
         </is>
       </c>
       <c r="L30" s="37" t="inlineStr">
@@ -3384,7 +3402,7 @@
       </c>
       <c r="M30" s="37" t="inlineStr">
         <is>
-          <t>Eleito governador do Paraná no 1º turno (04/10/2026).</t>
+          <t>Eleito governador do Paraná no 1º turno (04/10/2026). 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
       <c r="N30" s="24" t="inlineStr">
@@ -3456,7 +3474,7 @@
       </c>
       <c r="K31" s="37" t="inlineStr">
         <is>
-          <t>Correio da Manhã 07/05/2026 https://www.correiodamanha.com.br/politica/2026/05/283952-ciro-nogueira-receberia-mesada-do-master-diz-investigacao.html | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal</t>
+          <t>Correio da Manhã 07/05/2026 https://www.correiodamanha.com.br/politica/2026/05/283952-ciro-nogueira-receberia-mesada-do-master-diz-investigacao.html | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal | Supostos pagamentos mensais a Ciro Nogueira (agenciabrasil.ebc.com.br) https://agenciabrasil.ebc.com.br/justica/noticia/2026-05/mesada-e-viagens-internacionais-veja-o-que-pf-diz-sobre-ciro-nogueira | Viagens de Ciro e a suspeita de contrapartida política (g1.globo.com) https://g1.globo.com/jornal-nacional/noticia/2026/05/08/pf-suspeita-que-vorcaro-pagou-ao-menos-3-viagens-internacionais-do-senador-ciro-nogueira-do-pp.ghtml | Ciro na Operação Compliance Zero (agenciabrasil.ebc.com.br) https://agenciabrasil.ebc.com.br/justica/noticia/2026-05/policia-federal-deflagra-5a-fase-da-operacao-compliance-zero | Imagens de Ciro e Vorcaro nos Alpes (cnnbrasil.com.br) https://www.cnnbrasil.com.br/blogs/debora-bergamasco/politica/imagens-obtidas-pela-pf-mostram-ciro-nogueira-e-vorcaro-nos-alpes-franceses/ | O custeio da viagem a Courchevel (piaui.uol.com.br) https://piaui.uol.com.br/web/ciro-nogueira-daniel-vorcaro-alpes-franceses-imagens/</t>
         </is>
       </c>
       <c r="L31" s="37" t="inlineStr">
@@ -3466,7 +3484,7 @@
       </c>
       <c r="M31" s="37" t="inlineStr">
         <is>
-          <t>Identificação tratada como confirmada (antes: inferida); busca em 07/05/2026.</t>
+          <t>Identificação tratada como confirmada (antes: inferida); busca em 07/05/2026. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
         </is>
       </c>
       <c r="N31" s="24" t="inlineStr">
@@ -3485,8 +3503,288 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="37" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="B32" s="38" t="inlineStr">
+        <is>
+          <t>André Mendonça</t>
+        </is>
+      </c>
+      <c r="C32" s="37" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D32" s="37" t="inlineStr">
+        <is>
+          <t>Ministro do STF indicado por Jair Bolsonaro; ex-AGU e ex-ministro da Justiça. Relator do caso Master desde fev/2026, um mês após o instituto que fundou (ITER) receber R$ 5,2 mi de empresa de sócio de Vorcaro. Mensagens mostram o advogado de Vorcaro articulando encontros com ele em fev e mar/2025. Em set/2026 afastou o diretor-geral da PF e revogou a prisão do filho do Careca do INSS.</t>
+        </is>
+      </c>
+      <c r="E32" s="37" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F32" s="37" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G32" s="37" t="inlineStr">
+        <is>
+          <t>Não há processo contra ele nas fontes do acervo.</t>
+        </is>
+      </c>
+      <c r="H32" s="39" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I32" s="37" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J32" s="37" t="inlineStr">
+        <is>
+          <t>Dados do acervo a verdade.; fontes não reverificadas uma a uma. Os levantamentos de contratos do ITER (52 contratos e R$ 8,2 mi; 55 contratos e R$ 10,8 mi) são recortes diferentes e não se somam.</t>
+        </is>
+      </c>
+      <c r="K32" s="37" t="inlineStr">
+        <is>
+          <t>A visita à alfaiataria com o advogado de Vorcaro (iclnoticias.com.br) https://iclnoticias.com.br/vaza-mendonca-mensagens-e-audios-ineditos/ | Encomendas, recibos e pagamentos na alfaiataria (oglobo.globo.com) https://oglobo.globo.com/politica/noticia/2026/09/03/alfaiataria-visitada-por-mendonca-e-advogado-de-vorcaro-nao-esclarece-encomenda-nem-mostra-recibos-ternos-sob-medida-custam-a-partir-de-r-219-mil.ghtml | Encomendas, recibos e pagamentos na alfaiataria (paulomotoryn.substack.com) https://paulomotoryn.substack.com/p/exclusivo-vorcaro-gastou-r-500-mil | Encomendas, recibos e pagamentos na alfaiataria (metro1.com.br) https://www.metro1.com.br/noticias/politica/187938,notas-de-mendonca-em-alfaiataria-frequentada-por-vorcaro-registravam-sem-pagamento | Mensagens para agendar encontro com Mendonça (iclnoticias.com.br) https://iclnoticias.com.br/vaza-mendonca-mensagens-e-audios-ineditos/ | O convite a Bruno Bianco para a reunião (iclnoticias.com.br) https://iclnoticias.com.br/vaza-mendonca-mensagens-e-audios-ineditos/ | A reunião de fevereiro de 2025 (iclnoticias.com.br) https://iclnoticias.com.br/vaza-mendonca-mensagens-e-audios-ineditos/ | Encontro com Vorcaro na sede do ITER (iclnoticias.com.br) https://iclnoticias.com.br/vaza-mendonca-mensagens-e-audios-ineditos/ | Pedido de vista no julgamento sobre cemitérios (valor.globo.com) https://valor.globo.com/politica/noticia/2026/09/15/stf-em-ao-sobre-cemitrios-em-sp-dino-pede-nova-investigao-de-mendona.ghtml | Convites para coquetéis do instituto (iclnoticias.com.br) https://iclnoticias.com.br/vorcaro-foi-chamado-a-coquetel-de-mendonca/ | A viagem de helicóptero de Mendonça (noticias.uol.com.br) https://noticias.uol.com.br/colunas/daniela-lima/2026/09/22/mendonca-voou-em-aeronave-de-ex-parceiro-de-negocios-de-vorcaro.htm | Aporte de R$ 5,2 milhões ao ITER (noticias.uol.com.br) https://noticias.uol.com.br/ultimas-noticias/redacao/2026/09/17/ex-parceiro-de-vorcaro-pos-r-5-milhoes-em-instituto-de-mendonca.htm | Depoimento de Vorcaro sem a Polícia Federal (iclnoticias.com.br) https://iclnoticias.com.br/gabinete-mendonca-ouviu-vorcaro-horario-pf/ | O afastamento de um diretor da PF (cnnbrasil.com.br) https://www.cnnbrasil.com.br/blogs/teo-cury/politica/mendonca-ordenou-afastamento-de-diretor-geral-da-pf-sem-ouvir-pgr/ | A atuação do diretor afastado nos casos Master e INSS (iclnoticias.com.br) https://iclnoticias.com.br/diretor-da-pf-afastado-mendonca-prendeu-vorcaro/ | Revogação da prisão do filho do Careca do INSS (iclnoticias.com.br) https://iclnoticias.com.br/andre-mendonca-revoga-prisao-do-filho-do-careca/ | A contestação da AGU ao afastamento na PF (iclnoticias.com.br) https://iclnoticias.com.br/agu-mendonca-usurpou-competencia-fachin/ | A cronologia entre a operação de Dino e o afastamento (iclnoticias.com.br) https://iclnoticias.com.br/mendonca-cesinha-madureira-vorcaro-dino/ | Financiamento da campanha de Cezinha de Madureira (iclnoticias.com.br) https://iclnoticias.com.br/tarcisio-campanha-deputado-mendonca-vorcaro/ | A proximidade entre Cezinha e Mendonça (iclnoticias.com.br) https://iclnoticias.com.br/cezinha-de-madureira-tinha-porta-retrato-com-mendonca-na-sala-de-casa/ | 52 contratos do ITER com órgãos públicos (apublica.org) https://apublica.org/nota/instituto-de-andre-mendonca-e-alvo-de-representacoes-para-investigar-irregularidades/ | Outro levantamento: 55 contratos do instituto (iclnoticias.com.br) https://iclnoticias.com.br/instituto-de-andre-mendonca-faturou/ | A promoção do irmão de Mendonça (iclnoticias.com.br) https://iclnoticias.com.br/irmao-de-mendonca-foi-promovido-por-nunes/ | Votos relativos a Castro e contratos no Rio (iclnoticias.com.br) https://iclnoticias.com.br/mendonca-votou-a-favor-de-castro-4-vezes/ | Prazos diferentes para decisões sobre políticos (cnnbrasil.com.br) https://www.cnnbrasil.com.br/politica/mendonca-demora-9-dias-para-despachar-sobre-wagner-e-75-sobre-castro/ | O contraste nos prazos apontado pela PF (iclnoticias.com.br) https://iclnoticias.com.br/pf-aponta-diferenca-8-x-no-tempo-mendonca/ | A declaração de Gilmar sobre acesso a dados (iclnoticias.com.br) https://iclnoticias.com.br/gilmar-stf-dados-maste-ministros-mendonca/ | O pedido para rastrear o dinheiro do Master (iclnoticias.com.br) https://iclnoticias.com.br/pf-espera-ha-seis-meses-decisao-mendonca/ | A recomendação de sigilo sobre o celular de Vorcaro (iclnoticias.com.br) https://iclnoticias.com.br/contra-transparencia-mendonca-recomenda-manter/ | Tratamento de ministros em relatório da PF (iclnoticias.com.br) https://iclnoticias.com.br/relatorio-pf-mendonca-poupou-toffoli-kassio/ | O pedido de nulidade apresentado por Gonet (iclnoticias.com.br) https://iclnoticias.com.br/gonet-diz-que-mendonca-investigou-moraes/</t>
+        </is>
+      </c>
+      <c r="L32" s="37" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="M32" s="37" t="inlineStr">
+        <is>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N32" s="24" t="n"/>
+      <c r="O32" s="24" t="n"/>
+      <c r="P32" s="24" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="37" t="inlineStr">
+        <is>
+          <t>faria</t>
+        </is>
+      </c>
+      <c r="B33" s="38" t="inlineStr">
+        <is>
+          <t>Fábio Faria</t>
+        </is>
+      </c>
+      <c r="C33" s="37" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="D33" s="37" t="inlineStr">
+        <is>
+          <t>Ex-ministro das Comunicações de Jair Bolsonaro. Mensagens recuperadas pela PF o apontam como intermediário de Vorcaro com autoridades em Brasília e com ministros de tribunais superiores, inclusive na organização de festas. Empresa ligada a Vorcaro pagou R$ 67,5 mi por um projeto dele.</t>
+        </is>
+      </c>
+      <c r="E33" s="37" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F33" s="37" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G33" s="37" t="inlineStr">
+        <is>
+          <t>O acervo não informa se ele é formalmente investigado.</t>
+        </is>
+      </c>
+      <c r="H33" s="39" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I33" s="37" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J33" s="37" t="inlineStr">
+        <is>
+          <t>Dados do acervo a verdade.; fontes não reverificadas uma a uma.</t>
+        </is>
+      </c>
+      <c r="K33" s="37" t="inlineStr">
+        <is>
+          <t>Fábio Faria como interlocutor de Vorcaro (piaui.uol.com.br) https://piaui.uol.com.br/web/fabio-faria-daniel-vorcaro-lobby/ | R$ 67,5 milhões por projeto de Fábio Faria (tab.uol.com.br) https://tab.uol.com.br/noticias/redacao/2026/01/29/vorcaro-pagou-r-675-mi-em-projeto-eolico-de-fabio-faria-ex-ministro.htm | Convites a autoridades para festas e encontros (piaui.uol.com.br) https://piaui.uol.com.br/web/festa-suicas-vorcaro-fabio-faria/ | O grupo com Hugo Motta, Ciro e Fábio Faria (gazetadopovo.com.br) https://www.gazetadopovo.com.br/republica/vorcaro-grupo-motta-ciro-nogueira-fabio-faria-organizar-encontros/ | A intermediação de contatos com Moraes (g1.globo.com) https://g1.globo.com/politica/noticia/2026/09/01/ex-ministro-fabio-faria-atuou-para-intermediar-contatos-entre-vorcaro-e-moraes-aponta-pf.ghtml</t>
+        </is>
+      </c>
+      <c r="L33" s="37" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="M33" s="37" t="inlineStr">
+        <is>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N33" s="24" t="n"/>
+      <c r="O33" s="24" t="n"/>
+      <c r="P33" s="24" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="37" t="inlineStr">
+        <is>
+          <t>frias</t>
+        </is>
+      </c>
+      <c r="B34" s="38" t="inlineStr">
+        <is>
+          <t>Mario Frias</t>
+        </is>
+      </c>
+      <c r="C34" s="37" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="D34" s="37" t="inlineStr">
+        <is>
+          <t>Ex-secretário especial de Cultura de Jair Bolsonaro e produtor-executivo do filme Dark Horse. Áudio divulgado pelo Intercept mostra ele agradecendo Vorcaro pelo financiamento do filme.</t>
+        </is>
+      </c>
+      <c r="E34" s="37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="37" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G34" s="37" t="inlineStr">
+        <is>
+          <t>Segundo o PDF, investigado no caso do filme.</t>
+        </is>
+      </c>
+      <c r="H34" s="39" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I34" s="37" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J34" s="37" t="inlineStr">
+        <is>
+          <t>Situação de investigado vem do PDF do acervo; não reverificada.</t>
+        </is>
+      </c>
+      <c r="K34" s="37" t="inlineStr">
+        <is>
+          <t>Mario Frias e a produção de Dark Horse (intercept.com.br) https://www.intercept.com.br/2026/05/19/audio-mario-frias-daniel-vorcaro/</t>
+        </is>
+      </c>
+      <c r="L34" s="37" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="M34" s="37" t="inlineStr">
+        <is>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N34" s="24" t="n"/>
+      <c r="O34" s="24" t="n"/>
+      <c r="P34" s="24" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="37" t="inlineStr">
+        <is>
+          <t>gaspar</t>
+        </is>
+      </c>
+      <c r="B35" s="38" t="inlineStr">
+        <is>
+          <t>Alfredo Gaspar</t>
+        </is>
+      </c>
+      <c r="C35" s="37" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="D35" s="37" t="inlineStr">
+        <is>
+          <t>Vice na chapa de Flávio Bolsonaro em 2026.</t>
+        </is>
+      </c>
+      <c r="E35" s="37" t="inlineStr">
+        <is>
+          <t>Alagoas (AL)</t>
+        </is>
+      </c>
+      <c r="F35" s="37" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G35" s="37" t="inlineStr">
+        <is>
+          <t>Pedido de investigação por estupro de vulnerável arquivado pelo ministro Gilmar Mendes em out/2026, por falta de indícios suficientes. Ele nega.</t>
+        </is>
+      </c>
+      <c r="H35" s="39" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I35" s="37" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J35" s="37" t="inlineStr">
+        <is>
+          <t>O PDF original diz que ele “é investigado”; isso está desatualizado desde o arquivamento (Folha e UOL, 06/10/2026).</t>
+        </is>
+      </c>
+      <c r="K35" s="37" t="inlineStr">
+        <is>
+          <t>Alfredo Gaspar: pedido de investigação arquivado (metropoles.com) https://www.metropoles.com/colunas/igor-gadelha/denuncia-de-suposto-estupro-contra-vice-de-flavio-deve-avancar-no-stf | Alfredo Gaspar: pedido de investigação arquivado (folha.uol.com.br) https://www1.folha.uol.com.br/poder/2026/10/gilmar-arquiva-pedido-de-investigacao-contra-vice-de-flavio-bolsonaro-por-suspeita-de-estupro.shtml | Alfredo Gaspar: pedido de investigação arquivado (noticias.uol.com.br) https://noticias.uol.com.br/eleicoes/2026/10/06/gilmar-mendes-arquiva-stf-suspeita-estupro-alfredo-gaspar-vice-flavio.ghtm</t>
+        </is>
+      </c>
+      <c r="L35" s="37" t="inlineStr">
+        <is>
+          <t>21/10/2026</t>
+        </is>
+      </c>
+      <c r="M35" s="37" t="inlineStr">
+        <is>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N35" s="24" t="n"/>
+      <c r="O35" s="24" t="n"/>
+      <c r="P35" s="24" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M31"/>
+  <autoFilter ref="A1:P35"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3499,7 +3797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="24" min="1" max="1"/>
@@ -3589,7 +3887,7 @@
         </is>
       </c>
       <c r="F2" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A2)+COUNTIF(Edges!$B$2:$B$120,A2)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A2)+COUNTIF(Edges!$B$2:$B$182,A2)</f>
         <v/>
       </c>
       <c r="G2" s="24" t="n"/>
@@ -3624,7 +3922,7 @@
         </is>
       </c>
       <c r="F3" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A3)+COUNTIF(Edges!$B$2:$B$120,A3)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A3)+COUNTIF(Edges!$B$2:$B$182,A3)</f>
         <v/>
       </c>
     </row>
@@ -3655,7 +3953,7 @@
         </is>
       </c>
       <c r="F4" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A4)+COUNTIF(Edges!$B$2:$B$120,A4)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A4)+COUNTIF(Edges!$B$2:$B$182,A4)</f>
         <v/>
       </c>
     </row>
@@ -3686,7 +3984,7 @@
         </is>
       </c>
       <c r="F5" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A5)+COUNTIF(Edges!$B$2:$B$120,A5)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A5)+COUNTIF(Edges!$B$2:$B$182,A5)</f>
         <v/>
       </c>
     </row>
@@ -3717,7 +4015,7 @@
         </is>
       </c>
       <c r="F6" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A6)+COUNTIF(Edges!$B$2:$B$120,A6)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A6)+COUNTIF(Edges!$B$2:$B$182,A6)</f>
         <v/>
       </c>
     </row>
@@ -3748,7 +4046,7 @@
         </is>
       </c>
       <c r="F7" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A7)+COUNTIF(Edges!$B$2:$B$120,A7)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A7)+COUNTIF(Edges!$B$2:$B$182,A7)</f>
         <v/>
       </c>
     </row>
@@ -3779,7 +4077,7 @@
         </is>
       </c>
       <c r="F8" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A8)+COUNTIF(Edges!$B$2:$B$120,A8)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A8)+COUNTIF(Edges!$B$2:$B$182,A8)</f>
         <v/>
       </c>
       <c r="G8" s="24" t="n"/>
@@ -3814,7 +4112,7 @@
         </is>
       </c>
       <c r="F9" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A9)+COUNTIF(Edges!$B$2:$B$120,A9)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A9)+COUNTIF(Edges!$B$2:$B$182,A9)</f>
         <v/>
       </c>
       <c r="G9" s="24" t="n"/>
@@ -3849,7 +4147,7 @@
         </is>
       </c>
       <c r="F10" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A10)+COUNTIF(Edges!$B$2:$B$120,A10)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A10)+COUNTIF(Edges!$B$2:$B$182,A10)</f>
         <v/>
       </c>
     </row>
@@ -3880,7 +4178,7 @@
         </is>
       </c>
       <c r="F11" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A11)+COUNTIF(Edges!$B$2:$B$120,A11)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A11)+COUNTIF(Edges!$B$2:$B$182,A11)</f>
         <v/>
       </c>
       <c r="G11" s="24" t="n"/>
@@ -3915,7 +4213,7 @@
         </is>
       </c>
       <c r="F12" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A12)+COUNTIF(Edges!$B$2:$B$120,A12)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A12)+COUNTIF(Edges!$B$2:$B$182,A12)</f>
         <v/>
       </c>
       <c r="G12" s="24" t="inlineStr">
@@ -3962,7 +4260,7 @@
         </is>
       </c>
       <c r="F13" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A13)+COUNTIF(Edges!$B$2:$B$120,A13)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A13)+COUNTIF(Edges!$B$2:$B$182,A13)</f>
         <v/>
       </c>
     </row>
@@ -3993,7 +4291,7 @@
         </is>
       </c>
       <c r="F14" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A14)+COUNTIF(Edges!$B$2:$B$120,A14)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A14)+COUNTIF(Edges!$B$2:$B$182,A14)</f>
         <v/>
       </c>
       <c r="G14" s="24" t="n"/>
@@ -4028,7 +4326,7 @@
         </is>
       </c>
       <c r="F15" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A15)+COUNTIF(Edges!$B$2:$B$120,A15)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A15)+COUNTIF(Edges!$B$2:$B$182,A15)</f>
         <v/>
       </c>
       <c r="G15" s="24" t="n"/>
@@ -4063,7 +4361,7 @@
         </is>
       </c>
       <c r="F16" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A16)+COUNTIF(Edges!$B$2:$B$120,A16)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A16)+COUNTIF(Edges!$B$2:$B$182,A16)</f>
         <v/>
       </c>
       <c r="G16" s="24" t="inlineStr">
@@ -4110,7 +4408,7 @@
         </is>
       </c>
       <c r="F17" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A17)+COUNTIF(Edges!$B$2:$B$120,A17)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A17)+COUNTIF(Edges!$B$2:$B$182,A17)</f>
         <v/>
       </c>
       <c r="G17" s="24" t="inlineStr">
@@ -4157,7 +4455,7 @@
         </is>
       </c>
       <c r="F18" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A18)+COUNTIF(Edges!$B$2:$B$120,A18)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A18)+COUNTIF(Edges!$B$2:$B$182,A18)</f>
         <v/>
       </c>
     </row>
@@ -4188,7 +4486,7 @@
         </is>
       </c>
       <c r="F19" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A19)+COUNTIF(Edges!$B$2:$B$120,A19)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A19)+COUNTIF(Edges!$B$2:$B$182,A19)</f>
         <v/>
       </c>
     </row>
@@ -4219,7 +4517,7 @@
         </is>
       </c>
       <c r="F20" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A20)+COUNTIF(Edges!$B$2:$B$120,A20)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A20)+COUNTIF(Edges!$B$2:$B$182,A20)</f>
         <v/>
       </c>
     </row>
@@ -4250,7 +4548,7 @@
         </is>
       </c>
       <c r="F21" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A21)+COUNTIF(Edges!$B$2:$B$120,A21)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A21)+COUNTIF(Edges!$B$2:$B$182,A21)</f>
         <v/>
       </c>
     </row>
@@ -4281,7 +4579,7 @@
         </is>
       </c>
       <c r="F22" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A22)+COUNTIF(Edges!$B$2:$B$120,A22)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A22)+COUNTIF(Edges!$B$2:$B$182,A22)</f>
         <v/>
       </c>
       <c r="G22" s="24" t="n"/>
@@ -4316,7 +4614,7 @@
         </is>
       </c>
       <c r="F23" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A23)+COUNTIF(Edges!$B$2:$B$120,A23)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A23)+COUNTIF(Edges!$B$2:$B$182,A23)</f>
         <v/>
       </c>
       <c r="G23" s="24" t="n"/>
@@ -4351,7 +4649,7 @@
         </is>
       </c>
       <c r="F24" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A24)+COUNTIF(Edges!$B$2:$B$120,A24)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A24)+COUNTIF(Edges!$B$2:$B$182,A24)</f>
         <v/>
       </c>
     </row>
@@ -4382,7 +4680,7 @@
         </is>
       </c>
       <c r="F25" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A25)+COUNTIF(Edges!$B$2:$B$120,A25)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A25)+COUNTIF(Edges!$B$2:$B$182,A25)</f>
         <v/>
       </c>
     </row>
@@ -4413,7 +4711,7 @@
         </is>
       </c>
       <c r="F26" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A26)+COUNTIF(Edges!$B$2:$B$120,A26)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A26)+COUNTIF(Edges!$B$2:$B$182,A26)</f>
         <v/>
       </c>
     </row>
@@ -4444,7 +4742,7 @@
         </is>
       </c>
       <c r="F27" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A27)+COUNTIF(Edges!$B$2:$B$120,A27)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A27)+COUNTIF(Edges!$B$2:$B$182,A27)</f>
         <v/>
       </c>
     </row>
@@ -4475,7 +4773,7 @@
         </is>
       </c>
       <c r="F28" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A28)+COUNTIF(Edges!$B$2:$B$120,A28)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A28)+COUNTIF(Edges!$B$2:$B$182,A28)</f>
         <v/>
       </c>
     </row>
@@ -4506,7 +4804,7 @@
         </is>
       </c>
       <c r="F29" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A29)+COUNTIF(Edges!$B$2:$B$120,A29)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A29)+COUNTIF(Edges!$B$2:$B$182,A29)</f>
         <v/>
       </c>
     </row>
@@ -4537,7 +4835,7 @@
         </is>
       </c>
       <c r="F30" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A30)+COUNTIF(Edges!$B$2:$B$120,A30)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A30)+COUNTIF(Edges!$B$2:$B$182,A30)</f>
         <v/>
       </c>
       <c r="G30" s="24" t="n"/>
@@ -4572,7 +4870,7 @@
         </is>
       </c>
       <c r="F31" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A31)+COUNTIF(Edges!$B$2:$B$120,A31)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A31)+COUNTIF(Edges!$B$2:$B$182,A31)</f>
         <v/>
       </c>
     </row>
@@ -4603,7 +4901,7 @@
         </is>
       </c>
       <c r="F32" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A32)+COUNTIF(Edges!$B$2:$B$120,A32)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A32)+COUNTIF(Edges!$B$2:$B$182,A32)</f>
         <v/>
       </c>
     </row>
@@ -4634,7 +4932,7 @@
         </is>
       </c>
       <c r="F33" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A33)+COUNTIF(Edges!$B$2:$B$120,A33)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A33)+COUNTIF(Edges!$B$2:$B$182,A33)</f>
         <v/>
       </c>
       <c r="G33" s="24" t="n"/>
@@ -4669,7 +4967,7 @@
         </is>
       </c>
       <c r="F34" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A34)+COUNTIF(Edges!$B$2:$B$120,A34)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A34)+COUNTIF(Edges!$B$2:$B$182,A34)</f>
         <v/>
       </c>
       <c r="G34" s="24" t="n"/>
@@ -4704,7 +5002,7 @@
         </is>
       </c>
       <c r="F35" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A35)+COUNTIF(Edges!$B$2:$B$120,A35)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A35)+COUNTIF(Edges!$B$2:$B$182,A35)</f>
         <v/>
       </c>
     </row>
@@ -4735,7 +5033,7 @@
         </is>
       </c>
       <c r="F36" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A36)+COUNTIF(Edges!$B$2:$B$120,A36)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A36)+COUNTIF(Edges!$B$2:$B$182,A36)</f>
         <v/>
       </c>
     </row>
@@ -4766,7 +5064,7 @@
         </is>
       </c>
       <c r="F37" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A37)+COUNTIF(Edges!$B$2:$B$120,A37)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A37)+COUNTIF(Edges!$B$2:$B$182,A37)</f>
         <v/>
       </c>
     </row>
@@ -4797,7 +5095,7 @@
         </is>
       </c>
       <c r="F38" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A38)+COUNTIF(Edges!$B$2:$B$120,A38)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A38)+COUNTIF(Edges!$B$2:$B$182,A38)</f>
         <v/>
       </c>
       <c r="G38" s="24" t="n"/>
@@ -4832,7 +5130,7 @@
         </is>
       </c>
       <c r="F39" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A39)+COUNTIF(Edges!$B$2:$B$120,A39)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A39)+COUNTIF(Edges!$B$2:$B$182,A39)</f>
         <v/>
       </c>
       <c r="G39" s="24" t="n"/>
@@ -4867,7 +5165,7 @@
         </is>
       </c>
       <c r="F40" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A40)+COUNTIF(Edges!$B$2:$B$120,A40)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A40)+COUNTIF(Edges!$B$2:$B$182,A40)</f>
         <v/>
       </c>
       <c r="G40" s="24" t="n"/>
@@ -4902,7 +5200,7 @@
         </is>
       </c>
       <c r="F41" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A41)+COUNTIF(Edges!$B$2:$B$120,A41)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A41)+COUNTIF(Edges!$B$2:$B$182,A41)</f>
         <v/>
       </c>
       <c r="G41" s="24" t="n"/>
@@ -4937,7 +5235,7 @@
         </is>
       </c>
       <c r="F42" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A42)+COUNTIF(Edges!$B$2:$B$120,A42)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A42)+COUNTIF(Edges!$B$2:$B$182,A42)</f>
         <v/>
       </c>
       <c r="G42" s="24" t="n"/>
@@ -4972,7 +5270,7 @@
         </is>
       </c>
       <c r="F43" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A43)+COUNTIF(Edges!$B$2:$B$120,A43)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A43)+COUNTIF(Edges!$B$2:$B$182,A43)</f>
         <v/>
       </c>
     </row>
@@ -5003,7 +5301,7 @@
         </is>
       </c>
       <c r="F44" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A44)+COUNTIF(Edges!$B$2:$B$120,A44)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A44)+COUNTIF(Edges!$B$2:$B$182,A44)</f>
         <v/>
       </c>
     </row>
@@ -5034,7 +5332,7 @@
         </is>
       </c>
       <c r="F45" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A45)+COUNTIF(Edges!$B$2:$B$120,A45)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A45)+COUNTIF(Edges!$B$2:$B$182,A45)</f>
         <v/>
       </c>
     </row>
@@ -5065,7 +5363,7 @@
         </is>
       </c>
       <c r="F46" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A46)+COUNTIF(Edges!$B$2:$B$120,A46)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A46)+COUNTIF(Edges!$B$2:$B$182,A46)</f>
         <v/>
       </c>
     </row>
@@ -5096,7 +5394,7 @@
         </is>
       </c>
       <c r="F47" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A47)+COUNTIF(Edges!$B$2:$B$120,A47)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A47)+COUNTIF(Edges!$B$2:$B$182,A47)</f>
         <v/>
       </c>
     </row>
@@ -5127,7 +5425,7 @@
         </is>
       </c>
       <c r="F48" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A48)+COUNTIF(Edges!$B$2:$B$120,A48)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A48)+COUNTIF(Edges!$B$2:$B$182,A48)</f>
         <v/>
       </c>
       <c r="G48" s="24" t="n"/>
@@ -5162,7 +5460,7 @@
         </is>
       </c>
       <c r="F49" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A49)+COUNTIF(Edges!$B$2:$B$120,A49)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A49)+COUNTIF(Edges!$B$2:$B$182,A49)</f>
         <v/>
       </c>
     </row>
@@ -5193,7 +5491,7 @@
         </is>
       </c>
       <c r="F50" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A50)+COUNTIF(Edges!$B$2:$B$120,A50)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A50)+COUNTIF(Edges!$B$2:$B$182,A50)</f>
         <v/>
       </c>
     </row>
@@ -5224,7 +5522,7 @@
         </is>
       </c>
       <c r="F51" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A51)+COUNTIF(Edges!$B$2:$B$120,A51)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A51)+COUNTIF(Edges!$B$2:$B$182,A51)</f>
         <v/>
       </c>
     </row>
@@ -5255,7 +5553,7 @@
         </is>
       </c>
       <c r="F52" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A52)+COUNTIF(Edges!$B$2:$B$120,A52)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A52)+COUNTIF(Edges!$B$2:$B$182,A52)</f>
         <v/>
       </c>
       <c r="G52" s="24" t="inlineStr">
@@ -5302,7 +5600,7 @@
         </is>
       </c>
       <c r="F53" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A53)+COUNTIF(Edges!$B$2:$B$120,A53)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A53)+COUNTIF(Edges!$B$2:$B$182,A53)</f>
         <v/>
       </c>
       <c r="G53" s="24" t="inlineStr">
@@ -5349,7 +5647,7 @@
         </is>
       </c>
       <c r="F54" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A54)+COUNTIF(Edges!$B$2:$B$120,A54)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A54)+COUNTIF(Edges!$B$2:$B$182,A54)</f>
         <v/>
       </c>
       <c r="G54" s="24" t="inlineStr">
@@ -5396,7 +5694,7 @@
         </is>
       </c>
       <c r="F55" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A55)+COUNTIF(Edges!$B$2:$B$120,A55)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A55)+COUNTIF(Edges!$B$2:$B$182,A55)</f>
         <v/>
       </c>
       <c r="G55" s="24" t="inlineStr">
@@ -5443,7 +5741,7 @@
         </is>
       </c>
       <c r="F56" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A56)+COUNTIF(Edges!$B$2:$B$120,A56)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A56)+COUNTIF(Edges!$B$2:$B$182,A56)</f>
         <v/>
       </c>
     </row>
@@ -5474,7 +5772,7 @@
         </is>
       </c>
       <c r="F57" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A57)+COUNTIF(Edges!$B$2:$B$120,A57)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A57)+COUNTIF(Edges!$B$2:$B$182,A57)</f>
         <v/>
       </c>
       <c r="G57" s="24" t="inlineStr">
@@ -5521,7 +5819,7 @@
         </is>
       </c>
       <c r="F58" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$120,A58)+COUNTIF(Edges!$B$2:$B$120,A58)</f>
+        <f>COUNTIF(Edges!$A$2:$A$182,A58)+COUNTIF(Edges!$B$2:$B$182,A58)</f>
         <v/>
       </c>
       <c r="G58" s="24" t="inlineStr">
@@ -5540,6 +5838,916 @@
         </is>
       </c>
       <c r="J58" s="24" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="B59" s="45" t="inlineStr">
+        <is>
+          <t>André Mendonça</t>
+        </is>
+      </c>
+      <c r="C59" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D59" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E59" s="45" t="inlineStr">
+        <is>
+          <t>Ministro do STF indicado por Jair; relator do caso Master desde fev/2026</t>
+        </is>
+      </c>
+      <c r="F59" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A59)+COUNTIF(Edges!$B$2:$B$182,A59)</f>
+        <v/>
+      </c>
+      <c r="G59" s="24" t="n"/>
+      <c r="H59" s="24" t="n"/>
+      <c r="I59" s="24" t="n"/>
+      <c r="J59" s="24" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="45" t="inlineStr">
+        <is>
+          <t>iter</t>
+        </is>
+      </c>
+      <c r="B60" s="45" t="inlineStr">
+        <is>
+          <t>Instituto ITER</t>
+        </is>
+      </c>
+      <c r="C60" s="45" t="inlineStr">
+        <is>
+          <t>Instituição ou caso</t>
+        </is>
+      </c>
+      <c r="D60" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E60" s="45" t="inlineStr">
+        <is>
+          <t>Fundado por Mendonça; contratos públicos sem licitação; aporte de empresa de sócio de Vorcaro</t>
+        </is>
+      </c>
+      <c r="F60" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A60)+COUNTIF(Edges!$B$2:$B$182,A60)</f>
+        <v/>
+      </c>
+      <c r="G60" s="24" t="n"/>
+      <c r="H60" s="24" t="n"/>
+      <c r="I60" s="24" t="n"/>
+      <c r="J60" s="24" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="45" t="inlineStr">
+        <is>
+          <t>cirorocha</t>
+        </is>
+      </c>
+      <c r="B61" s="45" t="inlineStr">
+        <is>
+          <t>Ciro Rocha Soares</t>
+        </is>
+      </c>
+      <c r="C61" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D61" s="45" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="E61" s="45" t="inlineStr">
+        <is>
+          <t>Advogado de Vorcaro; mensagens o mostram aproximando o banqueiro de Mendonça</t>
+        </is>
+      </c>
+      <c r="F61" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A61)+COUNTIF(Edges!$B$2:$B$182,A61)</f>
+        <v/>
+      </c>
+      <c r="G61" s="24" t="n"/>
+      <c r="H61" s="24" t="n"/>
+      <c r="I61" s="24" t="n"/>
+      <c r="J61" s="24" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="45" t="inlineStr">
+        <is>
+          <t>cezinha</t>
+        </is>
+      </c>
+      <c r="B62" s="45" t="inlineStr">
+        <is>
+          <t>Cezinha de Madureira</t>
+        </is>
+      </c>
+      <c r="C62" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D62" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E62" s="45" t="inlineStr">
+        <is>
+          <t>Deputado; presente na reunião Mendonça–Vorcaro (fev/2025); alvo de operação autorizada por Dino</t>
+        </is>
+      </c>
+      <c r="F62" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A62)+COUNTIF(Edges!$B$2:$B$182,A62)</f>
+        <v/>
+      </c>
+      <c r="G62" s="24" t="n"/>
+      <c r="H62" s="24" t="n"/>
+      <c r="I62" s="24" t="n"/>
+      <c r="J62" s="24" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="45" t="inlineStr">
+        <is>
+          <t>bianco</t>
+        </is>
+      </c>
+      <c r="B63" s="45" t="inlineStr">
+        <is>
+          <t>Bruno Bianco Leal</t>
+        </is>
+      </c>
+      <c r="C63" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D63" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E63" s="45" t="inlineStr">
+        <is>
+          <t>Ex-AGU do governo Jair; convidado para a reunião com Vorcaro</t>
+        </is>
+      </c>
+      <c r="F63" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A63)+COUNTIF(Edges!$B$2:$B$182,A63)</f>
+        <v/>
+      </c>
+      <c r="G63" s="24" t="n"/>
+      <c r="H63" s="24" t="n"/>
+      <c r="I63" s="24" t="n"/>
+      <c r="J63" s="24" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="45" t="inlineStr">
+        <is>
+          <t>tarcisio</t>
+        </is>
+      </c>
+      <c r="B64" s="45" t="inlineStr">
+        <is>
+          <t>Tarcísio de Freitas</t>
+        </is>
+      </c>
+      <c r="C64" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D64" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E64" s="45" t="inlineStr">
+        <is>
+          <t>Governador de SP; recebeu R$ 2 mi de Zettel em 2022; governo dele contratou o ITER</t>
+        </is>
+      </c>
+      <c r="F64" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A64)+COUNTIF(Edges!$B$2:$B$182,A64)</f>
+        <v/>
+      </c>
+      <c r="G64" s="24" t="n"/>
+      <c r="H64" s="24" t="n"/>
+      <c r="I64" s="24" t="n"/>
+      <c r="J64" s="24" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="45" t="inlineStr">
+        <is>
+          <t>rnunes</t>
+        </is>
+      </c>
+      <c r="B65" s="45" t="inlineStr">
+        <is>
+          <t>Ricardo Nunes</t>
+        </is>
+      </c>
+      <c r="C65" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D65" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E65" s="45" t="inlineStr">
+        <is>
+          <t>Prefeito de SP; prefeitura contratou o ITER</t>
+        </is>
+      </c>
+      <c r="F65" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A65)+COUNTIF(Edges!$B$2:$B$182,A65)</f>
+        <v/>
+      </c>
+      <c r="G65" s="24" t="n"/>
+      <c r="H65" s="24" t="n"/>
+      <c r="I65" s="24" t="n"/>
+      <c r="J65" s="24" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="45" t="inlineStr">
+        <is>
+          <t>castro</t>
+        </is>
+      </c>
+      <c r="B66" s="45" t="inlineStr">
+        <is>
+          <t>Cláudio Castro</t>
+        </is>
+      </c>
+      <c r="C66" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D66" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E66" s="45" t="inlineStr">
+        <is>
+          <t>Governo dele no RJ contratou o ITER</t>
+        </is>
+      </c>
+      <c r="F66" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A66)+COUNTIF(Edges!$B$2:$B$182,A66)</f>
+        <v/>
+      </c>
+      <c r="G66" s="24" t="n"/>
+      <c r="H66" s="24" t="n"/>
+      <c r="I66" s="24" t="n"/>
+      <c r="J66" s="24" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="45" t="inlineStr">
+        <is>
+          <t>moraes</t>
+        </is>
+      </c>
+      <c r="B67" s="45" t="inlineStr">
+        <is>
+          <t>Alexandre de Moraes</t>
+        </is>
+      </c>
+      <c r="C67" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D67" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E67" s="45" t="inlineStr">
+        <is>
+          <t>Ministro do STF</t>
+        </is>
+      </c>
+      <c r="F67" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A67)+COUNTIF(Edges!$B$2:$B$182,A67)</f>
+        <v/>
+      </c>
+      <c r="G67" s="24" t="n"/>
+      <c r="H67" s="24" t="n"/>
+      <c r="I67" s="24" t="n"/>
+      <c r="J67" s="24" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="45" t="inlineStr">
+        <is>
+          <t>faria</t>
+        </is>
+      </c>
+      <c r="B68" s="45" t="inlineStr">
+        <is>
+          <t>Fábio Faria</t>
+        </is>
+      </c>
+      <c r="C68" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D68" s="45" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="E68" s="45" t="inlineStr">
+        <is>
+          <t>Ex-ministro das Comunicações de Jair; PF o aponta como articulador de Vorcaro em Brasília</t>
+        </is>
+      </c>
+      <c r="F68" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A68)+COUNTIF(Edges!$B$2:$B$182,A68)</f>
+        <v/>
+      </c>
+      <c r="G68" s="24" t="n"/>
+      <c r="H68" s="24" t="n"/>
+      <c r="I68" s="24" t="n"/>
+      <c r="J68" s="24" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="45" t="inlineStr">
+        <is>
+          <t>motta</t>
+        </is>
+      </c>
+      <c r="B69" s="45" t="inlineStr">
+        <is>
+          <t>Hugo Motta</t>
+        </is>
+      </c>
+      <c r="C69" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D69" s="45" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="E69" s="45" t="inlineStr">
+        <is>
+          <t>Presidente da Câmara; em grupo de mensagens com Vorcaro</t>
+        </is>
+      </c>
+      <c r="F69" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A69)+COUNTIF(Edges!$B$2:$B$182,A69)</f>
+        <v/>
+      </c>
+      <c r="G69" s="24" t="n"/>
+      <c r="H69" s="24" t="n"/>
+      <c r="I69" s="24" t="n"/>
+      <c r="J69" s="24" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="45" t="inlineStr">
+        <is>
+          <t>frias</t>
+        </is>
+      </c>
+      <c r="B70" s="45" t="inlineStr">
+        <is>
+          <t>Mario Frias</t>
+        </is>
+      </c>
+      <c r="C70" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D70" s="45" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="E70" s="45" t="inlineStr">
+        <is>
+          <t>Ex-secretário de Cultura de Jair; produtor-executivo de Dark Horse</t>
+        </is>
+      </c>
+      <c r="F70" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A70)+COUNTIF(Edges!$B$2:$B$182,A70)</f>
+        <v/>
+      </c>
+      <c r="G70" s="24" t="n"/>
+      <c r="H70" s="24" t="n"/>
+      <c r="I70" s="24" t="n"/>
+      <c r="J70" s="24" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="45" t="inlineStr">
+        <is>
+          <t>marcal</t>
+        </is>
+      </c>
+      <c r="B71" s="45" t="inlineStr">
+        <is>
+          <t>Pablo Marçal</t>
+        </is>
+      </c>
+      <c r="C71" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D71" s="45" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="E71" s="45" t="inlineStr">
+        <is>
+          <t>Voo internacional de R$ 1 mi pago por empresa da qual Vorcaro era sócio</t>
+        </is>
+      </c>
+      <c r="F71" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A71)+COUNTIF(Edges!$B$2:$B$182,A71)</f>
+        <v/>
+      </c>
+      <c r="G71" s="24" t="n"/>
+      <c r="H71" s="24" t="n"/>
+      <c r="I71" s="24" t="n"/>
+      <c r="J71" s="24" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="45" t="inlineStr">
+        <is>
+          <t>govlula</t>
+        </is>
+      </c>
+      <c r="B72" s="45" t="inlineStr">
+        <is>
+          <t>Governo Lula (Haddad, Gleisi, Mercadante)</t>
+        </is>
+      </c>
+      <c r="C72" s="45" t="inlineStr">
+        <is>
+          <t>Instituição ou caso</t>
+        </is>
+      </c>
+      <c r="D72" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E72" s="45" t="inlineStr">
+        <is>
+          <t>Mensagens: Vorcaro via Haddad como opositor e tentou “bloquear” Gleisi e Mercadante</t>
+        </is>
+      </c>
+      <c r="F72" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A72)+COUNTIF(Edges!$B$2:$B$182,A72)</f>
+        <v/>
+      </c>
+      <c r="G72" s="24" t="n"/>
+      <c r="H72" s="24" t="n"/>
+      <c r="I72" s="24" t="n"/>
+      <c r="J72" s="24" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="45" t="inlineStr">
+        <is>
+          <t>brb</t>
+        </is>
+      </c>
+      <c r="B73" s="45" t="inlineStr">
+        <is>
+          <t>BRB (Banco de Brasília)</t>
+        </is>
+      </c>
+      <c r="C73" s="45" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="D73" s="45" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="E73" s="45" t="inlineStr">
+        <is>
+          <t>Banco público do DF, citado no caso Master; financiou a mansão de Flávio</t>
+        </is>
+      </c>
+      <c r="F73" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A73)+COUNTIF(Edges!$B$2:$B$182,A73)</f>
+        <v/>
+      </c>
+      <c r="G73" s="24" t="n"/>
+      <c r="H73" s="24" t="n"/>
+      <c r="I73" s="24" t="n"/>
+      <c r="J73" s="24" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="45" t="inlineStr">
+        <is>
+          <t>mansaobsb</t>
+        </is>
+      </c>
+      <c r="B74" s="45" t="inlineStr">
+        <is>
+          <t>Mansão de Flávio em Brasília</t>
+        </is>
+      </c>
+      <c r="C74" s="45" t="inlineStr">
+        <is>
+          <t>Casa ou ativo</t>
+        </is>
+      </c>
+      <c r="D74" s="45" t="inlineStr">
+        <is>
+          <t>Casas e ativos</t>
+        </is>
+      </c>
+      <c r="E74" s="45" t="inlineStr">
+        <is>
+          <t>Avaliada em R$ 6 mi; terreno de 2.400 m²; quitada 27 anos antes do previsto</t>
+        </is>
+      </c>
+      <c r="F74" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A74)+COUNTIF(Edges!$B$2:$B$182,A74)</f>
+        <v/>
+      </c>
+      <c r="G74" s="24" t="n"/>
+      <c r="H74" s="24" t="n"/>
+      <c r="I74" s="24" t="n"/>
+      <c r="J74" s="24" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="45" t="inlineStr">
+        <is>
+          <t>kopenhagen</t>
+        </is>
+      </c>
+      <c r="B75" s="45" t="inlineStr">
+        <is>
+          <t>Loja Kopenhagen de Flávio</t>
+        </is>
+      </c>
+      <c r="C75" s="45" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="D75" s="45" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="E75" s="45" t="inlineStr">
+        <is>
+          <t>Franquia no Via Parque (RJ), já vendida; MP suspeitou de lavagem da rachadinha</t>
+        </is>
+      </c>
+      <c r="F75" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A75)+COUNTIF(Edges!$B$2:$B$182,A75)</f>
+        <v/>
+      </c>
+      <c r="G75" s="24" t="n"/>
+      <c r="H75" s="24" t="n"/>
+      <c r="I75" s="24" t="n"/>
+      <c r="J75" s="24" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="45" t="inlineStr">
+        <is>
+          <t>adriano</t>
+        </is>
+      </c>
+      <c r="B76" s="45" t="inlineStr">
+        <is>
+          <t>Adriano da Nóbrega</t>
+        </is>
+      </c>
+      <c r="C76" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D76" s="45" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="E76" s="45" t="inlineStr">
+        <is>
+          <t>Ex-capitão do Bope, apontado como chefe do Escritório do Crime; morto em fev/2020</t>
+        </is>
+      </c>
+      <c r="F76" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A76)+COUNTIF(Edges!$B$2:$B$182,A76)</f>
+        <v/>
+      </c>
+      <c r="G76" s="24" t="n"/>
+      <c r="H76" s="24" t="n"/>
+      <c r="I76" s="24" t="n"/>
+      <c r="J76" s="24" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="45" t="inlineStr">
+        <is>
+          <t>ronald</t>
+        </is>
+      </c>
+      <c r="B77" s="45" t="inlineStr">
+        <is>
+          <t>Ronald Paulo Alves Pereira</t>
+        </is>
+      </c>
+      <c r="C77" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D77" s="45" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="E77" s="45" t="inlineStr">
+        <is>
+          <t>Apontado como liderança de milícia no Rio; homenageado por Flávio em 2004</t>
+        </is>
+      </c>
+      <c r="F77" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A77)+COUNTIF(Edges!$B$2:$B$182,A77)</f>
+        <v/>
+      </c>
+      <c r="G77" s="24" t="n"/>
+      <c r="H77" s="24" t="n"/>
+      <c r="I77" s="24" t="n"/>
+      <c r="J77" s="24" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="45" t="inlineStr">
+        <is>
+          <t>orelha</t>
+        </is>
+      </c>
+      <c r="B78" s="45" t="inlineStr">
+        <is>
+          <t>Luís Carlos Felipe Martins (“Orelha”)</t>
+        </is>
+      </c>
+      <c r="C78" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D78" s="45" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="E78" s="45" t="inlineStr">
+        <is>
+          <t>Ex-PM expulso, ligado à milícia de Rio das Pedras; homenageado por Flávio; morto em 2021</t>
+        </is>
+      </c>
+      <c r="F78" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A78)+COUNTIF(Edges!$B$2:$B$182,A78)</f>
+        <v/>
+      </c>
+      <c r="G78" s="24" t="n"/>
+      <c r="H78" s="24" t="n"/>
+      <c r="I78" s="24" t="n"/>
+      <c r="J78" s="24" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>pms16</t>
+        </is>
+      </c>
+      <c r="B79" s="45" t="inlineStr">
+        <is>
+          <t>16 PMs denunciados</t>
+        </is>
+      </c>
+      <c r="C79" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D79" s="45" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="E79" s="45" t="inlineStr">
+        <is>
+          <t>Condecorados por Flávio e Carlos; denunciados como integrantes de organizações criminosas</t>
+        </is>
+      </c>
+      <c r="F79" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A79)+COUNTIF(Edges!$B$2:$B$182,A79)</f>
+        <v/>
+      </c>
+      <c r="G79" s="24" t="n"/>
+      <c r="H79" s="24" t="n"/>
+      <c r="I79" s="24" t="n"/>
+      <c r="J79" s="24" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="45" t="inlineStr">
+        <is>
+          <t>peixe</t>
+        </is>
+      </c>
+      <c r="B80" s="45" t="inlineStr">
+        <is>
+          <t>Robson Calixto (“Peixe”)</t>
+        </is>
+      </c>
+      <c r="C80" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D80" s="45" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="E80" s="45" t="inlineStr">
+        <is>
+          <t>Condenado no caso Marielle; negociou emenda com assessora de Flávio</t>
+        </is>
+      </c>
+      <c r="F80" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A80)+COUNTIF(Edges!$B$2:$B$182,A80)</f>
+        <v/>
+      </c>
+      <c r="G80" s="24" t="n"/>
+      <c r="H80" s="24" t="n"/>
+      <c r="I80" s="24" t="n"/>
+      <c r="J80" s="24" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="45" t="inlineStr">
+        <is>
+          <t>ongbrazao</t>
+        </is>
+      </c>
+      <c r="B81" s="45" t="inlineStr">
+        <is>
+          <t>ONG ligada aos irmãos Brazão</t>
+        </is>
+      </c>
+      <c r="C81" s="45" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="D81" s="45" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="E81" s="45" t="inlineStr">
+        <is>
+          <t>Recebeu emenda de Flávio; PF apura desvios</t>
+        </is>
+      </c>
+      <c r="F81" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A81)+COUNTIF(Edges!$B$2:$B$182,A81)</f>
+        <v/>
+      </c>
+      <c r="G81" s="24" t="n"/>
+      <c r="H81" s="24" t="n"/>
+      <c r="I81" s="24" t="n"/>
+      <c r="J81" s="24" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>gaspar</t>
+        </is>
+      </c>
+      <c r="B82" s="45" t="inlineStr">
+        <is>
+          <t>Alfredo Gaspar</t>
+        </is>
+      </c>
+      <c r="C82" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D82" s="45" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="E82" s="45" t="inlineStr">
+        <is>
+          <t>Vice na chapa de Flávio; pedido de investigação arquivado pelo STF (out/2026); nega</t>
+        </is>
+      </c>
+      <c r="F82" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A82)+COUNTIF(Edges!$B$2:$B$182,A82)</f>
+        <v/>
+      </c>
+      <c r="G82" s="24" t="n"/>
+      <c r="H82" s="24" t="n"/>
+      <c r="I82" s="24" t="n"/>
+      <c r="J82" s="24" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="45" t="inlineStr">
+        <is>
+          <t>jbcarvalho</t>
+        </is>
+      </c>
+      <c r="B83" s="45" t="inlineStr">
+        <is>
+          <t>Bispo JB Carvalho</t>
+        </is>
+      </c>
+      <c r="C83" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D83" s="45" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="E83" s="45" t="inlineStr">
+        <is>
+          <t>Pastor de Flávio; defendeu em livro retirar o título de padroeira de N. Sra. Aparecida</t>
+        </is>
+      </c>
+      <c r="F83" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A83)+COUNTIF(Edges!$B$2:$B$182,A83)</f>
+        <v/>
+      </c>
+      <c r="G83" s="24" t="n"/>
+      <c r="H83" s="24" t="n"/>
+      <c r="I83" s="24" t="n"/>
+      <c r="J83" s="24" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="45" t="inlineStr">
+        <is>
+          <t>pmacusado</t>
+        </is>
+      </c>
+      <c r="B84" s="45" t="inlineStr">
+        <is>
+          <t>PM acusado de matar menina de 5 anos</t>
+        </is>
+      </c>
+      <c r="C84" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D84" s="45" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="E84" s="45" t="inlineStr">
+        <is>
+          <t>Preso em flagrante no RJ; Flávio atuou como advogado dele no STJ</t>
+        </is>
+      </c>
+      <c r="F84" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$182,A84)+COUNTIF(Edges!$B$2:$B$182,A84)</f>
+        <v/>
+      </c>
+      <c r="G84" s="24" t="n"/>
+      <c r="H84" s="24" t="n"/>
+      <c r="I84" s="24" t="n"/>
+      <c r="J84" s="24" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F58"/>
@@ -5555,7 +6763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F120"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="24" min="1" max="2"/>
@@ -5618,11 +6826,11 @@
         </is>
       </c>
       <c r="E2" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A2,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A2,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F2" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B2,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B2,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -5648,11 +6856,11 @@
         </is>
       </c>
       <c r="E3" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A3,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A3,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F3" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B3,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B3,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -5678,11 +6886,11 @@
         </is>
       </c>
       <c r="E4" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A4,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A4,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F4" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B4,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B4,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -5708,11 +6916,11 @@
         </is>
       </c>
       <c r="E5" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A5,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A5,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F5" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B5,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B5,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -5738,11 +6946,11 @@
         </is>
       </c>
       <c r="E6" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A6,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A6,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F6" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B6,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B6,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -5768,11 +6976,11 @@
         </is>
       </c>
       <c r="E7" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A7,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A7,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F7" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B7,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B7,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -5798,11 +7006,11 @@
         </is>
       </c>
       <c r="E8" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A8,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A8,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F8" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B8,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B8,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -5828,11 +7036,11 @@
         </is>
       </c>
       <c r="E9" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A9,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A9,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F9" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B9,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B9,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -5858,11 +7066,11 @@
         </is>
       </c>
       <c r="E10" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A10,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A10,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F10" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B10,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B10,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -5888,11 +7096,11 @@
         </is>
       </c>
       <c r="E11" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A11,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A11,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F11" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B11,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B11,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -5918,11 +7126,11 @@
         </is>
       </c>
       <c r="E12" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A12,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A12,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F12" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B12,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B12,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -5948,11 +7156,11 @@
         </is>
       </c>
       <c r="E13" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A13,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A13,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F13" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B13,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B13,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -5978,11 +7186,11 @@
         </is>
       </c>
       <c r="E14" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A14,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A14,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F14" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B14,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B14,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6008,11 +7216,11 @@
         </is>
       </c>
       <c r="E15" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A15,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A15,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F15" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B15,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B15,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6038,11 +7246,11 @@
         </is>
       </c>
       <c r="E16" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A16,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A16,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F16" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B16,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B16,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6068,11 +7276,11 @@
         </is>
       </c>
       <c r="E17" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A17,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A17,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F17" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B17,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B17,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6098,11 +7306,11 @@
         </is>
       </c>
       <c r="E18" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A18,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A18,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F18" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B18,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B18,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6128,11 +7336,11 @@
         </is>
       </c>
       <c r="E19" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A19,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A19,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F19" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B19,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B19,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6158,11 +7366,11 @@
         </is>
       </c>
       <c r="E20" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A20,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A20,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F20" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B20,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B20,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6188,11 +7396,11 @@
         </is>
       </c>
       <c r="E21" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A21,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A21,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F21" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B21,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B21,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6218,11 +7426,11 @@
         </is>
       </c>
       <c r="E22" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A22,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A22,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F22" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B22,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B22,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6248,11 +7456,11 @@
         </is>
       </c>
       <c r="E23" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A23,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A23,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F23" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B23,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B23,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6278,11 +7486,11 @@
         </is>
       </c>
       <c r="E24" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A24,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A24,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F24" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B24,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B24,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6308,11 +7516,11 @@
         </is>
       </c>
       <c r="E25" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A25,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A25,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F25" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B25,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B25,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6338,11 +7546,11 @@
         </is>
       </c>
       <c r="E26" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A26,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A26,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F26" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B26,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B26,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6368,11 +7576,11 @@
         </is>
       </c>
       <c r="E27" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A27,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A27,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F27" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B27,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B27,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6398,11 +7606,11 @@
         </is>
       </c>
       <c r="E28" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A28,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A28,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F28" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B28,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B28,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6428,11 +7636,11 @@
         </is>
       </c>
       <c r="E29" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A29,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A29,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F29" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B29,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B29,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6458,11 +7666,11 @@
         </is>
       </c>
       <c r="E30" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A30,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A30,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F30" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B30,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B30,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6488,11 +7696,11 @@
         </is>
       </c>
       <c r="E31" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A31,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A31,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F31" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B31,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B31,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6518,11 +7726,11 @@
         </is>
       </c>
       <c r="E32" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A32,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A32,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F32" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B32,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B32,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6548,11 +7756,11 @@
         </is>
       </c>
       <c r="E33" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A33,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A33,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F33" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B33,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B33,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6578,11 +7786,11 @@
         </is>
       </c>
       <c r="E34" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A34,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A34,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F34" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B34,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B34,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6608,11 +7816,11 @@
         </is>
       </c>
       <c r="E35" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A35,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A35,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F35" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B35,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B35,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6638,11 +7846,11 @@
         </is>
       </c>
       <c r="E36" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A36,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A36,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F36" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B36,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B36,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6668,11 +7876,11 @@
         </is>
       </c>
       <c r="E37" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A37,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A37,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F37" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B37,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B37,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6698,11 +7906,11 @@
         </is>
       </c>
       <c r="E38" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A38,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A38,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F38" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B38,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B38,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6728,11 +7936,11 @@
         </is>
       </c>
       <c r="E39" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A39,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A39,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F39" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B39,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B39,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6758,11 +7966,11 @@
         </is>
       </c>
       <c r="E40" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A40,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A40,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F40" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B40,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B40,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6788,11 +7996,11 @@
         </is>
       </c>
       <c r="E41" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A41,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A41,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F41" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B41,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B41,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6818,11 +8026,11 @@
         </is>
       </c>
       <c r="E42" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A42,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A42,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F42" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B42,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B42,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6848,11 +8056,11 @@
         </is>
       </c>
       <c r="E43" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A43,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A43,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F43" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B43,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B43,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6878,11 +8086,11 @@
         </is>
       </c>
       <c r="E44" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A44,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A44,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F44" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B44,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B44,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6908,11 +8116,11 @@
         </is>
       </c>
       <c r="E45" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A45,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A45,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F45" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B45,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B45,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6938,11 +8146,11 @@
         </is>
       </c>
       <c r="E46" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A46,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A46,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F46" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B46,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B46,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6968,11 +8176,11 @@
         </is>
       </c>
       <c r="E47" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A47,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A47,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F47" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B47,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B47,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -6998,11 +8206,11 @@
         </is>
       </c>
       <c r="E48" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A48,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A48,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F48" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B48,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B48,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7028,11 +8236,11 @@
         </is>
       </c>
       <c r="E49" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A49,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A49,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F49" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B49,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B49,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7058,11 +8266,11 @@
         </is>
       </c>
       <c r="E50" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A50,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A50,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F50" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B50,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B50,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7088,11 +8296,11 @@
         </is>
       </c>
       <c r="E51" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A51,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A51,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F51" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B51,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B51,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7118,11 +8326,11 @@
         </is>
       </c>
       <c r="E52" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A52,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A52,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F52" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B52,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B52,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7148,11 +8356,11 @@
         </is>
       </c>
       <c r="E53" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A53,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A53,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F53" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B53,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B53,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7178,11 +8386,11 @@
         </is>
       </c>
       <c r="E54" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A54,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A54,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F54" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B54,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B54,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7208,11 +8416,11 @@
         </is>
       </c>
       <c r="E55" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A55,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A55,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F55" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B55,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B55,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7238,11 +8446,11 @@
         </is>
       </c>
       <c r="E56" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A56,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A56,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F56" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B56,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B56,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7268,11 +8476,11 @@
         </is>
       </c>
       <c r="E57" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A57,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A57,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F57" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B57,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B57,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7298,11 +8506,11 @@
         </is>
       </c>
       <c r="E58" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A58,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A58,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F58" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B58,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B58,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7328,11 +8536,11 @@
         </is>
       </c>
       <c r="E59" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A59,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A59,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F59" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B59,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B59,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7358,11 +8566,11 @@
         </is>
       </c>
       <c r="E60" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A60,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A60,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F60" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B60,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B60,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7388,11 +8596,11 @@
         </is>
       </c>
       <c r="E61" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A61,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A61,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F61" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B61,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B61,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7418,11 +8626,11 @@
         </is>
       </c>
       <c r="E62" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A62,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A62,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F62" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B62,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B62,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7448,11 +8656,11 @@
         </is>
       </c>
       <c r="E63" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A63,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A63,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F63" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B63,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B63,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7478,11 +8686,11 @@
         </is>
       </c>
       <c r="E64" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A64,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A64,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F64" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B64,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B64,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7508,11 +8716,11 @@
         </is>
       </c>
       <c r="E65" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A65,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A65,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F65" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B65,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B65,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7538,11 +8746,11 @@
         </is>
       </c>
       <c r="E66" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A66,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A66,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F66" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B66,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B66,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7568,11 +8776,11 @@
         </is>
       </c>
       <c r="E67" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A67,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A67,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F67" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B67,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B67,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7598,11 +8806,11 @@
         </is>
       </c>
       <c r="E68" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A68,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A68,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F68" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B68,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B68,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7628,11 +8836,11 @@
         </is>
       </c>
       <c r="E69" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A69,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A69,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F69" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B69,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B69,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7658,11 +8866,11 @@
         </is>
       </c>
       <c r="E70" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A70,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A70,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F70" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B70,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B70,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7688,11 +8896,11 @@
         </is>
       </c>
       <c r="E71" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A71,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A71,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F71" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B71,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B71,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7718,11 +8926,11 @@
         </is>
       </c>
       <c r="E72" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A72,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A72,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F72" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B72,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B72,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7748,11 +8956,11 @@
         </is>
       </c>
       <c r="E73" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A73,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A73,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F73" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B73,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B73,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7778,11 +8986,11 @@
         </is>
       </c>
       <c r="E74" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A74,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A74,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F74" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B74,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B74,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7808,11 +9016,11 @@
         </is>
       </c>
       <c r="E75" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A75,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A75,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F75" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B75,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B75,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7838,11 +9046,11 @@
         </is>
       </c>
       <c r="E76" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A76,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A76,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F76" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B76,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B76,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7868,11 +9076,11 @@
         </is>
       </c>
       <c r="E77" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A77,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A77,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F77" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B77,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B77,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7898,11 +9106,11 @@
         </is>
       </c>
       <c r="E78" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A78,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A78,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F78" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B78,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B78,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7928,11 +9136,11 @@
         </is>
       </c>
       <c r="E79" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A79,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A79,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F79" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B79,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B79,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7958,11 +9166,11 @@
         </is>
       </c>
       <c r="E80" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A80,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A80,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F80" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B80,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B80,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -7988,11 +9196,11 @@
         </is>
       </c>
       <c r="E81" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A81,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A81,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F81" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B81,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B81,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8018,11 +9226,11 @@
         </is>
       </c>
       <c r="E82" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A82,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A82,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F82" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B82,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B82,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8048,11 +9256,11 @@
         </is>
       </c>
       <c r="E83" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A83,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A83,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F83" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B83,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B83,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8078,11 +9286,11 @@
         </is>
       </c>
       <c r="E84" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A84,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A84,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F84" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B84,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B84,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8108,11 +9316,11 @@
         </is>
       </c>
       <c r="E85" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A85,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A85,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F85" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B85,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B85,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8138,11 +9346,11 @@
         </is>
       </c>
       <c r="E86" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A86,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A86,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F86" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B86,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B86,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8168,11 +9376,11 @@
         </is>
       </c>
       <c r="E87" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A87,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A87,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F87" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B87,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B87,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8198,11 +9406,11 @@
         </is>
       </c>
       <c r="E88" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A88,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A88,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F88" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B88,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B88,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8228,11 +9436,11 @@
         </is>
       </c>
       <c r="E89" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A89,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A89,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F89" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B89,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B89,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8258,11 +9466,11 @@
         </is>
       </c>
       <c r="E90" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A90,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A90,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F90" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B90,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B90,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8288,11 +9496,11 @@
         </is>
       </c>
       <c r="E91" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A91,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A91,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F91" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B91,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B91,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8318,11 +9526,11 @@
         </is>
       </c>
       <c r="E92" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A92,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A92,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F92" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B92,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B92,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8348,11 +9556,11 @@
         </is>
       </c>
       <c r="E93" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A93,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A93,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F93" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B93,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B93,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8378,11 +9586,11 @@
         </is>
       </c>
       <c r="E94" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A94,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A94,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F94" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B94,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B94,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8408,11 +9616,11 @@
         </is>
       </c>
       <c r="E95" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A95,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A95,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F95" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B95,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B95,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8438,11 +9646,11 @@
         </is>
       </c>
       <c r="E96" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A96,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A96,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F96" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B96,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B96,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8468,11 +9676,11 @@
         </is>
       </c>
       <c r="E97" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A97,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A97,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F97" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B97,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B97,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8498,11 +9706,11 @@
         </is>
       </c>
       <c r="E98" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A98,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A98,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F98" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B98,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B98,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8528,11 +9736,11 @@
         </is>
       </c>
       <c r="E99" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A99,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A99,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F99" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B99,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B99,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8558,11 +9766,11 @@
         </is>
       </c>
       <c r="E100" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A100,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A100,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F100" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B100,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B100,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8588,11 +9796,11 @@
         </is>
       </c>
       <c r="E101" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A101,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A101,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F101" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B101,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B101,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8618,11 +9826,11 @@
         </is>
       </c>
       <c r="E102" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A102,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A102,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F102" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B102,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B102,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8648,11 +9856,11 @@
         </is>
       </c>
       <c r="E103" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A103,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A103,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F103" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B103,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B103,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8678,11 +9886,11 @@
         </is>
       </c>
       <c r="E104" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A104,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A104,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F104" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B104,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B104,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8708,11 +9916,11 @@
         </is>
       </c>
       <c r="E105" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A105,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A105,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F105" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B105,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B105,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8738,11 +9946,11 @@
         </is>
       </c>
       <c r="E106" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A106,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A106,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F106" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B106,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B106,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8768,11 +9976,11 @@
         </is>
       </c>
       <c r="E107" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A107,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A107,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F107" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B107,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B107,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8798,11 +10006,11 @@
         </is>
       </c>
       <c r="E108" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A108,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A108,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F108" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B108,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B108,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8828,11 +10036,11 @@
         </is>
       </c>
       <c r="E109" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A109,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A109,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F109" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B109,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B109,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8858,11 +10066,11 @@
         </is>
       </c>
       <c r="E110" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A110,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A110,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F110" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B110,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B110,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8888,11 +10096,11 @@
         </is>
       </c>
       <c r="E111" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A111,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A111,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F111" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B111,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B111,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8918,11 +10126,11 @@
         </is>
       </c>
       <c r="E112" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A112,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A112,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F112" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B112,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B112,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8948,11 +10156,11 @@
         </is>
       </c>
       <c r="E113" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A113,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A113,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F113" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B113,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B113,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -8978,11 +10186,11 @@
         </is>
       </c>
       <c r="E114" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A114,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A114,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F114" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B114,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B114,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -9008,11 +10216,11 @@
         </is>
       </c>
       <c r="E115" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A115,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A115,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F115" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B115,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B115,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -9038,11 +10246,11 @@
         </is>
       </c>
       <c r="E116" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A116,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A116,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F116" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B116,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B116,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -9068,11 +10276,11 @@
         </is>
       </c>
       <c r="E117" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A117,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A117,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F117" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B117,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B117,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -9098,11 +10306,11 @@
         </is>
       </c>
       <c r="E118" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A118,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A118,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F118" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B118,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B118,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -9128,11 +10336,11 @@
         </is>
       </c>
       <c r="E119" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A119,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A119,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F119" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B119,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B119,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -9158,11 +10366,1871 @@
         </is>
       </c>
       <c r="E120" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(A120,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A120,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
       <c r="F120" s="45">
-        <f>INDEX(Nodes!$B$2:$B$58,MATCH(B120,Nodes!$A$2:$A$58,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B120,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="B121" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="C121" s="45" t="inlineStr">
+        <is>
+          <t>Visitas: um dia após a soltura e na véspera do anúncio da candidatura</t>
+        </is>
+      </c>
+      <c r="D121" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E121" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A121,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F121" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B121,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="B122" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="C122" s="45" t="inlineStr">
+        <is>
+          <t>Feriado de 1º de maio de 2025 na Flórida, dias após repasse ao filme (Piauí)</t>
+        </is>
+      </c>
+      <c r="D122" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E122" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A122,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F122" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B122,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="B123" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="C123" s="45" t="inlineStr">
+        <is>
+          <t>Ao menos 11 meses de contato no celular do banqueiro (Piauí); o Estadão fala em 3 meses e 6 encontros</t>
+        </is>
+      </c>
+      <c r="D123" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E123" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A123,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F123" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B123,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="45" t="inlineStr">
+        <is>
+          <t>brb</t>
+        </is>
+      </c>
+      <c r="B124" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="C124" s="45" t="inlineStr">
+        <is>
+          <t>Empréstimo para a mansão com juros abaixo do mercado; PF investiga</t>
+        </is>
+      </c>
+      <c r="D124" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E124" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A124,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F124" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B124,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="45" t="inlineStr">
+        <is>
+          <t>brb</t>
+        </is>
+      </c>
+      <c r="B125" s="45" t="inlineStr">
+        <is>
+          <t>mansaobsb</t>
+        </is>
+      </c>
+      <c r="C125" s="45" t="inlineStr">
+        <is>
+          <t>Financiou a compra</t>
+        </is>
+      </c>
+      <c r="D125" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E125" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A125,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F125" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B125,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="B126" s="45" t="inlineStr">
+        <is>
+          <t>mansaobsb</t>
+        </is>
+      </c>
+      <c r="C126" s="45" t="inlineStr">
+        <is>
+          <t>Comprou; ele diz pagar com renda de advogado</t>
+        </is>
+      </c>
+      <c r="D126" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E126" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A126,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F126" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B126,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="45" t="inlineStr">
+        <is>
+          <t>zetel</t>
+        </is>
+      </c>
+      <c r="B127" s="45" t="inlineStr">
+        <is>
+          <t>jair</t>
+        </is>
+      </c>
+      <c r="C127" s="45" t="inlineStr">
+        <is>
+          <t>Maior doador da campanha de 2022 (R$ 3 mi)</t>
+        </is>
+      </c>
+      <c r="D127" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E127" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A127,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F127" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B127,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="45" t="inlineStr">
+        <is>
+          <t>zetel</t>
+        </is>
+      </c>
+      <c r="B128" s="45" t="inlineStr">
+        <is>
+          <t>tarcisio</t>
+        </is>
+      </c>
+      <c r="C128" s="45" t="inlineStr">
+        <is>
+          <t>Doou R$ 2 mi à campanha de 2022</t>
+        </is>
+      </c>
+      <c r="D128" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E128" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A128,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F128" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B128,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="45" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B129" s="45" t="inlineStr">
+        <is>
+          <t>nunes</t>
+        </is>
+      </c>
+      <c r="C129" s="45" t="inlineStr">
+        <is>
+          <t>Contrato da “Turma do KN” de até R$ 427 mi, condicionado a êxito (CNN); ele nega agir pelo banco</t>
+        </is>
+      </c>
+      <c r="D129" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E129" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A129,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F129" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B129,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="B130" s="45" t="inlineStr">
+        <is>
+          <t>kevin</t>
+        </is>
+      </c>
+      <c r="C130" s="45" t="inlineStr">
+        <is>
+          <t>Diálogos citam suposta mesada de R$ 500 mil (CNN); Nunes nega que o filho tenha servido ao Master</t>
+        </is>
+      </c>
+      <c r="D130" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E130" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A130,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F130" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B130,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="45" t="inlineStr">
+        <is>
+          <t>zetel</t>
+        </is>
+      </c>
+      <c r="B131" s="45" t="inlineStr">
+        <is>
+          <t>nunes</t>
+        </is>
+      </c>
+      <c r="C131" s="45" t="inlineStr">
+        <is>
+          <t>Reportagem cita encontro com garota de programa em apartamento de Zettel; ministro nega irregularidades</t>
+        </is>
+      </c>
+      <c r="D131" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E131" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A131,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F131" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B131,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="45" t="inlineStr">
+        <is>
+          <t>jair</t>
+        </is>
+      </c>
+      <c r="B132" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="C132" s="45" t="inlineStr">
+        <is>
+          <t>Indicou ao STF</t>
+        </is>
+      </c>
+      <c r="D132" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E132" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A132,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F132" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B132,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="45" t="inlineStr">
+        <is>
+          <t>cirorocha</t>
+        </is>
+      </c>
+      <c r="B133" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C133" s="45" t="inlineStr">
+        <is>
+          <t>Advogado dele</t>
+        </is>
+      </c>
+      <c r="D133" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E133" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A133,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F133" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B133,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="45" t="inlineStr">
+        <is>
+          <t>cirorocha</t>
+        </is>
+      </c>
+      <c r="B134" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="C134" s="45" t="inlineStr">
+        <is>
+          <t>Levou o ministro a alfaiataria e articulou reunião com Vorcaro (mensagens)</t>
+        </is>
+      </c>
+      <c r="D134" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E134" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A134,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F134" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B134,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="B135" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C135" s="45" t="inlineStr">
+        <is>
+          <t>Reuniões em 19/02 e 14/03/2025 fora da agenda oficial</t>
+        </is>
+      </c>
+      <c r="D135" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E135" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A135,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F135" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B135,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="B136" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C136" s="45" t="inlineStr">
+        <is>
+          <t>Gabinete ouviu Vorcaro em 27/08/2026 sem a PF; recomendou sigilo do celular dele</t>
+        </is>
+      </c>
+      <c r="D136" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E136" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A136,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F136" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B136,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="45" t="inlineStr">
+        <is>
+          <t>bianco</t>
+        </is>
+      </c>
+      <c r="B137" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="C137" s="45" t="inlineStr">
+        <is>
+          <t>Convidado para a reunião com Vorcaro (fev/2025)</t>
+        </is>
+      </c>
+      <c r="D137" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E137" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A137,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F137" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B137,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="45" t="inlineStr">
+        <is>
+          <t>cezinha</t>
+        </is>
+      </c>
+      <c r="B138" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="C138" s="45" t="inlineStr">
+        <is>
+          <t>Na reunião de fev/2025; teria aproximado ministro e banqueiro</t>
+        </is>
+      </c>
+      <c r="D138" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E138" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A138,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F138" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B138,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="45" t="inlineStr">
+        <is>
+          <t>tarcisio</t>
+        </is>
+      </c>
+      <c r="B139" s="45" t="inlineStr">
+        <is>
+          <t>cezinha</t>
+        </is>
+      </c>
+      <c r="C139" s="45" t="inlineStr">
+        <is>
+          <t>Financiou 24% da campanha do deputado</t>
+        </is>
+      </c>
+      <c r="D139" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E139" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A139,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F139" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B139,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="B140" s="45" t="inlineStr">
+        <is>
+          <t>iter</t>
+        </is>
+      </c>
+      <c r="C140" s="45" t="inlineStr">
+        <is>
+          <t>Fundador</t>
+        </is>
+      </c>
+      <c r="D140" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E140" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A140,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F140" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B140,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="B141" s="45" t="inlineStr">
+        <is>
+          <t>iter</t>
+        </is>
+      </c>
+      <c r="C141" s="45" t="inlineStr">
+        <is>
+          <t>Empresa de sócio dele aportou R$ 5,2 mi (jan/2026); Vorcaro foi a coquetéis do instituto</t>
+        </is>
+      </c>
+      <c r="D141" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E141" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A141,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F141" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B141,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="B142" s="45" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="C142" s="45" t="inlineStr">
+        <is>
+          <t>Relator do caso Master no STF (sorteado em fev/2026)</t>
+        </is>
+      </c>
+      <c r="D142" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E142" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A142,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F142" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B142,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="B143" s="45" t="inlineStr">
+        <is>
+          <t>pf</t>
+        </is>
+      </c>
+      <c r="C143" s="45" t="inlineStr">
+        <is>
+          <t>Afastou o diretor-geral sem ouvir a PGR (set/2026); AGU vê usurpação de competência</t>
+        </is>
+      </c>
+      <c r="D143" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E143" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A143,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F143" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B143,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="B144" s="45" t="inlineStr">
+        <is>
+          <t>careca</t>
+        </is>
+      </c>
+      <c r="C144" s="45" t="inlineStr">
+        <is>
+          <t>Revogou a prisão do filho dele (09/09/2026)</t>
+        </is>
+      </c>
+      <c r="D144" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E144" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A144,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F144" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B144,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="45" t="inlineStr">
+        <is>
+          <t>pf</t>
+        </is>
+      </c>
+      <c r="B145" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="C145" s="45" t="inlineStr">
+        <is>
+          <t>Relatório aponta diferença de até 8x nos prazos de decisão e demora para rastrear o dinheiro</t>
+        </is>
+      </c>
+      <c r="D145" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E145" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A145,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F145" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B145,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="B146" s="45" t="inlineStr">
+        <is>
+          <t>moraes</t>
+        </is>
+      </c>
+      <c r="C146" s="45" t="inlineStr">
+        <is>
+          <t>PF: pressionou por Moraes; PGR diz que o investigou antes do aval do plenário</t>
+        </is>
+      </c>
+      <c r="D146" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E146" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A146,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F146" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B146,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="B147" s="45" t="inlineStr">
+        <is>
+          <t>nunes</t>
+        </is>
+      </c>
+      <c r="C147" s="45" t="inlineStr">
+        <is>
+          <t>PF: teria poupado Nunes e Toffoli</t>
+        </is>
+      </c>
+      <c r="D147" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E147" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A147,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F147" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B147,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="45" t="inlineStr">
+        <is>
+          <t>tarcisio</t>
+        </is>
+      </c>
+      <c r="B148" s="45" t="inlineStr">
+        <is>
+          <t>iter</t>
+        </is>
+      </c>
+      <c r="C148" s="45" t="inlineStr">
+        <is>
+          <t>Governo de SP contratou o instituto (R$ 1,6 mi, sem licitação)</t>
+        </is>
+      </c>
+      <c r="D148" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E148" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A148,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F148" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B148,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="45" t="inlineStr">
+        <is>
+          <t>rnunes</t>
+        </is>
+      </c>
+      <c r="B149" s="45" t="inlineStr">
+        <is>
+          <t>iter</t>
+        </is>
+      </c>
+      <c r="C149" s="45" t="inlineStr">
+        <is>
+          <t>Prefeitura de SP contratou o instituto (R$ 380 mil)</t>
+        </is>
+      </c>
+      <c r="D149" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E149" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A149,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F149" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B149,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="45" t="inlineStr">
+        <is>
+          <t>rnunes</t>
+        </is>
+      </c>
+      <c r="B150" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="C150" s="45" t="inlineStr">
+        <is>
+          <t>Promoveu o irmão do ministro após voto favorável à Prefeitura</t>
+        </is>
+      </c>
+      <c r="D150" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E150" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A150,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F150" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B150,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="45" t="inlineStr">
+        <is>
+          <t>castro</t>
+        </is>
+      </c>
+      <c r="B151" s="45" t="inlineStr">
+        <is>
+          <t>iter</t>
+        </is>
+      </c>
+      <c r="C151" s="45" t="inlineStr">
+        <is>
+          <t>Governo do RJ contratou o instituto (R$ 518 mil)</t>
+        </is>
+      </c>
+      <c r="D151" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E151" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A151,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F151" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B151,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="45" t="inlineStr">
+        <is>
+          <t>mendonca</t>
+        </is>
+      </c>
+      <c r="B152" s="45" t="inlineStr">
+        <is>
+          <t>castro</t>
+        </is>
+      </c>
+      <c r="C152" s="45" t="inlineStr">
+        <is>
+          <t>Votou a favor dele 4 vezes enquanto o instituto tinha contratos no Rio</t>
+        </is>
+      </c>
+      <c r="D152" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E152" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A152,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F152" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B152,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="B153" s="45" t="inlineStr">
+        <is>
+          <t>ciro</t>
+        </is>
+      </c>
+      <c r="C153" s="45" t="inlineStr">
+        <is>
+          <t>PF: mesada de R$ 300 mil a 500 mil e viagens pagas, incluindo Courchevel</t>
+        </is>
+      </c>
+      <c r="D153" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E153" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A153,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F153" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B153,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="45" t="inlineStr">
+        <is>
+          <t>ciro</t>
+        </is>
+      </c>
+      <c r="B154" s="45" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="C154" s="45" t="inlineStr">
+        <is>
+          <t>Autor da “Emenda Master” (garantia do FGC de R$ 250 mil para R$ 1 mi)</t>
+        </is>
+      </c>
+      <c r="D154" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E154" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A154,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F154" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B154,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="45" t="inlineStr">
+        <is>
+          <t>pf</t>
+        </is>
+      </c>
+      <c r="B155" s="45" t="inlineStr">
+        <is>
+          <t>ciro</t>
+        </is>
+      </c>
+      <c r="C155" s="45" t="inlineStr">
+        <is>
+          <t>Alvo da 5ª fase da Operação Compliance Zero</t>
+        </is>
+      </c>
+      <c r="D155" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E155" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A155,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F155" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B155,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="45" t="inlineStr">
+        <is>
+          <t>jair</t>
+        </is>
+      </c>
+      <c r="B156" s="45" t="inlineStr">
+        <is>
+          <t>faria</t>
+        </is>
+      </c>
+      <c r="C156" s="45" t="inlineStr">
+        <is>
+          <t>Ex-ministro das Comunicações</t>
+        </is>
+      </c>
+      <c r="D156" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E156" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A156,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F156" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B156,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="45" t="inlineStr">
+        <is>
+          <t>faria</t>
+        </is>
+      </c>
+      <c r="B157" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C157" s="45" t="inlineStr">
+        <is>
+          <t>PF: articulador dele em Brasília; empresa ligada ao banqueiro pagou R$ 67,5 mi por projeto de Faria</t>
+        </is>
+      </c>
+      <c r="D157" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E157" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A157,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F157" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B157,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="45" t="inlineStr">
+        <is>
+          <t>faria</t>
+        </is>
+      </c>
+      <c r="B158" s="45" t="inlineStr">
+        <is>
+          <t>moraes</t>
+        </is>
+      </c>
+      <c r="C158" s="45" t="inlineStr">
+        <is>
+          <t>PF: intermediou contatos entre Vorcaro e Moraes</t>
+        </is>
+      </c>
+      <c r="D158" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E158" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A158,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F158" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B158,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="45" t="inlineStr">
+        <is>
+          <t>motta</t>
+        </is>
+      </c>
+      <c r="B159" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C159" s="45" t="inlineStr">
+        <is>
+          <t>Grupo de mensagens com Vorcaro, Ciro e Faria para organizar encontros</t>
+        </is>
+      </c>
+      <c r="D159" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E159" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A159,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F159" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B159,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="45" t="inlineStr">
+        <is>
+          <t>jair</t>
+        </is>
+      </c>
+      <c r="B160" s="45" t="inlineStr">
+        <is>
+          <t>frias</t>
+        </is>
+      </c>
+      <c r="C160" s="45" t="inlineStr">
+        <is>
+          <t>Ex-secretário especial de Cultura</t>
+        </is>
+      </c>
+      <c r="D160" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E160" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A160,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F160" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B160,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="45" t="inlineStr">
+        <is>
+          <t>frias</t>
+        </is>
+      </c>
+      <c r="B161" s="45" t="inlineStr">
+        <is>
+          <t>ong</t>
+        </is>
+      </c>
+      <c r="C161" s="45" t="inlineStr">
+        <is>
+          <t>Produtor-executivo de Dark Horse</t>
+        </is>
+      </c>
+      <c r="D161" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E161" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A161,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F161" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B161,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="45" t="inlineStr">
+        <is>
+          <t>frias</t>
+        </is>
+      </c>
+      <c r="B162" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C162" s="45" t="inlineStr">
+        <is>
+          <t>Áudio agradece o financiamento do filme: “meu irmão”</t>
+        </is>
+      </c>
+      <c r="D162" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E162" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A162,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F162" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B162,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="B163" s="45" t="inlineStr">
+        <is>
+          <t>marcal</t>
+        </is>
+      </c>
+      <c r="C163" s="45" t="inlineStr">
+        <is>
+          <t>Empresa da qual Vorcaro era sócio pagou voo de R$ 1 mi</t>
+        </is>
+      </c>
+      <c r="D163" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E163" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A163,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F163" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B163,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="B164" s="45" t="inlineStr">
+        <is>
+          <t>govlula</t>
+        </is>
+      </c>
+      <c r="C164" s="45" t="inlineStr">
+        <is>
+          <t>Mensagens: via Haddad como opositor e pediu ajuda para “bloquear” Gleisi e Mercadante</t>
+        </is>
+      </c>
+      <c r="D164" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E164" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A164,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F164" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B164,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="45" t="inlineStr">
+        <is>
+          <t>gaspar</t>
+        </is>
+      </c>
+      <c r="B165" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="C165" s="45" t="inlineStr">
+        <is>
+          <t>Vice na chapa</t>
+        </is>
+      </c>
+      <c r="D165" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E165" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A165,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F165" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B165,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="45" t="inlineStr">
+        <is>
+          <t>jbcarvalho</t>
+        </is>
+      </c>
+      <c r="B166" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="C166" s="45" t="inlineStr">
+        <is>
+          <t>Flávio foi batizado na igreja dele (Folha)</t>
+        </is>
+      </c>
+      <c r="D166" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E166" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A166,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F166" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B166,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="45" t="inlineStr">
+        <is>
+          <t>kopenhagen</t>
+        </is>
+      </c>
+      <c r="B167" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="C167" s="45" t="inlineStr">
+        <is>
+          <t>Franquia dele; MP suspeitou de lavagem (1.512 depósitos em espécie)</t>
+        </is>
+      </c>
+      <c r="D167" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E167" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A167,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F167" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B167,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="B168" s="45" t="inlineStr">
+        <is>
+          <t>nunes</t>
+        </is>
+      </c>
+      <c r="C168" s="45" t="inlineStr">
+        <is>
+          <t>Ex-sócio na Kopenhagen cita lobby dele com Nunes (Brasil de Fato)</t>
+        </is>
+      </c>
+      <c r="D168" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E168" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A168,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F168" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B168,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="45" t="inlineStr">
+        <is>
+          <t>adriano</t>
+        </is>
+      </c>
+      <c r="B169" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="C169" s="45" t="inlineStr">
+        <is>
+          <t>Mãe e mulher empregadas no gabinete; homenageado por Flávio em 2003 e 2005</t>
+        </is>
+      </c>
+      <c r="D169" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E169" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A169,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F169" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B169,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="45" t="inlineStr">
+        <is>
+          <t>adriano</t>
+        </is>
+      </c>
+      <c r="B170" s="45" t="inlineStr">
+        <is>
+          <t>coaf</t>
+        </is>
+      </c>
+      <c r="C170" s="45" t="inlineStr">
+        <is>
+          <t>MP-RJ: mãe e mulher eram “assessoras fantasmas” e devolviam salário (310 desvios)</t>
+        </is>
+      </c>
+      <c r="D170" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E170" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A170,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F170" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B170,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="45" t="inlineStr">
+        <is>
+          <t>coaf</t>
+        </is>
+      </c>
+      <c r="B171" s="45" t="inlineStr">
+        <is>
+          <t>adriano</t>
+        </is>
+      </c>
+      <c r="C171" s="45" t="inlineStr">
+        <is>
+          <t>Dinheiro da rachadinha teria financiado prédios da milícia (Intercept)</t>
+        </is>
+      </c>
+      <c r="D171" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E171" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A171,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F171" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B171,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="B172" s="45" t="inlineStr">
+        <is>
+          <t>ronald</t>
+        </is>
+      </c>
+      <c r="C172" s="45" t="inlineStr">
+        <is>
+          <t>Homenageou em 2004</t>
+        </is>
+      </c>
+      <c r="D172" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E172" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A172,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F172" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B172,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="B173" s="45" t="inlineStr">
+        <is>
+          <t>orelha</t>
+        </is>
+      </c>
+      <c r="C173" s="45" t="inlineStr">
+        <is>
+          <t>Homenageou</t>
+        </is>
+      </c>
+      <c r="D173" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E173" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A173,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F173" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B173,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="45" t="inlineStr">
+        <is>
+          <t>adriano</t>
+        </is>
+      </c>
+      <c r="B174" s="45" t="inlineStr">
+        <is>
+          <t>orelha</t>
+        </is>
+      </c>
+      <c r="C174" s="45" t="inlineStr">
+        <is>
+          <t>Ligados</t>
+        </is>
+      </c>
+      <c r="D174" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E174" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A174,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F174" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B174,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="B175" s="45" t="inlineStr">
+        <is>
+          <t>pms16</t>
+        </is>
+      </c>
+      <c r="C175" s="45" t="inlineStr">
+        <is>
+          <t>Condecorou</t>
+        </is>
+      </c>
+      <c r="D175" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E175" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A175,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F175" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B175,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="45" t="inlineStr">
+        <is>
+          <t>carlos</t>
+        </is>
+      </c>
+      <c r="B176" s="45" t="inlineStr">
+        <is>
+          <t>pms16</t>
+        </is>
+      </c>
+      <c r="C176" s="45" t="inlineStr">
+        <is>
+          <t>Condecorou</t>
+        </is>
+      </c>
+      <c r="D176" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E176" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A176,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F176" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B176,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="B177" s="45" t="inlineStr">
+        <is>
+          <t>ongbrazao</t>
+        </is>
+      </c>
+      <c r="C177" s="45" t="inlineStr">
+        <is>
+          <t>Emenda para a ONG; PF apura</t>
+        </is>
+      </c>
+      <c r="D177" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E177" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A177,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F177" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B177,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="45" t="inlineStr">
+        <is>
+          <t>peixe</t>
+        </is>
+      </c>
+      <c r="B178" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="C178" s="45" t="inlineStr">
+        <is>
+          <t>Negociou emenda com assessora dele (Estadão)</t>
+        </is>
+      </c>
+      <c r="D178" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E178" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A178,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F178" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B178,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="45" t="inlineStr">
+        <is>
+          <t>peixe</t>
+        </is>
+      </c>
+      <c r="B179" s="45" t="inlineStr">
+        <is>
+          <t>ongbrazao</t>
+        </is>
+      </c>
+      <c r="C179" s="45" t="inlineStr">
+        <is>
+          <t>Ligado ao esquema dos irmãos Brazão</t>
+        </is>
+      </c>
+      <c r="D179" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E179" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A179,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F179" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B179,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="B180" s="45" t="inlineStr">
+        <is>
+          <t>pmacusado</t>
+        </is>
+      </c>
+      <c r="C180" s="45" t="inlineStr">
+        <is>
+          <t>Atuou como advogado dele; recurso no STJ reverteu decisão</t>
+        </is>
+      </c>
+      <c r="D180" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E180" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A180,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F180" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B180,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="45" t="inlineStr">
+        <is>
+          <t>willer</t>
+        </is>
+      </c>
+      <c r="B181" s="45" t="inlineStr">
+        <is>
+          <t>angra</t>
+        </is>
+      </c>
+      <c r="C181" s="45" t="inlineStr">
+        <is>
+          <t>Obteve a posse na Justiça; STJ reconheceu em 2025</t>
+        </is>
+      </c>
+      <c r="D181" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E181" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A181,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F181" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B181,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="45" t="inlineStr">
+        <is>
+          <t>jair</t>
+        </is>
+      </c>
+      <c r="B182" s="45" t="inlineStr">
+        <is>
+          <t>angra</t>
+        </is>
+      </c>
+      <c r="C182" s="45" t="inlineStr">
+        <is>
+          <t>Governo dele liberou em um dia a transferência do imóvel (ICL)</t>
+        </is>
+      </c>
+      <c r="D182" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E182" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A182,Nodes!$A$2:$A$84,0))</f>
+        <v/>
+      </c>
+      <c r="F182" s="45">
+        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B182,Nodes!$A$2:$A$84,0))</f>
         <v/>
       </c>
     </row>
@@ -9180,7 +12248,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="110" customWidth="1" style="24" min="1" max="1"/>
@@ -9256,6 +12324,34 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>21/10/2026: importados 26 nós, 62 conexões e 4 perfis do acervo a verdade. (https://bolsomaster.site, PDF em https://bolsomaster.site/documento-original.pdf). As fontes de cada item são as do acervo e não foram reverificadas uma a uma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Na importação, foi marcado como “Documentado” só o que é ato público ou fato noticiado sem disputa (indicação, doação registrada, homenagem, decisão judicial, contrato público). Suspeitas, mensagens, relatórios da PF sobre condutas e afirmações de ex-sócios ficaram como “Alegado ou contestado”.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Correções do próprio acervo aplicadas: honorários de até R$ 427 mi não são recebimento pessoal de Nunes; o caso do vice Alfredo Gaspar foi arquivado; números do celular de Vorcaro (Piauí × Estadão) não se somam; contratos do ITER são dois levantamentos diferentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Registros do acervo deixados de fora: registro-3 (comparação retórica do PDF; o próprio acervo diz que não comprova a origem do dinheiro); registro-5 (afirmação de exclusividade não verificada pelo acervo); registro-7 (comparação de valores entre casos diferentes); registro-8 (comparação de valores entre casos diferentes); registro-22 (hipótese do PDF sobre o esquema, com fonte em vídeo); registro-27 (já no mapa (Nunes preside o TSE)); registro-41 (pessoa não identificada com clareza); registro-87 (sem pessoa ou conexão específica); registro-88 (só título de reportagem); registro-91 (projeto de lei sem ligação direta com o mapa); registro-93 (post de Nikolas Ferreira sem ligação com o mapa); registro-126 (padrinho não identificado no texto).</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -971,7 +971,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="25">
       <c r="A4" s="28" t="inlineStr">
         <is>
@@ -1080,23 +1079,6 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="25">
       <c r="A28" s="35" t="inlineStr">
         <is>
@@ -1902,7 +1884,7 @@
       </c>
       <c r="K10" s="37" t="inlineStr">
         <is>
-          <t>Wikipedia pt https://pt.wikipedia.org/wiki/Fl%C3%A1vio_Bolsonaro | Tribuna do Sertão (link acima) | O Povo 23/07/2026 https://www.opovo.com.br/noticias/politica/2026/07/23/amp/andre-mendonca-autoriza-inquerito-sobre-repasses-para-dark-horse-filme-sobre-jair-bolsonaro.html | Resultado do 1º turno https://portaldeprefeitura.com.br/bastidores-da-politica/eleicoes-2026-com-100-das-secoes-totalizadas-flavio-tem-4703-e/633498/ | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal | JB 12/10/2026 https://www.jb.com.br/brasil/justica/2026/10/1061206-moraes-autoriza-flavio-bolsonaro-a-visitar-jair-bolsonaro-em-prisao-domiciliar.html | A investigação sobre o financiamento de Dark Horse (bbc.com) https://www.bbc.com/portuguese/articles/c4g5ky0r25jo | A investigação sobre o financiamento de Dark Horse (em.com.br) https://www.em.com.br/politica/2026/09/7498387-flavio-bolsonaro-vira-investigado-do-dark-horse-que-segue-sob-sigilo.html | O acordo de R$ 134 milhões para o filme (intercept.com.br) https://www.intercept.com.br/2026/05/13/audio-flavio-negociou-vorcaro-milhoes/ | A checagem de declarações sobre Vorcaro (aosfatos.org) https://www.aosfatos.org/noticias/flavio-mentiu-ao-menos-43-vezes-sobre-envolvimento-com-vorcaro/ | Os registros de contato no celular do banqueiro (piaui.uol.com.br) https://piaui.uol.com.br/web/mensagens-celular-flavio-vorcaro/ | As menções a encontros presenciais (estadao.com.br) https://www.estadao.com.br/politica/celular-de-vorcaro-tinha-tres-meses-de-conversa-com-flavio-bolsonaro-e-mencao-a-seis-encontros/ | O voo no jato de Vorcaro em janeiro de 2025 (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-viajou-em-jato-de-vorcaro/ | O apartamento de Fabiano Zettel e Willer Tomaz (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-zettel-tomaz-imovel-vila-nova-conceicao-sao-paulo/ | O aniversário em uma mansão gerida por empresa de Vorcaro (iclnoticias.com.br) https://iclnoticias.com.br/flavio-bolsonaro-aniversario-da-filha-em-mansao/ | E-mails sobre vínculo bancário com Willer Tomaz (noticias.uol.com.br) https://noticias.uol.com.br/colunas/fabio-serapiao/2026/10/10/flavio-dividia-conta-com-suspeito-de-lavar-dinheiro-do-inss-indicam-emails.htm | Endereço e contabilidade compartilhados em Brasília (iclnoticias.com.br) https://iclnoticias.com.br/empresas-de-flavio-bolsonaro-e-careca-do-inss/ | Cargo na Câmara, faculdade e estágio no Rio (bbc.com) https://www.bbc.com/portuguese/brasil-46828487 | A acusação de rachadinhas na Alerj (valor.globo.com) https://valor.globo.com/politica/eleicoes-2026/noticia/2026/09/01/flavio-bolsonaro-relembre-o-processo-da-rachadinha.ghtml | A acusação de rachadinhas na Alerj (folhadelondrina.com.br) https://www.folhadelondrina.com.br/ultimas-noticias/entenda-quais-provas-da-rachadinha-contra-flavio-bolsonaro-ainda-valem-3131387e.html | A investigação da loja Kopenhagen (oglobo.globo.com) https://oglobo.globo.com/politica/alvo-de-investigacao-das-rachadinhas-loja-de-flavio-bolsonaro-no-rio-vendida-1-24867874 | Imóveis comprados pela família e investigações (g1.globo.com) https://g1.globo.com/jornal-nacional/noticia/2022/08/31/reportagem-do-uol-revela-que-51-imoveis-comprados-pela-familia-bolsonaro-foram-pagos-em-dinheiro-vivo.ghtml | Imóveis comprados pela família e investigações (noticias.uol.com.br) https://noticias.uol.com.br/politica/ultimas-noticias/2022/08/30/imoveis-cla-bolsonaro-objeto-de-investigacao-suspeita-dinheiro-vivo.htm | Imóveis comprados pela família e investigações (estadao.com.br) https://www.estadao.com.br/politica/investigacao-sobre-flaviobolsonaro-alcanca-37-imoveis/ | A compra e a quitação da mansão em Brasília (oglobo.globo.com) https://oglobo.globo.com/politica/eleicoes-2026/noticia/2026/08/14/video-mansao-que-fez-patrimonio-de-flavio-disparar-fica-em-terreno-de-2400-m-e-foi-quitada-27-anos-antes-do-previsto.ghtml | A análise do MPF sobre 37 transações imobiliárias (cnnbrasil.com.br) https://www.cnnbrasil.com.br/politica/o-mpf-ve-fortes-indicios-de-lavagem-de-dinheiro-em-bens-de-flavio-bolsonaro/a | A acusação do MP-RJ sobre organização criminosa (g1.globo.com) https://g1.globo.com/rj/rio-de-janeiro/noticia/2019/12/19/mp-do-rj-detalha-suposto-esquema-de-corrupcao-envolvendo-entao-deputado-flavio-bolsonaro.ghtml?utm_source=twitter&amp;utm_medium=social&amp;utm_campaign=g1 | Destinação de emendas e entidades questionadas (revistaforum.com.br) https://revistaforum.com.br/politica/flavio-bolsonaro-emendas-ong-fantasma-e-instituto-de-miliciano/</t>
+          <t>Wikipedia pt https://pt.wikipedia.org/wiki/Fl%C3%A1vio_Bolsonaro | Tribuna do Sertão (link acima) | O Povo 23/07/2026 https://www.opovo.com.br/noticias/politica/2026/07/23/amp/andre-mendonca-autoriza-inquerito-sobre-repasses-para-dark-horse-filme-sobre-jair-bolsonaro.html | Resultado do 1º turno https://portaldeprefeitura.com.br/bastidores-da-politica/eleicoes-2026-com-100-das-secoes-totalizadas-flavio-tem-4703-e/633498/ | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal | JB 12/10/2026 https://www.jb.com.br/brasil/justica/2026/10/1061206-moraes-autoriza-flavio-bolsonaro-a-visitar-jair-bolsonaro-em-prisao-domiciliar.html | A investigação sobre o financiamento de Dark Horse (bbc.com) https://www.bbc.com/portuguese/articles/c4g5ky0r25jo | A investigação sobre o financiamento de Dark Horse (em.com.br) https://www.em.com.br/politica/2026/09/7498387-flavio-bolsonaro-vira-investigado-do-dark-horse-que-segue-sob-sigilo.html | O acordo de R$ 134 milhões para o filme (intercept.com.br) https://www.intercept.com.br/2026/05/13/audio-flavio-negociou-vorcaro-milhoes/ | A checagem de declarações sobre Vorcaro (aosfatos.org) https://www.aosfatos.org/noticias/flavio-mentiu-ao-menos-43-vezes-sobre-envolvimento-com-vorcaro/ | Os registros de contato no celular do banqueiro (piaui.uol.com.br) https://piaui.uol.com.br/web/mensagens-celular-flavio-vorcaro/ | As menções a encontros presenciais (estadao.com.br) https://www.estadao.com.br/politica/celular-de-vorcaro-tinha-tres-meses-de-conversa-com-flavio-bolsonaro-e-mencao-a-seis-encontros/ | O voo no jato de Vorcaro em janeiro de 2025 (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-viajou-em-jato-de-vorcaro/ | O apartamento de Fabiano Zettel e Willer Tomaz (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-zettel-tomaz-imovel-vila-nova-conceicao-sao-paulo/ | O aniversário em uma mansão gerida por empresa de Vorcaro (iclnoticias.com.br) https://iclnoticias.com.br/flavio-bolsonaro-aniversario-da-filha-em-mansao/ | E-mails sobre vínculo bancário com Willer Tomaz (noticias.uol.com.br) https://noticias.uol.com.br/colunas/fabio-serapiao/2026/10/10/flavio-dividia-conta-com-suspeito-de-lavar-dinheiro-do-inss-indicam-emails.htm | Endereço e contabilidade compartilhados em Brasília (iclnoticias.com.br) https://iclnoticias.com.br/empresas-de-flavio-bolsonaro-e-careca-do-inss/ | Cargo na Câmara, faculdade e estágio no Rio (bbc.com) https://www.bbc.com/portuguese/brasil-46828487 | A acusação de rachadinhas na Alerj (valor.globo.com) https://valor.globo.com/politica/eleicoes-2026/noticia/2026/09/01/flavio-bolsonaro-relembre-o-processo-da-rachadinha.ghtml | A acusação de rachadinhas na Alerj (folhadelondrina.com.br) https://www.folhadelondrina.com.br/ultimas-noticias/entenda-quais-provas-da-rachadinha-contra-flavio-bolsonaro-ainda-valem-3131387e.html | A investigação da loja Kopenhagen (oglobo.globo.com) https://oglobo.globo.com/politica/alvo-de-investigacao-das-rachadinhas-loja-de-flavio-bolsonaro-no-rio-vendida-1-24867874 | Imóveis comprados pela família e investigações (g1.globo.com) https://g1.globo.com/jornal-nacional/noticia/2022/08/31/reportagem-do-uol-revela-que-51-imoveis-comprados-pela-familia-bolsonaro-foram-pagos-em-dinheiro-vivo.ghtml | Imóveis comprados pela família e investigações (noticias.uol.com.br) https://noticias.uol.com.br/politica/ultimas-noticias/2022/08/30/imoveis-cla-bolsonaro-objeto-de-investigacao-suspeita-dinheiro-vivo.htm | Imóveis comprados pela família e investigações (estadao.com.br) https://www.estadao.com.br/politica/investigacao-sobre-flaviobolsonaro-alcanca-37-imoveis/ | A compra e a quitação da mansão em Brasília (oglobo.globo.com) https://oglobo.globo.com/politica/eleicoes-2026/noticia/2026/08/14/video-mansao-que-fez-patrimonio-de-flavio-disparar-fica-em-terreno-de-2400-m-e-foi-quitada-27-anos-antes-do-previsto.ghtml | A análise do MPF sobre 37 transações imobiliárias (cnnbrasil.com.br) https://www.maisgoias.com.br/politica/procurador-aponta-fortes-indicios-de-lavagem-de-dinheiro-em-bens-de-flavio-bolsonaro/ | A acusação do MP-RJ sobre organização criminosa (g1.globo.com) https://g1.globo.com/rj/rio-de-janeiro/noticia/2019/12/19/mp-do-rj-detalha-suposto-esquema-de-corrupcao-envolvendo-entao-deputado-flavio-bolsonaro.ghtml?utm_source=twitter&amp;utm_medium=social&amp;utm_campaign=g1 | Destinação de emendas e entidades questionadas (revistaforum.com.br) https://revistaforum.com.br/politica/flavio-bolsonaro-emendas-ong-fantasma-e-instituto-de-miliciano/</t>
         </is>
       </c>
       <c r="L10" s="37" t="inlineStr">
@@ -2925,7 +2907,7 @@
       </c>
       <c r="J24" s="37" t="inlineStr">
         <is>
-          <t>Em jun/2026 uma advogada publicou e retirou um vídeo sobre o caso, retratando-se por imprecisões. Acervo a verdade.: o advogado dele na disputa pela casa foi morto em 2024 no Rio. Nada nas fontes liga Flávio ou Willer ao homicídio. O PDF diz que a mansão é gerida por empresa de Vorcaro; o mapa a registra como da WT.</t>
+          <t>Em jun/2026 uma advogada publicou e retirou um vídeo sobre o caso, retratando-se por imprecisões. Acervo a verdade.: o PDF diz que o advogado morto em fev/2024 no Rio era de Richarlison, mas a ICL informa que Rodrigo Crespo representava a WT, do lado de Willer (que nega que ele tenha atuado). Nada nas fontes liga Flávio ou Willer ao homicídio. O PDF diz que a mansão é gerida por empresa de Vorcaro; o mapa a registra como da WT.</t>
         </is>
       </c>
       <c r="K24" s="37" t="inlineStr">
@@ -3761,7 +3743,7 @@
       </c>
       <c r="J35" s="37" t="inlineStr">
         <is>
-          <t>O PDF original diz que ele “é investigado”; isso está desatualizado desde o arquivamento (Folha e UOL, 06/10/2026).</t>
+          <t>A PGR também pediu o arquivamento; ele diz que a acusação é falsa e move ações contra quem a levou adiante. O PDF original diz que ele “é investigado”; isso está desatualizado desde o arquivamento (Folha e UOL, 06/10/2026).</t>
         </is>
       </c>
       <c r="K35" s="37" t="inlineStr">
@@ -5967,7 +5949,7 @@
       </c>
       <c r="E62" s="45" t="inlineStr">
         <is>
-          <t>Deputado; presente na reunião Mendonça–Vorcaro (fev/2025); alvo de operação autorizada por Dino</t>
+          <t>Deputado federal; ajudou a articular a reunião Mendonça–Vorcaro de mar/2025; alvo de operação autorizada por Dino</t>
         </is>
       </c>
       <c r="F62" s="45">
@@ -6282,7 +6264,7 @@
       </c>
       <c r="E71" s="45" t="inlineStr">
         <is>
-          <t>Voo internacional de R$ 1 mi pago por empresa da qual Vorcaro era sócio</t>
+          <t>Ex-coach; voo de R$ 1,17 mi pago pela Prime You, de que Vorcaro era sócio; confirmou o uso</t>
         </is>
       </c>
       <c r="F71" s="45">
@@ -6387,7 +6369,7 @@
       </c>
       <c r="E74" s="45" t="inlineStr">
         <is>
-          <t>Avaliada em R$ 6 mi; terreno de 2.400 m²; quitada 27 anos antes do previsto</t>
+          <t>R$ 6 mi, 2.400 m², Setor de Mansões Dom Bosco; R$ 3,1 mi financiados pelo BRB</t>
         </is>
       </c>
       <c r="F74" s="45">
@@ -6597,7 +6579,7 @@
       </c>
       <c r="E80" s="45" t="inlineStr">
         <is>
-          <t>Condenado no caso Marielle; negociou emenda com assessora de Flávio</t>
+          <t>Robson Calixto, PM da reserva condenado no caso Marielle; PF diz que intermediou emenda de Flávio</t>
         </is>
       </c>
       <c r="F80" s="45">
@@ -6632,7 +6614,7 @@
       </c>
       <c r="E81" s="45" t="inlineStr">
         <is>
-          <t>Recebeu emenda de Flávio; PF apura desvios</t>
+          <t>Instituto Ifop (Taquara, RJ); PF suspeita de ligação com os Brazão; a ONG nega</t>
         </is>
       </c>
       <c r="F81" s="45">
@@ -6702,7 +6684,7 @@
       </c>
       <c r="E83" s="45" t="inlineStr">
         <is>
-          <t>Pastor de Flávio; defendeu em livro retirar o título de padroeira de N. Sra. Aparecida</t>
+          <t>Bispo da Comunidade das Nações; defendeu em livro retirar o título de padroeira de N. Sra. Aparecida</t>
         </is>
       </c>
       <c r="F83" s="45">
@@ -10477,7 +10459,7 @@
       </c>
       <c r="C124" s="45" t="inlineStr">
         <is>
-          <t>Empréstimo para a mansão com juros abaixo do mercado; PF investiga</t>
+          <t>Empréstimo de R$ 3,1 mi a 3,71% a.a., abaixo da média do banco; PF investiga. Ele diz que a Justiça já atestou a regularidade e que o empréstimo está quitado</t>
         </is>
       </c>
       <c r="D124" s="45" t="inlineStr">
@@ -10537,7 +10519,7 @@
       </c>
       <c r="C126" s="45" t="inlineStr">
         <is>
-          <t>Comprou; ele diz pagar com renda de advogado</t>
+          <t>Comprou em 2021 por R$ 6 mi</t>
         </is>
       </c>
       <c r="D126" s="45" t="inlineStr">
@@ -10567,7 +10549,7 @@
       </c>
       <c r="C127" s="45" t="inlineStr">
         <is>
-          <t>Maior doador da campanha de 2022 (R$ 3 mi)</t>
+          <t>Doou R$ 3 mi à campanha de 2022, 2º maior doador depois do PL (CNN/TSE)</t>
         </is>
       </c>
       <c r="D127" s="45" t="inlineStr">
@@ -10597,7 +10579,7 @@
       </c>
       <c r="C128" s="45" t="inlineStr">
         <is>
-          <t>Doou R$ 2 mi à campanha de 2022</t>
+          <t>Doou R$ 2 mi à campanha de 2022, a maior doação de pessoa física (CNN/TSE)</t>
         </is>
       </c>
       <c r="D128" s="45" t="inlineStr">
@@ -10807,7 +10789,7 @@
       </c>
       <c r="C135" s="45" t="inlineStr">
         <is>
-          <t>Reuniões em 19/02 e 14/03/2025 fora da agenda oficial</t>
+          <t>Reunião reservada de 2 h em 14/03/2025, fora da agenda, no ITER (mensagens); não há prova de que tenha agido pelo Master</t>
         </is>
       </c>
       <c r="D135" s="45" t="inlineStr">
@@ -10897,7 +10879,7 @@
       </c>
       <c r="C138" s="45" t="inlineStr">
         <is>
-          <t>Na reunião de fev/2025; teria aproximado ministro e banqueiro</t>
+          <t>Ajudou a articular a reunião com Vorcaro de mar/2025 (mensagens)</t>
         </is>
       </c>
       <c r="D138" s="45" t="inlineStr">
@@ -11047,7 +11029,7 @@
       </c>
       <c r="C143" s="45" t="inlineStr">
         <is>
-          <t>Afastou o diretor-geral sem ouvir a PGR (set/2026); AGU vê usurpação de competência</t>
+          <t>Afastou o diretor-geral sem ouvir a PGR (08/09/2026), alegando monitoramento ilegal; AGU vê usurpação de competência</t>
         </is>
       </c>
       <c r="D143" s="45" t="inlineStr">
@@ -11347,7 +11329,7 @@
       </c>
       <c r="C153" s="45" t="inlineStr">
         <is>
-          <t>PF: mesada de R$ 300 mil a 500 mil e viagens pagas, incluindo Courchevel</t>
+          <t>PF: pagamentos mensais de R$ 300 mil a 500 mil e viagens pagas, incluindo Courchevel (~R$ 2 mi); ele nega ilicitude</t>
         </is>
       </c>
       <c r="D153" s="45" t="inlineStr">
@@ -11467,7 +11449,7 @@
       </c>
       <c r="C157" s="45" t="inlineStr">
         <is>
-          <t>PF: articulador dele em Brasília; empresa ligada ao banqueiro pagou R$ 67,5 mi por projeto de Faria</t>
+          <t>PF: articulador dele em Brasília; Vorcaro pagou R$ 67,5 mi por projeto eólico de Faria, que defende o valor</t>
         </is>
       </c>
       <c r="D157" s="45" t="inlineStr">
@@ -11637,7 +11619,7 @@
     <row r="163">
       <c r="A163" s="45" t="inlineStr">
         <is>
-          <t>vorcaro</t>
+          <t>primeu</t>
         </is>
       </c>
       <c r="B163" s="45" t="inlineStr">
@@ -11647,12 +11629,12 @@
       </c>
       <c r="C163" s="45" t="inlineStr">
         <is>
-          <t>Empresa da qual Vorcaro era sócio pagou voo de R$ 1 mi</t>
+          <t>Pagou voo SP–EUA de R$ 1,17 mi (2025); Marçal confirmou o uso (Valor)</t>
         </is>
       </c>
       <c r="D163" s="45" t="inlineStr">
         <is>
-          <t>Alegado ou contestado</t>
+          <t>Documentado</t>
         </is>
       </c>
       <c r="E163" s="45">
@@ -11737,7 +11719,7 @@
       </c>
       <c r="C166" s="45" t="inlineStr">
         <is>
-          <t>Flávio foi batizado na igreja dele (Folha)</t>
+          <t>Flávio foi batizado na Comunidade das Nações, igreja dele, em jan/2024 (Folha)</t>
         </is>
       </c>
       <c r="D166" s="45" t="inlineStr">
@@ -11797,7 +11779,7 @@
       </c>
       <c r="C168" s="45" t="inlineStr">
         <is>
-          <t>Ex-sócio na Kopenhagen cita lobby dele com Nunes (Brasil de Fato)</t>
+          <t>Ex-sócio cita lobby dele com Nunes em favor de cliente; sem comprovação independente (PlatôBR)</t>
         </is>
       </c>
       <c r="D168" s="45" t="inlineStr">
@@ -12067,7 +12049,7 @@
       </c>
       <c r="C177" s="45" t="inlineStr">
         <is>
-          <t>Emenda para a ONG; PF apura</t>
+          <t>Emenda de R$ 199 mil (nov/2023); PF apura. Ele diz que não cabe ao parlamentar auditar o uso</t>
         </is>
       </c>
       <c r="D177" s="45" t="inlineStr">
@@ -12097,7 +12079,7 @@
       </c>
       <c r="C178" s="45" t="inlineStr">
         <is>
-          <t>Negociou emenda com assessora dele (Estadão)</t>
+          <t>PF: intermediou a emenda com o gabinete dele (O Globo, Estadão)</t>
         </is>
       </c>
       <c r="D178" s="45" t="inlineStr">
@@ -12157,7 +12139,7 @@
       </c>
       <c r="C180" s="45" t="inlineStr">
         <is>
-          <t>Atuou como advogado dele; recurso no STJ reverteu decisão</t>
+          <t>Advogado dele no STJ (2024); recurso reverteu a ida a júri popular (coluna no iG)</t>
         </is>
       </c>
       <c r="D180" s="45" t="inlineStr">
@@ -12187,7 +12169,7 @@
       </c>
       <c r="C181" s="45" t="inlineStr">
         <is>
-          <t>Obteve a posse na Justiça; STJ reconheceu em 2025</t>
+          <t>Obteve a posse na Justiça na disputa com Richarlison</t>
         </is>
       </c>
       <c r="D181" s="45" t="inlineStr">
@@ -12248,7 +12230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="110" customWidth="1" style="24" min="1" max="1"/>
@@ -12325,30 +12307,37 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="24" t="inlineStr">
         <is>
           <t>21/10/2026: importados 26 nós, 62 conexões e 4 perfis do acervo a verdade. (https://bolsomaster.site, PDF em https://bolsomaster.site/documento-original.pdf). As fontes de cada item são as do acervo e não foram reverificadas uma a uma.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Na importação, foi marcado como “Documentado” só o que é ato público ou fato noticiado sem disputa (indicação, doação registrada, homenagem, decisão judicial, contrato público). Suspeitas, mensagens, relatórios da PF sobre condutas e afirmações de ex-sócios ficaram como “Alegado ou contestado”.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="24" t="inlineStr">
         <is>
           <t>Correções do próprio acervo aplicadas: honorários de até R$ 427 mi não são recebimento pessoal de Nunes; o caso do vice Alfredo Gaspar foi arquivado; números do celular de Vorcaro (Piauí × Estadão) não se somam; contratos do ITER são dois levantamentos diferentes.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="24" t="inlineStr">
         <is>
           <t>Registros do acervo deixados de fora: registro-3 (comparação retórica do PDF; o próprio acervo diz que não comprova a origem do dinheiro); registro-5 (afirmação de exclusividade não verificada pelo acervo); registro-7 (comparação de valores entre casos diferentes); registro-8 (comparação de valores entre casos diferentes); registro-22 (hipótese do PDF sobre o esquema, com fonte em vídeo); registro-27 (já no mapa (Nunes preside o TSE)); registro-41 (pessoa não identificada com clareza); registro-87 (sem pessoa ou conexão específica); registro-88 (só título de reportagem); registro-91 (projeto de lei sem ligação direta com o mapa); registro-93 (post de Nikolas Ferreira sem ligação com o mapa); registro-126 (padrinho não identificado no texto).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Checagem final (21/10/2026): 111 links testados (91 abrem; 19 bloqueiam robôs, como UOL, Intercept e Folha; 1 link da CNN quebrado foi trocado por Mais Goiás). Conferidas contra a fonte 22 matérias das conexões mais sensíveis. Corrigidos: Zettel foi o 2º doador de Jair, não o maior; o advogado morto em 2024 representava a WT, não Richarlison; a posse de Willer reconhecida pelo STJ não foi confirmada; Mendonça teve uma reunião reservada confirmada (14/03/2025), não duas; o voo de Marçal foi pago pela Prime You (R$ 1,17 mi). Respostas dos citados foram adicionadas (Flávio sobre o BRB e a emenda, Ciro, Faria, Marçal, Gaspar).</t>
         </is>
       </c>
     </row>

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Perfis'!$A$1:$P$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Perfis'!$A$1:$P$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Nodes'!$A$1:$F$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Edges'!$A$1:$F$120</definedName>
   </definedNames>
@@ -971,6 +971,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="25">
       <c r="A4" s="28" t="inlineStr">
         <is>
@@ -995,7 +996,7 @@
         </is>
       </c>
       <c r="B5" s="24">
-        <f>COUNTIF(Perfis!$H$2:$H$35,A5)</f>
+        <f>COUNTIF(Perfis!$H$2:$H$36,A5)</f>
         <v/>
       </c>
       <c r="C5" s="30" t="inlineStr">
@@ -1011,7 +1012,7 @@
         </is>
       </c>
       <c r="B6" s="24">
-        <f>COUNTIF(Perfis!$H$2:$H$35,A6)</f>
+        <f>COUNTIF(Perfis!$H$2:$H$36,A6)</f>
         <v/>
       </c>
       <c r="C6" s="30" t="inlineStr">
@@ -1027,12 +1028,12 @@
         </is>
       </c>
       <c r="B7" s="24">
-        <f>COUNTIF(Perfis!$H$2:$H$35,A7)</f>
+        <f>COUNTIF(Perfis!$H$2:$H$36,A7)</f>
         <v/>
       </c>
       <c r="C7" s="30" t="inlineStr">
         <is>
-          <t>Fábio Luís Lula da Silva; Roberta Moreira Luchsinger; Willer Tomaz; Flávio Bolsonaro; Carlos Bolsonaro; Frederick Wassef; Ciro Nogueira; Mario Frias</t>
+          <t>Fábio Luís Lula da Silva; Roberta Moreira Luchsinger; Willer Tomaz; Flávio Bolsonaro; Carlos Bolsonaro; Frederick Wassef; Ciro Nogueira; Mario Frias; Weverton Rocha</t>
         </is>
       </c>
     </row>
@@ -1043,7 +1044,7 @@
         </is>
       </c>
       <c r="B8" s="24">
-        <f>COUNTIF(Perfis!$H$2:$H$35,A8)</f>
+        <f>COUNTIF(Perfis!$H$2:$H$36,A8)</f>
         <v/>
       </c>
       <c r="C8" s="30" t="inlineStr">
@@ -1059,7 +1060,7 @@
         </is>
       </c>
       <c r="B9" s="24">
-        <f>COUNTIF(Perfis!$H$2:$H$35,A9)</f>
+        <f>COUNTIF(Perfis!$H$2:$H$36,A9)</f>
         <v/>
       </c>
       <c r="C9" s="30" t="inlineStr">
@@ -1079,6 +1080,23 @@
         <v/>
       </c>
     </row>
+    <row r="11"/>
+    <row r="12"/>
+    <row r="13"/>
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22"/>
+    <row r="23"/>
+    <row r="24"/>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="25">
       <c r="A28" s="35" t="inlineStr">
         <is>
@@ -1150,7 +1168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="24" min="1" max="1"/>
@@ -1618,7 +1636,7 @@
       </c>
       <c r="D7" s="37" t="inlineStr">
         <is>
-          <t>Advogado em Brasília. Preso em 2017 sob suspeita de tentar interferir na Operação Greenfield (fundos de pensão). Alvo de busca em ago/2026 na Operação Sem Desconto (caso ligado ao senador Weverton Rocha). O inquérito sobre ele e Flávio (suposta lavagem via bets, Rede Loto) chegou ao STF em 08/10/2026 (relator Moraes) e foi revelado em 18–19/10. A PF diz que uma conta dele movimentou ~R$ 130 mi entre mar e mai/2025. Dono de empresas como WT, Alcazar e Cathedral.</t>
+          <t>Advogado em Brasília. Preso em 2017 sob suspeita de tentar interferir na Operação Greenfield (fundos de pensão). Alvo de busca em ago/2026 na Operação Sem Desconto (caso ligado ao senador Weverton Rocha). O inquérito sobre ele e Flávio (suposta lavagem via bets, Rede Loto) chegou ao STF em 08/10/2026 (relator Moraes) e foi revelado em 18–19/10. A PF diz que uma conta dele movimentou ~R$ 130 mi entre mar e mai/2025. Dono de empresas como WT, Alcazar e Cathedral. Segundo a piauí (20/10/2026), criou em jan/2023 a offshore Cathedral, única acionista da Rede Loto (Best Bet), licenciada pela Loterj. Um e-mail achado pela PF mostra que ele se apresentou como sócio da Rio Pag, que processava pagamentos da Loterj; depois admitiu participação indireta. A PF achou sala oculta, sem dinheiro, em hangares de empresas dele no Aeroporto de Brasília. Na Operação Sem Desconto, a PF o descreve como “hub financeiro” do senador Weverton Rocha. Confirmou ao Metrópoles que viajou ao exterior com a família.</t>
         </is>
       </c>
       <c r="E7" s="37" t="inlineStr">
@@ -1633,7 +1651,7 @@
       </c>
       <c r="G7" s="37" t="inlineStr">
         <is>
-          <t>Investigado; nega irregularidades e fala em "pescaria probatória". Nas fontes não há denúncia nem condenação.</t>
+          <t>Investigado; nega irregularidades e fala em "pescaria probatória". Nas fontes não há denúncia nem condenação. Diz que não há sócios ocultos nem contas não declaradas, que a sala do hangar serve a empresas de transporte de valores e que não tem restrição judicial para viajar.</t>
         </is>
       </c>
       <c r="H7" s="41" t="inlineStr">
@@ -1648,22 +1666,22 @@
       </c>
       <c r="J7" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Data da saída do país não confirmada: o UOL News citou registros da PF de 21/08/2026 (chegada aos EUA em 22/08), mas a Fórum/Metrópoles (19/10) fala em viagem na semana anterior. A defesa diz que a Rede Loto nunca chegou a operar.</t>
         </is>
       </c>
       <c r="K7" s="37" t="inlineStr">
         <is>
-          <t>A Tarde https://atarde.com.br/eleicoes/quem-e-willer-tomaz-advogado-suspeito-de-ligacao-com-flavio-bolsonaro-1406358 | Tribuna do Sertão 19/10/2026 https://www.tribunadosertao.com.br/poder-e-governo/2026/10/19/1000284-flavio-bolsonaro-e-investigado-pela-pf-por-suspeita-de-lavagem-de-dinheiro-com-advogado-willer-tomaz | CartaCapital 18/10/2026 https://www.cartacapital.com.br/politica/flavio-bolsonaro-e-alvo-de-segundo-inquerito-no-stf-por-suspeita-de-lavagem-de-dinheiro/ | CNN Brasil https://www.cnnbrasil.com.br/politica/advogado-amigo-de-flavio-movimentou-r-130-milhoes-em-tres-meses-diz-pf/ | O voo no jato de Vorcaro em janeiro de 2025 (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-viajou-em-jato-de-vorcaro/ | E-mails sobre vínculo bancário com Willer Tomaz (noticias.uol.com.br) https://noticias.uol.com.br/colunas/fabio-serapiao/2026/10/10/flavio-dividia-conta-com-suspeito-de-lavar-dinheiro-do-inss-indicam-emails.htm | A disputa pelo imóvel comprado por Richarlison (iclnoticias.com.br) https://iclnoticias.com.br/advogado-defendia-amigo-de-flavio-bolsonaro/ | A disputa pelo imóvel comprado por Richarlison (iclnoticias.com.br) https://iclnoticias.com.br/pf-e-acionada-flavio-bolsonaro-richarlisson/</t>
+          <t>A Tarde https://atarde.com.br/eleicoes/quem-e-willer-tomaz-advogado-suspeito-de-ligacao-com-flavio-bolsonaro-1406358 | Tribuna do Sertão 19/10/2026 https://www.tribunadosertao.com.br/poder-e-governo/2026/10/19/1000284-flavio-bolsonaro-e-investigado-pela-pf-por-suspeita-de-lavagem-de-dinheiro-com-advogado-willer-tomaz | CartaCapital 18/10/2026 https://www.cartacapital.com.br/politica/flavio-bolsonaro-e-alvo-de-segundo-inquerito-no-stf-por-suspeita-de-lavagem-de-dinheiro/ | CNN Brasil https://www.cnnbrasil.com.br/politica/advogado-amigo-de-flavio-movimentou-r-130-milhoes-em-tres-meses-diz-pf/ | O voo no jato de Vorcaro em janeiro de 2025 (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-viajou-em-jato-de-vorcaro/ | E-mails sobre vínculo bancário com Willer Tomaz (noticias.uol.com.br) https://noticias.uol.com.br/colunas/fabio-serapiao/2026/10/10/flavio-dividia-conta-com-suspeito-de-lavar-dinheiro-do-inss-indicam-emails.htm | A disputa pelo imóvel comprado por Richarlison (iclnoticias.com.br) https://iclnoticias.com.br/advogado-defendia-amigo-de-flavio-bolsonaro/ | A disputa pelo imóvel comprado por Richarlison (iclnoticias.com.br) https://iclnoticias.com.br/pf-e-acionada-flavio-bolsonaro-richarlisson/ | Portal Porque (resume piauí, 20/10/2026) https://www.portalporque.com.br/brasil/revista-piaui-aponta-que-flavio-bolsonaro-foi-socio-indireto-de-bet/ | Correio da Manhã (via O Globo, Malu Gaspar) https://www.correiodamanha.com.br/politica/2026/10/328716-aliado-de-flavio-bolsonaro-admitiu-ser-socio-de-empresa-da-loterj-apos-negar-ligacao-revela-e-mail.html | Goiás 246 (via Estadão) https://www.goias246.com.br/noticia/34906/politica/pf-aponta-sala-estruturada-para-guardar-valores-em-hangar-de-empresas-do-advogado-willer-tomaz.html | Poder360 04/08/2026 https://www.poder360.com.br/poder-justica/pf-investiga-advogado-amigo-de-flavio-em-operacao-sobre-o-inss/ | Revista Fórum (via Metrópoles, 19/10/2026) https://revistaforum.com.br/politica/willer-tomaz-flavio-bolsonaro-viaja-preocupa-pf/</t>
         </is>
       </c>
       <c r="L7" s="37" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="M7" s="37" t="inlineStr">
         <is>
-          <t>Data de entrada no STF (08/10/2026), valores e confirmação da busca de ago/2026. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
+          <t>Data de entrada no STF (08/10/2026), valores e confirmação da busca de ago/2026. 21/10/2026: importado do acervo a verdade. (bolsomaster.site). 22/10/2026: rodada UOL News (bets, Loterj, hangar, Weverton).</t>
         </is>
       </c>
       <c r="N7" s="24" t="inlineStr">
@@ -1849,7 +1867,7 @@
       </c>
       <c r="D10" s="37" t="inlineStr">
         <is>
-          <t>Nascido em 30/04/1981, Resende (RJ). Advogado e empresário; deputado estadual desde 2003, senador pelo RJ desde 2019. Candidato do PL à Presidência: no 1º turno (04/10/2026) teve 47,03% dos votos válidos contra 45,16% de Lula; o 2º turno é em 25/10/2026. Rachadinha: denunciado pelo MPRJ em out/2020 com Queiroz e outros 15; provas anuladas pelo STJ/STF em nov/2021; denúncia rejeitada e caso arquivado em 2022. Hoje há dois inquéritos no STF: (1) Dark Horse, autorizado por Mendonça em 23/07/2026 (~US$ 24 mi negociados; Coaf/piauí apontam ~US$ 12,3 mi repassados por Vorcaro ao fundo Havengate); em 10/09 a PF fez a Operação Make Up (49 mandados; alvos incluem a produtora Karina Gama e o deputado Mário Frias). (2) lavagem com Willer Tomaz, chegou ao STF em 08/10/2026 (relator Moraes). Em 12/10 Moraes liberou as visitas dele ao pai, suspensas desde julho por ele ter publicado uma carta de Jair.</t>
+          <t>Nascido em 30/04/1981, Resende (RJ). Advogado e empresário; deputado estadual desde 2003, senador pelo RJ desde 2019. Candidato do PL à Presidência: no 1º turno (04/10/2026) teve 47,03% dos votos válidos contra 45,16% de Lula; o 2º turno é em 25/10/2026. Rachadinha: denunciado pelo MPRJ em out/2020 com Queiroz e outros 15; provas anuladas pelo STJ/STF em nov/2021; denúncia rejeitada e caso arquivado em 2022. Hoje há dois inquéritos no STF: (1) Dark Horse, autorizado por Mendonça em 23/07/2026 (~US$ 24 mi negociados; Coaf/piauí apontam ~US$ 12,3 mi repassados por Vorcaro ao fundo Havengate); em 10/09 a PF fez a Operação Make Up (49 mandados; alvos incluem a produtora Karina Gama e o deputado Mário Frias). (2) lavagem com Willer Tomaz, chegou ao STF em 08/10/2026 (relator Moraes). Em 12/10 Moraes liberou as visitas dele ao pai, suspensas desde julho por ele ter publicado uma carta de Jair. Out/2026: a piauí aponta, com documentos da PF, que ele pode ter sido sócio oculto da Best Bet, de Willer, por ter sido “usuário master” da conta da offshore Alcazar (excluído por e-mail de 22/05/2025). A Folha revelou voos dele na Europa em 2025 com canhotos em nome da Cathedral, dona da bet.</t>
         </is>
       </c>
       <c r="E10" s="37" t="inlineStr">
@@ -1864,7 +1882,7 @@
       </c>
       <c r="G10" s="37" t="inlineStr">
         <is>
-          <t>Nega: chama o 2º inquérito de politicamente motivado e a relação com Willer de amizade entre famílias; diz que o filme foi patrocínio. Sem denúncia nova nem condenação.</t>
+          <t>Nega: chama o 2º inquérito de politicamente motivado e a relação com Willer de amizade entre famílias; diz que o filme foi patrocínio. Sem denúncia nova nem condenação. Sobre a bet e os voos: diz que nunca teve acesso a contas de empresas de Willer e que a relação é “exclusivamente de amizade”; chama a associação de “mera ilação”.</t>
         </is>
       </c>
       <c r="H10" s="41" t="inlineStr">
@@ -1884,17 +1902,17 @@
       </c>
       <c r="K10" s="37" t="inlineStr">
         <is>
-          <t>Wikipedia pt https://pt.wikipedia.org/wiki/Fl%C3%A1vio_Bolsonaro | Tribuna do Sertão (link acima) | O Povo 23/07/2026 https://www.opovo.com.br/noticias/politica/2026/07/23/amp/andre-mendonca-autoriza-inquerito-sobre-repasses-para-dark-horse-filme-sobre-jair-bolsonaro.html | Resultado do 1º turno https://portaldeprefeitura.com.br/bastidores-da-politica/eleicoes-2026-com-100-das-secoes-totalizadas-flavio-tem-4703-e/633498/ | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal | JB 12/10/2026 https://www.jb.com.br/brasil/justica/2026/10/1061206-moraes-autoriza-flavio-bolsonaro-a-visitar-jair-bolsonaro-em-prisao-domiciliar.html | A investigação sobre o financiamento de Dark Horse (bbc.com) https://www.bbc.com/portuguese/articles/c4g5ky0r25jo | A investigação sobre o financiamento de Dark Horse (em.com.br) https://www.em.com.br/politica/2026/09/7498387-flavio-bolsonaro-vira-investigado-do-dark-horse-que-segue-sob-sigilo.html | O acordo de R$ 134 milhões para o filme (intercept.com.br) https://www.intercept.com.br/2026/05/13/audio-flavio-negociou-vorcaro-milhoes/ | A checagem de declarações sobre Vorcaro (aosfatos.org) https://www.aosfatos.org/noticias/flavio-mentiu-ao-menos-43-vezes-sobre-envolvimento-com-vorcaro/ | Os registros de contato no celular do banqueiro (piaui.uol.com.br) https://piaui.uol.com.br/web/mensagens-celular-flavio-vorcaro/ | As menções a encontros presenciais (estadao.com.br) https://www.estadao.com.br/politica/celular-de-vorcaro-tinha-tres-meses-de-conversa-com-flavio-bolsonaro-e-mencao-a-seis-encontros/ | O voo no jato de Vorcaro em janeiro de 2025 (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-viajou-em-jato-de-vorcaro/ | O apartamento de Fabiano Zettel e Willer Tomaz (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-zettel-tomaz-imovel-vila-nova-conceicao-sao-paulo/ | O aniversário em uma mansão gerida por empresa de Vorcaro (iclnoticias.com.br) https://iclnoticias.com.br/flavio-bolsonaro-aniversario-da-filha-em-mansao/ | E-mails sobre vínculo bancário com Willer Tomaz (noticias.uol.com.br) https://noticias.uol.com.br/colunas/fabio-serapiao/2026/10/10/flavio-dividia-conta-com-suspeito-de-lavar-dinheiro-do-inss-indicam-emails.htm | Endereço e contabilidade compartilhados em Brasília (iclnoticias.com.br) https://iclnoticias.com.br/empresas-de-flavio-bolsonaro-e-careca-do-inss/ | Cargo na Câmara, faculdade e estágio no Rio (bbc.com) https://www.bbc.com/portuguese/brasil-46828487 | A acusação de rachadinhas na Alerj (valor.globo.com) https://valor.globo.com/politica/eleicoes-2026/noticia/2026/09/01/flavio-bolsonaro-relembre-o-processo-da-rachadinha.ghtml | A acusação de rachadinhas na Alerj (folhadelondrina.com.br) https://www.folhadelondrina.com.br/ultimas-noticias/entenda-quais-provas-da-rachadinha-contra-flavio-bolsonaro-ainda-valem-3131387e.html | A investigação da loja Kopenhagen (oglobo.globo.com) https://oglobo.globo.com/politica/alvo-de-investigacao-das-rachadinhas-loja-de-flavio-bolsonaro-no-rio-vendida-1-24867874 | Imóveis comprados pela família e investigações (g1.globo.com) https://g1.globo.com/jornal-nacional/noticia/2022/08/31/reportagem-do-uol-revela-que-51-imoveis-comprados-pela-familia-bolsonaro-foram-pagos-em-dinheiro-vivo.ghtml | Imóveis comprados pela família e investigações (noticias.uol.com.br) https://noticias.uol.com.br/politica/ultimas-noticias/2022/08/30/imoveis-cla-bolsonaro-objeto-de-investigacao-suspeita-dinheiro-vivo.htm | Imóveis comprados pela família e investigações (estadao.com.br) https://www.estadao.com.br/politica/investigacao-sobre-flaviobolsonaro-alcanca-37-imoveis/ | A compra e a quitação da mansão em Brasília (oglobo.globo.com) https://oglobo.globo.com/politica/eleicoes-2026/noticia/2026/08/14/video-mansao-que-fez-patrimonio-de-flavio-disparar-fica-em-terreno-de-2400-m-e-foi-quitada-27-anos-antes-do-previsto.ghtml | A análise do MPF sobre 37 transações imobiliárias (cnnbrasil.com.br) https://www.maisgoias.com.br/politica/procurador-aponta-fortes-indicios-de-lavagem-de-dinheiro-em-bens-de-flavio-bolsonaro/ | A acusação do MP-RJ sobre organização criminosa (g1.globo.com) https://g1.globo.com/rj/rio-de-janeiro/noticia/2019/12/19/mp-do-rj-detalha-suposto-esquema-de-corrupcao-envolvendo-entao-deputado-flavio-bolsonaro.ghtml?utm_source=twitter&amp;utm_medium=social&amp;utm_campaign=g1 | Destinação de emendas e entidades questionadas (revistaforum.com.br) https://revistaforum.com.br/politica/flavio-bolsonaro-emendas-ong-fantasma-e-instituto-de-miliciano/</t>
+          <t>Wikipedia pt https://pt.wikipedia.org/wiki/Fl%C3%A1vio_Bolsonaro | Tribuna do Sertão (link acima) | O Povo 23/07/2026 https://www.opovo.com.br/noticias/politica/2026/07/23/amp/andre-mendonca-autoriza-inquerito-sobre-repasses-para-dark-horse-filme-sobre-jair-bolsonaro.html | Resultado do 1º turno https://portaldeprefeitura.com.br/bastidores-da-politica/eleicoes-2026-com-100-das-secoes-totalizadas-flavio-tem-4703-e/633498/ | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal | JB 12/10/2026 https://www.jb.com.br/brasil/justica/2026/10/1061206-moraes-autoriza-flavio-bolsonaro-a-visitar-jair-bolsonaro-em-prisao-domiciliar.html | A investigação sobre o financiamento de Dark Horse (bbc.com) https://www.bbc.com/portuguese/articles/c4g5ky0r25jo | A investigação sobre o financiamento de Dark Horse (em.com.br) https://www.em.com.br/politica/2026/09/7498387-flavio-bolsonaro-vira-investigado-do-dark-horse-que-segue-sob-sigilo.html | O acordo de R$ 134 milhões para o filme (intercept.com.br) https://www.intercept.com.br/2026/05/13/audio-flavio-negociou-vorcaro-milhoes/ | A checagem de declarações sobre Vorcaro (aosfatos.org) https://www.aosfatos.org/noticias/flavio-mentiu-ao-menos-43-vezes-sobre-envolvimento-com-vorcaro/ | Os registros de contato no celular do banqueiro (piaui.uol.com.br) https://piaui.uol.com.br/web/mensagens-celular-flavio-vorcaro/ | As menções a encontros presenciais (estadao.com.br) https://www.estadao.com.br/politica/celular-de-vorcaro-tinha-tres-meses-de-conversa-com-flavio-bolsonaro-e-mencao-a-seis-encontros/ | O voo no jato de Vorcaro em janeiro de 2025 (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-viajou-em-jato-de-vorcaro/ | O apartamento de Fabiano Zettel e Willer Tomaz (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-zettel-tomaz-imovel-vila-nova-conceicao-sao-paulo/ | O aniversário em uma mansão gerida por empresa de Vorcaro (iclnoticias.com.br) https://iclnoticias.com.br/flavio-bolsonaro-aniversario-da-filha-em-mansao/ | E-mails sobre vínculo bancário com Willer Tomaz (noticias.uol.com.br) https://noticias.uol.com.br/colunas/fabio-serapiao/2026/10/10/flavio-dividia-conta-com-suspeito-de-lavar-dinheiro-do-inss-indicam-emails.htm | Endereço e contabilidade compartilhados em Brasília (iclnoticias.com.br) https://iclnoticias.com.br/empresas-de-flavio-bolsonaro-e-careca-do-inss/ | Cargo na Câmara, faculdade e estágio no Rio (bbc.com) https://www.bbc.com/portuguese/brasil-46828487 | A acusação de rachadinhas na Alerj (valor.globo.com) https://valor.globo.com/politica/eleicoes-2026/noticia/2026/09/01/flavio-bolsonaro-relembre-o-processo-da-rachadinha.ghtml | A acusação de rachadinhas na Alerj (folhadelondrina.com.br) https://www.folhadelondrina.com.br/ultimas-noticias/entenda-quais-provas-da-rachadinha-contra-flavio-bolsonaro-ainda-valem-3131387e.html | A investigação da loja Kopenhagen (oglobo.globo.com) https://oglobo.globo.com/politica/alvo-de-investigacao-das-rachadinhas-loja-de-flavio-bolsonaro-no-rio-vendida-1-24867874 | Imóveis comprados pela família e investigações (g1.globo.com) https://g1.globo.com/jornal-nacional/noticia/2022/08/31/reportagem-do-uol-revela-que-51-imoveis-comprados-pela-familia-bolsonaro-foram-pagos-em-dinheiro-vivo.ghtml | Imóveis comprados pela família e investigações (noticias.uol.com.br) https://noticias.uol.com.br/politica/ultimas-noticias/2022/08/30/imoveis-cla-bolsonaro-objeto-de-investigacao-suspeita-dinheiro-vivo.htm | Imóveis comprados pela família e investigações (estadao.com.br) https://www.estadao.com.br/politica/investigacao-sobre-flaviobolsonaro-alcanca-37-imoveis/ | A compra e a quitação da mansão em Brasília (oglobo.globo.com) https://oglobo.globo.com/politica/eleicoes-2026/noticia/2026/08/14/video-mansao-que-fez-patrimonio-de-flavio-disparar-fica-em-terreno-de-2400-m-e-foi-quitada-27-anos-antes-do-previsto.ghtml | A análise do MPF sobre 37 transações imobiliárias (cnnbrasil.com.br) https://www.maisgoias.com.br/politica/procurador-aponta-fortes-indicios-de-lavagem-de-dinheiro-em-bens-de-flavio-bolsonaro/ | A acusação do MP-RJ sobre organização criminosa (g1.globo.com) https://g1.globo.com/rj/rio-de-janeiro/noticia/2019/12/19/mp-do-rj-detalha-suposto-esquema-de-corrupcao-envolvendo-entao-deputado-flavio-bolsonaro.ghtml?utm_source=twitter&amp;utm_medium=social&amp;utm_campaign=g1 | Destinação de emendas e entidades questionadas (revistaforum.com.br) https://revistaforum.com.br/politica/flavio-bolsonaro-emendas-ong-fantasma-e-instituto-de-miliciano/ | Portal Porque (resume piauí, 20/10/2026) https://www.portalporque.com.br/brasil/revista-piaui-aponta-que-flavio-bolsonaro-foi-socio-indireto-de-bet/ | Notícias ao Minuto (resume piauí) https://www.noticiasaominuto.com.br/politica/2422338/flavio-bolsonaro-e-dono-de-bet-entenda-o-que-a-pf-investiga | Mais Goiás (via Folha, 16/10/2026) https://www.maisgoias.com.br/brasil/pf-descobre-voos-de-flavio-bolsonaro-pagos-por-dono-de-bet-que-e-investigado-por-fraudes-no-inss/</t>
         </is>
       </c>
       <c r="L10" s="37" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>22/10/2026</t>
         </is>
       </c>
       <c r="M10" s="37" t="inlineStr">
         <is>
-          <t>Resultado do 1º turno; 2º inquérito no STF; Operação Make Up; visitas ao pai liberadas. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
+          <t>Resultado do 1º turno; 2º inquérito no STF; Operação Make Up; visitas ao pai liberadas. 21/10/2026: importado do acervo a verdade. (bolsomaster.site). 22/10/2026: rodada UOL News (bets, Loterj, hangar, Weverton).</t>
         </is>
       </c>
       <c r="N10" s="24" t="inlineStr">
@@ -3765,8 +3783,78 @@
       <c r="O35" s="24" t="n"/>
       <c r="P35" s="24" t="n"/>
     </row>
+    <row r="36">
+      <c r="A36" s="37" t="inlineStr">
+        <is>
+          <t>weverton</t>
+        </is>
+      </c>
+      <c r="B36" s="38" t="inlineStr">
+        <is>
+          <t>Weverton Rocha</t>
+        </is>
+      </c>
+      <c r="C36" s="37" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D36" s="37" t="inlineStr">
+        <is>
+          <t>Senador pelo Maranhão (PDT) e vice-líder do governo Lula no Senado. Investigado na Operação Sem Desconto (caso INSS): a PF diz que ele formulava demandas e cobrava pagamentos numa estrutura ligada a Willer Tomaz, que mora numa casa de R$ 6 mi registrada na WT e que a mulher dele, Samya Rocha, recebeu mais de R$ 11 mi de empresas de Willer. Buscas em 04/08/2026, autorizadas por André Mendonça.</t>
+        </is>
+      </c>
+      <c r="E36" s="37" t="inlineStr">
+        <is>
+          <t>Maranhão (MA); mandato em Brasília</t>
+        </is>
+      </c>
+      <c r="F36" s="37" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G36" s="37" t="inlineStr">
+        <is>
+          <t>Investigado, sem denúncia. Diz que as movimentações vêm de atividades profissionais declaradas à Receita e que é alvo por suas posições políticas. Willer diz que os repasses a Samya são honorários de advogada associada.</t>
+        </is>
+      </c>
+      <c r="H36" s="39" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I36" s="37" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J36" s="37" t="inlineStr">
+        <is>
+          <t>“Braço direito” é expressão do UOL News; a PF descreve a estrutura de Willer como “hub financeiro, patrimonial e logístico” do senador.</t>
+        </is>
+      </c>
+      <c r="K36" s="37" t="inlineStr">
+        <is>
+          <t>Poder360 04/08/2026 https://www.poder360.com.br/poder-justica/pf-investiga-advogado-amigo-de-flavio-em-operacao-sobre-o-inss/ | O Povo 04/08/2026 https://www.opovo.com.br/noticias/politica/2026/08/04/pf-investiga-senador-weverton-rocha-por-suspeita-de-desvios-no-inss.html</t>
+        </is>
+      </c>
+      <c r="L36" s="37" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M36" s="37" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada UOL News (bets, Loterj, hangar, Weverton). Perfil novo.</t>
+        </is>
+      </c>
+      <c r="N36" s="24" t="n"/>
+      <c r="O36" s="24" t="n"/>
+      <c r="P36" s="24" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P35"/>
+  <autoFilter ref="A1:P36"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3779,7 +3867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J84"/>
+  <dimension ref="A1:J91"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="24" min="1" max="1"/>
@@ -3869,7 +3957,7 @@
         </is>
       </c>
       <c r="F2" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A2)+COUNTIF(Edges!$B$2:$B$182,A2)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A2)+COUNTIF(Edges!$B$2:$B$198,A2)</f>
         <v/>
       </c>
       <c r="G2" s="24" t="n"/>
@@ -3904,7 +3992,7 @@
         </is>
       </c>
       <c r="F3" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A3)+COUNTIF(Edges!$B$2:$B$182,A3)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A3)+COUNTIF(Edges!$B$2:$B$198,A3)</f>
         <v/>
       </c>
     </row>
@@ -3935,7 +4023,7 @@
         </is>
       </c>
       <c r="F4" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A4)+COUNTIF(Edges!$B$2:$B$182,A4)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A4)+COUNTIF(Edges!$B$2:$B$198,A4)</f>
         <v/>
       </c>
     </row>
@@ -3966,7 +4054,7 @@
         </is>
       </c>
       <c r="F5" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A5)+COUNTIF(Edges!$B$2:$B$182,A5)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A5)+COUNTIF(Edges!$B$2:$B$198,A5)</f>
         <v/>
       </c>
     </row>
@@ -3997,7 +4085,7 @@
         </is>
       </c>
       <c r="F6" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A6)+COUNTIF(Edges!$B$2:$B$182,A6)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A6)+COUNTIF(Edges!$B$2:$B$198,A6)</f>
         <v/>
       </c>
     </row>
@@ -4028,7 +4116,7 @@
         </is>
       </c>
       <c r="F7" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A7)+COUNTIF(Edges!$B$2:$B$182,A7)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A7)+COUNTIF(Edges!$B$2:$B$198,A7)</f>
         <v/>
       </c>
     </row>
@@ -4059,7 +4147,7 @@
         </is>
       </c>
       <c r="F8" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A8)+COUNTIF(Edges!$B$2:$B$182,A8)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A8)+COUNTIF(Edges!$B$2:$B$198,A8)</f>
         <v/>
       </c>
       <c r="G8" s="24" t="n"/>
@@ -4094,7 +4182,7 @@
         </is>
       </c>
       <c r="F9" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A9)+COUNTIF(Edges!$B$2:$B$182,A9)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A9)+COUNTIF(Edges!$B$2:$B$198,A9)</f>
         <v/>
       </c>
       <c r="G9" s="24" t="n"/>
@@ -4129,7 +4217,7 @@
         </is>
       </c>
       <c r="F10" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A10)+COUNTIF(Edges!$B$2:$B$182,A10)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A10)+COUNTIF(Edges!$B$2:$B$198,A10)</f>
         <v/>
       </c>
     </row>
@@ -4160,7 +4248,7 @@
         </is>
       </c>
       <c r="F11" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A11)+COUNTIF(Edges!$B$2:$B$182,A11)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A11)+COUNTIF(Edges!$B$2:$B$198,A11)</f>
         <v/>
       </c>
       <c r="G11" s="24" t="n"/>
@@ -4195,7 +4283,7 @@
         </is>
       </c>
       <c r="F12" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A12)+COUNTIF(Edges!$B$2:$B$182,A12)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A12)+COUNTIF(Edges!$B$2:$B$198,A12)</f>
         <v/>
       </c>
       <c r="G12" s="24" t="inlineStr">
@@ -4242,7 +4330,7 @@
         </is>
       </c>
       <c r="F13" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A13)+COUNTIF(Edges!$B$2:$B$182,A13)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A13)+COUNTIF(Edges!$B$2:$B$198,A13)</f>
         <v/>
       </c>
     </row>
@@ -4273,7 +4361,7 @@
         </is>
       </c>
       <c r="F14" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A14)+COUNTIF(Edges!$B$2:$B$182,A14)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A14)+COUNTIF(Edges!$B$2:$B$198,A14)</f>
         <v/>
       </c>
       <c r="G14" s="24" t="n"/>
@@ -4308,7 +4396,7 @@
         </is>
       </c>
       <c r="F15" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A15)+COUNTIF(Edges!$B$2:$B$182,A15)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A15)+COUNTIF(Edges!$B$2:$B$198,A15)</f>
         <v/>
       </c>
       <c r="G15" s="24" t="n"/>
@@ -4343,7 +4431,7 @@
         </is>
       </c>
       <c r="F16" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A16)+COUNTIF(Edges!$B$2:$B$182,A16)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A16)+COUNTIF(Edges!$B$2:$B$198,A16)</f>
         <v/>
       </c>
       <c r="G16" s="24" t="inlineStr">
@@ -4390,7 +4478,7 @@
         </is>
       </c>
       <c r="F17" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A17)+COUNTIF(Edges!$B$2:$B$182,A17)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A17)+COUNTIF(Edges!$B$2:$B$198,A17)</f>
         <v/>
       </c>
       <c r="G17" s="24" t="inlineStr">
@@ -4437,7 +4525,7 @@
         </is>
       </c>
       <c r="F18" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A18)+COUNTIF(Edges!$B$2:$B$182,A18)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A18)+COUNTIF(Edges!$B$2:$B$198,A18)</f>
         <v/>
       </c>
     </row>
@@ -4468,7 +4556,7 @@
         </is>
       </c>
       <c r="F19" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A19)+COUNTIF(Edges!$B$2:$B$182,A19)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A19)+COUNTIF(Edges!$B$2:$B$198,A19)</f>
         <v/>
       </c>
     </row>
@@ -4499,7 +4587,7 @@
         </is>
       </c>
       <c r="F20" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A20)+COUNTIF(Edges!$B$2:$B$182,A20)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A20)+COUNTIF(Edges!$B$2:$B$198,A20)</f>
         <v/>
       </c>
     </row>
@@ -4530,7 +4618,7 @@
         </is>
       </c>
       <c r="F21" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A21)+COUNTIF(Edges!$B$2:$B$182,A21)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A21)+COUNTIF(Edges!$B$2:$B$198,A21)</f>
         <v/>
       </c>
     </row>
@@ -4561,7 +4649,7 @@
         </is>
       </c>
       <c r="F22" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A22)+COUNTIF(Edges!$B$2:$B$182,A22)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A22)+COUNTIF(Edges!$B$2:$B$198,A22)</f>
         <v/>
       </c>
       <c r="G22" s="24" t="n"/>
@@ -4596,7 +4684,7 @@
         </is>
       </c>
       <c r="F23" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A23)+COUNTIF(Edges!$B$2:$B$182,A23)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A23)+COUNTIF(Edges!$B$2:$B$198,A23)</f>
         <v/>
       </c>
       <c r="G23" s="24" t="n"/>
@@ -4631,7 +4719,7 @@
         </is>
       </c>
       <c r="F24" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A24)+COUNTIF(Edges!$B$2:$B$182,A24)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A24)+COUNTIF(Edges!$B$2:$B$198,A24)</f>
         <v/>
       </c>
     </row>
@@ -4662,7 +4750,7 @@
         </is>
       </c>
       <c r="F25" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A25)+COUNTIF(Edges!$B$2:$B$182,A25)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A25)+COUNTIF(Edges!$B$2:$B$198,A25)</f>
         <v/>
       </c>
     </row>
@@ -4693,7 +4781,7 @@
         </is>
       </c>
       <c r="F26" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A26)+COUNTIF(Edges!$B$2:$B$182,A26)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A26)+COUNTIF(Edges!$B$2:$B$198,A26)</f>
         <v/>
       </c>
     </row>
@@ -4724,7 +4812,7 @@
         </is>
       </c>
       <c r="F27" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A27)+COUNTIF(Edges!$B$2:$B$182,A27)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A27)+COUNTIF(Edges!$B$2:$B$198,A27)</f>
         <v/>
       </c>
     </row>
@@ -4755,7 +4843,7 @@
         </is>
       </c>
       <c r="F28" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A28)+COUNTIF(Edges!$B$2:$B$182,A28)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A28)+COUNTIF(Edges!$B$2:$B$198,A28)</f>
         <v/>
       </c>
     </row>
@@ -4786,7 +4874,7 @@
         </is>
       </c>
       <c r="F29" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A29)+COUNTIF(Edges!$B$2:$B$182,A29)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A29)+COUNTIF(Edges!$B$2:$B$198,A29)</f>
         <v/>
       </c>
     </row>
@@ -4817,7 +4905,7 @@
         </is>
       </c>
       <c r="F30" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A30)+COUNTIF(Edges!$B$2:$B$182,A30)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A30)+COUNTIF(Edges!$B$2:$B$198,A30)</f>
         <v/>
       </c>
       <c r="G30" s="24" t="n"/>
@@ -4852,7 +4940,7 @@
         </is>
       </c>
       <c r="F31" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A31)+COUNTIF(Edges!$B$2:$B$182,A31)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A31)+COUNTIF(Edges!$B$2:$B$198,A31)</f>
         <v/>
       </c>
     </row>
@@ -4883,7 +4971,7 @@
         </is>
       </c>
       <c r="F32" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A32)+COUNTIF(Edges!$B$2:$B$182,A32)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A32)+COUNTIF(Edges!$B$2:$B$198,A32)</f>
         <v/>
       </c>
     </row>
@@ -4914,7 +5002,7 @@
         </is>
       </c>
       <c r="F33" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A33)+COUNTIF(Edges!$B$2:$B$182,A33)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A33)+COUNTIF(Edges!$B$2:$B$198,A33)</f>
         <v/>
       </c>
       <c r="G33" s="24" t="n"/>
@@ -4949,7 +5037,7 @@
         </is>
       </c>
       <c r="F34" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A34)+COUNTIF(Edges!$B$2:$B$182,A34)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A34)+COUNTIF(Edges!$B$2:$B$198,A34)</f>
         <v/>
       </c>
       <c r="G34" s="24" t="n"/>
@@ -4984,7 +5072,7 @@
         </is>
       </c>
       <c r="F35" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A35)+COUNTIF(Edges!$B$2:$B$182,A35)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A35)+COUNTIF(Edges!$B$2:$B$198,A35)</f>
         <v/>
       </c>
     </row>
@@ -5015,7 +5103,7 @@
         </is>
       </c>
       <c r="F36" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A36)+COUNTIF(Edges!$B$2:$B$182,A36)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A36)+COUNTIF(Edges!$B$2:$B$198,A36)</f>
         <v/>
       </c>
     </row>
@@ -5046,7 +5134,7 @@
         </is>
       </c>
       <c r="F37" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A37)+COUNTIF(Edges!$B$2:$B$182,A37)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A37)+COUNTIF(Edges!$B$2:$B$198,A37)</f>
         <v/>
       </c>
     </row>
@@ -5077,7 +5165,7 @@
         </is>
       </c>
       <c r="F38" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A38)+COUNTIF(Edges!$B$2:$B$182,A38)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A38)+COUNTIF(Edges!$B$2:$B$198,A38)</f>
         <v/>
       </c>
       <c r="G38" s="24" t="n"/>
@@ -5112,7 +5200,7 @@
         </is>
       </c>
       <c r="F39" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A39)+COUNTIF(Edges!$B$2:$B$182,A39)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A39)+COUNTIF(Edges!$B$2:$B$198,A39)</f>
         <v/>
       </c>
       <c r="G39" s="24" t="n"/>
@@ -5147,7 +5235,7 @@
         </is>
       </c>
       <c r="F40" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A40)+COUNTIF(Edges!$B$2:$B$182,A40)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A40)+COUNTIF(Edges!$B$2:$B$198,A40)</f>
         <v/>
       </c>
       <c r="G40" s="24" t="n"/>
@@ -5182,7 +5270,7 @@
         </is>
       </c>
       <c r="F41" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A41)+COUNTIF(Edges!$B$2:$B$182,A41)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A41)+COUNTIF(Edges!$B$2:$B$198,A41)</f>
         <v/>
       </c>
       <c r="G41" s="24" t="n"/>
@@ -5217,7 +5305,7 @@
         </is>
       </c>
       <c r="F42" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A42)+COUNTIF(Edges!$B$2:$B$182,A42)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A42)+COUNTIF(Edges!$B$2:$B$198,A42)</f>
         <v/>
       </c>
       <c r="G42" s="24" t="n"/>
@@ -5252,7 +5340,7 @@
         </is>
       </c>
       <c r="F43" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A43)+COUNTIF(Edges!$B$2:$B$182,A43)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A43)+COUNTIF(Edges!$B$2:$B$198,A43)</f>
         <v/>
       </c>
     </row>
@@ -5283,7 +5371,7 @@
         </is>
       </c>
       <c r="F44" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A44)+COUNTIF(Edges!$B$2:$B$182,A44)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A44)+COUNTIF(Edges!$B$2:$B$198,A44)</f>
         <v/>
       </c>
     </row>
@@ -5314,7 +5402,7 @@
         </is>
       </c>
       <c r="F45" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A45)+COUNTIF(Edges!$B$2:$B$182,A45)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A45)+COUNTIF(Edges!$B$2:$B$198,A45)</f>
         <v/>
       </c>
     </row>
@@ -5345,7 +5433,7 @@
         </is>
       </c>
       <c r="F46" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A46)+COUNTIF(Edges!$B$2:$B$182,A46)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A46)+COUNTIF(Edges!$B$2:$B$198,A46)</f>
         <v/>
       </c>
     </row>
@@ -5376,7 +5464,7 @@
         </is>
       </c>
       <c r="F47" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A47)+COUNTIF(Edges!$B$2:$B$182,A47)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A47)+COUNTIF(Edges!$B$2:$B$198,A47)</f>
         <v/>
       </c>
     </row>
@@ -5407,7 +5495,7 @@
         </is>
       </c>
       <c r="F48" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A48)+COUNTIF(Edges!$B$2:$B$182,A48)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A48)+COUNTIF(Edges!$B$2:$B$198,A48)</f>
         <v/>
       </c>
       <c r="G48" s="24" t="n"/>
@@ -5442,7 +5530,7 @@
         </is>
       </c>
       <c r="F49" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A49)+COUNTIF(Edges!$B$2:$B$182,A49)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A49)+COUNTIF(Edges!$B$2:$B$198,A49)</f>
         <v/>
       </c>
     </row>
@@ -5473,7 +5561,7 @@
         </is>
       </c>
       <c r="F50" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A50)+COUNTIF(Edges!$B$2:$B$182,A50)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A50)+COUNTIF(Edges!$B$2:$B$198,A50)</f>
         <v/>
       </c>
     </row>
@@ -5504,7 +5592,7 @@
         </is>
       </c>
       <c r="F51" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A51)+COUNTIF(Edges!$B$2:$B$182,A51)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A51)+COUNTIF(Edges!$B$2:$B$198,A51)</f>
         <v/>
       </c>
     </row>
@@ -5535,7 +5623,7 @@
         </is>
       </c>
       <c r="F52" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A52)+COUNTIF(Edges!$B$2:$B$182,A52)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A52)+COUNTIF(Edges!$B$2:$B$198,A52)</f>
         <v/>
       </c>
       <c r="G52" s="24" t="inlineStr">
@@ -5582,7 +5670,7 @@
         </is>
       </c>
       <c r="F53" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A53)+COUNTIF(Edges!$B$2:$B$182,A53)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A53)+COUNTIF(Edges!$B$2:$B$198,A53)</f>
         <v/>
       </c>
       <c r="G53" s="24" t="inlineStr">
@@ -5629,7 +5717,7 @@
         </is>
       </c>
       <c r="F54" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A54)+COUNTIF(Edges!$B$2:$B$182,A54)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A54)+COUNTIF(Edges!$B$2:$B$198,A54)</f>
         <v/>
       </c>
       <c r="G54" s="24" t="inlineStr">
@@ -5676,7 +5764,7 @@
         </is>
       </c>
       <c r="F55" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A55)+COUNTIF(Edges!$B$2:$B$182,A55)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A55)+COUNTIF(Edges!$B$2:$B$198,A55)</f>
         <v/>
       </c>
       <c r="G55" s="24" t="inlineStr">
@@ -5723,7 +5811,7 @@
         </is>
       </c>
       <c r="F56" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A56)+COUNTIF(Edges!$B$2:$B$182,A56)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A56)+COUNTIF(Edges!$B$2:$B$198,A56)</f>
         <v/>
       </c>
     </row>
@@ -5754,7 +5842,7 @@
         </is>
       </c>
       <c r="F57" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A57)+COUNTIF(Edges!$B$2:$B$182,A57)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A57)+COUNTIF(Edges!$B$2:$B$198,A57)</f>
         <v/>
       </c>
       <c r="G57" s="24" t="inlineStr">
@@ -5801,7 +5889,7 @@
         </is>
       </c>
       <c r="F58" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A58)+COUNTIF(Edges!$B$2:$B$182,A58)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A58)+COUNTIF(Edges!$B$2:$B$198,A58)</f>
         <v/>
       </c>
       <c r="G58" s="24" t="inlineStr">
@@ -5848,7 +5936,7 @@
         </is>
       </c>
       <c r="F59" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A59)+COUNTIF(Edges!$B$2:$B$182,A59)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A59)+COUNTIF(Edges!$B$2:$B$198,A59)</f>
         <v/>
       </c>
       <c r="G59" s="24" t="n"/>
@@ -5883,7 +5971,7 @@
         </is>
       </c>
       <c r="F60" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A60)+COUNTIF(Edges!$B$2:$B$182,A60)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A60)+COUNTIF(Edges!$B$2:$B$198,A60)</f>
         <v/>
       </c>
       <c r="G60" s="24" t="n"/>
@@ -5918,7 +6006,7 @@
         </is>
       </c>
       <c r="F61" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A61)+COUNTIF(Edges!$B$2:$B$182,A61)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A61)+COUNTIF(Edges!$B$2:$B$198,A61)</f>
         <v/>
       </c>
       <c r="G61" s="24" t="n"/>
@@ -5953,7 +6041,7 @@
         </is>
       </c>
       <c r="F62" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A62)+COUNTIF(Edges!$B$2:$B$182,A62)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A62)+COUNTIF(Edges!$B$2:$B$198,A62)</f>
         <v/>
       </c>
       <c r="G62" s="24" t="n"/>
@@ -5988,7 +6076,7 @@
         </is>
       </c>
       <c r="F63" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A63)+COUNTIF(Edges!$B$2:$B$182,A63)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A63)+COUNTIF(Edges!$B$2:$B$198,A63)</f>
         <v/>
       </c>
       <c r="G63" s="24" t="n"/>
@@ -6023,7 +6111,7 @@
         </is>
       </c>
       <c r="F64" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A64)+COUNTIF(Edges!$B$2:$B$182,A64)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A64)+COUNTIF(Edges!$B$2:$B$198,A64)</f>
         <v/>
       </c>
       <c r="G64" s="24" t="n"/>
@@ -6058,7 +6146,7 @@
         </is>
       </c>
       <c r="F65" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A65)+COUNTIF(Edges!$B$2:$B$182,A65)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A65)+COUNTIF(Edges!$B$2:$B$198,A65)</f>
         <v/>
       </c>
       <c r="G65" s="24" t="n"/>
@@ -6093,7 +6181,7 @@
         </is>
       </c>
       <c r="F66" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A66)+COUNTIF(Edges!$B$2:$B$182,A66)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A66)+COUNTIF(Edges!$B$2:$B$198,A66)</f>
         <v/>
       </c>
       <c r="G66" s="24" t="n"/>
@@ -6128,7 +6216,7 @@
         </is>
       </c>
       <c r="F67" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A67)+COUNTIF(Edges!$B$2:$B$182,A67)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A67)+COUNTIF(Edges!$B$2:$B$198,A67)</f>
         <v/>
       </c>
       <c r="G67" s="24" t="n"/>
@@ -6163,7 +6251,7 @@
         </is>
       </c>
       <c r="F68" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A68)+COUNTIF(Edges!$B$2:$B$182,A68)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A68)+COUNTIF(Edges!$B$2:$B$198,A68)</f>
         <v/>
       </c>
       <c r="G68" s="24" t="n"/>
@@ -6198,7 +6286,7 @@
         </is>
       </c>
       <c r="F69" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A69)+COUNTIF(Edges!$B$2:$B$182,A69)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A69)+COUNTIF(Edges!$B$2:$B$198,A69)</f>
         <v/>
       </c>
       <c r="G69" s="24" t="n"/>
@@ -6233,7 +6321,7 @@
         </is>
       </c>
       <c r="F70" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A70)+COUNTIF(Edges!$B$2:$B$182,A70)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A70)+COUNTIF(Edges!$B$2:$B$198,A70)</f>
         <v/>
       </c>
       <c r="G70" s="24" t="n"/>
@@ -6268,7 +6356,7 @@
         </is>
       </c>
       <c r="F71" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A71)+COUNTIF(Edges!$B$2:$B$182,A71)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A71)+COUNTIF(Edges!$B$2:$B$198,A71)</f>
         <v/>
       </c>
       <c r="G71" s="24" t="n"/>
@@ -6303,7 +6391,7 @@
         </is>
       </c>
       <c r="F72" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A72)+COUNTIF(Edges!$B$2:$B$182,A72)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A72)+COUNTIF(Edges!$B$2:$B$198,A72)</f>
         <v/>
       </c>
       <c r="G72" s="24" t="n"/>
@@ -6338,7 +6426,7 @@
         </is>
       </c>
       <c r="F73" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A73)+COUNTIF(Edges!$B$2:$B$182,A73)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A73)+COUNTIF(Edges!$B$2:$B$198,A73)</f>
         <v/>
       </c>
       <c r="G73" s="24" t="n"/>
@@ -6373,7 +6461,7 @@
         </is>
       </c>
       <c r="F74" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A74)+COUNTIF(Edges!$B$2:$B$182,A74)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A74)+COUNTIF(Edges!$B$2:$B$198,A74)</f>
         <v/>
       </c>
       <c r="G74" s="24" t="n"/>
@@ -6408,7 +6496,7 @@
         </is>
       </c>
       <c r="F75" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A75)+COUNTIF(Edges!$B$2:$B$182,A75)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A75)+COUNTIF(Edges!$B$2:$B$198,A75)</f>
         <v/>
       </c>
       <c r="G75" s="24" t="n"/>
@@ -6443,7 +6531,7 @@
         </is>
       </c>
       <c r="F76" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A76)+COUNTIF(Edges!$B$2:$B$182,A76)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A76)+COUNTIF(Edges!$B$2:$B$198,A76)</f>
         <v/>
       </c>
       <c r="G76" s="24" t="n"/>
@@ -6478,7 +6566,7 @@
         </is>
       </c>
       <c r="F77" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A77)+COUNTIF(Edges!$B$2:$B$182,A77)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A77)+COUNTIF(Edges!$B$2:$B$198,A77)</f>
         <v/>
       </c>
       <c r="G77" s="24" t="n"/>
@@ -6513,7 +6601,7 @@
         </is>
       </c>
       <c r="F78" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A78)+COUNTIF(Edges!$B$2:$B$182,A78)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A78)+COUNTIF(Edges!$B$2:$B$198,A78)</f>
         <v/>
       </c>
       <c r="G78" s="24" t="n"/>
@@ -6548,7 +6636,7 @@
         </is>
       </c>
       <c r="F79" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A79)+COUNTIF(Edges!$B$2:$B$182,A79)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A79)+COUNTIF(Edges!$B$2:$B$198,A79)</f>
         <v/>
       </c>
       <c r="G79" s="24" t="n"/>
@@ -6583,7 +6671,7 @@
         </is>
       </c>
       <c r="F80" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A80)+COUNTIF(Edges!$B$2:$B$182,A80)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A80)+COUNTIF(Edges!$B$2:$B$198,A80)</f>
         <v/>
       </c>
       <c r="G80" s="24" t="n"/>
@@ -6618,7 +6706,7 @@
         </is>
       </c>
       <c r="F81" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A81)+COUNTIF(Edges!$B$2:$B$182,A81)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A81)+COUNTIF(Edges!$B$2:$B$198,A81)</f>
         <v/>
       </c>
       <c r="G81" s="24" t="n"/>
@@ -6653,7 +6741,7 @@
         </is>
       </c>
       <c r="F82" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A82)+COUNTIF(Edges!$B$2:$B$182,A82)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A82)+COUNTIF(Edges!$B$2:$B$198,A82)</f>
         <v/>
       </c>
       <c r="G82" s="24" t="n"/>
@@ -6688,7 +6776,7 @@
         </is>
       </c>
       <c r="F83" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A83)+COUNTIF(Edges!$B$2:$B$182,A83)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A83)+COUNTIF(Edges!$B$2:$B$198,A83)</f>
         <v/>
       </c>
       <c r="G83" s="24" t="n"/>
@@ -6723,13 +6811,258 @@
         </is>
       </c>
       <c r="F84" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$182,A84)+COUNTIF(Edges!$B$2:$B$182,A84)</f>
+        <f>COUNTIF(Edges!$A$2:$A$198,A84)+COUNTIF(Edges!$B$2:$B$198,A84)</f>
         <v/>
       </c>
       <c r="G84" s="24" t="n"/>
       <c r="H84" s="24" t="n"/>
       <c r="I84" s="24" t="n"/>
       <c r="J84" s="24" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>cathedral</t>
+        </is>
+      </c>
+      <c r="B85" s="45" t="inlineStr">
+        <is>
+          <t>Cathedral Holdings</t>
+        </is>
+      </c>
+      <c r="C85" s="45" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="D85" s="45" t="inlineStr">
+        <is>
+          <t>Willer Tomaz e sua rede</t>
+        </is>
+      </c>
+      <c r="E85" s="45" t="inlineStr">
+        <is>
+          <t>Offshore na Ilha da Madeira criada por Willer em jan/2023; única acionista da Rede Loto</t>
+        </is>
+      </c>
+      <c r="F85" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$198,A85)+COUNTIF(Edges!$B$2:$B$198,A85)</f>
+        <v/>
+      </c>
+      <c r="G85" s="24" t="n"/>
+      <c r="H85" s="24" t="n"/>
+      <c r="I85" s="24" t="n"/>
+      <c r="J85" s="24" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>bestbet</t>
+        </is>
+      </c>
+      <c r="B86" s="45" t="inlineStr">
+        <is>
+          <t>Best Bet (Rede Loto)</t>
+        </is>
+      </c>
+      <c r="C86" s="45" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="D86" s="45" t="inlineStr">
+        <is>
+          <t>Willer Tomaz e sua rede</t>
+        </is>
+      </c>
+      <c r="E86" s="45" t="inlineStr">
+        <is>
+          <t>Bet licenciada pela Loterj em mai/2023; a defesa diz que nunca chegou a operar</t>
+        </is>
+      </c>
+      <c r="F86" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$198,A86)+COUNTIF(Edges!$B$2:$B$198,A86)</f>
+        <v/>
+      </c>
+      <c r="G86" s="24" t="n"/>
+      <c r="H86" s="24" t="n"/>
+      <c r="I86" s="24" t="n"/>
+      <c r="J86" s="24" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="45" t="inlineStr">
+        <is>
+          <t>riopag</t>
+        </is>
+      </c>
+      <c r="B87" s="45" t="inlineStr">
+        <is>
+          <t>Rio Pag</t>
+        </is>
+      </c>
+      <c r="C87" s="45" t="inlineStr">
+        <is>
+          <t>Empresa</t>
+        </is>
+      </c>
+      <c r="D87" s="45" t="inlineStr">
+        <is>
+          <t>Willer Tomaz e sua rede</t>
+        </is>
+      </c>
+      <c r="E87" s="45" t="inlineStr">
+        <is>
+          <t>Processava pagamentos da Loterj; contrato rescindido pelo estado, que cobra ~R$ 4 mi</t>
+        </is>
+      </c>
+      <c r="F87" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$198,A87)+COUNTIF(Edges!$B$2:$B$198,A87)</f>
+        <v/>
+      </c>
+      <c r="G87" s="24" t="n"/>
+      <c r="H87" s="24" t="n"/>
+      <c r="I87" s="24" t="n"/>
+      <c r="J87" s="24" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="45" t="inlineStr">
+        <is>
+          <t>loterj</t>
+        </is>
+      </c>
+      <c r="B88" s="45" t="inlineStr">
+        <is>
+          <t>Loterj</t>
+        </is>
+      </c>
+      <c r="C88" s="45" t="inlineStr">
+        <is>
+          <t>Instituição ou caso</t>
+        </is>
+      </c>
+      <c r="D88" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E88" s="45" t="inlineStr">
+        <is>
+          <t>Loteria do Estado do RJ; licenciou a Best Bet e contratou a Rio Pag em 2023</t>
+        </is>
+      </c>
+      <c r="F88" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$198,A88)+COUNTIF(Edges!$B$2:$B$198,A88)</f>
+        <v/>
+      </c>
+      <c r="G88" s="24" t="n"/>
+      <c r="H88" s="24" t="n"/>
+      <c r="I88" s="24" t="n"/>
+      <c r="J88" s="24" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="45" t="inlineStr">
+        <is>
+          <t>cancado</t>
+        </is>
+      </c>
+      <c r="B89" s="45" t="inlineStr">
+        <is>
+          <t>Hazenclever Cançado</t>
+        </is>
+      </c>
+      <c r="C89" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D89" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E89" s="45" t="inlineStr">
+        <is>
+          <t>Ex-presidente da Loterj; assinou a licença da Best Bet</t>
+        </is>
+      </c>
+      <c r="F89" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$198,A89)+COUNTIF(Edges!$B$2:$B$198,A89)</f>
+        <v/>
+      </c>
+      <c r="G89" s="24" t="n"/>
+      <c r="H89" s="24" t="n"/>
+      <c r="I89" s="24" t="n"/>
+      <c r="J89" s="24" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="45" t="inlineStr">
+        <is>
+          <t>hangar</t>
+        </is>
+      </c>
+      <c r="B90" s="45" t="inlineStr">
+        <is>
+          <t>Hangares de Willer (Aeroporto de Brasília)</t>
+        </is>
+      </c>
+      <c r="C90" s="45" t="inlineStr">
+        <is>
+          <t>Casa ou ativo</t>
+        </is>
+      </c>
+      <c r="D90" s="45" t="inlineStr">
+        <is>
+          <t>Casas e ativos</t>
+        </is>
+      </c>
+      <c r="E90" s="45" t="inlineStr">
+        <is>
+          <t>Hangares 36 e 37; PF achou sala oculta e máquina de contar, sem dinheiro; Willer diz que atende transporte de valores</t>
+        </is>
+      </c>
+      <c r="F90" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$198,A90)+COUNTIF(Edges!$B$2:$B$198,A90)</f>
+        <v/>
+      </c>
+      <c r="G90" s="24" t="n"/>
+      <c r="H90" s="24" t="n"/>
+      <c r="I90" s="24" t="n"/>
+      <c r="J90" s="24" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="45" t="inlineStr">
+        <is>
+          <t>weverton</t>
+        </is>
+      </c>
+      <c r="B91" s="45" t="inlineStr">
+        <is>
+          <t>Weverton Rocha</t>
+        </is>
+      </c>
+      <c r="C91" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D91" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E91" s="45" t="inlineStr">
+        <is>
+          <t>Senador (PDT-MA), vice-líder do governo Lula; investigado na Operação Sem Desconto; nega</t>
+        </is>
+      </c>
+      <c r="F91" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$198,A91)+COUNTIF(Edges!$B$2:$B$198,A91)</f>
+        <v/>
+      </c>
+      <c r="G91" s="24" t="n"/>
+      <c r="H91" s="24" t="n"/>
+      <c r="I91" s="24" t="n"/>
+      <c r="J91" s="24" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F58"/>
@@ -6745,7 +7078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F198"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="24" min="1" max="2"/>
@@ -6808,11 +7141,11 @@
         </is>
       </c>
       <c r="E2" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A2,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A2,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F2" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B2,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B2,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -6838,11 +7171,11 @@
         </is>
       </c>
       <c r="E3" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A3,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A3,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F3" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B3,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B3,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -6868,11 +7201,11 @@
         </is>
       </c>
       <c r="E4" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A4,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A4,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F4" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B4,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B4,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -6898,11 +7231,11 @@
         </is>
       </c>
       <c r="E5" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A5,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A5,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F5" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B5,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B5,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -6928,11 +7261,11 @@
         </is>
       </c>
       <c r="E6" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A6,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A6,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F6" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B6,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B6,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -6958,11 +7291,11 @@
         </is>
       </c>
       <c r="E7" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A7,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A7,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F7" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B7,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B7,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -6988,11 +7321,11 @@
         </is>
       </c>
       <c r="E8" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A8,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A8,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F8" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B8,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B8,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7018,11 +7351,11 @@
         </is>
       </c>
       <c r="E9" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A9,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A9,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F9" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B9,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B9,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7048,11 +7381,11 @@
         </is>
       </c>
       <c r="E10" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A10,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A10,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F10" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B10,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B10,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7078,11 +7411,11 @@
         </is>
       </c>
       <c r="E11" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A11,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A11,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F11" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B11,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B11,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7108,11 +7441,11 @@
         </is>
       </c>
       <c r="E12" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A12,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A12,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F12" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B12,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B12,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7138,11 +7471,11 @@
         </is>
       </c>
       <c r="E13" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A13,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A13,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F13" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B13,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B13,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7168,11 +7501,11 @@
         </is>
       </c>
       <c r="E14" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A14,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A14,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F14" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B14,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B14,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7198,11 +7531,11 @@
         </is>
       </c>
       <c r="E15" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A15,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A15,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F15" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B15,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B15,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7228,11 +7561,11 @@
         </is>
       </c>
       <c r="E16" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A16,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A16,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F16" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B16,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B16,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7258,11 +7591,11 @@
         </is>
       </c>
       <c r="E17" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A17,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A17,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F17" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B17,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B17,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7288,11 +7621,11 @@
         </is>
       </c>
       <c r="E18" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A18,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A18,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F18" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B18,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B18,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7318,11 +7651,11 @@
         </is>
       </c>
       <c r="E19" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A19,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A19,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F19" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B19,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B19,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7348,11 +7681,11 @@
         </is>
       </c>
       <c r="E20" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A20,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A20,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F20" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B20,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B20,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7378,11 +7711,11 @@
         </is>
       </c>
       <c r="E21" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A21,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A21,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F21" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B21,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B21,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7408,11 +7741,11 @@
         </is>
       </c>
       <c r="E22" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A22,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A22,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F22" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B22,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B22,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7438,11 +7771,11 @@
         </is>
       </c>
       <c r="E23" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A23,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A23,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F23" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B23,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B23,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7468,11 +7801,11 @@
         </is>
       </c>
       <c r="E24" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A24,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A24,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F24" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B24,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B24,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7489,7 +7822,7 @@
       </c>
       <c r="C25" s="45" t="inlineStr">
         <is>
-          <t>Flávio era “usuário master”; excluído após a 1ª operação</t>
+          <t>PF/piauí: Flávio era “usuário master” da conta da Alcazar; e-mail de 22/05/2025 pediu a exclusão dele. Ele nega ter tido acesso</t>
         </is>
       </c>
       <c r="D25" s="45" t="inlineStr">
@@ -7498,11 +7831,11 @@
         </is>
       </c>
       <c r="E25" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A25,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A25,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F25" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B25,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B25,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7528,11 +7861,11 @@
         </is>
       </c>
       <c r="E26" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A26,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A26,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F26" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B26,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B26,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7558,11 +7891,11 @@
         </is>
       </c>
       <c r="E27" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A27,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A27,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F27" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B27,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B27,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7588,11 +7921,11 @@
         </is>
       </c>
       <c r="E28" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A28,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A28,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F28" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B28,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B28,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7618,11 +7951,11 @@
         </is>
       </c>
       <c r="E29" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A29,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A29,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F29" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B29,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B29,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7648,11 +7981,11 @@
         </is>
       </c>
       <c r="E30" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A30,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A30,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F30" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B30,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B30,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7678,11 +8011,11 @@
         </is>
       </c>
       <c r="E31" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A31,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A31,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F31" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B31,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B31,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7708,11 +8041,11 @@
         </is>
       </c>
       <c r="E32" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A32,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A32,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F32" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B32,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B32,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7738,11 +8071,11 @@
         </is>
       </c>
       <c r="E33" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A33,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A33,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F33" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B33,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B33,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7768,11 +8101,11 @@
         </is>
       </c>
       <c r="E34" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A34,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A34,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F34" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B34,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B34,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7798,11 +8131,11 @@
         </is>
       </c>
       <c r="E35" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A35,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A35,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F35" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B35,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B35,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7828,11 +8161,11 @@
         </is>
       </c>
       <c r="E36" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A36,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A36,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F36" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B36,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B36,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7858,11 +8191,11 @@
         </is>
       </c>
       <c r="E37" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A37,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A37,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F37" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B37,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B37,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7888,11 +8221,11 @@
         </is>
       </c>
       <c r="E38" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A38,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A38,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F38" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B38,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B38,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7918,11 +8251,11 @@
         </is>
       </c>
       <c r="E39" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A39,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A39,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F39" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B39,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B39,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7948,11 +8281,11 @@
         </is>
       </c>
       <c r="E40" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A40,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A40,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F40" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B40,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B40,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -7978,11 +8311,11 @@
         </is>
       </c>
       <c r="E41" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A41,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A41,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F41" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B41,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B41,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8008,11 +8341,11 @@
         </is>
       </c>
       <c r="E42" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A42,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A42,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F42" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B42,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B42,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8038,11 +8371,11 @@
         </is>
       </c>
       <c r="E43" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A43,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A43,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F43" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B43,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B43,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8068,11 +8401,11 @@
         </is>
       </c>
       <c r="E44" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A44,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A44,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F44" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B44,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B44,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8098,11 +8431,11 @@
         </is>
       </c>
       <c r="E45" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A45,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A45,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F45" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B45,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B45,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8128,11 +8461,11 @@
         </is>
       </c>
       <c r="E46" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A46,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A46,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F46" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B46,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B46,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8158,11 +8491,11 @@
         </is>
       </c>
       <c r="E47" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A47,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A47,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F47" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B47,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B47,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8188,11 +8521,11 @@
         </is>
       </c>
       <c r="E48" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A48,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A48,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F48" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B48,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B48,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8218,11 +8551,11 @@
         </is>
       </c>
       <c r="E49" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A49,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A49,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F49" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B49,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B49,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8248,11 +8581,11 @@
         </is>
       </c>
       <c r="E50" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A50,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A50,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F50" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B50,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B50,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8278,11 +8611,11 @@
         </is>
       </c>
       <c r="E51" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A51,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A51,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F51" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B51,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B51,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8308,11 +8641,11 @@
         </is>
       </c>
       <c r="E52" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A52,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A52,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F52" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B52,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B52,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8338,11 +8671,11 @@
         </is>
       </c>
       <c r="E53" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A53,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A53,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F53" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B53,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B53,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8368,11 +8701,11 @@
         </is>
       </c>
       <c r="E54" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A54,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A54,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F54" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B54,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B54,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8398,11 +8731,11 @@
         </is>
       </c>
       <c r="E55" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A55,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A55,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F55" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B55,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B55,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8428,11 +8761,11 @@
         </is>
       </c>
       <c r="E56" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A56,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A56,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F56" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B56,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B56,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8458,11 +8791,11 @@
         </is>
       </c>
       <c r="E57" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A57,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A57,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F57" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B57,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B57,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8488,11 +8821,11 @@
         </is>
       </c>
       <c r="E58" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A58,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A58,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F58" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B58,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B58,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8518,11 +8851,11 @@
         </is>
       </c>
       <c r="E59" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A59,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A59,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F59" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B59,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B59,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8548,11 +8881,11 @@
         </is>
       </c>
       <c r="E60" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A60,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A60,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F60" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B60,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B60,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8578,11 +8911,11 @@
         </is>
       </c>
       <c r="E61" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A61,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A61,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F61" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B61,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B61,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8608,11 +8941,11 @@
         </is>
       </c>
       <c r="E62" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A62,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A62,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F62" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B62,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B62,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8638,11 +8971,11 @@
         </is>
       </c>
       <c r="E63" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A63,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A63,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F63" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B63,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B63,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8668,11 +9001,11 @@
         </is>
       </c>
       <c r="E64" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A64,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A64,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F64" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B64,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B64,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8698,11 +9031,11 @@
         </is>
       </c>
       <c r="E65" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A65,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A65,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F65" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B65,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B65,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8728,11 +9061,11 @@
         </is>
       </c>
       <c r="E66" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A66,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A66,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F66" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B66,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B66,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8758,11 +9091,11 @@
         </is>
       </c>
       <c r="E67" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A67,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A67,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F67" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B67,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B67,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8788,11 +9121,11 @@
         </is>
       </c>
       <c r="E68" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A68,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A68,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F68" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B68,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B68,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8818,11 +9151,11 @@
         </is>
       </c>
       <c r="E69" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A69,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A69,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F69" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B69,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B69,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8848,11 +9181,11 @@
         </is>
       </c>
       <c r="E70" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A70,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A70,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F70" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B70,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B70,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8878,11 +9211,11 @@
         </is>
       </c>
       <c r="E71" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A71,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A71,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F71" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B71,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B71,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8908,11 +9241,11 @@
         </is>
       </c>
       <c r="E72" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A72,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A72,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F72" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B72,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B72,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8938,11 +9271,11 @@
         </is>
       </c>
       <c r="E73" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A73,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A73,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F73" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B73,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B73,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8968,11 +9301,11 @@
         </is>
       </c>
       <c r="E74" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A74,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A74,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F74" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B74,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B74,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -8998,11 +9331,11 @@
         </is>
       </c>
       <c r="E75" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A75,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A75,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F75" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B75,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B75,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9028,11 +9361,11 @@
         </is>
       </c>
       <c r="E76" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A76,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A76,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F76" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B76,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B76,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9058,11 +9391,11 @@
         </is>
       </c>
       <c r="E77" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A77,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A77,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F77" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B77,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B77,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9088,11 +9421,11 @@
         </is>
       </c>
       <c r="E78" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A78,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A78,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F78" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B78,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B78,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9118,11 +9451,11 @@
         </is>
       </c>
       <c r="E79" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A79,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A79,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F79" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B79,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B79,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9148,11 +9481,11 @@
         </is>
       </c>
       <c r="E80" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A80,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A80,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F80" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B80,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B80,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9178,11 +9511,11 @@
         </is>
       </c>
       <c r="E81" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A81,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A81,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F81" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B81,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B81,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9208,11 +9541,11 @@
         </is>
       </c>
       <c r="E82" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A82,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A82,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F82" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B82,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B82,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9238,11 +9571,11 @@
         </is>
       </c>
       <c r="E83" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A83,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A83,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F83" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B83,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B83,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9268,11 +9601,11 @@
         </is>
       </c>
       <c r="E84" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A84,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A84,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F84" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B84,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B84,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9298,11 +9631,11 @@
         </is>
       </c>
       <c r="E85" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A85,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A85,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F85" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B85,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B85,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9328,11 +9661,11 @@
         </is>
       </c>
       <c r="E86" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A86,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A86,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F86" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B86,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B86,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9358,11 +9691,11 @@
         </is>
       </c>
       <c r="E87" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A87,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A87,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F87" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B87,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B87,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9388,11 +9721,11 @@
         </is>
       </c>
       <c r="E88" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A88,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A88,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F88" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B88,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B88,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9418,11 +9751,11 @@
         </is>
       </c>
       <c r="E89" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A89,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A89,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F89" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B89,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B89,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9448,11 +9781,11 @@
         </is>
       </c>
       <c r="E90" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A90,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A90,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F90" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B90,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B90,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9478,11 +9811,11 @@
         </is>
       </c>
       <c r="E91" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A91,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A91,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F91" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B91,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B91,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9508,11 +9841,11 @@
         </is>
       </c>
       <c r="E92" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A92,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A92,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F92" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B92,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B92,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9538,11 +9871,11 @@
         </is>
       </c>
       <c r="E93" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A93,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A93,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F93" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B93,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B93,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9568,11 +9901,11 @@
         </is>
       </c>
       <c r="E94" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A94,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A94,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F94" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B94,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B94,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9598,11 +9931,11 @@
         </is>
       </c>
       <c r="E95" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A95,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A95,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F95" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B95,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B95,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9628,11 +9961,11 @@
         </is>
       </c>
       <c r="E96" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A96,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A96,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F96" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B96,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B96,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9658,11 +9991,11 @@
         </is>
       </c>
       <c r="E97" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A97,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A97,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F97" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B97,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B97,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9688,11 +10021,11 @@
         </is>
       </c>
       <c r="E98" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A98,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A98,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F98" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B98,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B98,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9718,11 +10051,11 @@
         </is>
       </c>
       <c r="E99" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A99,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A99,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F99" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B99,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B99,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9748,11 +10081,11 @@
         </is>
       </c>
       <c r="E100" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A100,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A100,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F100" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B100,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B100,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9778,11 +10111,11 @@
         </is>
       </c>
       <c r="E101" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A101,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A101,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F101" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B101,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B101,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9808,11 +10141,11 @@
         </is>
       </c>
       <c r="E102" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A102,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A102,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F102" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B102,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B102,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9838,11 +10171,11 @@
         </is>
       </c>
       <c r="E103" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A103,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A103,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F103" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B103,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B103,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9868,11 +10201,11 @@
         </is>
       </c>
       <c r="E104" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A104,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A104,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F104" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B104,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B104,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9898,11 +10231,11 @@
         </is>
       </c>
       <c r="E105" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A105,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A105,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F105" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B105,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B105,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9928,11 +10261,11 @@
         </is>
       </c>
       <c r="E106" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A106,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A106,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F106" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B106,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B106,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9958,11 +10291,11 @@
         </is>
       </c>
       <c r="E107" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A107,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A107,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F107" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B107,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B107,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -9988,11 +10321,11 @@
         </is>
       </c>
       <c r="E108" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A108,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A108,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F108" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B108,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B108,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10018,11 +10351,11 @@
         </is>
       </c>
       <c r="E109" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A109,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A109,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F109" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B109,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B109,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10048,11 +10381,11 @@
         </is>
       </c>
       <c r="E110" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A110,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A110,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F110" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B110,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B110,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10078,11 +10411,11 @@
         </is>
       </c>
       <c r="E111" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A111,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A111,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F111" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B111,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B111,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10108,11 +10441,11 @@
         </is>
       </c>
       <c r="E112" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A112,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A112,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F112" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B112,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B112,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10138,11 +10471,11 @@
         </is>
       </c>
       <c r="E113" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A113,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A113,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F113" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B113,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B113,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10168,11 +10501,11 @@
         </is>
       </c>
       <c r="E114" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A114,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A114,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F114" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B114,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B114,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10198,11 +10531,11 @@
         </is>
       </c>
       <c r="E115" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A115,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A115,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F115" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B115,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B115,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10228,11 +10561,11 @@
         </is>
       </c>
       <c r="E116" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A116,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A116,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F116" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B116,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B116,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10258,11 +10591,11 @@
         </is>
       </c>
       <c r="E117" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A117,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A117,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F117" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B117,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B117,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10288,11 +10621,11 @@
         </is>
       </c>
       <c r="E118" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A118,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A118,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F118" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B118,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B118,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10318,11 +10651,11 @@
         </is>
       </c>
       <c r="E119" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A119,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A119,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F119" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B119,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B119,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10348,11 +10681,11 @@
         </is>
       </c>
       <c r="E120" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A120,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A120,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F120" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B120,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B120,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10378,11 +10711,11 @@
         </is>
       </c>
       <c r="E121" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A121,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A121,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F121" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B121,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B121,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10408,11 +10741,11 @@
         </is>
       </c>
       <c r="E122" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A122,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A122,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F122" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B122,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B122,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10438,11 +10771,11 @@
         </is>
       </c>
       <c r="E123" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A123,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A123,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F123" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B123,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B123,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10468,11 +10801,11 @@
         </is>
       </c>
       <c r="E124" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A124,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A124,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F124" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B124,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B124,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10498,11 +10831,11 @@
         </is>
       </c>
       <c r="E125" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A125,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A125,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F125" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B125,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B125,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10528,11 +10861,11 @@
         </is>
       </c>
       <c r="E126" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A126,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A126,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F126" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B126,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B126,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10558,11 +10891,11 @@
         </is>
       </c>
       <c r="E127" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A127,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A127,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F127" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B127,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B127,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10588,11 +10921,11 @@
         </is>
       </c>
       <c r="E128" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A128,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A128,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F128" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B128,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B128,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10618,11 +10951,11 @@
         </is>
       </c>
       <c r="E129" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A129,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A129,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F129" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B129,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B129,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10648,11 +10981,11 @@
         </is>
       </c>
       <c r="E130" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A130,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A130,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F130" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B130,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B130,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10678,11 +11011,11 @@
         </is>
       </c>
       <c r="E131" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A131,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A131,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F131" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B131,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B131,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10708,11 +11041,11 @@
         </is>
       </c>
       <c r="E132" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A132,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A132,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F132" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B132,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B132,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10738,11 +11071,11 @@
         </is>
       </c>
       <c r="E133" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A133,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A133,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F133" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B133,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B133,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10768,11 +11101,11 @@
         </is>
       </c>
       <c r="E134" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A134,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A134,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F134" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B134,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B134,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10798,11 +11131,11 @@
         </is>
       </c>
       <c r="E135" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A135,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A135,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F135" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B135,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B135,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10828,11 +11161,11 @@
         </is>
       </c>
       <c r="E136" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A136,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A136,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F136" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B136,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B136,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10858,11 +11191,11 @@
         </is>
       </c>
       <c r="E137" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A137,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A137,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F137" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B137,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B137,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10888,11 +11221,11 @@
         </is>
       </c>
       <c r="E138" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A138,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A138,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F138" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B138,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B138,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10918,11 +11251,11 @@
         </is>
       </c>
       <c r="E139" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A139,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A139,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F139" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B139,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B139,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10948,11 +11281,11 @@
         </is>
       </c>
       <c r="E140" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A140,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A140,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F140" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B140,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B140,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -10978,11 +11311,11 @@
         </is>
       </c>
       <c r="E141" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A141,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A141,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F141" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B141,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B141,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11008,11 +11341,11 @@
         </is>
       </c>
       <c r="E142" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A142,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A142,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F142" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B142,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B142,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11038,11 +11371,11 @@
         </is>
       </c>
       <c r="E143" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A143,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A143,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F143" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B143,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B143,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11068,11 +11401,11 @@
         </is>
       </c>
       <c r="E144" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A144,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A144,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F144" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B144,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B144,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11098,11 +11431,11 @@
         </is>
       </c>
       <c r="E145" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A145,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A145,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F145" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B145,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B145,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11128,11 +11461,11 @@
         </is>
       </c>
       <c r="E146" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A146,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A146,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F146" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B146,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B146,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11158,11 +11491,11 @@
         </is>
       </c>
       <c r="E147" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A147,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A147,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F147" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B147,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B147,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11188,11 +11521,11 @@
         </is>
       </c>
       <c r="E148" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A148,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A148,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F148" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B148,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B148,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11218,11 +11551,11 @@
         </is>
       </c>
       <c r="E149" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A149,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A149,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F149" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B149,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B149,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11248,11 +11581,11 @@
         </is>
       </c>
       <c r="E150" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A150,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A150,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F150" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B150,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B150,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11278,11 +11611,11 @@
         </is>
       </c>
       <c r="E151" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A151,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A151,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F151" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B151,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B151,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11308,11 +11641,11 @@
         </is>
       </c>
       <c r="E152" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A152,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A152,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F152" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B152,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B152,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11338,11 +11671,11 @@
         </is>
       </c>
       <c r="E153" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A153,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A153,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F153" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B153,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B153,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11368,11 +11701,11 @@
         </is>
       </c>
       <c r="E154" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A154,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A154,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F154" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B154,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B154,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11398,11 +11731,11 @@
         </is>
       </c>
       <c r="E155" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A155,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A155,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F155" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B155,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B155,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11428,11 +11761,11 @@
         </is>
       </c>
       <c r="E156" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A156,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A156,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F156" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B156,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B156,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11458,11 +11791,11 @@
         </is>
       </c>
       <c r="E157" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A157,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A157,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F157" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B157,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B157,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11488,11 +11821,11 @@
         </is>
       </c>
       <c r="E158" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A158,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A158,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F158" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B158,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B158,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11518,11 +11851,11 @@
         </is>
       </c>
       <c r="E159" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A159,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A159,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F159" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B159,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B159,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11548,11 +11881,11 @@
         </is>
       </c>
       <c r="E160" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A160,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A160,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F160" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B160,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B160,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11578,11 +11911,11 @@
         </is>
       </c>
       <c r="E161" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A161,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A161,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F161" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B161,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B161,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11608,11 +11941,11 @@
         </is>
       </c>
       <c r="E162" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A162,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A162,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F162" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B162,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B162,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11638,11 +11971,11 @@
         </is>
       </c>
       <c r="E163" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A163,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A163,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F163" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B163,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B163,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11668,11 +12001,11 @@
         </is>
       </c>
       <c r="E164" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A164,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A164,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F164" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B164,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B164,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11698,11 +12031,11 @@
         </is>
       </c>
       <c r="E165" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A165,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A165,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F165" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B165,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B165,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11728,11 +12061,11 @@
         </is>
       </c>
       <c r="E166" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A166,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A166,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F166" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B166,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B166,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11758,11 +12091,11 @@
         </is>
       </c>
       <c r="E167" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A167,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A167,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F167" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B167,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B167,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11788,11 +12121,11 @@
         </is>
       </c>
       <c r="E168" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A168,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A168,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F168" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B168,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B168,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11818,11 +12151,11 @@
         </is>
       </c>
       <c r="E169" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A169,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A169,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F169" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B169,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B169,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11848,11 +12181,11 @@
         </is>
       </c>
       <c r="E170" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A170,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A170,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F170" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B170,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B170,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11878,11 +12211,11 @@
         </is>
       </c>
       <c r="E171" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A171,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A171,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F171" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B171,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B171,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11908,11 +12241,11 @@
         </is>
       </c>
       <c r="E172" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A172,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A172,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F172" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B172,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B172,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11938,11 +12271,11 @@
         </is>
       </c>
       <c r="E173" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A173,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A173,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F173" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B173,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B173,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11968,11 +12301,11 @@
         </is>
       </c>
       <c r="E174" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A174,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A174,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F174" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B174,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B174,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -11998,11 +12331,11 @@
         </is>
       </c>
       <c r="E175" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A175,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A175,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F175" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B175,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B175,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -12028,11 +12361,11 @@
         </is>
       </c>
       <c r="E176" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A176,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A176,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F176" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B176,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B176,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -12058,11 +12391,11 @@
         </is>
       </c>
       <c r="E177" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A177,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A177,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F177" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B177,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B177,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -12088,11 +12421,11 @@
         </is>
       </c>
       <c r="E178" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A178,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A178,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F178" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B178,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B178,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -12118,11 +12451,11 @@
         </is>
       </c>
       <c r="E179" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A179,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A179,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F179" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B179,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B179,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -12148,11 +12481,11 @@
         </is>
       </c>
       <c r="E180" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A180,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A180,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F180" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B180,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B180,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -12178,11 +12511,11 @@
         </is>
       </c>
       <c r="E181" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A181,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A181,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F181" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B181,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B181,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -12208,11 +12541,491 @@
         </is>
       </c>
       <c r="E182" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(A182,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A182,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
       <c r="F182" s="45">
-        <f>INDEX(Nodes!$B$2:$B$84,MATCH(B182,Nodes!$A$2:$A$84,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B182,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="45" t="inlineStr">
+        <is>
+          <t>willer</t>
+        </is>
+      </c>
+      <c r="B183" s="45" t="inlineStr">
+        <is>
+          <t>cathedral</t>
+        </is>
+      </c>
+      <c r="C183" s="45" t="inlineStr">
+        <is>
+          <t>Criou em jan/2023; sócio com Jorge Barbosa Dias</t>
+        </is>
+      </c>
+      <c r="D183" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E183" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A183,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F183" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B183,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="45" t="inlineStr">
+        <is>
+          <t>cathedral</t>
+        </is>
+      </c>
+      <c r="B184" s="45" t="inlineStr">
+        <is>
+          <t>bestbet</t>
+        </is>
+      </c>
+      <c r="C184" s="45" t="inlineStr">
+        <is>
+          <t>Única acionista da Rede Loto (nome fantasia Best Bet)</t>
+        </is>
+      </c>
+      <c r="D184" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E184" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A184,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F184" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B184,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="45" t="inlineStr">
+        <is>
+          <t>cathedral</t>
+        </is>
+      </c>
+      <c r="B185" s="45" t="inlineStr">
+        <is>
+          <t>alcazar</t>
+        </is>
+      </c>
+      <c r="C185" s="45" t="inlineStr">
+        <is>
+          <t>Mesmo dono, administrador e endereço no Funchal; auditor ouvido pela piauí vê possível financiamento</t>
+        </is>
+      </c>
+      <c r="D185" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E185" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A185,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F185" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B185,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="B186" s="45" t="inlineStr">
+        <is>
+          <t>bestbet</t>
+        </is>
+      </c>
+      <c r="C186" s="45" t="inlineStr">
+        <is>
+          <t>piauí/PF: possível sócio oculto, via acesso à conta da Alcazar; ele e Willer negam</t>
+        </is>
+      </c>
+      <c r="D186" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E186" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A186,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F186" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B186,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="45" t="inlineStr">
+        <is>
+          <t>loterj</t>
+        </is>
+      </c>
+      <c r="B187" s="45" t="inlineStr">
+        <is>
+          <t>bestbet</t>
+        </is>
+      </c>
+      <c r="C187" s="45" t="inlineStr">
+        <is>
+          <t>Licença de mai/2023</t>
+        </is>
+      </c>
+      <c r="D187" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E187" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A187,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F187" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B187,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="45" t="inlineStr">
+        <is>
+          <t>cancado</t>
+        </is>
+      </c>
+      <c r="B188" s="45" t="inlineStr">
+        <is>
+          <t>bestbet</t>
+        </is>
+      </c>
+      <c r="C188" s="45" t="inlineStr">
+        <is>
+          <t>Assinou a licença como presidente da Loterj</t>
+        </is>
+      </c>
+      <c r="D188" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E188" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A188,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F188" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B188,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="B189" s="45" t="inlineStr">
+        <is>
+          <t>cancado</t>
+        </is>
+      </c>
+      <c r="C189" s="45" t="inlineStr">
+        <is>
+          <t>Teria indicado à presidência da Loterj (Folha)</t>
+        </is>
+      </c>
+      <c r="D189" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E189" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A189,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F189" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B189,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="45" t="inlineStr">
+        <is>
+          <t>castro</t>
+        </is>
+      </c>
+      <c r="B190" s="45" t="inlineStr">
+        <is>
+          <t>loterj</t>
+        </is>
+      </c>
+      <c r="C190" s="45" t="inlineStr">
+        <is>
+          <t>Loteria do governo dele; contratos de 2023</t>
+        </is>
+      </c>
+      <c r="D190" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E190" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A190,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F190" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B190,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="45" t="inlineStr">
+        <is>
+          <t>cathedral</t>
+        </is>
+      </c>
+      <c r="B191" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="C191" s="45" t="inlineStr">
+        <is>
+          <t>PF: canhotos de voos Lisboa–Nice e Cascais–Nice–Paris (2025) em nome da empresa; a defesa diz que Willer pagou e que eram passeios entre famílias</t>
+        </is>
+      </c>
+      <c r="D191" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E191" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A191,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F191" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B191,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="45" t="inlineStr">
+        <is>
+          <t>willer</t>
+        </is>
+      </c>
+      <c r="B192" s="45" t="inlineStr">
+        <is>
+          <t>riopag</t>
+        </is>
+      </c>
+      <c r="C192" s="45" t="inlineStr">
+        <is>
+          <t>E-mail achado pela PF: se apresentou como sócio; antes negava, depois admitiu participação indireta (O Globo)</t>
+        </is>
+      </c>
+      <c r="D192" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E192" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A192,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F192" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B192,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="45" t="inlineStr">
+        <is>
+          <t>loterj</t>
+        </is>
+      </c>
+      <c r="B193" s="45" t="inlineStr">
+        <is>
+          <t>riopag</t>
+        </is>
+      </c>
+      <c r="C193" s="45" t="inlineStr">
+        <is>
+          <t>Contratou em 2023; o estado rescindiu e cobra ~R$ 4 mi, a empresa contesta</t>
+        </is>
+      </c>
+      <c r="D193" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E193" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A193,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F193" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B193,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="45" t="inlineStr">
+        <is>
+          <t>willer</t>
+        </is>
+      </c>
+      <c r="B194" s="45" t="inlineStr">
+        <is>
+          <t>hangar</t>
+        </is>
+      </c>
+      <c r="C194" s="45" t="inlineStr">
+        <is>
+          <t>Ocupados por duas empresas de aviação dele</t>
+        </is>
+      </c>
+      <c r="D194" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E194" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A194,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F194" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B194,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="45" t="inlineStr">
+        <is>
+          <t>pf</t>
+        </is>
+      </c>
+      <c r="B195" s="45" t="inlineStr">
+        <is>
+          <t>hangar</t>
+        </is>
+      </c>
+      <c r="C195" s="45" t="inlineStr">
+        <is>
+          <t>Busca em ago/2026: sala oculta, máquina de contar e malas vazias, sem dinheiro (Estadão); Willer nega uso irregular</t>
+        </is>
+      </c>
+      <c r="D195" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E195" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A195,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F195" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B195,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="45" t="inlineStr">
+        <is>
+          <t>pf</t>
+        </is>
+      </c>
+      <c r="B196" s="45" t="inlineStr">
+        <is>
+          <t>weverton</t>
+        </is>
+      </c>
+      <c r="C196" s="45" t="inlineStr">
+        <is>
+          <t>Operação Sem Desconto (04/08/2026), autorizada por Mendonça</t>
+        </is>
+      </c>
+      <c r="D196" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E196" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A196,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F196" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B196,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="45" t="inlineStr">
+        <is>
+          <t>willer</t>
+        </is>
+      </c>
+      <c r="B197" s="45" t="inlineStr">
+        <is>
+          <t>weverton</t>
+        </is>
+      </c>
+      <c r="C197" s="45" t="inlineStr">
+        <is>
+          <t>PF: a estrutura dele era “hub financeiro” do senador; a mulher do senador recebeu R$ 11 mi de empresas dele. Ambos negam</t>
+        </is>
+      </c>
+      <c r="D197" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E197" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A197,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F197" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B197,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="45" t="inlineStr">
+        <is>
+          <t>weverton</t>
+        </is>
+      </c>
+      <c r="B198" s="45" t="inlineStr">
+        <is>
+          <t>wt</t>
+        </is>
+      </c>
+      <c r="C198" s="45" t="inlineStr">
+        <is>
+          <t>PF: mora em casa de R$ 6 mi registrada na WT; Willer diz que é negócio regular da imobiliária</t>
+        </is>
+      </c>
+      <c r="D198" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E198" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A198,Nodes!$A$2:$A$91,0))</f>
+        <v/>
+      </c>
+      <c r="F198" s="45">
+        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B198,Nodes!$A$2:$A$91,0))</f>
         <v/>
       </c>
     </row>
@@ -12230,7 +13043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A16"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="110" customWidth="1" style="24" min="1" max="1"/>
@@ -12335,9 +13148,16 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>Checagem final (21/10/2026): 111 links testados (91 abrem; 19 bloqueiam robôs, como UOL, Intercept e Folha; 1 link da CNN quebrado foi trocado por Mais Goiás). Conferidas contra a fonte 22 matérias das conexões mais sensíveis. Corrigidos: Zettel foi o 2º doador de Jair, não o maior; o advogado morto em 2024 representava a WT, não Richarlison; a posse de Willer reconhecida pelo STJ não foi confirmada; Mendonça teve uma reunião reservada confirmada (14/03/2025), não duas; o voo de Marçal foi pago pela Prime You (R$ 1,17 mi). Respostas dos citados foram adicionadas (Flávio sobre o BRB e a emenda, Ciro, Faria, Marçal, Gaspar).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada a partir do UOL News (Dani Lima, 21/10). Entraram só itens com reportagem escrita: Best Bet/Cathedral (piauí), voos pagos pela Cathedral (Folha), Rio Pag (O Globo), sala no hangar (Estadão) e Operação Sem Desconto (Poder360, O Povo). Ficaram de fora, sem texto publicado: a festa no hangar em 2024 com Flávio e Valdemar, as tratativas da indicação de Nunes no rancho de Willer e a origem em loja de informática em Taguatinga. O comunicado de relatores da ONU sobre a Meta, no mesmo vídeo, não tem relação com o mapa.</t>
         </is>
       </c>
     </row>

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -971,7 +971,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="15" customHeight="1" s="25">
       <c r="A4" s="28" t="inlineStr">
         <is>
@@ -1080,23 +1079,6 @@
         <v/>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15"/>
-    <row r="16"/>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
-    <row r="24"/>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28" ht="15" customHeight="1" s="25">
       <c r="A28" s="35" t="inlineStr">
         <is>
@@ -4436,17 +4418,17 @@
       </c>
       <c r="G16" s="24" t="inlineStr">
         <is>
-          <t>santander.jpg</t>
+          <t>santander.png</t>
         </is>
       </c>
       <c r="H16" s="24" t="inlineStr">
         <is>
-          <t>Simplus Menegati · CC BY-SA 4.0</t>
+          <t>Interbrand · domínio público (logo simples, sem direito autoral)</t>
         </is>
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>https://commons.wikimedia.org/wiki/File:Agencia_Banco_Santander_de_Telemaco_Borba.jpg</t>
+          <t>https://commons.wikimedia.org/wiki/File:Banco_Santander_Logotipo.svg</t>
         </is>
       </c>
       <c r="J16" s="24" t="inlineStr"/>
@@ -4908,9 +4890,21 @@
         <f>COUNTIF(Edges!$A$2:$A$198,A30)+COUNTIF(Edges!$B$2:$B$198,A30)</f>
         <v/>
       </c>
-      <c r="G30" s="24" t="n"/>
-      <c r="H30" s="24" t="n"/>
-      <c r="I30" s="24" t="n"/>
+      <c r="G30" s="24" t="inlineStr">
+        <is>
+          <t>master.png</t>
+        </is>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
+        <is>
+          <t>Banco Master · domínio público (logo simples, sem direito autoral)</t>
+        </is>
+      </c>
+      <c r="I30" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Logotipo_do_Banco_Master.svg</t>
+        </is>
+      </c>
       <c r="J30" s="24" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1" s="25">
@@ -13155,7 +13149,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="24" t="inlineStr">
         <is>
           <t>22/10/2026: rodada a partir do UOL News (Dani Lima, 21/10). Entraram só itens com reportagem escrita: Best Bet/Cathedral (piauí), voos pagos pela Cathedral (Folha), Rio Pag (O Globo), sala no hangar (Estadão) e Operação Sem Desconto (Poder360, O Povo). Ficaram de fora, sem texto publicado: a festa no hangar em 2024 com Flávio e Valdemar, as tratativas da indicação de Nunes no rancho de Willer e a origem em loja de informática em Taguatinga. O comunicado de relatores da ONU sobre a Meta, no mesmo vídeo, não tem relação com o mapa.</t>
         </is>

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C26" s="37" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="D26" s="37" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C27" s="37" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="D27" s="37" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="C28" s="37" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="D28" s="37" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="C29" s="37" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="D29" s="37" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="C30" s="37" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="D30" s="37" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="C31" s="37" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="D31" s="37" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="C32" s="37" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="D32" s="37" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="C36" s="37" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="D36" s="37" t="inlineStr">
@@ -5387,7 +5387,7 @@
       </c>
       <c r="D45" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="E45" s="45" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="D46" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="E46" s="45" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="D47" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="E47" s="45" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="D48" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="E48" s="45" t="inlineStr">
@@ -5515,7 +5515,7 @@
       </c>
       <c r="D49" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E49" s="45" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="D50" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E50" s="45" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="D51" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E51" s="45" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="D52" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E52" s="45" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="D53" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="E53" s="45" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="D54" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="E54" s="45" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="D55" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="E55" s="45" t="inlineStr">
@@ -5796,7 +5796,7 @@
       </c>
       <c r="D56" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E56" s="45" t="inlineStr">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="D57" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="E57" s="45" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="D58" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="E58" s="45" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="D59" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="E59" s="45" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="D60" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="E60" s="45" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="D62" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E62" s="45" t="inlineStr">
@@ -6061,7 +6061,7 @@
       </c>
       <c r="D63" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E63" s="45" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="D64" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E64" s="45" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D65" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E65" s="45" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D66" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E66" s="45" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="D67" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Justiça e investigação</t>
         </is>
       </c>
       <c r="E67" s="45" t="inlineStr">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="D72" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E72" s="45" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="D88" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E88" s="45" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="D89" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E89" s="45" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="D91" s="45" t="inlineStr">
         <is>
-          <t>Poder e Justiça</t>
+          <t>Política e governo</t>
         </is>
       </c>
       <c r="E91" s="45" t="inlineStr">

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -1150,7 +1150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P91"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="24" min="1" max="1"/>
@@ -3548,12 +3548,24 @@
       </c>
       <c r="M32" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo).</t>
-        </is>
-      </c>
-      <c r="N32" s="24" t="n"/>
-      <c r="O32" s="24" t="n"/>
-      <c r="P32" s="24" t="n"/>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada.</t>
+        </is>
+      </c>
+      <c r="N32" s="24" t="inlineStr">
+        <is>
+          <t>mendonca.jpg</t>
+        </is>
+      </c>
+      <c r="O32" s="24" t="inlineStr">
+        <is>
+          <t>Luis Macedo/Câmara dos Deputados · CC BY 3.0</t>
+        </is>
+      </c>
+      <c r="P32" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Andr%C3%A9_Luiz_de_Almeida_Mendon%C3%A7a_(cropped).jpg</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="37" t="inlineStr">
@@ -3618,12 +3630,24 @@
       </c>
       <c r="M33" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo).</t>
-        </is>
-      </c>
-      <c r="N33" s="24" t="n"/>
-      <c r="O33" s="24" t="n"/>
-      <c r="P33" s="24" t="n"/>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada.</t>
+        </is>
+      </c>
+      <c r="N33" s="24" t="inlineStr">
+        <is>
+          <t>faria.jpg</t>
+        </is>
+      </c>
+      <c r="O33" s="24" t="inlineStr">
+        <is>
+          <t>Luis Macedo/Câmara dos Deputados · CC BY 3.0</t>
+        </is>
+      </c>
+      <c r="P33" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:F%C3%A1bio_Faria_(cropped).jpg</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="37" t="inlineStr">
@@ -3688,12 +3712,24 @@
       </c>
       <c r="M34" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo).</t>
-        </is>
-      </c>
-      <c r="N34" s="24" t="n"/>
-      <c r="O34" s="24" t="n"/>
-      <c r="P34" s="24" t="n"/>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada.</t>
+        </is>
+      </c>
+      <c r="N34" s="24" t="inlineStr">
+        <is>
+          <t>frias.jpg</t>
+        </is>
+      </c>
+      <c r="O34" s="24" t="inlineStr">
+        <is>
+          <t>Isac Nóbrega/PR · CC BY 2.0</t>
+        </is>
+      </c>
+      <c r="P34" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:M%C3%A1rio_Frias_em_2020.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="37" t="inlineStr">
@@ -3758,12 +3794,24 @@
       </c>
       <c r="M35" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo).</t>
-        </is>
-      </c>
-      <c r="N35" s="24" t="n"/>
-      <c r="O35" s="24" t="n"/>
-      <c r="P35" s="24" t="n"/>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada.</t>
+        </is>
+      </c>
+      <c r="N35" s="24" t="inlineStr">
+        <is>
+          <t>gaspar.jpg</t>
+        </is>
+      </c>
+      <c r="O35" s="24" t="inlineStr">
+        <is>
+          <t>Kayo Magalhães/Câmara dos Deputados · CC BY 3.0</t>
+        </is>
+      </c>
+      <c r="P35" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Alfredo_Gaspar_Deputado_Federal_(cropped).jpg</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="37" t="inlineStr">
@@ -3828,12 +3876,4009 @@
       </c>
       <c r="M36" s="37" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada UOL News (bets, Loterj, hangar, Weverton). Perfil novo.</t>
-        </is>
-      </c>
-      <c r="N36" s="24" t="n"/>
-      <c r="O36" s="24" t="n"/>
-      <c r="P36" s="24" t="n"/>
+          <t>22/10/2026: rodada UOL News (bets, Loterj, hangar, Weverton). Perfil novo. 22/10/2026: foto adicionada.</t>
+        </is>
+      </c>
+      <c r="N36" s="24" t="inlineStr">
+        <is>
+          <t>weverton.jpg</t>
+        </is>
+      </c>
+      <c r="O36" s="24" t="inlineStr">
+        <is>
+          <t>Rodrigo Viana/Senado Federal · CC BY 2.0</t>
+        </is>
+      </c>
+      <c r="P36" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Senadores_da_56%C2%AA_Legislatura_-_Weverton_Rocha_(32121443327).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="inlineStr">
+        <is>
+          <t>pf</t>
+        </is>
+      </c>
+      <c r="B37" s="24" t="inlineStr">
+        <is>
+          <t>Polícia Federal</t>
+        </is>
+      </c>
+      <c r="C37" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>Polícia judiciária da União. Conduz as duas frentes centrais do mapa: a Operação Compliance Zero (Banco Master; prendeu Daniel Vorcaro em 17/11/2025 e teve várias fases em 2026) e a Operação Sem Desconto (descontos ilegais em aposentadorias do INSS; deflagrada com a CGU em abr/2025, com nova fase em 04/08/2026 contra Willer Tomaz e familiares de Weverton Rocha). Em out/2026 enviou ao STF um segundo inquérito sobre Flávio Bolsonaro, por suspeita de lavagem ligada a Willer.</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="inlineStr">
+        <is>
+          <t>Sede em Brasília (DF); atuação nacional</t>
+        </is>
+      </c>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" s="24" t="inlineStr">
+        <is>
+          <t>Em 08/09/2026 o ministro André Mendonça afastou o diretor-geral Andrei Rodrigues e o diretor de Inteligência, sem ouvir a PGR; a AGU contestou a decisão.</t>
+        </is>
+      </c>
+      <c r="H37" s="24" t="inlineStr">
+        <is>
+          <t>Órgão público</t>
+        </is>
+      </c>
+      <c r="I37" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J37" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K37" s="24" t="inlineStr">
+        <is>
+          <t>Entenda a operação que prendeu Vorcaro (cnnbrasil.com.br) https://www.cnnbrasil.com.br/economia/mercado/entenda-operacao-que-prendeu-daniel-vorcaro-dono-do-banco-master/ | Nova fase da Sem Desconto mira Weverton e Willer (congressoemfoco.com.br) https://www.congressoemfoco.com.br/noticia/120986/fraudes-no-inss-pf-mira-weverton-rocha-e-advogado-willer-tomaz | Afastamento do diretor-geral da PF (cnnbrasil.com.br) https://www.cnnbrasil.com.br/blogs/teo-cury/politica/mendonca-ordenou-afastamento-de-diretor-geral-da-pf-sem-ouvir-pgr/ | Segundo inquérito contra Flávio no STF (oliberal.com) https://www.oliberal.com/politica/flavio-e-investigado-em-2-inquerito-no-stf-para-apurar-suspeitas-de-lavagem-com-advogado-1.1183991</t>
+        </is>
+      </c>
+      <c r="L37" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M37" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N37" s="24" t="inlineStr">
+        <is>
+          <t>pf.jpg</t>
+        </is>
+      </c>
+      <c r="O37" s="24" t="inlineStr">
+        <is>
+          <t>Agência Senado · CC BY 2.0</t>
+        </is>
+      </c>
+      <c r="P37" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Sede_da_Pol%C3%ADcia_Federal_(52830107256).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>angra</t>
+        </is>
+      </c>
+      <c r="B38" s="24" t="inlineStr">
+        <is>
+          <t>Mansão em Angra dos Reis</t>
+        </is>
+      </c>
+      <c r="C38" s="24" t="inlineStr">
+        <is>
+          <t>Casas e ativos</t>
+        </is>
+      </c>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>Mansão na Ilha Comprida, em Angra dos Reis, avaliada em cerca de R$ 10 mi. Foi comprada em 2020 pela empresa de Richarlison e de seu empresário; em 2022 a posse foi transferida na Justiça à WT Administração de Imóveis, de Willer Tomaz, que diz ter pago pendências da antiga dona (M Locadora) por sub-rogação. O processo terminou em 2025, favorável a Willer. A Prime You, de que Vorcaro era sócio, administrou o imóvel, e Flávio fez lá o aniversário da filha.</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="inlineStr">
+        <is>
+          <t>Ilha Comprida, Angra dos Reis (RJ)</t>
+        </is>
+      </c>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="24" t="inlineStr">
+        <is>
+          <t>Disputa civil encerrada em favor da WT. Em out/2026 Richarlison pediu à PF que investigue o caso; não há inquérito específico sobre o imóvel nas fontes.</t>
+        </is>
+      </c>
+      <c r="H38" s="24" t="inlineStr">
+        <is>
+          <t>Bem citado</t>
+        </is>
+      </c>
+      <c r="I38" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J38" s="24" t="inlineStr">
+        <is>
+          <t>Flávio diz não ter relação com o imóvel e chamou a associação de "factualmente infundada e eleitoralmente motivada". Willer chama os antigos ocupantes de "invasores".</t>
+        </is>
+      </c>
+      <c r="K38" s="24" t="inlineStr">
+        <is>
+          <t>Richarlison disputa imóvel com amigo de Flávio (poder360.com.br) https://www.poder360.com.br/justica/richarlison-briga-na-justica-com-amigo-de-flavio-bolsonaro/ | Richarlison pede apuração à PF (sbtnews.sbt.com.br) https://sbtnews.sbt.com.br/noticia/brasil/richarlison-apuracao-pf-disputa-ilha-flavio-bolsonaro | Empresas e imóveis em nome de Lídia Mazelli (iclnoticias.com.br) https://iclnoticias.com.br/domestica-preside-empresas-fraude-flavio/</t>
+        </is>
+      </c>
+      <c r="L38" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M38" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="inlineStr">
+        <is>
+          <t>master</t>
+        </is>
+      </c>
+      <c r="B39" s="24" t="inlineStr">
+        <is>
+          <t>Banco Master</t>
+        </is>
+      </c>
+      <c r="C39" s="24" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>Banco de Daniel Vorcaro. Cresceu vendendo CDBs com rendimento acima do mercado, apoiados na garantia do FGC. O Banco Central decretou a liquidação extrajudicial em 18/11/2025, no dia da Operação Compliance Zero (Vorcaro foi preso na noite anterior, em Guarulhos), que apura gestão fraudulenta e venda de carteiras de crédito sem lastro. O BRB, banco público do DF, pôs cerca de R$ 12 bi no Master comprando carteiras que a investigação aponta como fraudulentas.</t>
+        </is>
+      </c>
+      <c r="E39" s="24" t="inlineStr">
+        <is>
+          <t>São Paulo (SP)</t>
+        </is>
+      </c>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G39" s="24" t="inlineStr">
+        <is>
+          <t>Em liquidação extrajudicial pelo BC desde nov/2025. Ex-dirigentes investigados no STF (relator André Mendonça); Vorcaro preso.</t>
+        </is>
+      </c>
+      <c r="H39" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I39" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J39" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K39" s="24" t="inlineStr">
+        <is>
+          <t>Banco Master tem liquidação decretada (bloomberglinea.com.br) https://www.bloomberglinea.com.br/negocios/banco-master-tem-liquidacao-decretada-e-daniel-vorcaro-e-preso-pela-policia-federal/ | Entenda a operação que prendeu Vorcaro (cnnbrasil.com.br) https://www.cnnbrasil.com.br/economia/mercado/entenda-operacao-que-prendeu-daniel-vorcaro-dono-do-banco-master/ | PF prende ex-presidente do BRB (timesbrasil.com.br) https://timesbrasil.com.br/brasil/operacoes-da-pf/pf-prende-paulo-henrique-costa-ex-presidente-do-brb-em-nova-fase-da-compliance-zero/</t>
+        </is>
+      </c>
+      <c r="L39" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M39" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N39" s="24" t="inlineStr">
+        <is>
+          <t>master.png</t>
+        </is>
+      </c>
+      <c r="O39" s="24" t="inlineStr">
+        <is>
+          <t>Banco Master · domínio público (logo simples, sem direito autoral)</t>
+        </is>
+      </c>
+      <c r="P39" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Logotipo_do_Banco_Master.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>coaf</t>
+        </is>
+      </c>
+      <c r="B40" s="24" t="inlineStr">
+        <is>
+          <t>Caso rachadinha / COAF</t>
+        </is>
+      </c>
+      <c r="C40" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>Investigação do MP-RJ sobre devolução de salários ("rachadinha") no gabinete de Flávio na Alerj. Começou com relatório do Coaf de 2018 que apontou R$ 1,2 mi em movimentações atípicas de Fabrício Queiroz. Em nov/2020 Flávio foi denunciado por peculato, lavagem e organização criminosa (desvio estimado em cerca de R$ 6 mi). O STJ anulou quebras de sigilo em fev/2021, e em 30/11/2021 a Segunda Turma do STF anulou quatro relatórios do Coaf (3 a 1, com voto de Nunes Marques).</t>
+        </is>
+      </c>
+      <c r="E40" s="24" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (RJ)</t>
+        </is>
+      </c>
+      <c r="F40" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G40" s="24" t="inlineStr">
+        <is>
+          <t>Com as anulações, a denúncia original ficou sem efeito e o caso voltou praticamente à estaca zero. Flávio sempre negou irregularidades.</t>
+        </is>
+      </c>
+      <c r="H40" s="24" t="inlineStr">
+        <is>
+          <t>Caso</t>
+        </is>
+      </c>
+      <c r="I40" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J40" s="24" t="inlineStr">
+        <is>
+          <t>O primeiro relatório do Coaf, sobre Queiroz, foi mantido; os anulados são os posteriores.</t>
+        </is>
+      </c>
+      <c r="K40" s="24" t="inlineStr">
+        <is>
+          <t>STF anula 4 relatórios do Coaf (poder360.com.br) https://www.poder360.com.br/justica/stf-anula-4-relatorios-do-coaf-que-miravam-flavio-no-caso-das-rachadinhas/ | Segunda Turma anula provas contra Flávio (correiobraziliense.com.br) https://www.correiobraziliense.com.br/politica/2021/11/4967209-segunda-turma-anula-provas-contra-flavio-bolsonaro-no-inquerito-das-rachadinhas.html</t>
+        </is>
+      </c>
+      <c r="L40" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M40" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="inlineStr">
+        <is>
+          <t>jato</t>
+        </is>
+      </c>
+      <c r="B41" s="24" t="inlineStr">
+        <is>
+          <t>Jato (3 cotistas)</t>
+        </is>
+      </c>
+      <c r="C41" s="24" t="inlineStr">
+        <is>
+          <t>Casas e ativos</t>
+        </is>
+      </c>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>Embraer Legacy 650, prefixo PP-NLR, dividido em três cotas: Alcazar Holdings (de Willer Tomaz), Prime You (de que Vorcaro era sócio) e Laerte Cosentino. Flávio voou nele com Willer em jan/2025, entre Brasília e a Flórida, segundo a piauí. Segundo O Globo, Alexandre de Moraes e a esposa também desembarcaram desse jato em ago/2025.</t>
+        </is>
+      </c>
+      <c r="E41" s="24" t="inlineStr">
+        <is>
+          <t>Base no Brasil (DF/SP)</t>
+        </is>
+      </c>
+      <c r="F41" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G41" s="24" t="inlineStr">
+        <is>
+          <t>O jato aparece em inquéritos da PF sobre Willer e Flávio; não há processo sobre a aeronave em si.</t>
+        </is>
+      </c>
+      <c r="H41" s="24" t="inlineStr">
+        <is>
+          <t>Bem citado</t>
+        </is>
+      </c>
+      <c r="I41" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J41" s="24" t="inlineStr">
+        <is>
+          <t>As fontes divergem sobre o registro: uma cita a Fraction 024 Administração de Bem Próprio, outra a Prime Aviation. Flávio diz que voou de carona, por amizade; Willer diz que não sabia que a Prime You era de Vorcaro.</t>
+        </is>
+      </c>
+      <c r="K41" s="24" t="inlineStr">
+        <is>
+          <t>Flávio era usuário master de conta de offshore sócia do jato (maisgoias.com.br) https://www.maisgoias.com.br/brasil/flavio-bolsonaro-era-usuario-master-de-conta-de-offshore-socia-do-jato-usado-por-vorcaro/ | Moraes flagrado desembarcando do PP-NLR (diariodepernambuco.com.br) https://www.diariodepernambuco.com.br/politica/2026/09/11724483-alexandre-de-moraes-foi-flagrado-desembarcando-de-jatinho-de-vorcaro.html</t>
+        </is>
+      </c>
+      <c r="L41" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M41" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="inlineStr">
+        <is>
+          <t>primeu</t>
+        </is>
+      </c>
+      <c r="B42" s="24" t="inlineStr">
+        <is>
+          <t>Prime U</t>
+        </is>
+      </c>
+      <c r="C42" s="24" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="D42" s="24" t="inlineStr">
+        <is>
+          <t>Prime You: empresa de compartilhamento e gestão de bens de alto padrão (cotas de aviões, barcos, casas e carros). Vorcaro foi sócio até set/2025, quando a participação passou a um fundo. Administra mansões, um hotel em Campos do Jordão e jatos; era cotista do jato usado por Flávio e administrou a mansão de Angra. Segundo o Valor, pagou em 2025 um voo de R$ 1,17 mi usado por Pablo Marçal.</t>
+        </is>
+      </c>
+      <c r="E42" s="24" t="inlineStr">
+        <is>
+          <t>São Paulo (SP)</t>
+        </is>
+      </c>
+      <c r="F42" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G42" s="24" t="inlineStr">
+        <is>
+          <t>Sem acusação formal contra a empresa nas fontes.</t>
+        </is>
+      </c>
+      <c r="H42" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I42" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J42" s="24" t="inlineStr">
+        <is>
+          <t>A empresa diz que administrar um bem "não implica necessariamente propriedade direta" de Vorcaro.</t>
+        </is>
+      </c>
+      <c r="K42" s="24" t="inlineStr">
+        <is>
+          <t>Mansões, hotel e jatos administrados pela Prime You (jornalgrandebahia.com.br) https://jornalgrandebahia.com.br/2026/03/ex-banqueiro-daniel-vorcaro-tem-mansoes-hotel-de-luxo-e-jatos-administrados-pela-prime-you-empresa-da-qual-foi-socio/ | Empresa de Vorcaro pagou voo de Marçal (gp1.com.br) https://www.gp1.com.br/brasil/noticia/2026/10/2/empresa-ligada-a-daniel-vorcaro-pagou-voo-de-r-117-milhao-usado-por-pablo-marcal-633016.html</t>
+        </is>
+      </c>
+      <c r="L42" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M42" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="inlineStr">
+        <is>
+          <t>alcazar</t>
+        </is>
+      </c>
+      <c r="B43" s="24" t="inlineStr">
+        <is>
+          <t>Alcazar Holdings</t>
+        </is>
+      </c>
+      <c r="C43" s="24" t="inlineStr">
+        <is>
+          <t>Willer Tomaz e sua rede</t>
+        </is>
+      </c>
+      <c r="D43" s="24" t="inlineStr">
+        <is>
+          <t>Offshore registrada na Ilha da Madeira (Portugal) em 2023, que tem Willer Tomaz como único sócio. É cotista do jato PP-NLR e tinha conta no Santander em que, segundo a PF, Flávio aparecia como "usuário master"; a conta teria movimentado cerca de R$ 130 mi entre mar e mai/2025. Divide dono, administrador e endereço no Funchal com a Cathedral Holdings, dona da Best Bet.</t>
+        </is>
+      </c>
+      <c r="E43" s="24" t="inlineStr">
+        <is>
+          <t>Funchal, Ilha da Madeira (Portugal)</t>
+        </is>
+      </c>
+      <c r="F43" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G43" s="24" t="inlineStr">
+        <is>
+          <t>Citada no inquérito da PF enviado ao STF em out/2026 (relator Alexandre de Moraes) sobre suspeita de lavagem envolvendo Flávio e Willer.</t>
+        </is>
+      </c>
+      <c r="H43" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I43" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J43" s="24" t="inlineStr">
+        <is>
+          <t>Willer atribui o vínculo de Flávio à conta a um erro cadastral do Santander, já corrigido. Flávio nega ter tido conta com Willer.</t>
+        </is>
+      </c>
+      <c r="K43" s="24" t="inlineStr">
+        <is>
+          <t>Flávio era usuário master de conta de offshore (maisgoias.com.br) https://www.maisgoias.com.br/brasil/flavio-bolsonaro-era-usuario-master-de-conta-de-offshore-socia-do-jato-usado-por-vorcaro/ | Offshore ligada a Flávio e o mercado de bets (jornalopcao.com.br) https://www.jornalopcao.com.br/ultimas-noticias/offshore-ligada-a-flavio-bolsonaro-reune-conexoes-com-o-mercado-de-bets-879306/ | Segundo inquérito contra Flávio no STF (oliberal.com) https://www.oliberal.com/politica/flavio-e-investigado-em-2-inquerito-no-stf-para-apurar-suspeitas-de-lavagem-com-advogado-1.1183991</t>
+        </is>
+      </c>
+      <c r="L43" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M43" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="inlineStr">
+        <is>
+          <t>wt</t>
+        </is>
+      </c>
+      <c r="B44" s="24" t="inlineStr">
+        <is>
+          <t>WT (e outras 13 empresas)</t>
+        </is>
+      </c>
+      <c r="C44" s="24" t="inlineStr">
+        <is>
+          <t>Willer Tomaz e sua rede</t>
+        </is>
+      </c>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>WT Administração de Imóveis e Bens, empresa de Willer Tomaz. Ficou com a mansão de Angra e comprou de Fabiano Zettel um apartamento em SP. É uma de cerca de 14 empresas ligadas a Willer (Jet Line, Ícaro Aviation, Friponor, RioPag/Capital Pretium, Alcazar etc.) que tiveram Lídia Mazelli como diretora; a WT até jul/2024. A PF diz que Weverton Rocha mora numa casa de R$ 6 mi registrada na WT.</t>
+        </is>
+      </c>
+      <c r="E44" s="24" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F44" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G44" s="24" t="inlineStr">
+        <is>
+          <t>Citada na Operação Sem Desconto (ago/2026). Willer diz que os negócios da imobiliária são regulares.</t>
+        </is>
+      </c>
+      <c r="H44" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I44" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J44" s="24" t="inlineStr">
+        <is>
+          <t>A reportagem do ICL fala em 14 empresas, mas nomeia 13.</t>
+        </is>
+      </c>
+      <c r="K44" s="24" t="inlineStr">
+        <is>
+          <t>Doméstica preside no papel empresas de Willer (iclnoticias.com.br) https://iclnoticias.com.br/domestica-preside-empresas-fraude-flavio/ | Apartamento usado por Flávio foi vendido à WT (diariodocomercio.com.br) https://diariodocomercio.com.br/politica/flavio-bolsonaro-apartamento-pf/ | Nova fase da Sem Desconto (congressoemfoco.com.br) https://www.congressoemfoco.com.br/noticia/120986/fraudes-no-inss-pf-mira-weverton-rocha-e-advogado-willer-tomaz</t>
+        </is>
+      </c>
+      <c r="L44" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M44" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="inlineStr">
+        <is>
+          <t>iter</t>
+        </is>
+      </c>
+      <c r="B45" s="24" t="inlineStr">
+        <is>
+          <t>Instituto ITER</t>
+        </is>
+      </c>
+      <c r="C45" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>Instituto de ensino jurídico em São Paulo de que André Mendonça era sócio. Recebeu ao menos 52 contratos sem licitação de prefeituras, estados e tribunais (R$ 8,2 mi em dois anos, segundo a Revista Fórum), entre eles o governo de SP (R$ 1,6 mi), a Prefeitura de SP (R$ 380 mil) e o governo do RJ (R$ 518 mil). Em jan/2026 recebeu R$ 5,2 mi de empresa de um ex-parceiro de negócios de Vorcaro. Mendonça recebeu Vorcaro na sede do instituto em 14/03/2025.</t>
+        </is>
+      </c>
+      <c r="E45" s="24" t="inlineStr">
+        <is>
+          <t>São Paulo (SP)</t>
+        </is>
+      </c>
+      <c r="F45" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G45" s="24" t="inlineStr">
+        <is>
+          <t>Alvo de representações de parlamentares do PSOL ao TCM-SP, ao TCE-SP e ao MP-SP (set/2026). Mendonça anunciou que deixaria a sociedade.</t>
+        </is>
+      </c>
+      <c r="H45" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I45" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J45" s="24" t="inlineStr">
+        <is>
+          <t>Os levantamentos de contratos (52 e R$ 8,2 mi; 55 e R$ 10,8 mi) são recortes diferentes e não se somam.</t>
+        </is>
+      </c>
+      <c r="K45" s="24" t="inlineStr">
+        <is>
+          <t>Instituto de Mendonça é alvo de representações (apublica.org) https://apublica.org/nota/instituto-de-andre-mendonca-e-alvo-de-representacoes-para-investigar-irregularidades/ | Ex-parceiro de Vorcaro pôs R$ 5 mi no instituto (noticias.uol.com.br) https://noticias.uol.com.br/ultimas-noticias/redacao/2026/09/17/ex-parceiro-de-vorcaro-pos-r-5-milhoes-em-instituto-de-mendonca.htm | Mendonça diz que deixará sociedade (dgabc.com.br) https://www.dgabc.com.br/Noticia/4344940/mendonca-diz-que-deixara-sociedade-no-instituto-iter</t>
+        </is>
+      </c>
+      <c r="L45" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M45" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="24" t="inlineStr">
+        <is>
+          <t>triplex</t>
+        </is>
+      </c>
+      <c r="B46" s="24" t="inlineStr">
+        <is>
+          <t>Triplex de Vorcaro</t>
+        </is>
+      </c>
+      <c r="C46" s="24" t="inlineStr">
+        <is>
+          <t>Casas e ativos</t>
+        </is>
+      </c>
+      <c r="D46" s="24" t="inlineStr">
+        <is>
+          <t>Apartamento de Daniel Vorcaro no Itaim Bibi, em São Paulo. Segundo a piauí, com base em relatos de promoters e mensagens, recebia às quartas e quintas festas fechadas com garotas de programa. A reportagem cita entre os frequentadores o ministro Nunes Marques e o filho Kevin, e o ex-ministro Fábio Faria.</t>
+        </is>
+      </c>
+      <c r="E46" s="24" t="inlineStr">
+        <is>
+          <t>Itaim Bibi, São Paulo (SP)</t>
+        </is>
+      </c>
+      <c r="F46" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G46" s="24" t="inlineStr">
+        <is>
+          <t>Não há processo sobre o imóvel nas fontes. As festas aparecem em mensagens obtidas pela PF e em reportagens.</t>
+        </is>
+      </c>
+      <c r="H46" s="24" t="inlineStr">
+        <is>
+          <t>Bem citado</t>
+        </is>
+      </c>
+      <c r="I46" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J46" s="24" t="inlineStr">
+        <is>
+          <t>O gabinete de Nunes Marques nega contato com Vorcaro. Os relatos não foram verificados de forma independente pela imprensa que os reproduziu.</t>
+        </is>
+      </c>
+      <c r="K46" s="24" t="inlineStr">
+        <is>
+          <t>A semana de festas fechadas de Vorcaro (diariodepernambuco.com.br) https://www.diariodepernambuco.com.br/politica/2026/10/11725610-terca-no-bar-quarta-e-quinta-no-triplex-a-semana-de-festas-fechadas-de-vorcaro.html | Vorcaro coordenou noitada para Nunes Marques (diariodepernambuco.com.br) https://www.diariodepernambuco.com.br/politica/2026/10/11726793-vorcaro-coordenou-noitada-em-triplex-para-ministro-kassio-nunes-marques.html</t>
+        </is>
+      </c>
+      <c r="L46" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M46" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="inlineStr">
+        <is>
+          <t>tarcisio</t>
+        </is>
+      </c>
+      <c r="B47" s="24" t="inlineStr">
+        <is>
+          <t>Tarcísio de Freitas</t>
+        </is>
+      </c>
+      <c r="C47" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>Governador de São Paulo (Republicanos) desde 2023 e ex-ministro da Infraestrutura de Jair Bolsonaro. Na campanha de 2022 recebeu R$ 2 mi de Fabiano Zettel, cunhado de Vorcaro, a maior doação de pessoa física. O governo dele contratou o Instituto ITER, de Mendonça, sem licitação (R$ 1,6 mi), e ele financiou 24% da campanha do deputado Cezinha de Madureira.</t>
+        </is>
+      </c>
+      <c r="E47" s="24" t="inlineStr">
+        <is>
+          <t>São Paulo (SP)</t>
+        </is>
+      </c>
+      <c r="F47" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G47" s="24" t="inlineStr">
+        <is>
+          <t>Não há investigação contra ele nas fontes.</t>
+        </is>
+      </c>
+      <c r="H47" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I47" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J47" s="24" t="inlineStr">
+        <is>
+          <t>O governo de SP diz que a campanha seguiu a lei, teve mais de 600 doadores e contas aprovadas, e que Tarcísio não tem vínculo com Zettel.</t>
+        </is>
+      </c>
+      <c r="K47" s="24" t="inlineStr">
+        <is>
+          <t>Alvo da PF doou R$ 5 mi a Bolsonaro e Tarcísio (cnnbrasil.com.br) https://www.cnnbrasil.com.br/politica/alvo-da-pf-doou-r-5-mi-para-campanhas-de-bolsonaro-e-tarcisio-em-2022/ | Contratos do ITER com governos (apublica.org) https://apublica.org/nota/instituto-de-andre-mendonca-e-alvo-de-representacoes-para-investigar-irregularidades/ | Financiamento da campanha de Cezinha (iclnoticias.com.br) https://iclnoticias.com.br/tarcisio-campanha-deputado-mendonca-vorcaro/</t>
+        </is>
+      </c>
+      <c r="L47" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M47" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N47" s="24" t="inlineStr">
+        <is>
+          <t>tarcisio.jpg</t>
+        </is>
+      </c>
+      <c r="O47" s="24" t="inlineStr">
+        <is>
+          <t>Ciete Silvério/Governo do Estado de SP · CC BY 2.0</t>
+        </is>
+      </c>
+      <c r="P47" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Governador_do_Estado_de_S%C3%A3o_Paulo,_Tarc%C3%ADsio_de_Freitas_-_Foto_Oficial.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="24" t="inlineStr">
+        <is>
+          <t>castro</t>
+        </is>
+      </c>
+      <c r="B48" s="24" t="inlineStr">
+        <is>
+          <t>Cláudio Castro</t>
+        </is>
+      </c>
+      <c r="C48" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>Ex-governador do Rio de Janeiro (PL), no cargo de 2021 a mar/2026. O governo dele contratou o ITER, de Mendonça (R$ 518 mil), e nomeou Hazenclever Cançado para a Loterj, que licenciou a Best Bet e contratou a RioPag. Renunciou em 23/03/2026 e foi tornado inelegível pelo TSE no dia seguinte. Em mai/2026 desistiu de concorrer ao Senado, depois de ser citado em fase da Operação Compliance Zero sobre aportes do Rio Previdência no Master.</t>
+        </is>
+      </c>
+      <c r="E48" s="24" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (RJ)</t>
+        </is>
+      </c>
+      <c r="F48" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G48" s="24" t="inlineStr">
+        <is>
+          <t>Inelegível até 2030 por abuso de poder político e econômico na eleição de 2022 (TSE, 5 a 2, 24/03/2026); disse que recorreria. Mendonça escreveu que há indícios, "em tese", de vínculo próximo dele com Vorcaro.</t>
+        </is>
+      </c>
+      <c r="H48" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I48" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J48" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K48" s="24" t="inlineStr">
+        <is>
+          <t>TSE torna Castro inelegível (jovempan.com.br) https://jovempan.com.br/politica/tse-forma-maioria-para-tornar-castro-inelegivel-por-8-anos/ | Castro desiste do Senado após operações (oantagonista.com.br) https://oantagonista.com.br/brasil/claudio-castro-comunica-ao-pl-desistencia-de-candidatura-ao-senado-apos-operacoes/ | Mendonça votou a favor de Castro 4 vezes (iclnoticias.com.br) https://iclnoticias.com.br/mendonca-votou-a-favor-de-castro-4-vezes/</t>
+        </is>
+      </c>
+      <c r="L48" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M48" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N48" s="24" t="inlineStr">
+        <is>
+          <t>castro.jpg</t>
+        </is>
+      </c>
+      <c r="O48" s="24" t="inlineStr">
+        <is>
+          <t>Alan Santos/PR · CC BY 2.0</t>
+        </is>
+      </c>
+      <c r="P48" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Cl%C3%A1udio_Castro,_governador_do_Rio_de_Janeiro.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="inlineStr">
+        <is>
+          <t>moraes</t>
+        </is>
+      </c>
+      <c r="B49" s="24" t="inlineStr">
+        <is>
+          <t>Alexandre de Moraes</t>
+        </is>
+      </c>
+      <c r="C49" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>Ministro do STF desde 2017 e ex-presidente do TSE. É relator do segundo inquérito da PF contra Flávio Bolsonaro, sobre suspeita de lavagem com Willer Tomaz (out/2026). Segundo O Globo, ele e a esposa, a advogada Viviane Barci, desembarcaram em ago/2025 do jato PP-NLR, o mesmo usado por Flávio. O escritório dela tinha contratos com o Banco Master. A PF diz que Fábio Faria intermediou contatos entre Vorcaro e Moraes.</t>
+        </is>
+      </c>
+      <c r="E49" s="24" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F49" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G49" s="24" t="inlineStr">
+        <is>
+          <t>Não é investigado nas fontes. O PGR Paulo Gonet sustenta que Mendonça o investigou antes de aval do plenário.</t>
+        </is>
+      </c>
+      <c r="H49" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I49" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J49" s="24" t="inlineStr">
+        <is>
+          <t>Moraes tinha dito que nunca viajou em aviões de Vorcaro e nega que tenha existido o acordo de pagamento em cotas de jato citado pela PF.</t>
+        </is>
+      </c>
+      <c r="K49" s="24" t="inlineStr">
+        <is>
+          <t>Moraes flagrado desembarcando de jatinho de Vorcaro (diariodepernambuco.com.br) https://www.diariodepernambuco.com.br/politica/2026/09/11724483-alexandre-de-moraes-foi-flagrado-desembarcando-de-jatinho-de-vorcaro.html | Segundo inquérito contra Flávio no STF (oliberal.com) https://www.oliberal.com/politica/flavio-e-investigado-em-2-inquerito-no-stf-para-apurar-suspeitas-de-lavagem-com-advogado-1.1183991 | Gonet diz que Mendonça investigou Moraes (iclnoticias.com.br) https://iclnoticias.com.br/gonet-diz-que-mendonca-investigou-moraes/</t>
+        </is>
+      </c>
+      <c r="L49" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M49" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N49" s="24" t="inlineStr">
+        <is>
+          <t>moraes.jpg</t>
+        </is>
+      </c>
+      <c r="O49" s="24" t="inlineStr">
+        <is>
+          <t>Isac Nóbrega · CC BY 2.0</t>
+        </is>
+      </c>
+      <c r="P49" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Ministro_Alexandre_de_Moraes_como_presidente_do_TSE.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="24" t="inlineStr">
+        <is>
+          <t>rnunes</t>
+        </is>
+      </c>
+      <c r="B50" s="24" t="inlineStr">
+        <is>
+          <t>Ricardo Nunes</t>
+        </is>
+      </c>
+      <c r="C50" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>Prefeito de São Paulo (MDB) desde 2021, reeleito em 2024. A prefeitura contratou o ITER, de Mendonça (R$ 380 mil). Segundo o ICL, o irmão do ministro, Alexandre de Almeida Mendonça, chegou a secretário-executivo da SP Regula em jun/2026, por portaria de Nunes, depois de Mendonça votar na direção defendida pela prefeitura no caso das concessões funerárias no STF.</t>
+        </is>
+      </c>
+      <c r="E50" s="24" t="inlineStr">
+        <is>
+          <t>São Paulo (SP)</t>
+        </is>
+      </c>
+      <c r="F50" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G50" s="24" t="inlineStr">
+        <is>
+          <t>Não há investigação contra ele nas fontes.</t>
+        </is>
+      </c>
+      <c r="H50" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I50" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J50" s="24" t="inlineStr">
+        <is>
+          <t>A prefeitura diz que não houve promoção (mesmo nível, mesma remuneração), que a mudança veio mais de um ano após o voto e chama a insinuação de "irresponsável e sem fundamento".</t>
+        </is>
+      </c>
+      <c r="K50" s="24" t="inlineStr">
+        <is>
+          <t>Irmão de Mendonça foi promovido por Nunes (iclnoticias.com.br) https://iclnoticias.com.br/irmao-de-mendonca-foi-promovido-por-nunes/ | Contratos do ITER (apublica.org) https://apublica.org/nota/instituto-de-andre-mendonca-e-alvo-de-representacoes-para-investigar-irregularidades/</t>
+        </is>
+      </c>
+      <c r="L50" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M50" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N50" s="24" t="inlineStr">
+        <is>
+          <t>rnunes.jpg</t>
+        </is>
+      </c>
+      <c r="O50" s="24" t="inlineStr">
+        <is>
+          <t>Celso Silva/Governo do Estado de SP · CC BY 2.0</t>
+        </is>
+      </c>
+      <c r="P50" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Ricardo_Nunes,_December_2024.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="inlineStr">
+        <is>
+          <t>cezinha</t>
+        </is>
+      </c>
+      <c r="B51" s="24" t="inlineStr">
+        <is>
+          <t>Cezinha de Madureira</t>
+        </is>
+      </c>
+      <c r="C51" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>Deputado federal por São Paulo, no terceiro mandato, e liderança da Assembleia de Deus Ministério de Madureira. Mensagens obtidas pela PF mostram que ele e o advogado Ciro Rocha Soares articularam os encontros de Vorcaro com Mendonça em fev e mar/2025; em 13/03/2025 marcou a reunião do dia seguinte, na sede do ITER. Tarcísio financiou 24% da campanha dele.</t>
+        </is>
+      </c>
+      <c r="E51" s="24" t="inlineStr">
+        <is>
+          <t>São Paulo (SP); mandato em Brasília</t>
+        </is>
+      </c>
+      <c r="F51" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G51" s="24" t="inlineStr">
+        <is>
+          <t>Alvo de operação autorizada pelo ministro Flávio Dino (2026). Sem denúncia nas fontes.</t>
+        </is>
+      </c>
+      <c r="H51" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I51" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J51" s="24" t="inlineStr">
+        <is>
+          <t>As reportagens não trazem resposta dele.</t>
+        </is>
+      </c>
+      <c r="K51" s="24" t="inlineStr">
+        <is>
+          <t>Mensagens e áudios inéditos sobre Mendonça (iclnoticias.com.br) https://iclnoticias.com.br/vaza-mendonca-mensagens-e-audios-ineditos/ | Áudios revelam encontro entre Vorcaro e Mendonça (bahianoticias.com.br) https://www.bahianoticias.com.br/justica/noticia/75274-audios-e-mensagens-revelam-encontro-entre-vorcaro-e-mendonca-ministro-admite-e-diz-que-se-limitou-a-ouvi-lo | Operação de Dino e afastamento na PF (iclnoticias.com.br) https://iclnoticias.com.br/mendonca-cesinha-madureira-vorcaro-dino/</t>
+        </is>
+      </c>
+      <c r="L51" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M51" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N51" s="24" t="inlineStr">
+        <is>
+          <t>cezinha.jpg</t>
+        </is>
+      </c>
+      <c r="O51" s="24" t="inlineStr">
+        <is>
+          <t>Câmara dos Deputados · CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="P51" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Cezinha_de_Madureira.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="24" t="inlineStr">
+        <is>
+          <t>cancado</t>
+        </is>
+      </c>
+      <c r="B52" s="24" t="inlineStr">
+        <is>
+          <t>Hazenclever Cançado</t>
+        </is>
+      </c>
+      <c r="C52" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>Hazenclever Lopes Cançado, advogado e servidor federal, ex-assessor do senador Magno Malta. Foi nomeado presidente da Loterj por Cláudio Castro em jul/2022 e, nessa função, assinou em 25/05/2023 a licença da Rede Loto (Best Bet), a primeira bet autorizada pelo estado.</t>
+        </is>
+      </c>
+      <c r="E52" s="24" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (RJ)</t>
+        </is>
+      </c>
+      <c r="F52" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G52" s="24" t="inlineStr">
+        <is>
+          <t>Não há investigação contra ele nas fontes.</t>
+        </is>
+      </c>
+      <c r="H52" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I52" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J52" s="24" t="inlineStr">
+        <is>
+          <t>A indicação dele por Flávio é atribuída à Folha ("teria"). Ele não comentou até a publicação das reportagens.</t>
+        </is>
+      </c>
+      <c r="K52" s="24" t="inlineStr">
+        <is>
+          <t>Loterj tem novo presidente (bnldata.com.br) https://bnldata.com.br/?p=105308 | Bet de investigado pagou voos de Flávio (diariodepernambuco.com.br) https://www.diariodepernambuco.com.br/politica/2026/10/11726788-bet-de-investigado-por-fraude-no-inss-pagou-voos-de-flavio-bolsonaro-na-europa-aponta-pf.html</t>
+        </is>
+      </c>
+      <c r="L52" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M52" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="inlineStr">
+        <is>
+          <t>motta</t>
+        </is>
+      </c>
+      <c r="B53" s="24" t="inlineStr">
+        <is>
+          <t>Hugo Motta</t>
+        </is>
+      </c>
+      <c r="C53" s="24" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>Deputado federal pela Paraíba (Republicanos) e presidente da Câmara desde fev/2025. Integrava com Vorcaro, Ciro Nogueira e Fábio Faria um grupo de mensagens criado em abr/2024 para combinar jantares, viagens e encontros; as últimas mensagens são da noite da prisão de Vorcaro (17/11/2025). Segundo a reportagem, Ciro o apresentou a Vorcaro para uma possível sociedade num terreno em João Pessoa.</t>
+        </is>
+      </c>
+      <c r="E53" s="24" t="inlineStr">
+        <is>
+          <t>Paraíba (PB); mandato em Brasília</t>
+        </is>
+      </c>
+      <c r="F53" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G53" s="24" t="inlineStr">
+        <is>
+          <t>Não é investigado nas fontes.</t>
+        </is>
+      </c>
+      <c r="H53" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I53" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J53" s="24" t="inlineStr">
+        <is>
+          <t>A assessoria de Motta disse que não se pronunciaria.</t>
+        </is>
+      </c>
+      <c r="K53" s="24" t="inlineStr">
+        <is>
+          <t>Grupo com Motta, Ciro e Faria organizava encontros (gazetadopovo.com.br) https://www.gazetadopovo.com.br/republica/vorcaro-grupo-motta-ciro-nogueira-fabio-faria-organizar-encontros/ | Vorcaro cita encontros com Hugo Motta (poder360.com.br) https://www.poder360.com.br/poder-economia/vorcaro-cita-encontros-com-hugo-motta-e-elogia-emenda-de-ciro-nogueira/</t>
+        </is>
+      </c>
+      <c r="L53" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M53" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N53" s="24" t="inlineStr">
+        <is>
+          <t>motta.jpg</t>
+        </is>
+      </c>
+      <c r="O53" s="24" t="inlineStr">
+        <is>
+          <t>Gilclécio Lucena · CC BY 4.0</t>
+        </is>
+      </c>
+      <c r="P53" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Deputado_Federal_Hugo_Motta_(cropped).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="24" t="inlineStr">
+        <is>
+          <t>marcal</t>
+        </is>
+      </c>
+      <c r="B54" s="24" t="inlineStr">
+        <is>
+          <t>Pablo Marçal</t>
+        </is>
+      </c>
+      <c r="C54" s="24" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>Empresário e influenciador, ex-coach; foi candidato a prefeito de São Paulo em 2024. Segundo o Valor, com base em mensagens do celular de Vorcaro, a Prime You pagou um voo de R$ 1,17 mi de São Paulo a Nova York usado por ele entre mai e jun/2025.</t>
+        </is>
+      </c>
+      <c r="E54" s="24" t="inlineStr">
+        <is>
+          <t>São Paulo (SP)</t>
+        </is>
+      </c>
+      <c r="F54" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G54" s="24" t="inlineStr">
+        <is>
+          <t>Não é investigado no caso Master nas fontes.</t>
+        </is>
+      </c>
+      <c r="H54" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I54" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J54" s="24" t="inlineStr">
+        <is>
+          <t>Marçal confirmou o voo e disse que se ofereceu para pagar; segundo ele, Vorcaro sugeriu que testasse o avião antes de comprar um parecido.</t>
+        </is>
+      </c>
+      <c r="K54" s="24" t="inlineStr">
+        <is>
+          <t>Empresa de Vorcaro pagou voo de Marçal (gp1.com.br) https://www.gp1.com.br/brasil/noticia/2026/10/2/empresa-ligada-a-daniel-vorcaro-pagou-voo-de-r-117-milhao-usado-por-pablo-marcal-633016.html | Vorcaro bancou voo e mandou ocultar valor (revistaforum.com.br) https://revistaforum.com.br/politica/vorcaro-voo-pablo-marcal/</t>
+        </is>
+      </c>
+      <c r="L54" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M54" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N54" s="24" t="inlineStr">
+        <is>
+          <t>marcal.jpg</t>
+        </is>
+      </c>
+      <c r="O54" s="24" t="inlineStr">
+        <is>
+          <t>TV Brasil Central · CC BY 3.0</t>
+        </is>
+      </c>
+      <c r="P54" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Pablo_Mar%C3%A7al_(cropped).png</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="24" t="inlineStr">
+        <is>
+          <t>bianco</t>
+        </is>
+      </c>
+      <c r="B55" s="24" t="inlineStr">
+        <is>
+          <t>Bruno Bianco Leal</t>
+        </is>
+      </c>
+      <c r="C55" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>Advogado-geral da União de ago/2021 a jan/2023, sucessor de Mendonça no governo Jair Bolsonaro. Depois atuou na iniciativa privada ligado ao Banco Master e passou a integrar a defesa de Vorcaro. Mensagens mostram o advogado Ciro Rocha Soares pedindo que ele fosse convidado para a reunião com Mendonça de 19/02/2025.</t>
+        </is>
+      </c>
+      <c r="E55" s="24" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F55" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G55" s="24" t="inlineStr">
+        <is>
+          <t>Não é investigado nas fontes.</t>
+        </is>
+      </c>
+      <c r="H55" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I55" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J55" s="24" t="inlineStr">
+        <is>
+          <t>As mensagens mostram o convite, mas não se ele compareceu.</t>
+        </is>
+      </c>
+      <c r="K55" s="24" t="inlineStr">
+        <is>
+          <t>Mensagens e áudios inéditos sobre Mendonça (iclnoticias.com.br) https://iclnoticias.com.br/vaza-mendonca-mensagens-e-audios-ineditos/ | Áudios revelam encontro entre Vorcaro e Mendonça (bahianoticias.com.br) https://www.bahianoticias.com.br/justica/noticia/75274-audios-e-mensagens-revelam-encontro-entre-vorcaro-e-mendonca-ministro-admite-e-diz-que-se-limitou-a-ouvi-lo</t>
+        </is>
+      </c>
+      <c r="L55" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M55" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N55" s="24" t="inlineStr">
+        <is>
+          <t>bianco.jpg</t>
+        </is>
+      </c>
+      <c r="O55" s="24" t="inlineStr">
+        <is>
+          <t>Marcos Corrêa/PR · CC BY 2.0</t>
+        </is>
+      </c>
+      <c r="P55" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Bruno_Bianco.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="24" t="inlineStr">
+        <is>
+          <t>jbcarvalho</t>
+        </is>
+      </c>
+      <c r="B56" s="24" t="inlineStr">
+        <is>
+          <t>Bispo JB Carvalho</t>
+        </is>
+      </c>
+      <c r="C56" s="24" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>João Batista Araújo Carvalho Lima, bispo fundador da Comunidade das Nações, igreja com mais de 50 unidades no Brasil, nos EUA e em Portugal. Flávio e a mulher, Fernanda, foram batizados na igreja, em Brasília, em jan/2024. Em livro de 2001 ele defendeu tirar de Nossa Senhora Aparecida o título de padroeira; os trechos voltaram a circular em set/2026.</t>
+        </is>
+      </c>
+      <c r="E56" s="24" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F56" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G56" s="24" t="inlineStr">
+        <is>
+          <t>Não há processo contra ele nas fontes. Uma associação pediu à Justiça Federal a retirada do livro.</t>
+        </is>
+      </c>
+      <c r="H56" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I56" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J56" s="24" t="inlineStr">
+        <is>
+          <t>As reportagens não trazem resposta dele.</t>
+        </is>
+      </c>
+      <c r="K56" s="24" t="inlineStr">
+        <is>
+          <t>A ligação de Flávio com o bispo (tvtnews.com.br) https://tvtnews.com.br/?p=804749 | Bispo que batizou Flávio criticou Nossa Senhora (poder360.com.br) https://www.poder360.com.br/poder-gente/bispo-que-batizou-flavio-criticou-nossa-senhora-em-livro/</t>
+        </is>
+      </c>
+      <c r="L56" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M56" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N56" s="24" t="inlineStr">
+        <is>
+          <t>jbcarvalho.jpg</t>
+        </is>
+      </c>
+      <c r="O56" s="24" t="inlineStr">
+        <is>
+          <t>Povoselinguas · CC BY 3.0</t>
+        </is>
+      </c>
+      <c r="P56" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:JB_Carvalho_(3x4_cropped).webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="inlineStr">
+        <is>
+          <t>stf</t>
+        </is>
+      </c>
+      <c r="B57" s="24" t="inlineStr">
+        <is>
+          <t>STF</t>
+        </is>
+      </c>
+      <c r="C57" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>Supremo Tribunal Federal. Concentra os casos do mapa que envolvem autoridades com foro: o caso Master (relator André Mendonça desde fev/2026), o inquérito sobre o dinheiro de Vorcaro para o filme Dark Horse (Mendonça) e o inquérito sobre suspeita de lavagem de Flávio com Willer Tomaz (Alexandre de Moraes, out/2026). Em 2021 a Segunda Turma anulou relatórios do Coaf do caso da rachadinha.</t>
+        </is>
+      </c>
+      <c r="E57" s="24" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F57" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G57" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H57" s="24" t="inlineStr">
+        <is>
+          <t>Órgão público</t>
+        </is>
+      </c>
+      <c r="I57" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J57" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K57" s="24" t="inlineStr">
+        <is>
+          <t>STF anula 4 relatórios do Coaf (poder360.com.br) https://www.poder360.com.br/justica/stf-anula-4-relatorios-do-coaf-que-miravam-flavio-no-caso-das-rachadinhas/ | Segundo inquérito contra Flávio no STF (oliberal.com) https://www.oliberal.com/politica/flavio-e-investigado-em-2-inquerito-no-stf-para-apurar-suspeitas-de-lavagem-com-advogado-1.1183991</t>
+        </is>
+      </c>
+      <c r="L57" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M57" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N57" s="24" t="inlineStr">
+        <is>
+          <t>stf.jpg</t>
+        </is>
+      </c>
+      <c r="O57" s="24" t="inlineStr">
+        <is>
+          <t>Daderot · CC0 (domínio público)</t>
+        </is>
+      </c>
+      <c r="P57" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Supremo_Tribunal_Federal_building_in_Brasilia_-_DSC00288.JPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="24" t="inlineStr">
+        <is>
+          <t>abin</t>
+        </is>
+      </c>
+      <c r="B58" s="24" t="inlineStr">
+        <is>
+          <t>Abin</t>
+        </is>
+      </c>
+      <c r="C58" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>Agência Brasileira de Inteligência. Na investigação da "Abin paralela", a PF achou o áudio de uma reunião de 25/08/2020 entre Jair Bolsonaro, Augusto Heleno e o então diretor Alexandre Ramagem, possivelmente com uma advogada de Flávio, em que Ramagem sugere processos contra auditores da Receita para blindar Flávio no caso da rachadinha.</t>
+        </is>
+      </c>
+      <c r="E58" s="24" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F58" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G58" s="24" t="inlineStr">
+        <is>
+          <t>O episódio faz parte do inquérito sobre uso ilegal do sistema First Mile por servidores da Abin.</t>
+        </is>
+      </c>
+      <c r="H58" s="24" t="inlineStr">
+        <is>
+          <t>Órgão público</t>
+        </is>
+      </c>
+      <c r="I58" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J58" s="24" t="inlineStr">
+        <is>
+          <t>Flávio diz não ter "nenhuma relação" com a Abin.</t>
+        </is>
+      </c>
+      <c r="K58" s="24" t="inlineStr">
+        <is>
+          <t>Áudio de Ramagem sugere investigar auditores (poder360.com.br) https://www.poder360.com.br/poder-justica/audio-de-ramagem-sugere-investigar-auditores-para-blindar-flavio/ | PF investiga se Abin ajudou defesa de Flávio (congressoemfoco.com.br) https://congressoemfoco.com.br/noticia/7623/pf-investiga-se-abin-ajudou-defesa-de-flavio-bolsonaro-senador-nega</t>
+        </is>
+      </c>
+      <c r="L58" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M58" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N58" s="24" t="inlineStr">
+        <is>
+          <t>abin.jpg</t>
+        </is>
+      </c>
+      <c r="O58" s="24" t="inlineStr">
+        <is>
+          <t>Antonio Cruz/Agência Brasil · CC BY 3.0 BR</t>
+        </is>
+      </c>
+      <c r="P58" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Pr%C3%A9dio_da_Abin.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="24" t="inlineStr">
+        <is>
+          <t>cpi</t>
+        </is>
+      </c>
+      <c r="B59" s="24" t="inlineStr">
+        <is>
+          <t>CPI da pandemia (Covaxin)</t>
+        </is>
+      </c>
+      <c r="C59" s="24" t="inlineStr">
+        <is>
+          <t>Willer Tomaz e sua rede</t>
+        </is>
+      </c>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>CPI da Pandemia do Senado (abr a out/2021), relatada por Renan Calheiros. Investigou, entre outros pontos, a compra da vacina Covaxin pelo Ministério da Saúde. Flávio, então senador do Patriota, atuou na comissão como defensor do governo do pai.</t>
+        </is>
+      </c>
+      <c r="E59" s="24" t="inlineStr">
+        <is>
+          <t>Senado Federal, Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F59" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G59" s="24" t="inlineStr">
+        <is>
+          <t>O relatório final pediu indiciamentos; a CPI foi encerrada em out/2021.</t>
+        </is>
+      </c>
+      <c r="H59" s="24" t="inlineStr">
+        <is>
+          <t>Órgão público</t>
+        </is>
+      </c>
+      <c r="I59" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J59" s="24" t="inlineStr">
+        <is>
+          <t>A citação de Willer Tomaz no caso Covaxin e o cancelamento da quebra do sigilo dele vêm do vídeo de origem e não foram reverificados nesta rodada.</t>
+        </is>
+      </c>
+      <c r="K59" s="24" t="inlineStr">
+        <is>
+          <t>Flávio Bolsonaro na CPI da Pandemia (congressoemfoco.com.br) https://congressoemfoco.com.br/artigo/14228/flavio-bolsonaro-na-cpi-da-pandemia | CPI aprova convocações e quebras de sigilo (senado.leg.br) https://www12.senado.leg.br/radio/1/noticia/2021/06/23/cpi-da-pandemia-aprovou-novas-convocacoes-quebras-de-sigilos-e-pedidos-de-informacoes</t>
+        </is>
+      </c>
+      <c r="L59" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M59" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N59" s="24" t="inlineStr">
+        <is>
+          <t>cpi.jpg</t>
+        </is>
+      </c>
+      <c r="O59" s="24" t="inlineStr">
+        <is>
+          <t>Agência Senado · CC BY 2.0</t>
+        </is>
+      </c>
+      <c r="P59" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:CPIPANDEMIA_-_Comiss%C3%A3o_Parlamentar_de_Inqu%C3%A9rito_da_Pandemia_(1).jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="24" t="inlineStr">
+        <is>
+          <t>loterj</t>
+        </is>
+      </c>
+      <c r="B60" s="24" t="inlineStr">
+        <is>
+          <t>Loterj</t>
+        </is>
+      </c>
+      <c r="C60" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>Loteria do Estado do Rio de Janeiro, autarquia estadual. Em mai/2023, sob a presidência de Hazenclever Cançado, licenciou a Rede Loto (Best Bet), a primeira bet autorizada no país, sem exigir a identificação dos beneficiários finais. Em 2023 contratou a RioPag para intermediar os pagamentos das bets; a empresa faturou R$ 187,8 mi em taxas entre jun/2023 e ago/2026.</t>
+        </is>
+      </c>
+      <c r="E60" s="24" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (RJ)</t>
+        </is>
+      </c>
+      <c r="F60" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G60" s="24" t="inlineStr">
+        <is>
+          <t>Rescindiu o contrato da RioPag em 22/09/2026 e cobra R$ 9,4 mi; uma liminar suspendeu a rescisão.</t>
+        </is>
+      </c>
+      <c r="H60" s="24" t="inlineStr">
+        <is>
+          <t>Órgão público</t>
+        </is>
+      </c>
+      <c r="I60" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J60" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K60" s="24" t="inlineStr">
+        <is>
+          <t>Loterj licencia a Rede Loto (lotterydaily.com) https://lotterydaily.com/2023/06/06/retail/rios-loterj-achieves-2023-betting-ambitions-with-rede-loto-contract/ | Bet de investigado pagou voos de Flávio (diariodepernambuco.com.br) https://www.diariodepernambuco.com.br/politica/2026/10/11726788-bet-de-investigado-por-fraude-no-inss-pagou-voos-de-flavio-bolsonaro-na-europa-aponta-pf.html | Loterj rescinde contrato com a RioPag (bnldata.com.br) https://bnldata.com.br/loterj-rescinde-contrato-com-riopag-e-cobra-r-94-mi-da-empresa/</t>
+        </is>
+      </c>
+      <c r="L60" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M60" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="24" t="inlineStr">
+        <is>
+          <t>pgr</t>
+        </is>
+      </c>
+      <c r="B61" s="24" t="inlineStr">
+        <is>
+          <t>Procuradoria-Geral (PGR)</t>
+        </is>
+      </c>
+      <c r="C61" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>Procuradoria-Geral da República, chefiada por Paulo Gonet. Cabe a ela denunciar autoridades com foro no STF, como os investigados do caso Master. Em 2026 negociava com a PF a delação de Vorcaro e sustentou que Mendonça investigou Alexandre de Moraes sem aval do plenário. Não foi ouvida antes do afastamento do diretor-geral da PF.</t>
+        </is>
+      </c>
+      <c r="E61" s="24" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F61" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H61" s="24" t="inlineStr">
+        <is>
+          <t>Órgão público</t>
+        </is>
+      </c>
+      <c r="I61" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J61" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K61" s="24" t="inlineStr">
+        <is>
+          <t>Afastamento do diretor-geral da PF sem ouvir a PGR (cnnbrasil.com.br) https://www.cnnbrasil.com.br/blogs/teo-cury/politica/mendonca-ordenou-afastamento-de-diretor-geral-da-pf-sem-ouvir-pgr/ | Gonet diz que Mendonça investigou Moraes (iclnoticias.com.br) https://iclnoticias.com.br/gonet-diz-que-mendonca-investigou-moraes/ | Delação de Vorcaro em negociação (timesbrasil.com.br) https://timesbrasil.com.br/brasil/operacoes-da-pf/pf-prende-paulo-henrique-costa-ex-presidente-do-brb-em-nova-fase-da-compliance-zero/</t>
+        </is>
+      </c>
+      <c r="L61" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M61" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N61" s="24" t="inlineStr">
+        <is>
+          <t>pgr.jpg</t>
+        </is>
+      </c>
+      <c r="O61" s="24" t="inlineStr">
+        <is>
+          <t>Webysther · CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="P61" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Webysther_20180212174501_-_PGR_-_Procuradoria_Geral_da_Rep%C3%BAblica.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="inlineStr">
+        <is>
+          <t>receita</t>
+        </is>
+      </c>
+      <c r="B62" s="24" t="inlineStr">
+        <is>
+          <t>Receita Federal</t>
+        </is>
+      </c>
+      <c r="C62" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D62" s="24" t="inlineStr">
+        <is>
+          <t>Receita Federal. O secretário José Barroso Tostes Neto teve três reuniões com Flávio em ago e set/2020, a pedido do senador e com a advogada dele no caso Queiroz; a última teria sido na casa de Flávio. Os temas declarados foram a situação fiscal de pessoas e empresas ligadas a ele e supostas condutas irregulares de servidores do órgão.</t>
+        </is>
+      </c>
+      <c r="E62" s="24" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F62" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G62" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H62" s="24" t="inlineStr">
+        <is>
+          <t>Órgão público</t>
+        </is>
+      </c>
+      <c r="I62" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J62" s="24" t="inlineStr">
+        <is>
+          <t>O local da última reunião é relatado com "teria".</t>
+        </is>
+      </c>
+      <c r="K62" s="24" t="inlineStr">
+        <is>
+          <t>Receita confirma visita de secretário a Flávio (poder360.com.br) https://www.poder360.com.br/governo/receita-federal-confirma-visita-de-secretario-do-fisco-a-flavio-bolsonaro/ | Chefe da Receita foi à casa de Flávio (infomoney.com.br) https://www.infomoney.com.br/?p=2535322</t>
+        </is>
+      </c>
+      <c r="L62" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M62" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N62" s="24" t="inlineStr">
+        <is>
+          <t>receita.jpg</t>
+        </is>
+      </c>
+      <c r="O62" s="24" t="inlineStr">
+        <is>
+          <t>Academia de Letras de Campo Maior · CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="P62" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Ag%C3%AAncia_da_Receita_Federal_de_Campo_Maior,_Piau%C3%AD,_Brasil.JPG</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="inlineStr">
+        <is>
+          <t>tse</t>
+        </is>
+      </c>
+      <c r="B63" s="24" t="inlineStr">
+        <is>
+          <t>TSE</t>
+        </is>
+      </c>
+      <c r="C63" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D63" s="24" t="inlineStr">
+        <is>
+          <t>Tribunal Superior Eleitoral. Kassio Nunes Marques assumiu a presidência em mai/2026 e conduz as eleições de 2026. Em mar/2026 o tribunal tornou Cláudio Castro inelegível; Nunes Marques votou pela absolvição.</t>
+        </is>
+      </c>
+      <c r="E63" s="24" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F63" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H63" s="24" t="inlineStr">
+        <is>
+          <t>Órgão público</t>
+        </is>
+      </c>
+      <c r="I63" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J63" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K63" s="24" t="inlineStr">
+        <is>
+          <t>Nunes Marques assume a presidência do TSE (poder360.com.br) https://www.poder360.com.br/brasil/nunes-marques-assume-presidencia-do-tse/ | TSE torna Castro inelegível (jovempan.com.br) https://jovempan.com.br/politica/tse-forma-maioria-para-tornar-castro-inelegivel-por-8-anos/</t>
+        </is>
+      </c>
+      <c r="L63" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M63" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N63" s="24" t="inlineStr">
+        <is>
+          <t>tse.jpg</t>
+        </is>
+      </c>
+      <c r="O63" s="24" t="inlineStr">
+        <is>
+          <t>Alexandresena · CC BY-SA 4.0</t>
+        </is>
+      </c>
+      <c r="P63" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Sede_do_Tribunal_Superior_Eleitoral,_em_Bras%C3%ADlia.jpg</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="24" t="inlineStr">
+        <is>
+          <t>brb</t>
+        </is>
+      </c>
+      <c r="B64" s="24" t="inlineStr">
+        <is>
+          <t>BRB (Banco de Brasília)</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="D64" s="24" t="inlineStr">
+        <is>
+          <t>Banco de Brasília, banco público controlado pelo governo do DF. Pôs cerca de R$ 12 bi no Master comprando carteiras de crédito consignado que a investigação aponta como fraudulentas, e tentou comprar o próprio Master em 2025. O ex-presidente Paulo Henrique Costa foi afastado em nov/2025 e preso em 16/04/2026 na Compliance Zero. Em 2021 financiou R$ 3,1 mi da mansão de Flávio em Brasília.</t>
+        </is>
+      </c>
+      <c r="E64" s="24" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F64" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" s="24" t="inlineStr">
+        <is>
+          <t>Ex-dirigentes investigados no inquérito do caso Master. A PF também apura as condições do empréstimo a Flávio.</t>
+        </is>
+      </c>
+      <c r="H64" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I64" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J64" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K64" s="24" t="inlineStr">
+        <is>
+          <t>PF prende ex-presidente do BRB (timesbrasil.com.br) https://timesbrasil.com.br/brasil/operacoes-da-pf/pf-prende-paulo-henrique-costa-ex-presidente-do-brb-em-nova-fase-da-compliance-zero/ | PF apura financiamento do BRB a Flávio (diariodepernambuco.com.br) https://www.diariodepernambuco.com.br/politica/2026/10/11725606-pf-apura-condicoes-de-financiamento-do-brb-a-flavio-bolsonaro-para-mansao-de-rs-6-milhoes.html</t>
+        </is>
+      </c>
+      <c r="L64" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M64" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N64" s="24" t="inlineStr">
+        <is>
+          <t>brb.png</t>
+        </is>
+      </c>
+      <c r="O64" s="24" t="inlineStr">
+        <is>
+          <t>Banco de Brasília · domínio público (logo simples, sem direito autoral)</t>
+        </is>
+      </c>
+      <c r="P64" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Logotipo_do_Banco_de_Bras%C3%ADlia.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="24" t="inlineStr">
+        <is>
+          <t>govlula</t>
+        </is>
+      </c>
+      <c r="B65" s="24" t="inlineStr">
+        <is>
+          <t>Governo Lula (Haddad, Gleisi, Mercadante)</t>
+        </is>
+      </c>
+      <c r="C65" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D65" s="24" t="inlineStr">
+        <is>
+          <t>Ministros do governo Lula citados em mensagens do celular de Vorcaro. Em 29/10/2025, enquanto a compra do Master pelo BRB estava em análise no Banco Central, Vorcaro escreveu que Fernando Haddad era "um dos meus maiores opositores". A planilha também registra pedido de ajuda para "bloquear" Gleisi Hoffmann e Aloizio Mercadante.</t>
+        </is>
+      </c>
+      <c r="E65" s="24" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F65" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G65" s="24" t="inlineStr">
+        <is>
+          <t>Nenhum dos ministros é investigado nas fontes.</t>
+        </is>
+      </c>
+      <c r="H65" s="24" t="inlineStr">
+        <is>
+          <t>Órgão público</t>
+        </is>
+      </c>
+      <c r="I65" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J65" s="24" t="inlineStr">
+        <is>
+          <t>Haddad diz que nunca recebeu Vorcaro e que recusou "diversas vezes" encontrá-lo. O trecho sobre Gleisi e Mercadante não foi reverificado nesta rodada.</t>
+        </is>
+      </c>
+      <c r="K65" s="24" t="inlineStr">
+        <is>
+          <t>Vorcaro sobre Haddad: um de meus maiores opositores (em.com.br) https://www.em.com.br/politica/2026/10/7513704-vorcaro-sobre-haddad-um-de-meus-maiores-opositores.html | Haddad nega ter recebido Vorcaro (dgabc.com.br) https://www.dgabc.com.br/Noticia/4346805/haddad-nega-ter-recebido-vorcaro-ou-estado-no-mesmo-ambiente-que-ele</t>
+        </is>
+      </c>
+      <c r="L65" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M65" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="inlineStr">
+        <is>
+          <t>adriano</t>
+        </is>
+      </c>
+      <c r="B66" s="24" t="inlineStr">
+        <is>
+          <t>Adriano da Nóbrega</t>
+        </is>
+      </c>
+      <c r="C66" s="24" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="D66" s="24" t="inlineStr">
+        <is>
+          <t>Adriano Magalhães da Nóbrega, ex-capitão do Bope apontado pelo MP-RJ como chefe do Escritório do Crime e da milícia de Rio das Pedras. Flávio o homenageou com moção de louvor em 2003 e com a Medalha Tiradentes em jun/2005, quando ele estava preso por homicídio (depois absolvido, em 2007). A mãe e a mulher dele trabalharam no gabinete de Flávio na Alerj.</t>
+        </is>
+      </c>
+      <c r="E66" s="24" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (RJ)</t>
+        </is>
+      </c>
+      <c r="F66" s="24" t="inlineStr">
+        <is>
+          <t>Morto (fev/2020)</t>
+        </is>
+      </c>
+      <c r="G66" s="24" t="inlineStr">
+        <is>
+          <t>Foragido desde a Operação Os Intocáveis (jan/2019); morto pela polícia na Bahia em fev/2020.</t>
+        </is>
+      </c>
+      <c r="H66" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I66" s="24" t="inlineStr">
+        <is>
+          <t>Apontado pelo MP-RJ como chefe da milícia de Rio das Pedras e do Escritório do Crime.</t>
+        </is>
+      </c>
+      <c r="J66" s="24" t="inlineStr">
+        <is>
+          <t>Mesmo sendo uma figura notória, fica sem foto porque não era pessoa pública por escolha.</t>
+        </is>
+      </c>
+      <c r="K66" s="24" t="inlineStr">
+        <is>
+          <t>Ex-PM estava preso quando Flávio o homenageou (agazeta.com.br) https://www.agazeta.com.br/brasil/ex-pm-estava-preso-por-homicidio-quando-flavio-bolsonaro-o-homenageou-0119 | Miliciano ligado a Flávio é morto (congressoemfoco.com.br) https://www.congressoemfoco.com.br/governo/miliciano-ligado-a-flavio-bolsonaro-e-morto-durante-operacao/ | Entre medalhas e milícias (vermelho.org.br) https://vermelho.org.br/?p=740865</t>
+        </is>
+      </c>
+      <c r="L66" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M66" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="24" t="inlineStr">
+        <is>
+          <t>ronald</t>
+        </is>
+      </c>
+      <c r="B67" s="24" t="inlineStr">
+        <is>
+          <t>Ronald Paulo Alves Pereira</t>
+        </is>
+      </c>
+      <c r="C67" s="24" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="D67" s="24" t="inlineStr">
+        <is>
+          <t>Major da PM do Rio. Flávio apresentou em 2004 uma moção de louvor a ele na Alerj. Foi preso em jan/2019 na Operação Os Intocáveis, contra a milícia de Rio das Pedras, e em fev/2026 condenado pela Primeira Turma do STF a 56 anos de prisão no caso Marielle Franco e Anderson Gomes.</t>
+        </is>
+      </c>
+      <c r="E67" s="24" t="inlineStr">
+        <is>
+          <t>Cumpre pena na Penitenciária Federal de Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F67" s="24" t="inlineStr">
+        <is>
+          <t>Vivo (preso)</t>
+        </is>
+      </c>
+      <c r="G67" s="24" t="inlineStr">
+        <is>
+          <t>Condenado pelo STF (56 anos); trânsito em julgado declarado em 13/07/2026.</t>
+        </is>
+      </c>
+      <c r="H67" s="24" t="inlineStr">
+        <is>
+          <t>Condenado</t>
+        </is>
+      </c>
+      <c r="I67" s="24" t="inlineStr">
+        <is>
+          <t>Preso na operação contra a milícia de Rio das Pedras e Muzema.</t>
+        </is>
+      </c>
+      <c r="J67" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K67" s="24" t="inlineStr">
+        <is>
+          <t>Moraes determina cumprimento das penas no caso Marielle (agenciabrasil.ebc.com.br) https://agenciabrasil.ebc.com.br/justica/noticia/2026-07/caso-marielle-moraes-determina-cumprimento-imediato-de-penas | Flávio homenageou em 2004 suspeito do caso Marielle (jb.com.br) https://www.jb.com.br/rio/2019/01/974171-flavio-bolsonaro-homenageou-em-2004-suspeito-de-participar-da-morte-de-marielle.html</t>
+        </is>
+      </c>
+      <c r="L67" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M67" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="24" t="inlineStr">
+        <is>
+          <t>orelha</t>
+        </is>
+      </c>
+      <c r="B68" s="24" t="inlineStr">
+        <is>
+          <t>Luís Carlos Felipe Martins (“Orelha”)</t>
+        </is>
+      </c>
+      <c r="C68" s="24" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>Não consegui confirmar em fonte pública a identidade nem o histórico de "Orelha" como descritos na planilha (ex-PM ligado à milícia de Rio das Pedras, homenageado por Flávio e morto em 2021). O nó fica sem perfil detalhado até haver fonte.</t>
+        </is>
+      </c>
+      <c r="E68" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F68" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H68" s="24" t="inlineStr">
+        <is>
+          <t>Não pesquisado</t>
+        </is>
+      </c>
+      <c r="I68" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J68" s="24" t="inlineStr">
+        <is>
+          <t>Identidade não confirmada: mais vale faltar do que atribuir algo à pessoa errada.</t>
+        </is>
+      </c>
+      <c r="K68" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L68" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M68" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="24" t="inlineStr">
+        <is>
+          <t>peixe</t>
+        </is>
+      </c>
+      <c r="B69" s="24" t="inlineStr">
+        <is>
+          <t>Robson Calixto (“Peixe”)</t>
+        </is>
+      </c>
+      <c r="C69" s="24" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="D69" s="24" t="inlineStr">
+        <is>
+          <t>Robson Calixto da Fonseca, PM da reserva e ex-assessor de Domingos Brazão na Alerj e no TCE-RJ. Em fev/2026 o STF o condenou a 9 anos por integrar organização criminosa armada ligada ao assassinato de Marielle Franco; não foi condenado pelos homicídios. Segundo a PF, em out/2023 pediu a uma assessora de Flávio uma emenda de R$ 199 mil para o Instituto Ifop, paga em nov/2023.</t>
+        </is>
+      </c>
+      <c r="E69" s="24" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (RJ)</t>
+        </is>
+      </c>
+      <c r="F69" s="24" t="inlineStr">
+        <is>
+          <t>Vivo (preso)</t>
+        </is>
+      </c>
+      <c r="G69" s="24" t="inlineStr">
+        <is>
+          <t>Condenado pelo STF a 9 anos (organização criminosa armada); trânsito em julgado em jul/2026. A PF apura a emenda.</t>
+        </is>
+      </c>
+      <c r="H69" s="24" t="inlineStr">
+        <is>
+          <t>Condenado</t>
+        </is>
+      </c>
+      <c r="I69" s="24" t="inlineStr">
+        <is>
+          <t>A PGR o descreveu como operador e intermediário dos irmãos Brazão.</t>
+        </is>
+      </c>
+      <c r="J69" s="24" t="inlineStr">
+        <is>
+          <t>Flávio diz que a emenda seguiu critérios técnicos e que a execução cabe ao beneficiário.</t>
+        </is>
+      </c>
+      <c r="K69" s="24" t="inlineStr">
+        <is>
+          <t>Quem é Peixe (tvtnews.com.br) https://tvtnews.com.br/?p=804271 | PF apura emenda de Flávio para ONG dos Brazão (infomoney.com.br) https://www.infomoney.com.br/politica/pf-apura-emenda-de-flavio-para-ong-suspeita-de-integrar-esquema-dos-irmaos-brazao/ | Penas do caso Marielle (agenciabrasil.ebc.com.br) https://agenciabrasil.ebc.com.br/justica/noticia/2026-07/caso-marielle-moraes-determina-cumprimento-imediato-de-penas</t>
+        </is>
+      </c>
+      <c r="L69" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M69" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="24" t="inlineStr">
+        <is>
+          <t>pms16</t>
+        </is>
+      </c>
+      <c r="B70" s="24" t="inlineStr">
+        <is>
+          <t>16 PMs denunciados</t>
+        </is>
+      </c>
+      <c r="C70" s="24" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="D70" s="24" t="inlineStr">
+        <is>
+          <t>Grupo de policiais militares que receberam homenagens de Flávio e Carlos Bolsonaro e depois foram denunciados por organização criminosa ou ligação com milícias. Entre os casos documentados estão quatro PMs da Operação Quarto Elemento, denunciados por extorsão de comerciantes e mototaxistas. Os nomes individuais não são listados aqui.</t>
+        </is>
+      </c>
+      <c r="E70" s="24" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (RJ)</t>
+        </is>
+      </c>
+      <c r="F70" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G70" s="24" t="inlineStr">
+        <is>
+          <t>Denunciados pelo MP-RJ; a situação varia caso a caso.</t>
+        </is>
+      </c>
+      <c r="H70" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I70" s="24" t="inlineStr">
+        <is>
+          <t>Parte do grupo é ligada a milícias, segundo o MP-RJ.</t>
+        </is>
+      </c>
+      <c r="J70" s="24" t="inlineStr">
+        <is>
+          <t>O total de 16 vem do vídeo de origem. A fonte reverificada nomeia seis homenageados denunciados e não confirma o total.</t>
+        </is>
+      </c>
+      <c r="K70" s="24" t="inlineStr">
+        <is>
+          <t>Entre medalhas e milícias (vermelho.org.br) https://vermelho.org.br/?p=740865 | Milicianos presos foram homenageados por Flávio na Alerj (istoe.com.br) https://istoe.com.br/milicianos-presos-no-rio-foram-homenageados-por-flavio-bolsonaro-na-alerj/</t>
+        </is>
+      </c>
+      <c r="L70" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M70" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="24" t="inlineStr">
+        <is>
+          <t>pmacusado</t>
+        </is>
+      </c>
+      <c r="B71" s="24" t="inlineStr">
+        <is>
+          <t>PM acusado de matar menina de 5 anos</t>
+        </is>
+      </c>
+      <c r="C71" s="24" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="D71" s="24" t="inlineStr">
+        <is>
+          <t>Policial militar denunciado pelo MP-RJ por um disparo de fuzil que matou uma criança de 5 anos durante patrulha em Niterói, em fev/2021. Flávio integrou a defesa e assinou um recurso ao STJ em 2024 para evitar o júri popular. O STJ negou o recurso, e o PM aguarda o júri.</t>
+        </is>
+      </c>
+      <c r="E71" s="24" t="inlineStr">
+        <is>
+          <t>Niterói (RJ)</t>
+        </is>
+      </c>
+      <c r="F71" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G71" s="24" t="inlineStr">
+        <is>
+          <t>Réu; pronunciado a júri popular, sem mais recursos. A prisão preventiva foi revogada em nov/2021.</t>
+        </is>
+      </c>
+      <c r="H71" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I71" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J71" s="24" t="inlineStr">
+        <is>
+          <t>Por envolver uma criança, o mapa não traz o nome da vítima. A defesa do PM diz que ele reagiu a um ataque; o MP-RJ diz que não houve confronto.</t>
+        </is>
+      </c>
+      <c r="K71" s="24" t="inlineStr">
+        <is>
+          <t>Flávio atuou na defesa de PM acusado (iclnoticias.com.br) https://iclnoticias.com.br/flavio-bolsonaro-defesa-pm-acusado-matar-menina/ | Flávio advogou para PM (eshoje.com.br) https://eshoje.com.br/brasil/2026/10/flavio-advogou-para-pm/</t>
+        </is>
+      </c>
+      <c r="L71" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M71" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="24" t="inlineStr">
+        <is>
+          <t>cirorocha</t>
+        </is>
+      </c>
+      <c r="B72" s="24" t="inlineStr">
+        <is>
+          <t>Ciro Rocha Soares</t>
+        </is>
+      </c>
+      <c r="C72" s="24" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="D72" s="24" t="inlineStr">
+        <is>
+          <t>Advogado baiano, sócio da Rocha Soares Advogados Associados (Salvador) e ex-ouvidor do Ministério do Turismo (2016-2017). Em mensagens obtidas pela PF aparece articulando, com Cezinha de Madureira, a aproximação de Vorcaro com Mendonça: em 08/02/2025 mandou foto e áudio dizendo que levara o ministro a uma alfaiataria "trabalhando por você".</t>
+        </is>
+      </c>
+      <c r="E72" s="24" t="inlineStr">
+        <is>
+          <t>Salvador (BA)</t>
+        </is>
+      </c>
+      <c r="F72" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G72" s="24" t="inlineStr">
+        <is>
+          <t>Não há acusação contra ele nas fontes.</t>
+        </is>
+      </c>
+      <c r="H72" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I72" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J72" s="24" t="inlineStr">
+        <is>
+          <t>Ele diz que não há irregularidade em pedir conversas com magistrados e que Vorcaro não era investigado em fev/2025.</t>
+        </is>
+      </c>
+      <c r="K72" s="24" t="inlineStr">
+        <is>
+          <t>Mensagens e áudios inéditos sobre Mendonça (iclnoticias.com.br) https://iclnoticias.com.br/vaza-mendonca-mensagens-e-audios-ineditos/ | Áudios revelam encontro entre Vorcaro e Mendonça (bahianoticias.com.br) https://www.bahianoticias.com.br/justica/noticia/75274-audios-e-mensagens-revelam-encontro-entre-vorcaro-e-mendonca-ministro-admite-e-diz-que-se-limitou-a-ouvi-lo</t>
+        </is>
+      </c>
+      <c r="L72" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M72" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="24" t="inlineStr">
+        <is>
+          <t>ong</t>
+        </is>
+      </c>
+      <c r="B73" s="24" t="inlineStr">
+        <is>
+          <t>ONG e produtora do filme</t>
+        </is>
+      </c>
+      <c r="C73" s="24" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="D73" s="24" t="inlineStr">
+        <is>
+          <t>Entidades ligadas a Karina Ferreira da Gama, sócia da GoUp, produtora do filme Dark Horse, sobre Jair Bolsonaro: o Instituto Conhecer Brasil e a Associação (ou Academia) Nacional de Cultura. Receberam emendas de deputados paulistas. Segundo o Intercept, houve negociação de US$ 24 mi de Vorcaro para o filme; Flávio admitiu ter recebido mais de US$ 12 mi, que chama de "patrocínio".</t>
+        </is>
+      </c>
+      <c r="E73" s="24" t="inlineStr">
+        <is>
+          <t>Av. Paulista, São Paulo (SP)</t>
+        </is>
+      </c>
+      <c r="F73" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G73" s="24" t="inlineStr">
+        <is>
+          <t>Flávio é investigado no STF pelo dinheiro do filme (relator André Mendonça). A Prefeitura de SP pediu explicações a uma das entidades sobre despesas.</t>
+        </is>
+      </c>
+      <c r="H73" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I73" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J73" s="24" t="inlineStr">
+        <is>
+          <t>Karina diz que Vorcaro foi intermediário e que o dinheiro veio do fundo Heavengate, do Texas. O papel de tesoureiro de fachada atribuído ao eletricista vem do vídeo e não foi reverificado.</t>
+        </is>
+      </c>
+      <c r="K73" s="24" t="inlineStr">
+        <is>
+          <t>Produtora diz que filme já custou R$ 65,7 mi (oliberal.com) https://www.oliberal.com/politica/produtora-diz-que-filme-de-bolsonaro-ja-custou-r-65-7-milhoes-vorcaro-bancou-90-do-custo-1.1123519 | Deputados indicaram R$ 700 mil a entidades da produtora (cnnbrasil.com.br) https://www.cnnbrasil.com.br/politica/deputados-de-sp-indicaram-r-700-mil-a-entidades-da-produtora-de-dark-horse/ | Prefeitura pede explicações a ONG ligada a Dark Horse (dgabc.com.br) https://www.dgabc.com.br/Noticia/4334231/prefeitura-de-sp-pede-explicacoes-a-ong-ligada-a-dark-horse-por-despesas-de-rs-13-4-milhoes</t>
+        </is>
+      </c>
+      <c r="L73" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M73" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="24" t="inlineStr">
+        <is>
+          <t>bestbet</t>
+        </is>
+      </c>
+      <c r="B74" s="24" t="inlineStr">
+        <is>
+          <t>Best Bet (Rede Loto)</t>
+        </is>
+      </c>
+      <c r="C74" s="24" t="inlineStr">
+        <is>
+          <t>Willer Tomaz e sua rede</t>
+        </is>
+      </c>
+      <c r="D74" s="24" t="inlineStr">
+        <is>
+          <t>Nome fantasia da Rede Loto, registrada em SP em fev/2023 e licenciada pela Loterj em 25/05/2023, a primeira bet autorizada no país. A única acionista é a Cathedral Holdings, de Willer Tomaz e sócios. A PF apura se Willer controla a empresa de fato e encontrou canhotos de voos de Flávio na Europa (2025) pagos via Cathedral.</t>
+        </is>
+      </c>
+      <c r="E74" s="24" t="inlineStr">
+        <is>
+          <t>São Paulo (SP)</t>
+        </is>
+      </c>
+      <c r="F74" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G74" s="24" t="inlineStr">
+        <is>
+          <t>Citada no inquérito enviado ao STF em out/2026 (relator Moraes).</t>
+        </is>
+      </c>
+      <c r="H74" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I74" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J74" s="24" t="inlineStr">
+        <is>
+          <t>A defesa diz que a bet nunca chegou a operar e que os voos foram pagos por Willer, como passeios entre famílias.</t>
+        </is>
+      </c>
+      <c r="K74" s="24" t="inlineStr">
+        <is>
+          <t>Bet de investigado pagou voos de Flávio (diariodepernambuco.com.br) https://www.diariodepernambuco.com.br/politica/2026/10/11726788-bet-de-investigado-por-fraude-no-inss-pagou-voos-de-flavio-bolsonaro-na-europa-aponta-pf.html | Segundo inquérito contra Flávio no STF (oliberal.com) https://www.oliberal.com/politica/flavio-e-investigado-em-2-inquerito-no-stf-para-apurar-suspeitas-de-lavagem-com-advogado-1.1183991</t>
+        </is>
+      </c>
+      <c r="L74" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M74" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="24" t="inlineStr">
+        <is>
+          <t>cathedral</t>
+        </is>
+      </c>
+      <c r="B75" s="24" t="inlineStr">
+        <is>
+          <t>Cathedral Holdings</t>
+        </is>
+      </c>
+      <c r="C75" s="24" t="inlineStr">
+        <is>
+          <t>Willer Tomaz e sua rede</t>
+        </is>
+      </c>
+      <c r="D75" s="24" t="inlineStr">
+        <is>
+          <t>Cathedral Holdings S.A., aberta na Ilha da Madeira (Portugal) em jan/2023 só com sócios brasileiros: Willer Tomaz, a mulher e a irmã dele, Jorge Barbosa Dias e um parente de Dias. É a única acionista da Rede Loto (Best Bet). Segundo a PF, pagou voos de Flávio e da mulher entre Lisboa, Cascais, Nice e Paris em abr e mai/2025.</t>
+        </is>
+      </c>
+      <c r="E75" s="24" t="inlineStr">
+        <is>
+          <t>Funchal, Ilha da Madeira (Portugal)</t>
+        </is>
+      </c>
+      <c r="F75" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G75" s="24" t="inlineStr">
+        <is>
+          <t>Citada no inquérito da PF sobre Flávio e Willer (STF, out/2026).</t>
+        </is>
+      </c>
+      <c r="H75" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I75" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J75" s="24" t="inlineStr">
+        <is>
+          <t>Dias foi processado por jogo ilegal e lavagem em 2022 e absolvido em 2023. A defesa diz que os voos foram pagos por Willer.</t>
+        </is>
+      </c>
+      <c r="K75" s="24" t="inlineStr">
+        <is>
+          <t>Bet de investigado pagou voos de Flávio (diariodepernambuco.com.br) https://www.diariodepernambuco.com.br/politica/2026/10/11726788-bet-de-investigado-por-fraude-no-inss-pagou-voos-de-flavio-bolsonaro-na-europa-aponta-pf.html | Bet de investigado pagou voos de Flávio, aponta PF (bahianoticias.com.br) https://www.bahianoticias.com.br/folha/noticia/412847-bet-de-investigado-por-fraude-do-inss-pagou-voos-de-flavio-bolsonaro-na-europa</t>
+        </is>
+      </c>
+      <c r="L75" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M75" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="24" t="inlineStr">
+        <is>
+          <t>bravo</t>
+        </is>
+      </c>
+      <c r="B76" s="24" t="inlineStr">
+        <is>
+          <t>Bravo Grafeno</t>
+        </is>
+      </c>
+      <c r="C76" s="24" t="inlineStr">
+        <is>
+          <t>Esquema do INSS</t>
+        </is>
+      </c>
+      <c r="D76" s="24" t="inlineStr">
+        <is>
+          <t>Fábrica de capacetes aberta em jun/2024, com capital de R$ 100 mil, que tem como sócios Flávio e Carlos Bolsonaro (Jair já foi sócio e é garoto-propaganda). Está registrada na sala 2601 de um edifício em Águas Claras (DF), mesmo endereço de ao menos 16 empresas ligadas ao Careca do INSS, e usa o mesmo contador, Alexandre Caetano dos Reis.</t>
+        </is>
+      </c>
+      <c r="E76" s="24" t="inlineStr">
+        <is>
+          <t>Águas Claras (DF)</t>
+        </is>
+      </c>
+      <c r="F76" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G76" s="24" t="inlineStr">
+        <is>
+          <t>Não há acusação contra a empresa nas fontes.</t>
+        </is>
+      </c>
+      <c r="H76" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I76" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J76" s="24" t="inlineStr">
+        <is>
+          <t>O escritório do contador diz que a sala é um coworking de outra empresa. Flávio nega envolvimento com o caso INSS.</t>
+        </is>
+      </c>
+      <c r="K76" s="24" t="inlineStr">
+        <is>
+          <t>Empresas de Flávio e do Careca dividem a mesma sala (brasildefato.com.br) https://www.brasildefato.com.br/2026/09/11/empresas-de-flavio-bolsonaro-e-careca-do-inss-dividem-a-mesma-sala-em-brasilia/ | Mesma sala e mesmo contador (bahianoticias.com.br) https://www.bahianoticias.com.br/noticia/321055-empresas-de-flavio-bolsonaro-e-do-careca-do-inss-dividem-a-mesma-sala-e-possuem-o-mesmo-contador</t>
+        </is>
+      </c>
+      <c r="L76" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M76" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="24" t="inlineStr">
+        <is>
+          <t>escf</t>
+        </is>
+      </c>
+      <c r="B77" s="24" t="inlineStr">
+        <is>
+          <t>Escritório de advocacia de Flávio</t>
+        </is>
+      </c>
+      <c r="C77" s="24" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="D77" s="24" t="inlineStr">
+        <is>
+          <t>Banca de advocacia de Flávio, ativa desde 2021 e com sede na casa do senador, em Brasília. É administrada à distância por Letícia Caetano dos Reis, e a contabilidade é feita pelo escritório do irmão dela, Alexandre. Em abr/2025 emitiu nota de R$ 500 mil por "assessoria jurídica" a uma empresa ligada a uma consultoria que recebeu R$ 58 mi do Master.</t>
+        </is>
+      </c>
+      <c r="E77" s="24" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F77" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" s="24" t="inlineStr">
+        <is>
+          <t>Não há acusação contra o escritório nas fontes. Figura em ao menos 18 processos.</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I77" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J77" s="24" t="inlineStr">
+        <is>
+          <t>Flávio alega sigilo profissional e não revela os clientes.</t>
+        </is>
+      </c>
+      <c r="K77" s="24" t="inlineStr">
+        <is>
+          <t>Escritório de Flávio que emitiu nota de R$ 500 mil (tribunadosertao.com.br) https://www.tribunadosertao.com.br/poder-e-governo/2026/07/26/946935-escritorio-de-advocacia-de-flavio-que-emitiu-nota-de-r-500-mil-tem-atuacao-discreta-e-gestao-a-distancia | Firma de advocacia de Flávio (apublica.org) https://apublica.org/2022/06/firma-de-advocacia-de-flavio-bolsonaro-tem-contratos-consideraveis-diz-administradora/</t>
+        </is>
+      </c>
+      <c r="L77" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M77" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="24" t="inlineStr">
+        <is>
+          <t>consult</t>
+        </is>
+      </c>
+      <c r="B78" s="24" t="inlineStr">
+        <is>
+          <t>Consultoria do amigo de Nunes</t>
+        </is>
+      </c>
+      <c r="C78" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D78" s="24" t="inlineStr">
+        <is>
+          <t>Consult Inteligência Tributária. Segundo relatório do Coaf, recebeu R$ 6,6 mi do Banco Master e R$ 11,3 mi da JBS entre 2024 e 2025, e repassou R$ 281,6 mil, em 11 parcelas, ao escritório de Kevin Marques, filho do ministro Nunes Marques.</t>
+        </is>
+      </c>
+      <c r="E78" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F78" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G78" s="24" t="inlineStr">
+        <is>
+          <t>Aparece em relatório do Coaf sobre movimentações atípicas; sem acusação formal nas fontes.</t>
+        </is>
+      </c>
+      <c r="H78" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I78" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J78" s="24" t="inlineStr">
+        <is>
+          <t>As reportagens não nomeiam o dono, e a ligação "amigo de Nunes" vem do vídeo de origem, sem confirmação. A defesa de Kevin diz que ele prestou serviços tributários e nunca recebeu direto das empresas. A JBS diz que contrata consultorias pela complexidade tributária.</t>
+        </is>
+      </c>
+      <c r="K78" s="24" t="inlineStr">
+        <is>
+          <t>Quem é Kevin Nunes Marques (istoe.com.br) https://istoe.com.br/quem-e-kelvin-nunes-marques-filho-do-ministro-do-stf-que-diz | Consultoria ligada ao Master e à JBS contratou filho de Nunes Marques (metropoles.com) https://www.metropoles.com/brasil/consultoria-ligada-ao-master-e-a-jbs-contratou-filho-de-nunes-marques</t>
+        </is>
+      </c>
+      <c r="L78" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M78" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="24" t="inlineStr">
+        <is>
+          <t>riopag</t>
+        </is>
+      </c>
+      <c r="B79" s="24" t="inlineStr">
+        <is>
+          <t>Rio Pag</t>
+        </is>
+      </c>
+      <c r="C79" s="24" t="inlineStr">
+        <is>
+          <t>Willer Tomaz e sua rede</t>
+        </is>
+      </c>
+      <c r="D79" s="24" t="inlineStr">
+        <is>
+          <t>Intermediadora de pagamentos (depósitos e saques) das bets licenciadas pela Loterj, contratada em 2023. Faturou R$ 187,8 mi em taxas entre jun/2023 e ago/2026. A única acionista é a Capital Pretium, representada por Lídia Mazelli. Em e-mail achado pela PF, Willer se apresentou como sócio.</t>
+        </is>
+      </c>
+      <c r="E79" s="24" t="inlineStr">
+        <is>
+          <t>Rio de Janeiro (RJ)</t>
+        </is>
+      </c>
+      <c r="F79" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G79" s="24" t="inlineStr">
+        <is>
+          <t>A Loterj rescindiu o contrato em 22/09/2026 e cobra R$ 9,4 mi, acusando a empresa de reter R$ 20,9 mi; três dias depois uma liminar suspendeu a rescisão.</t>
+        </is>
+      </c>
+      <c r="H79" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I79" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J79" s="24" t="inlineStr">
+        <is>
+          <t>Willer nega ser sócio ou gestor e diz que a relação é só de advogado. Antes dizia não ter participação; depois admitiu participação indireta (O Globo).</t>
+        </is>
+      </c>
+      <c r="K79" s="24" t="inlineStr">
+        <is>
+          <t>Empresa ligada a amigo de Flávio faturou R$ 187,8 mi (ncnews.com.br) https://ncnews.com.br/?p=55340 | Loterj rescinde contrato com a RioPag (bnldata.com.br) https://bnldata.com.br/loterj-rescinde-contrato-com-riopag-e-cobra-r-94-mi-da-empresa/</t>
+        </is>
+      </c>
+      <c r="L79" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M79" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="24" t="inlineStr">
+        <is>
+          <t>luri</t>
+        </is>
+      </c>
+      <c r="B80" s="24" t="inlineStr">
+        <is>
+          <t>Allure Eventos</t>
+        </is>
+      </c>
+      <c r="C80" s="24" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="D80" s="24" t="inlineStr">
+        <is>
+          <t>Allure Eventos, agência de eventos de Felipe Nisti Cataldo. Segundo o UOL, recrutava mulheres, inclusive estrangeiras, para festas privadas de Vorcaro no Brasil e no exterior. Mensagens indicam Vorcaro como sócio oculto, e um contrato de dez/2023 previa a compra de 50% da agência por R$ 1,5 mi.</t>
+        </is>
+      </c>
+      <c r="E80" s="24" t="inlineStr">
+        <is>
+          <t>São Paulo (SP)</t>
+        </is>
+      </c>
+      <c r="F80" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G80" s="24" t="inlineStr">
+        <is>
+          <t>A PF abriu inquérito em mai/2026 sobre a contratação das estrangeiras.</t>
+        </is>
+      </c>
+      <c r="H80" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I80" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J80" s="24" t="inlineStr">
+        <is>
+          <t>O nó se chamava "Luri Eventos", provável erro de transcrição do vídeo; as reportagens grafam Allure Eventos (confirmado em 22/10/2026). O dono confirma o interesse de Vorcaro, mas nega que a compra tenha avançado e contesta a versão das mensagens. Uma das reportagens não afirma explicitamente que a Allure é a agência usada no recrutamento.</t>
+        </is>
+      </c>
+      <c r="K80" s="24" t="inlineStr">
+        <is>
+          <t>Mensagens apontam Vorcaro como sócio de agência (maisgoias.com.br) https://www.maisgoias.com.br/brasil/justica/mensagens-apontam-vorcaro-como-socio-de-agencia-que-recrutava-refugiadas-para-prostituicao/ | Mensagens ligam Vorcaro a recrutamento (jornalopcao.com.br) https://www.jornalopcao.com.br/ultimas-noticias/daniel-vorcaro-esquema-prostituicao-878361/ | Mensagens ligam Vorcaro a esquema de recrutamento (acritica.net) https://acritica.net/policia/mensagens-ligam-daniel-vorcaro-a-esquema-de-prostituicao-e-recrutamento-de-refugiadas/</t>
+        </is>
+      </c>
+      <c r="L80" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M80" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 22/10/2026: renomeado de "Luri Eventos" para "Allure Eventos".</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="24" t="inlineStr">
+        <is>
+          <t>ongbrazao</t>
+        </is>
+      </c>
+      <c r="B81" s="24" t="inlineStr">
+        <is>
+          <t>ONG ligada aos irmãos Brazão</t>
+        </is>
+      </c>
+      <c r="C81" s="24" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="D81" s="24" t="inlineStr">
+        <is>
+          <t>Instituto de Formação Profissional José Carlos Procópio (Ifop), numa sala comercial em Taquara, Zona Oeste do Rio, área de influência dos Brazão. Recebeu R$ 199 mil de emenda de Flávio em 29/11/2023 para um projeto de futebol infantil. A PF apura se o repasse fez parte de um esquema de desvio de verbas de entidades ligadas aos Brazão, que teriam recebido R$ 268 mi entre 2020 e 2024.</t>
+        </is>
+      </c>
+      <c r="E81" s="24" t="inlineStr">
+        <is>
+          <t>Taquara, Rio de Janeiro (RJ)</t>
+        </is>
+      </c>
+      <c r="F81" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G81" s="24" t="inlineStr">
+        <is>
+          <t>Investigação da PF em andamento; sem denúncia nas fontes.</t>
+        </is>
+      </c>
+      <c r="H81" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I81" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J81" s="24" t="inlineStr">
+        <is>
+          <t>O Ifop nega relação com Peixe ou com os Brazão e diz que prestou contas ao Ministério do Esporte e devolveu o que sobrou.</t>
+        </is>
+      </c>
+      <c r="K81" s="24" t="inlineStr">
+        <is>
+          <t>PF apura emenda de Flávio para ONG dos Brazão (infomoney.com.br) https://www.infomoney.com.br/politica/pf-apura-emenda-de-flavio-para-ong-suspeita-de-integrar-esquema-dos-irmaos-brazao/ | Quem é Peixe (tvtnews.com.br) https://tvtnews.com.br/?p=804271</t>
+        </is>
+      </c>
+      <c r="L81" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M81" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="24" t="inlineStr">
+        <is>
+          <t>kopenhagen</t>
+        </is>
+      </c>
+      <c r="B82" s="24" t="inlineStr">
+        <is>
+          <t>Loja Kopenhagen de Flávio</t>
+        </is>
+      </c>
+      <c r="C82" s="24" t="inlineStr">
+        <is>
+          <t>Flávio e família</t>
+        </is>
+      </c>
+      <c r="D82" s="24" t="inlineStr">
+        <is>
+          <t>Franquia de chocolates no Shopping Via Parque (Barra da Tijuca), da empresa Bolsotini Chocolates e Café, de Flávio e do sócio Alexandre Santini, comprada entre 2014 e 2015. O MP-RJ suspeitou que a loja servia para lavar dinheiro da rachadinha, com até R$ 2,1 mi "legalizados" e depósitos em espécie desproporcionais ao faturamento. A operação foi repassada ao grupo CRM em fev/2021.</t>
+        </is>
+      </c>
+      <c r="E82" s="24" t="inlineStr">
+        <is>
+          <t>Barra da Tijuca, Rio de Janeiro (RJ)</t>
+        </is>
+      </c>
+      <c r="F82" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G82" s="24" t="inlineStr">
+        <is>
+          <t>Fazia parte da denúncia da rachadinha, que perdeu efeito com as anulações de provas.</t>
+        </is>
+      </c>
+      <c r="H82" s="24" t="inlineStr">
+        <is>
+          <t>Caso</t>
+        </is>
+      </c>
+      <c r="I82" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J82" s="24" t="inlineStr">
+        <is>
+          <t>Flávio nega crime e diz que as operações da loja eram legais. A marca Kopenhagen não é parte do caso; por isso o nó fica sem logo.</t>
+        </is>
+      </c>
+      <c r="K82" s="24" t="inlineStr">
+        <is>
+          <t>Flávio entrega loja investigada pelo MP (poder360.com.br) https://www.poder360.com.br/brasil/flavio-bolsonaro-entrega-loja-de-chocolates-investigada-pelo-mp/ | Investigação apura se loja lavou R$ 2,1 mi (opovo.com.br) https://www.opovo.com.br/noticias/politica/2020/08/20/investigacao-apura-se-loja-de-flavio-bolsonaro--lavou--r--2-1-milhoes.html</t>
+        </is>
+      </c>
+      <c r="L82" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M82" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="24" t="inlineStr">
+        <is>
+          <t>santander</t>
+        </is>
+      </c>
+      <c r="B83" s="24" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="C83" s="24" t="inlineStr">
+        <is>
+          <t>Willer Tomaz e sua rede</t>
+        </is>
+      </c>
+      <c r="D83" s="24" t="inlineStr">
+        <is>
+          <t>Banco onde a Alcazar Holdings, de Willer Tomaz, mantinha conta. Segundo a PF e a piauí, Flávio aparecia como "usuário master" dessa conta, e um e-mail da secretária de Willer em 22/05/2025 pediu ao banco a exclusão dele, confirmada no mesmo dia.</t>
+        </is>
+      </c>
+      <c r="E83" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F83" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G83" s="24" t="inlineStr">
+        <is>
+          <t>O banco não é investigado; a conta é citada no inquérito sobre Flávio e Willer.</t>
+        </is>
+      </c>
+      <c r="H83" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I83" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J83" s="24" t="inlineStr">
+        <is>
+          <t>Willer atribui o vínculo a um erro cadastral do banco.</t>
+        </is>
+      </c>
+      <c r="K83" s="24" t="inlineStr">
+        <is>
+          <t>Flávio era usuário master de conta de offshore (maisgoias.com.br) https://www.maisgoias.com.br/brasil/flavio-bolsonaro-era-usuario-master-de-conta-de-offshore-socia-do-jato-usado-por-vorcaro/ | Offshore ligada a Flávio (jornalopcao.com.br) https://www.jornalopcao.com.br/ultimas-noticias/offshore-ligada-a-flavio-bolsonaro-reune-conexoes-com-o-mercado-de-bets-879306/</t>
+        </is>
+      </c>
+      <c r="L83" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M83" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N83" s="24" t="inlineStr">
+        <is>
+          <t>santander.png</t>
+        </is>
+      </c>
+      <c r="O83" s="24" t="inlineStr">
+        <is>
+          <t>Interbrand · domínio público (logo simples, sem direito autoral)</t>
+        </is>
+      </c>
+      <c r="P83" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Banco_Santander_Logotipo.svg</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="24" t="inlineStr">
+        <is>
+          <t>bets</t>
+        </is>
+      </c>
+      <c r="B84" s="24" t="inlineStr">
+        <is>
+          <t>Blaze e sites de apostas</t>
+        </is>
+      </c>
+      <c r="C84" s="24" t="inlineStr">
+        <is>
+          <t>Willer Tomaz e sua rede</t>
+        </is>
+      </c>
+      <c r="D84" s="24" t="inlineStr">
+        <is>
+          <t>Plataforma de apostas Blaze. Segundo o Metrópoles, Willer Tomaz movimentou cerca de R$ 5 bi em apostas de cassino on-line nela em 2025, com prejuízo líquido de R$ 163 mi. Ele foi à Justiça de SP alegando vício e cobrando a plataforma. A PF abriu frente de investigação sobre possível lavagem por apostas.</t>
+        </is>
+      </c>
+      <c r="E84" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F84" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G84" s="24" t="inlineStr">
+        <is>
+          <t>A plataforma não é acusada nas fontes. A Justiça de SP negou o pedido de ressarcimento de Willer.</t>
+        </is>
+      </c>
+      <c r="H84" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I84" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J84" s="24" t="inlineStr">
+        <is>
+          <t>Willer nega lavagem e diz que tudo passou pela própria conta, de forma rastreável. As fontes divergem sobre o valor cobrado na ação (R$ 20 mi ou R$ 163 mi).</t>
+        </is>
+      </c>
+      <c r="K84" s="24" t="inlineStr">
+        <is>
+          <t>Willer movimenta R$ 5 bi em apostas (bahianoticias.com.br) https://www.bahianoticias.com.br/noticia/321709-advogado-willer-tomaz-movimenta-r-5-bi-em-apostas-e-registra-prejuizo-de-r-163-mi | Justiça de SP nega ressarcimento a Willer (bnldata.com.br) https://bnldata.com.br/?p=189317</t>
+        </is>
+      </c>
+      <c r="L84" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M84" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+      <c r="N84" s="24" t="inlineStr">
+        <is>
+          <t>bets.png</t>
+        </is>
+      </c>
+      <c r="O84" s="24" t="inlineStr">
+        <is>
+          <t>blaze.com · domínio público (logo simples, sem direito autoral)</t>
+        </is>
+      </c>
+      <c r="P84" s="24" t="inlineStr">
+        <is>
+          <t>https://commons.wikimedia.org/wiki/File:Blaze_apostas_logo.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="24" t="inlineStr">
+        <is>
+          <t>aptosp</t>
+        </is>
+      </c>
+      <c r="B85" s="24" t="inlineStr">
+        <is>
+          <t>Apartamento de luxo em SP</t>
+        </is>
+      </c>
+      <c r="C85" s="24" t="inlineStr">
+        <is>
+          <t>Casas e ativos</t>
+        </is>
+      </c>
+      <c r="D85" s="24" t="inlineStr">
+        <is>
+          <t>Apartamento de 159 m² em São Paulo. Fabiano Zettel, cunhado de Vorcaro, comprou em abr/2025 por R$ 5,5 mi e vendeu em fev/2026 à WT, de Willer, por R$ 3,5 mi. Segundo a piauí, Flávio ficou lá por vários dias em ago/2026, onde se reuniu com a equipe e gravou vídeos de campanha.</t>
+        </is>
+      </c>
+      <c r="E85" s="24" t="inlineStr">
+        <is>
+          <t>São Paulo (SP)</t>
+        </is>
+      </c>
+      <c r="F85" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G85" s="24" t="inlineStr">
+        <is>
+          <t>Não há processo sobre o imóvel nas fontes.</t>
+        </is>
+      </c>
+      <c r="H85" s="24" t="inlineStr">
+        <is>
+          <t>Bem citado</t>
+        </is>
+      </c>
+      <c r="I85" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J85" s="24" t="inlineStr">
+        <is>
+          <t>Flávio disse à piauí que só se hospedou em hotéis da região. Willer diz não conhecer Zettel nem Vorcaro.</t>
+        </is>
+      </c>
+      <c r="K85" s="24" t="inlineStr">
+        <is>
+          <t>Flávio usou em campanha imóvel de advogado alvo da PF (diariodocomercio.com.br) https://diariodocomercio.com.br/politica/flavio-bolsonaro-apartamento-pf/ | Apartamento pertenceu a cunhado de Vorcaro (timesbrasil.com.br) https://timesbrasil.com.br/brasil/apartamento-usado-por-flavio-bolsonaro-durante-campanha-eleitoral-pertenceu-a-cunhado-de-daniel-vorcaro/</t>
+        </is>
+      </c>
+      <c r="L85" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M85" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="24" t="inlineStr">
+        <is>
+          <t>atibaia</t>
+        </is>
+      </c>
+      <c r="B86" s="24" t="inlineStr">
+        <is>
+          <t>Casa de Wassef em Atibaia</t>
+        </is>
+      </c>
+      <c r="C86" s="24" t="inlineStr">
+        <is>
+          <t>Casas e ativos</t>
+        </is>
+      </c>
+      <c r="D86" s="24" t="inlineStr">
+        <is>
+          <t>Casa do advogado Frederick Wassef, que defendia Flávio e Jair Bolsonaro, em Atibaia (SP). Fabrício Queiroz foi preso lá em 18/06/2020, na Operação Anjo, desdobramento da Furna da Onça.</t>
+        </is>
+      </c>
+      <c r="E86" s="24" t="inlineStr">
+        <is>
+          <t>Atibaia (SP)</t>
+        </is>
+      </c>
+      <c r="F86" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G86" s="24" t="inlineStr">
+        <is>
+          <t>Não há processo sobre o imóvel.</t>
+        </is>
+      </c>
+      <c r="H86" s="24" t="inlineStr">
+        <is>
+          <t>Bem citado</t>
+        </is>
+      </c>
+      <c r="I86" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J86" s="24" t="inlineStr">
+        <is>
+          <t>Wassef negou ter escondido Queiroz.</t>
+        </is>
+      </c>
+      <c r="K86" s="24" t="inlineStr">
+        <is>
+          <t>Queiroz é preso em Atibaia (poder360.com.br) https://www.poder360.com.br/justica/fabricio-queiroz-ex-assessor-de-flavio-bolsonaro-e-preso/ | Advogado de Bolsonaro diz que não escondeu Queiroz (poder360.com.br) https://poder360.com.br/justica/advogado-de-bolsonaro-diz-que-nao-escondeu-queiroz-e-nega-ser-o-anjo/</t>
+        </is>
+      </c>
+      <c r="L86" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M86" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="24" t="inlineStr">
+        <is>
+          <t>mansaobsb</t>
+        </is>
+      </c>
+      <c r="B87" s="24" t="inlineStr">
+        <is>
+          <t>Mansão de Flávio em Brasília</t>
+        </is>
+      </c>
+      <c r="C87" s="24" t="inlineStr">
+        <is>
+          <t>Casas e ativos</t>
+        </is>
+      </c>
+      <c r="D87" s="24" t="inlineStr">
+        <is>
+          <t>Casa comprada por Flávio em 2021 por R$ 6 mi, num terreno de 2.400 m² no Setor de Mansões Dom Bosco (Lago Sul). Foram R$ 2,87 mi de entrada e R$ 3,1 mi financiados pelo BRB a 3,71% ao ano, abaixo da média do banco; ele quitou em cerca de três anos. Também abriga o escritório de advocacia dele.</t>
+        </is>
+      </c>
+      <c r="E87" s="24" t="inlineStr">
+        <is>
+          <t>Lago Sul, Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F87" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G87" s="24" t="inlineStr">
+        <is>
+          <t>A PF apura as condições do empréstimo dentro do inquérito BRB-Master.</t>
+        </is>
+      </c>
+      <c r="H87" s="24" t="inlineStr">
+        <is>
+          <t>Bem citado</t>
+        </is>
+      </c>
+      <c r="I87" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J87" s="24" t="inlineStr">
+        <is>
+          <t>Flávio diz que a compra foi legal, paga com a venda de outro imóvel e da loja de chocolates.</t>
+        </is>
+      </c>
+      <c r="K87" s="24" t="inlineStr">
+        <is>
+          <t>PF apura financiamento do BRB a Flávio (diariodepernambuco.com.br) https://www.diariodepernambuco.com.br/politica/2026/10/11725606-pf-apura-condicoes-de-financiamento-do-brb-a-flavio-bolsonaro-para-mansao-de-rs-6-milhoes.html | PF investiga financiamento de mansão de Flávio (jb.com.br) https://www.jb.com.br/brasil/policia/2026/10/1061098-pf-investiga-financiamento-de-mansao-de-flavio-bolsonaro-em-brasilia.html</t>
+        </is>
+      </c>
+      <c r="L87" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M87" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="24" t="inlineStr">
+        <is>
+          <t>hangar</t>
+        </is>
+      </c>
+      <c r="B88" s="24" t="inlineStr">
+        <is>
+          <t>Hangares de Willer (Aeroporto de Brasília)</t>
+        </is>
+      </c>
+      <c r="C88" s="24" t="inlineStr">
+        <is>
+          <t>Casas e ativos</t>
+        </is>
+      </c>
+      <c r="D88" s="24" t="inlineStr">
+        <is>
+          <t>Hangares 36 e 37 do Aeroporto de Brasília, operados por empresas de aviação de Willer Tomaz (Ícaro Aviation e Jet Line). Na busca de ago/2026 da Operação Sem Desconto, a PF encontrou uma sala oculta, máquina de contar e malas vazias, sem dinheiro.</t>
+        </is>
+      </c>
+      <c r="E88" s="24" t="inlineStr">
+        <is>
+          <t>Aeroporto de Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F88" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G88" s="24" t="inlineStr">
+        <is>
+          <t>Alvo de busca na Operação Sem Desconto (ago/2026).</t>
+        </is>
+      </c>
+      <c r="H88" s="24" t="inlineStr">
+        <is>
+          <t>Bem citado</t>
+        </is>
+      </c>
+      <c r="I88" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J88" s="24" t="inlineStr">
+        <is>
+          <t>Willer nega uso irregular e diz que o espaço atende transporte de valores.</t>
+        </is>
+      </c>
+      <c r="K88" s="24" t="inlineStr">
+        <is>
+          <t>Empresas e hangar de Willer (iclnoticias.com.br) https://iclnoticias.com.br/domestica-preside-empresas-fraude-flavio/ | PF mira advogado camaleão de Brasília (opovo.com.br) https://www.opovo.com.br/noticias/economia/2026/08/04/fraudes-do-inss-pf-mira-advogado-camaleao-de-brasilia-por-suspeita-de-lavagem-para-senador.html</t>
+        </is>
+      </c>
+      <c r="L88" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M88" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="24" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>Sala em Águas Claras (DF)</t>
+        </is>
+      </c>
+      <c r="C89" s="24" t="inlineStr">
+        <is>
+          <t>Esquema do INSS</t>
+        </is>
+      </c>
+      <c r="D89" s="24" t="inlineStr">
+        <is>
+          <t>Sala 2601 de um edifício comercial em Águas Claras (DF). É o endereço de ao menos 16 empresas ligadas ao Careca do INSS, oito delas abertas no mesmo dia (05/10/2023), e da Bravo Grafeno, de Flávio e Carlos. Uma das empresas do Careca, a Prospect, recebeu R$ 204,2 mi de entidades, segundo a CPMI do INSS.</t>
+        </is>
+      </c>
+      <c r="E89" s="24" t="inlineStr">
+        <is>
+          <t>Águas Claras (DF)</t>
+        </is>
+      </c>
+      <c r="F89" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G89" s="24" t="inlineStr">
+        <is>
+          <t>Várias empresas do endereço são investigadas no caso INSS; algumas foram baixadas.</t>
+        </is>
+      </c>
+      <c r="H89" s="24" t="inlineStr">
+        <is>
+          <t>Bem citado</t>
+        </is>
+      </c>
+      <c r="I89" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J89" s="24" t="inlineStr">
+        <is>
+          <t>O escritório do contador diz que a sala é um coworking de outra empresa.</t>
+        </is>
+      </c>
+      <c r="K89" s="24" t="inlineStr">
+        <is>
+          <t>Empresas de Flávio e do Careca dividem a mesma sala (brasildefato.com.br) https://www.brasildefato.com.br/2026/09/11/empresas-de-flavio-bolsonaro-e-careca-do-inss-dividem-a-mesma-sala-em-brasilia/ | Mesma sala e mesmo contador (bahianoticias.com.br) https://www.bahianoticias.com.br/noticia/321055-empresas-de-flavio-bolsonaro-e-do-careca-do-inss-dividem-a-mesma-sala-e-possuem-o-mesmo-contador</t>
+        </is>
+      </c>
+      <c r="L89" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M89" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="24" t="inlineStr">
+        <is>
+          <t>escw</t>
+        </is>
+      </c>
+      <c r="B90" s="24" t="inlineStr">
+        <is>
+          <t>Escritório de Willer</t>
+        </is>
+      </c>
+      <c r="C90" s="24" t="inlineStr">
+        <is>
+          <t>Willer Tomaz e sua rede</t>
+        </is>
+      </c>
+      <c r="D90" s="24" t="inlineStr">
+        <is>
+          <t>Escritório de advocacia de Willer Tomaz em Brasília. Foi alvo de busca da PF em 04/08/2026, na nova fase da Operação Sem Desconto, quando os agentes encontraram uma máquina de contar cédulas.</t>
+        </is>
+      </c>
+      <c r="E90" s="24" t="inlineStr">
+        <is>
+          <t>Brasília (DF)</t>
+        </is>
+      </c>
+      <c r="F90" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G90" s="24" t="inlineStr">
+        <is>
+          <t>Alvo de busca e apreensão autorizada por André Mendonça.</t>
+        </is>
+      </c>
+      <c r="H90" s="24" t="inlineStr">
+        <is>
+          <t>Bem citado</t>
+        </is>
+      </c>
+      <c r="I90" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J90" s="24" t="inlineStr">
+        <is>
+          <t>O dinheiro escondido em livros-cofre vem do vídeo de origem; as reportagens reverificadas citam a máquina de contar, mas não os livros-cofre. A defesa diz que a busca se deve ao empréstimo pessoal do avião a Weverton.</t>
+        </is>
+      </c>
+      <c r="K90" s="24" t="inlineStr">
+        <is>
+          <t>PF acha máquina de contar cédulas (metropoles.com) https://www.metropoles.com/colunas/mirelle-pinheiro/fraude-no-inss-pf-acha-maquina-de-contar-cedulas-e-pilhas-de-dinheiro | Uma máquina de dinheiro no escritório do advogado (oantagonista.com.br) https://oantagonista.com.br/brasil/uma-maquina-de-dinheiro-no-escritorio-do-advogado-ligado-a-weverton-rocha/</t>
+        </is>
+      </c>
+      <c r="L90" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M90" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="24" t="inlineStr">
+        <is>
+          <t>assoc</t>
+        </is>
+      </c>
+      <c r="B91" s="24" t="inlineStr">
+        <is>
+          <t>Associações de aposentados</t>
+        </is>
+      </c>
+      <c r="C91" s="24" t="inlineStr">
+        <is>
+          <t>Esquema do INSS</t>
+        </is>
+      </c>
+      <c r="D91" s="24" t="inlineStr">
+        <is>
+          <t>Entidades que descontavam mensalidades direto de aposentadorias e pensões do INSS. PF e CGU estimam R$ 6,3 bi descontados entre 2019 e 2024; em pesquisa da CGU, 97% dos beneficiários ouvidos disseram não ter autorizado. A Operação Sem Desconto (abr/2025) derrubou o presidente do INSS, e o dinheiro passava pelo esquema atribuído ao Careca do INSS.</t>
+        </is>
+      </c>
+      <c r="E91" s="24" t="inlineStr">
+        <is>
+          <t>Nacional</t>
+        </is>
+      </c>
+      <c r="F91" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G91" s="24" t="inlineStr">
+        <is>
+          <t>Convênios suspensos; o governo prometeu ressarcir os aposentados.</t>
+        </is>
+      </c>
+      <c r="H91" s="24" t="inlineStr">
+        <is>
+          <t>Investigado / alvo (sem denúncia)</t>
+        </is>
+      </c>
+      <c r="I91" s="24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J91" s="24" t="inlineStr">
+        <is>
+          <t>Nem todo o valor é ilegal: parte dos segurados autorizou os descontos.</t>
+        </is>
+      </c>
+      <c r="K91" s="24" t="inlineStr">
+        <is>
+          <t>Como funcionava o esquema de fraude no INSS (opovo.com.br) https://www.opovo.com.br/noticias/brasil/2025/04/30/como-funcionava-o-esquema-bilionario-de-fraude-no-inss.html | Crise no INSS (congressoemfoco.com.br) https://www.congressoemfoco.com.br/noticia/108221/crise-no-inss-entenda-escandalo-que-derrubou-ministro-da-previdencia</t>
+        </is>
+      </c>
+      <c r="L91" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026</t>
+        </is>
+      </c>
+      <c r="M91" s="24" t="inlineStr">
+        <is>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P36"/>
@@ -5012,7 +9057,7 @@
       </c>
       <c r="B34" s="45" t="inlineStr">
         <is>
-          <t>Luri Eventos</t>
+          <t>Allure Eventos</t>
         </is>
       </c>
       <c r="C34" s="45" t="inlineStr">
@@ -6661,7 +10706,7 @@
       </c>
       <c r="E80" s="45" t="inlineStr">
         <is>
-          <t>Robson Calixto, PM da reserva condenado no caso Marielle; PF diz que intermediou emenda de Flávio</t>
+          <t>PM da reserva condenado no caso Marielle (organização criminosa); PF diz que intermediou emenda de Flávio</t>
         </is>
       </c>
       <c r="F80" s="45">
@@ -6906,7 +10951,7 @@
       </c>
       <c r="E87" s="45" t="inlineStr">
         <is>
-          <t>Processava pagamentos da Loterj; contrato rescindido pelo estado, que cobra ~R$ 4 mi</t>
+          <t>Processava pagamentos das bets da Loterj; o estado rescindiu em set/2026 e cobra R$ 9,4 mi (liminar suspendeu)</t>
         </is>
       </c>
       <c r="F87" s="45">
@@ -12856,7 +16901,7 @@
       </c>
       <c r="C193" s="45" t="inlineStr">
         <is>
-          <t>Contratou em 2023; o estado rescindiu e cobra ~R$ 4 mi, a empresa contesta</t>
+          <t>Contratou em 2023; o estado rescindiu em set/2026 e cobra R$ 9,4 mi (liminar suspendeu); a empresa contesta</t>
         </is>
       </c>
       <c r="D193" s="45" t="inlineStr">

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -7094,7 +7094,7 @@
       </c>
       <c r="J80" s="24" t="inlineStr">
         <is>
-          <t>O nó se chamava "Luri Eventos", provável erro de transcrição do vídeo; as reportagens grafam Allure Eventos (confirmado em 22/10/2026). O dono confirma o interesse de Vorcaro, mas nega que a compra tenha avançado e contesta a versão das mensagens. Uma das reportagens não afirma explicitamente que a Allure é a agência usada no recrutamento.</t>
+          <t>O dono confirma o interesse de Vorcaro, mas nega que a compra tenha avançado e contesta a versão das mensagens. Uma das reportagens não afirma explicitamente que a Allure é a agência usada no recrutamento.</t>
         </is>
       </c>
       <c r="K80" s="24" t="inlineStr">
@@ -7109,7 +7109,7 @@
       </c>
       <c r="M80" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo). 22/10/2026: renomeado de "Luri Eventos" para "Allure Eventos".</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
         </is>
       </c>
     </row>

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -1150,7 +1150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:P91"/>
+  <dimension ref="A1:P97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="24" min="1" max="1"/>
@@ -1879,22 +1879,22 @@
       </c>
       <c r="J10" s="37" t="inlineStr">
         <is>
-          <t>Acervo a verdade.: Aos Fatos contou ao menos 43 declarações falsas dele sobre a relação com Vorcaro. Os números do celular variam por fonte (Piauí: 11 meses e 110 registros; Estadão: 3 meses e 6 encontros) e não devem ser somados. Os R$ 134 mi negociados e ≥ R$ 61 mi repassados foram para o filme, o que não comprova recebimento pessoal.</t>
+          <t>Acervo a verdade.: Aos Fatos contou ao menos 43 declarações falsas dele sobre a relação com Vorcaro. Os números do celular variam por fonte (Piauí: 11 meses e 110 registros; Estadão: 3 meses e 6 encontros) e não devem ser somados. Os R$ 134 mi negociados e ≥ R$ 61 mi repassados foram para o filme, o que não comprova recebimento pessoal. Contato no celular de Vorcaro (piauí, 19/10/2026): Não quis se pronunciar à piauí. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
         </is>
       </c>
       <c r="K10" s="37" t="inlineStr">
         <is>
-          <t>Wikipedia pt https://pt.wikipedia.org/wiki/Fl%C3%A1vio_Bolsonaro | Tribuna do Sertão (link acima) | O Povo 23/07/2026 https://www.opovo.com.br/noticias/politica/2026/07/23/amp/andre-mendonca-autoriza-inquerito-sobre-repasses-para-dark-horse-filme-sobre-jair-bolsonaro.html | Resultado do 1º turno https://portaldeprefeitura.com.br/bastidores-da-politica/eleicoes-2026-com-100-das-secoes-totalizadas-flavio-tem-4703-e/633498/ | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal | JB 12/10/2026 https://www.jb.com.br/brasil/justica/2026/10/1061206-moraes-autoriza-flavio-bolsonaro-a-visitar-jair-bolsonaro-em-prisao-domiciliar.html | A investigação sobre o financiamento de Dark Horse (bbc.com) https://www.bbc.com/portuguese/articles/c4g5ky0r25jo | A investigação sobre o financiamento de Dark Horse (em.com.br) https://www.em.com.br/politica/2026/09/7498387-flavio-bolsonaro-vira-investigado-do-dark-horse-que-segue-sob-sigilo.html | O acordo de R$ 134 milhões para o filme (intercept.com.br) https://www.intercept.com.br/2026/05/13/audio-flavio-negociou-vorcaro-milhoes/ | A checagem de declarações sobre Vorcaro (aosfatos.org) https://www.aosfatos.org/noticias/flavio-mentiu-ao-menos-43-vezes-sobre-envolvimento-com-vorcaro/ | Os registros de contato no celular do banqueiro (piaui.uol.com.br) https://piaui.uol.com.br/web/mensagens-celular-flavio-vorcaro/ | As menções a encontros presenciais (estadao.com.br) https://www.estadao.com.br/politica/celular-de-vorcaro-tinha-tres-meses-de-conversa-com-flavio-bolsonaro-e-mencao-a-seis-encontros/ | O voo no jato de Vorcaro em janeiro de 2025 (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-viajou-em-jato-de-vorcaro/ | O apartamento de Fabiano Zettel e Willer Tomaz (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-zettel-tomaz-imovel-vila-nova-conceicao-sao-paulo/ | O aniversário em uma mansão gerida por empresa de Vorcaro (iclnoticias.com.br) https://iclnoticias.com.br/flavio-bolsonaro-aniversario-da-filha-em-mansao/ | E-mails sobre vínculo bancário com Willer Tomaz (noticias.uol.com.br) https://noticias.uol.com.br/colunas/fabio-serapiao/2026/10/10/flavio-dividia-conta-com-suspeito-de-lavar-dinheiro-do-inss-indicam-emails.htm | Endereço e contabilidade compartilhados em Brasília (iclnoticias.com.br) https://iclnoticias.com.br/empresas-de-flavio-bolsonaro-e-careca-do-inss/ | Cargo na Câmara, faculdade e estágio no Rio (bbc.com) https://www.bbc.com/portuguese/brasil-46828487 | A acusação de rachadinhas na Alerj (valor.globo.com) https://valor.globo.com/politica/eleicoes-2026/noticia/2026/09/01/flavio-bolsonaro-relembre-o-processo-da-rachadinha.ghtml | A acusação de rachadinhas na Alerj (folhadelondrina.com.br) https://www.folhadelondrina.com.br/ultimas-noticias/entenda-quais-provas-da-rachadinha-contra-flavio-bolsonaro-ainda-valem-3131387e.html | A investigação da loja Kopenhagen (oglobo.globo.com) https://oglobo.globo.com/politica/alvo-de-investigacao-das-rachadinhas-loja-de-flavio-bolsonaro-no-rio-vendida-1-24867874 | Imóveis comprados pela família e investigações (g1.globo.com) https://g1.globo.com/jornal-nacional/noticia/2022/08/31/reportagem-do-uol-revela-que-51-imoveis-comprados-pela-familia-bolsonaro-foram-pagos-em-dinheiro-vivo.ghtml | Imóveis comprados pela família e investigações (noticias.uol.com.br) https://noticias.uol.com.br/politica/ultimas-noticias/2022/08/30/imoveis-cla-bolsonaro-objeto-de-investigacao-suspeita-dinheiro-vivo.htm | Imóveis comprados pela família e investigações (estadao.com.br) https://www.estadao.com.br/politica/investigacao-sobre-flaviobolsonaro-alcanca-37-imoveis/ | A compra e a quitação da mansão em Brasília (oglobo.globo.com) https://oglobo.globo.com/politica/eleicoes-2026/noticia/2026/08/14/video-mansao-que-fez-patrimonio-de-flavio-disparar-fica-em-terreno-de-2400-m-e-foi-quitada-27-anos-antes-do-previsto.ghtml | A análise do MPF sobre 37 transações imobiliárias (cnnbrasil.com.br) https://www.maisgoias.com.br/politica/procurador-aponta-fortes-indicios-de-lavagem-de-dinheiro-em-bens-de-flavio-bolsonaro/ | A acusação do MP-RJ sobre organização criminosa (g1.globo.com) https://g1.globo.com/rj/rio-de-janeiro/noticia/2019/12/19/mp-do-rj-detalha-suposto-esquema-de-corrupcao-envolvendo-entao-deputado-flavio-bolsonaro.ghtml?utm_source=twitter&amp;utm_medium=social&amp;utm_campaign=g1 | Destinação de emendas e entidades questionadas (revistaforum.com.br) https://revistaforum.com.br/politica/flavio-bolsonaro-emendas-ong-fantasma-e-instituto-de-miliciano/ | Portal Porque (resume piauí, 20/10/2026) https://www.portalporque.com.br/brasil/revista-piaui-aponta-que-flavio-bolsonaro-foi-socio-indireto-de-bet/ | Notícias ao Minuto (resume piauí) https://www.noticiasaominuto.com.br/politica/2422338/flavio-bolsonaro-e-dono-de-bet-entenda-o-que-a-pf-investiga | Mais Goiás (via Folha, 16/10/2026) https://www.maisgoias.com.br/brasil/pf-descobre-voos-de-flavio-bolsonaro-pagos-por-dono-de-bet-que-e-investigado-por-fraudes-no-inss/</t>
+          <t>Wikipedia pt https://pt.wikipedia.org/wiki/Fl%C3%A1vio_Bolsonaro | Tribuna do Sertão (link acima) | O Povo 23/07/2026 https://www.opovo.com.br/noticias/politica/2026/07/23/amp/andre-mendonca-autoriza-inquerito-sobre-repasses-para-dark-horse-filme-sobre-jair-bolsonaro.html | Resultado do 1º turno https://portaldeprefeitura.com.br/bastidores-da-politica/eleicoes-2026-com-100-das-secoes-totalizadas-flavio-tem-4703-e/633498/ | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal | JB 12/10/2026 https://www.jb.com.br/brasil/justica/2026/10/1061206-moraes-autoriza-flavio-bolsonaro-a-visitar-jair-bolsonaro-em-prisao-domiciliar.html | A investigação sobre o financiamento de Dark Horse (bbc.com) https://www.bbc.com/portuguese/articles/c4g5ky0r25jo | A investigação sobre o financiamento de Dark Horse (em.com.br) https://www.em.com.br/politica/2026/09/7498387-flavio-bolsonaro-vira-investigado-do-dark-horse-que-segue-sob-sigilo.html | O acordo de R$ 134 milhões para o filme (intercept.com.br) https://www.intercept.com.br/2026/05/13/audio-flavio-negociou-vorcaro-milhoes/ | A checagem de declarações sobre Vorcaro (aosfatos.org) https://www.aosfatos.org/noticias/flavio-mentiu-ao-menos-43-vezes-sobre-envolvimento-com-vorcaro/ | Os registros de contato no celular do banqueiro (piaui.uol.com.br) https://piaui.uol.com.br/web/mensagens-celular-flavio-vorcaro/ | As menções a encontros presenciais (estadao.com.br) https://www.estadao.com.br/politica/celular-de-vorcaro-tinha-tres-meses-de-conversa-com-flavio-bolsonaro-e-mencao-a-seis-encontros/ | O voo no jato de Vorcaro em janeiro de 2025 (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-viajou-em-jato-de-vorcaro/ | O apartamento de Fabiano Zettel e Willer Tomaz (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-zettel-tomaz-imovel-vila-nova-conceicao-sao-paulo/ | O aniversário em uma mansão gerida por empresa de Vorcaro (iclnoticias.com.br) https://iclnoticias.com.br/flavio-bolsonaro-aniversario-da-filha-em-mansao/ | E-mails sobre vínculo bancário com Willer Tomaz (noticias.uol.com.br) https://noticias.uol.com.br/colunas/fabio-serapiao/2026/10/10/flavio-dividia-conta-com-suspeito-de-lavar-dinheiro-do-inss-indicam-emails.htm | Endereço e contabilidade compartilhados em Brasília (iclnoticias.com.br) https://iclnoticias.com.br/empresas-de-flavio-bolsonaro-e-careca-do-inss/ | Cargo na Câmara, faculdade e estágio no Rio (bbc.com) https://www.bbc.com/portuguese/brasil-46828487 | A acusação de rachadinhas na Alerj (valor.globo.com) https://valor.globo.com/politica/eleicoes-2026/noticia/2026/09/01/flavio-bolsonaro-relembre-o-processo-da-rachadinha.ghtml | A acusação de rachadinhas na Alerj (folhadelondrina.com.br) https://www.folhadelondrina.com.br/ultimas-noticias/entenda-quais-provas-da-rachadinha-contra-flavio-bolsonaro-ainda-valem-3131387e.html | A investigação da loja Kopenhagen (oglobo.globo.com) https://oglobo.globo.com/politica/alvo-de-investigacao-das-rachadinhas-loja-de-flavio-bolsonaro-no-rio-vendida-1-24867874 | Imóveis comprados pela família e investigações (g1.globo.com) https://g1.globo.com/jornal-nacional/noticia/2022/08/31/reportagem-do-uol-revela-que-51-imoveis-comprados-pela-familia-bolsonaro-foram-pagos-em-dinheiro-vivo.ghtml | Imóveis comprados pela família e investigações (noticias.uol.com.br) https://noticias.uol.com.br/politica/ultimas-noticias/2022/08/30/imoveis-cla-bolsonaro-objeto-de-investigacao-suspeita-dinheiro-vivo.htm | Imóveis comprados pela família e investigações (estadao.com.br) https://www.estadao.com.br/politica/investigacao-sobre-flaviobolsonaro-alcanca-37-imoveis/ | A compra e a quitação da mansão em Brasília (oglobo.globo.com) https://oglobo.globo.com/politica/eleicoes-2026/noticia/2026/08/14/video-mansao-que-fez-patrimonio-de-flavio-disparar-fica-em-terreno-de-2400-m-e-foi-quitada-27-anos-antes-do-previsto.ghtml | A análise do MPF sobre 37 transações imobiliárias (cnnbrasil.com.br) https://www.maisgoias.com.br/politica/procurador-aponta-fortes-indicios-de-lavagem-de-dinheiro-em-bens-de-flavio-bolsonaro/ | A acusação do MP-RJ sobre organização criminosa (g1.globo.com) https://g1.globo.com/rj/rio-de-janeiro/noticia/2019/12/19/mp-do-rj-detalha-suposto-esquema-de-corrupcao-envolvendo-entao-deputado-flavio-bolsonaro.ghtml?utm_source=twitter&amp;utm_medium=social&amp;utm_campaign=g1 | Destinação de emendas e entidades questionadas (revistaforum.com.br) https://revistaforum.com.br/politica/flavio-bolsonaro-emendas-ong-fantasma-e-instituto-de-miliciano/ | Portal Porque (resume piauí, 20/10/2026) https://www.portalporque.com.br/brasil/revista-piaui-aponta-que-flavio-bolsonaro-foi-socio-indireto-de-bet/ | Notícias ao Minuto (resume piauí) https://www.noticiasaominuto.com.br/politica/2422338/flavio-bolsonaro-e-dono-de-bet-entenda-o-que-a-pf-investiga | Mais Goiás (via Folha, 16/10/2026) https://www.maisgoias.com.br/brasil/pf-descobre-voos-de-flavio-bolsonaro-pagos-por-dono-de-bet-que-e-investigado-por-fraudes-no-inss/ | Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/</t>
         </is>
       </c>
       <c r="L10" s="37" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M10" s="37" t="inlineStr">
         <is>
-          <t>Resultado do 1º turno; 2º inquérito no STF; Operação Make Up; visitas ao pai liberadas. 21/10/2026: importado do acervo a verdade. (bolsomaster.site). 22/10/2026: rodada UOL News (bets, Loterj, hangar, Weverton).</t>
+          <t>Resultado do 1º turno; 2º inquérito no STF; Operação Make Up; visitas ao pai liberadas. 21/10/2026: importado do acervo a verdade. (bolsomaster.site). 22/10/2026: rodada UOL News (bets, Loterj, hangar, Weverton). 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem.</t>
         </is>
       </c>
       <c r="N10" s="24" t="inlineStr">
@@ -3451,22 +3451,22 @@
       </c>
       <c r="J31" s="37" t="inlineStr">
         <is>
-          <t>Identificação confirmada: o "Círio Nogueira" da transcrição é o senador Ciro Nogueira, investigado no caso Master (busca em 07/05/2026). A aba Notes original ainda diz "inferida".</t>
+          <t>Identificação confirmada: o "Círio Nogueira" da transcrição é o senador Ciro Nogueira, investigado no caso Master (busca em 07/05/2026). A aba Notes original ainda diz "inferida". Contato no celular de Vorcaro (piauí, 19/10/2026): Não respondeu à piauí. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
         </is>
       </c>
       <c r="K31" s="37" t="inlineStr">
         <is>
-          <t>Correio da Manhã 07/05/2026 https://www.correiodamanha.com.br/politica/2026/05/283952-ciro-nogueira-receberia-mesada-do-master-diz-investigacao.html | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal | Supostos pagamentos mensais a Ciro Nogueira (agenciabrasil.ebc.com.br) https://agenciabrasil.ebc.com.br/justica/noticia/2026-05/mesada-e-viagens-internacionais-veja-o-que-pf-diz-sobre-ciro-nogueira | Viagens de Ciro e a suspeita de contrapartida política (g1.globo.com) https://g1.globo.com/jornal-nacional/noticia/2026/05/08/pf-suspeita-que-vorcaro-pagou-ao-menos-3-viagens-internacionais-do-senador-ciro-nogueira-do-pp.ghtml | Ciro na Operação Compliance Zero (agenciabrasil.ebc.com.br) https://agenciabrasil.ebc.com.br/justica/noticia/2026-05/policia-federal-deflagra-5a-fase-da-operacao-compliance-zero | Imagens de Ciro e Vorcaro nos Alpes (cnnbrasil.com.br) https://www.cnnbrasil.com.br/blogs/debora-bergamasco/politica/imagens-obtidas-pela-pf-mostram-ciro-nogueira-e-vorcaro-nos-alpes-franceses/ | O custeio da viagem a Courchevel (piaui.uol.com.br) https://piaui.uol.com.br/web/ciro-nogueira-daniel-vorcaro-alpes-franceses-imagens/</t>
+          <t>Correio da Manhã 07/05/2026 https://www.correiodamanha.com.br/politica/2026/05/283952-ciro-nogueira-receberia-mesada-do-master-diz-investigacao.html | Wikipedia (Banco Master scandal) https://en.wikipedia.org/wiki/Banco_Master_scandal | Supostos pagamentos mensais a Ciro Nogueira (agenciabrasil.ebc.com.br) https://agenciabrasil.ebc.com.br/justica/noticia/2026-05/mesada-e-viagens-internacionais-veja-o-que-pf-diz-sobre-ciro-nogueira | Viagens de Ciro e a suspeita de contrapartida política (g1.globo.com) https://g1.globo.com/jornal-nacional/noticia/2026/05/08/pf-suspeita-que-vorcaro-pagou-ao-menos-3-viagens-internacionais-do-senador-ciro-nogueira-do-pp.ghtml | Ciro na Operação Compliance Zero (agenciabrasil.ebc.com.br) https://agenciabrasil.ebc.com.br/justica/noticia/2026-05/policia-federal-deflagra-5a-fase-da-operacao-compliance-zero | Imagens de Ciro e Vorcaro nos Alpes (cnnbrasil.com.br) https://www.cnnbrasil.com.br/blogs/debora-bergamasco/politica/imagens-obtidas-pela-pf-mostram-ciro-nogueira-e-vorcaro-nos-alpes-franceses/ | O custeio da viagem a Courchevel (piaui.uol.com.br) https://piaui.uol.com.br/web/ciro-nogueira-daniel-vorcaro-alpes-franceses-imagens/ | Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/</t>
         </is>
       </c>
       <c r="L31" s="37" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M31" s="37" t="inlineStr">
         <is>
-          <t>Identificação tratada como confirmada (antes: inferida); busca em 07/05/2026. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
+          <t>Identificação tratada como confirmada (antes: inferida); busca em 07/05/2026. 21/10/2026: importado do acervo a verdade. (bolsomaster.site). 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem.</t>
         </is>
       </c>
       <c r="N31" s="24" t="inlineStr">
@@ -3615,22 +3615,22 @@
       </c>
       <c r="J33" s="37" t="inlineStr">
         <is>
-          <t>Dados do acervo a verdade.; fontes não reverificadas uma a uma.</t>
+          <t>Dados do acervo a verdade.; fontes não reverificadas uma a uma. Contato no celular de Vorcaro (piauí, 19/10/2026): Respondeu à piauí que deixou o setor público em dez/2022 e conheceu Vorcaro no fim de 2023. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
         </is>
       </c>
       <c r="K33" s="37" t="inlineStr">
         <is>
-          <t>Fábio Faria como interlocutor de Vorcaro (piaui.uol.com.br) https://piaui.uol.com.br/web/fabio-faria-daniel-vorcaro-lobby/ | R$ 67,5 milhões por projeto de Fábio Faria (tab.uol.com.br) https://tab.uol.com.br/noticias/redacao/2026/01/29/vorcaro-pagou-r-675-mi-em-projeto-eolico-de-fabio-faria-ex-ministro.htm | Convites a autoridades para festas e encontros (piaui.uol.com.br) https://piaui.uol.com.br/web/festa-suicas-vorcaro-fabio-faria/ | O grupo com Hugo Motta, Ciro e Fábio Faria (gazetadopovo.com.br) https://www.gazetadopovo.com.br/republica/vorcaro-grupo-motta-ciro-nogueira-fabio-faria-organizar-encontros/ | A intermediação de contatos com Moraes (g1.globo.com) https://g1.globo.com/politica/noticia/2026/09/01/ex-ministro-fabio-faria-atuou-para-intermediar-contatos-entre-vorcaro-e-moraes-aponta-pf.ghtml</t>
+          <t>Fábio Faria como interlocutor de Vorcaro (piaui.uol.com.br) https://piaui.uol.com.br/web/fabio-faria-daniel-vorcaro-lobby/ | R$ 67,5 milhões por projeto de Fábio Faria (tab.uol.com.br) https://tab.uol.com.br/noticias/redacao/2026/01/29/vorcaro-pagou-r-675-mi-em-projeto-eolico-de-fabio-faria-ex-ministro.htm | Convites a autoridades para festas e encontros (piaui.uol.com.br) https://piaui.uol.com.br/web/festa-suicas-vorcaro-fabio-faria/ | O grupo com Hugo Motta, Ciro e Fábio Faria (gazetadopovo.com.br) https://www.gazetadopovo.com.br/republica/vorcaro-grupo-motta-ciro-nogueira-fabio-faria-organizar-encontros/ | A intermediação de contatos com Moraes (g1.globo.com) https://g1.globo.com/politica/noticia/2026/09/01/ex-ministro-fabio-faria-atuou-para-intermediar-contatos-entre-vorcaro-e-moraes-aponta-pf.ghtml | Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/</t>
         </is>
       </c>
       <c r="L33" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M33" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada.</t>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada. 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem.</t>
         </is>
       </c>
       <c r="N33" s="24" t="inlineStr">
@@ -3697,22 +3697,22 @@
       </c>
       <c r="J34" s="37" t="inlineStr">
         <is>
-          <t>Situação de investigado vem do PDF do acervo; não reverificada.</t>
+          <t>Situação de investigado vem do PDF do acervo; não reverificada. Contato no celular de Vorcaro (piauí, 19/10/2026): A reportagem da piauí não reproduz a resposta dele. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
         </is>
       </c>
       <c r="K34" s="37" t="inlineStr">
         <is>
-          <t>Mario Frias e a produção de Dark Horse (intercept.com.br) https://www.intercept.com.br/2026/05/19/audio-mario-frias-daniel-vorcaro/</t>
+          <t>Mario Frias e a produção de Dark Horse (intercept.com.br) https://www.intercept.com.br/2026/05/19/audio-mario-frias-daniel-vorcaro/ | Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/</t>
         </is>
       </c>
       <c r="L34" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M34" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada.</t>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada. 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem.</t>
         </is>
       </c>
       <c r="N34" s="24" t="inlineStr">
@@ -4725,22 +4725,22 @@
       </c>
       <c r="J48" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Contato no celular de Vorcaro (piauí, 19/10/2026): A reportagem da piauí não reproduz a resposta dele. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
         </is>
       </c>
       <c r="K48" s="24" t="inlineStr">
         <is>
-          <t>TSE torna Castro inelegível (jovempan.com.br) https://jovempan.com.br/politica/tse-forma-maioria-para-tornar-castro-inelegivel-por-8-anos/ | Castro desiste do Senado após operações (oantagonista.com.br) https://oantagonista.com.br/brasil/claudio-castro-comunica-ao-pl-desistencia-de-candidatura-ao-senado-apos-operacoes/ | Mendonça votou a favor de Castro 4 vezes (iclnoticias.com.br) https://iclnoticias.com.br/mendonca-votou-a-favor-de-castro-4-vezes/</t>
+          <t>TSE torna Castro inelegível (jovempan.com.br) https://jovempan.com.br/politica/tse-forma-maioria-para-tornar-castro-inelegivel-por-8-anos/ | Castro desiste do Senado após operações (oantagonista.com.br) https://oantagonista.com.br/brasil/claudio-castro-comunica-ao-pl-desistencia-de-candidatura-ao-senado-apos-operacoes/ | Mendonça votou a favor de Castro 4 vezes (iclnoticias.com.br) https://iclnoticias.com.br/mendonca-votou-a-favor-de-castro-4-vezes/ | Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/</t>
         </is>
       </c>
       <c r="L48" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M48" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem.</t>
         </is>
       </c>
       <c r="N48" s="24" t="inlineStr">
@@ -4971,22 +4971,22 @@
       </c>
       <c r="J51" s="24" t="inlineStr">
         <is>
-          <t>As reportagens não trazem resposta dele.</t>
+          <t>As reportagens não trazem resposta dele. Contato no celular de Vorcaro (piauí, 19/10/2026): Não respondeu à piauí. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
         </is>
       </c>
       <c r="K51" s="24" t="inlineStr">
         <is>
-          <t>Mensagens e áudios inéditos sobre Mendonça (iclnoticias.com.br) https://iclnoticias.com.br/vaza-mendonca-mensagens-e-audios-ineditos/ | Áudios revelam encontro entre Vorcaro e Mendonça (bahianoticias.com.br) https://www.bahianoticias.com.br/justica/noticia/75274-audios-e-mensagens-revelam-encontro-entre-vorcaro-e-mendonca-ministro-admite-e-diz-que-se-limitou-a-ouvi-lo | Operação de Dino e afastamento na PF (iclnoticias.com.br) https://iclnoticias.com.br/mendonca-cesinha-madureira-vorcaro-dino/</t>
+          <t>Mensagens e áudios inéditos sobre Mendonça (iclnoticias.com.br) https://iclnoticias.com.br/vaza-mendonca-mensagens-e-audios-ineditos/ | Áudios revelam encontro entre Vorcaro e Mendonça (bahianoticias.com.br) https://www.bahianoticias.com.br/justica/noticia/75274-audios-e-mensagens-revelam-encontro-entre-vorcaro-e-mendonca-ministro-admite-e-diz-que-se-limitou-a-ouvi-lo | Operação de Dino e afastamento na PF (iclnoticias.com.br) https://iclnoticias.com.br/mendonca-cesinha-madureira-vorcaro-dino/ | Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/</t>
         </is>
       </c>
       <c r="L51" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M51" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem.</t>
         </is>
       </c>
       <c r="N51" s="24" t="inlineStr">
@@ -5120,22 +5120,22 @@
       </c>
       <c r="J53" s="24" t="inlineStr">
         <is>
-          <t>A assessoria de Motta disse que não se pronunciaria.</t>
+          <t>A assessoria de Motta disse que não se pronunciaria. Contato no celular de Vorcaro (piauí, 19/10/2026): Não respondeu à piauí. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
         </is>
       </c>
       <c r="K53" s="24" t="inlineStr">
         <is>
-          <t>Grupo com Motta, Ciro e Faria organizava encontros (gazetadopovo.com.br) https://www.gazetadopovo.com.br/republica/vorcaro-grupo-motta-ciro-nogueira-fabio-faria-organizar-encontros/ | Vorcaro cita encontros com Hugo Motta (poder360.com.br) https://www.poder360.com.br/poder-economia/vorcaro-cita-encontros-com-hugo-motta-e-elogia-emenda-de-ciro-nogueira/</t>
+          <t>Grupo com Motta, Ciro e Faria organizava encontros (gazetadopovo.com.br) https://www.gazetadopovo.com.br/republica/vorcaro-grupo-motta-ciro-nogueira-fabio-faria-organizar-encontros/ | Vorcaro cita encontros com Hugo Motta (poder360.com.br) https://www.poder360.com.br/poder-economia/vorcaro-cita-encontros-com-hugo-motta-e-elogia-emenda-de-ciro-nogueira/ | Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/</t>
         </is>
       </c>
       <c r="L53" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M53" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem.</t>
         </is>
       </c>
       <c r="N53" s="24" t="inlineStr">
@@ -5202,22 +5202,22 @@
       </c>
       <c r="J54" s="24" t="inlineStr">
         <is>
-          <t>Marçal confirmou o voo e disse que se ofereceu para pagar; segundo ele, Vorcaro sugeriu que testasse o avião antes de comprar um parecido.</t>
+          <t>Marçal confirmou o voo e disse que se ofereceu para pagar; segundo ele, Vorcaro sugeriu que testasse o avião antes de comprar um parecido. Contato no celular de Vorcaro (piauí, 19/10/2026): Não respondeu à piauí. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
         </is>
       </c>
       <c r="K54" s="24" t="inlineStr">
         <is>
-          <t>Empresa de Vorcaro pagou voo de Marçal (gp1.com.br) https://www.gp1.com.br/brasil/noticia/2026/10/2/empresa-ligada-a-daniel-vorcaro-pagou-voo-de-r-117-milhao-usado-por-pablo-marcal-633016.html | Vorcaro bancou voo e mandou ocultar valor (revistaforum.com.br) https://revistaforum.com.br/politica/vorcaro-voo-pablo-marcal/</t>
+          <t>Empresa de Vorcaro pagou voo de Marçal (gp1.com.br) https://www.gp1.com.br/brasil/noticia/2026/10/2/empresa-ligada-a-daniel-vorcaro-pagou-voo-de-r-117-milhao-usado-por-pablo-marcal-633016.html | Vorcaro bancou voo e mandou ocultar valor (revistaforum.com.br) https://revistaforum.com.br/politica/vorcaro-voo-pablo-marcal/ | Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/</t>
         </is>
       </c>
       <c r="L54" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M54" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem.</t>
         </is>
       </c>
       <c r="N54" s="24" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="J55" s="24" t="inlineStr">
         <is>
-          <t>As mensagens mostram o convite, mas não se ele compareceu.</t>
+          <t>As mensagens mostram o convite, mas não se ele compareceu. Contato no celular de Vorcaro (piauí, 19/10/2026): Respondeu à piauí que é advogado, que só conheceu Vorcaro mais de um ano após deixar o serviço público e que as interações foram profissionais. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
         </is>
       </c>
       <c r="K55" s="24" t="inlineStr">
         <is>
-          <t>Mensagens e áudios inéditos sobre Mendonça (iclnoticias.com.br) https://iclnoticias.com.br/vaza-mendonca-mensagens-e-audios-ineditos/ | Áudios revelam encontro entre Vorcaro e Mendonça (bahianoticias.com.br) https://www.bahianoticias.com.br/justica/noticia/75274-audios-e-mensagens-revelam-encontro-entre-vorcaro-e-mendonca-ministro-admite-e-diz-que-se-limitou-a-ouvi-lo</t>
+          <t>Mensagens e áudios inéditos sobre Mendonça (iclnoticias.com.br) https://iclnoticias.com.br/vaza-mendonca-mensagens-e-audios-ineditos/ | Áudios revelam encontro entre Vorcaro e Mendonça (bahianoticias.com.br) https://www.bahianoticias.com.br/justica/noticia/75274-audios-e-mensagens-revelam-encontro-entre-vorcaro-e-mendonca-ministro-admite-e-diz-que-se-limitou-a-ouvi-lo | Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/</t>
         </is>
       </c>
       <c r="L55" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M55" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem.</t>
         </is>
       </c>
       <c r="N55" s="24" t="inlineStr">
@@ -7877,6 +7877,396 @@
       <c r="M91" s="24" t="inlineStr">
         <is>
           <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="24" t="inlineStr">
+        <is>
+          <t>rueda</t>
+        </is>
+      </c>
+      <c r="B92" s="24" t="inlineStr">
+        <is>
+          <t>Antonio Rueda</t>
+        </is>
+      </c>
+      <c r="C92" s="24" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="D92" s="24" t="inlineStr">
+        <is>
+          <t>Presidente do União Brasil desde 2024. Admitiu à piauí ter prestado serviços de advocacia ao Master (“dezenas de pareceres e centenas de reuniões”). Aparece com 2.712 interações no celular de Vorcaro (nov/2023 a set/2025), o 4º maior volume entre os 56 políticos; 64% delas expiraram ou foram apagadas, quase todas depois de 12/07/2024, data em que a planilha registra um temporizador de 1 dia.</t>
+        </is>
+      </c>
+      <c r="E92" s="24" t="n"/>
+      <c r="F92" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G92" s="24" t="inlineStr">
+        <is>
+          <t>As fontes lidas não informam se ele é formalmente investigado. Vorcaro o cita em proposta de delação rejeitada pela PF e pela PGR (UOL, set/2026); ele nega irregularidades.</t>
+        </is>
+      </c>
+      <c r="H92" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I92" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J92" s="24" t="inlineStr">
+        <is>
+          <t>Diz ter apenas “contatos sociais eventuais” com Vorcaro e que atuou como advogado do banco (“Prezado, eu era advogado do banco. Obrigado.”, à piauí). Nega irregularidades e disse ao UOL ter dificuldade em comentar documento ao qual não teve acesso. A piauí cita 2.636 interações (sem as 76 ligações do iPhone); aqui vale o total da planilha. Os números de contato são do levantamento piauí/InterSecLab sobre o celular de Vorcaro (base 18/11/2025): medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
+        </is>
+      </c>
+      <c r="K92" s="24" t="inlineStr">
+        <is>
+          <t>Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/ | Rueda admite que advogou para o Master (infomoney.com.br) https://www.infomoney.com.br/politica/rueda-admite-que-advogou-para-o-master-apos-alegar-relacao-social-com-vorcaro/ | ACM Neto e Rueda recebiam 10% de aportes, diz Vorcaro em proposta de delação (bahianoticias.com.br) https://www.bahianoticias.com.br/noticia/320957-acm-neto-e-rueda-recebiam-10-de-aportes-de-previdencias-do-banco-master-diz-vorcaro-em-proposta-de-delacao</t>
+        </is>
+      </c>
+      <c r="L92" s="24" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="M92" s="24" t="inlineStr">
+        <is>
+          <t>23/10/2026: perfil novo (base piauí/InterSecLab, rodada de verificação).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="24" t="inlineStr">
+        <is>
+          <t>wajngarten</t>
+        </is>
+      </c>
+      <c r="B93" s="24" t="inlineStr">
+        <is>
+          <t>Fabio Wajngarten</t>
+        </is>
+      </c>
+      <c r="C93" s="24" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="D93" s="24" t="inlineStr">
+        <is>
+          <t>Ex-secretário especial de Comunicação Social do governo Bolsonaro. Integra a defesa de Vorcaro na área de comunicação desde o 1º semestre de 2025. Segundo a Folha (documentos da Receita enviados à CPI do Crime), a WF Comunicação, empresa dele, recebeu do Banco Master ao menos R$ 3,8 mi em 2025. A piauí cita mensagem de 28/04/2025 com dados para pagamento de R$ 3,2 mi à WF. Aparece com 1.151 interações no celular de Vorcaro (mar a nov/2025), o 6º maior volume; 93% expiraram.</t>
+        </is>
+      </c>
+      <c r="E93" s="24" t="n"/>
+      <c r="F93" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G93" s="24" t="inlineStr">
+        <is>
+          <t>As fontes lidas não informam se ele é formalmente investigado.</t>
+        </is>
+      </c>
+      <c r="H93" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I93" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J93" s="24" t="inlineStr">
+        <is>
+          <t>Diz à piauí que atuou como “agregador de notícias”, distribuindo notícias a mais de 200 contatos; segundo a Folha, afirma que o contrato é confidencial e que não é mais politicamente exposto. Os R$ 3,2 mi (mensagem de 28/04/2025, piauí) e os R$ 3,8 mi (Receita, via Folha) são dados distintos: não somar nem igualar. Os números de contato são do levantamento piauí/InterSecLab sobre o celular de Vorcaro (base 18/11/2025): medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
+        </is>
+      </c>
+      <c r="K93" s="24" t="inlineStr">
+        <is>
+          <t>Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/ | Braço direito de Bolsonaro recebe R$ 3 milhões para defender Vorcaro (atarde.com.br) https://atarde.com.br/politica/braco-direito-de-bolsonaro-recebe-r-3-milhoes-para-defender-vorcaro-1385380 | Ex-secretário de Bolsonaro recebeu R$ 3,8 milhões para defender Vorcaro (portaltela.com) https://www.portaltela.com/noticias/politica/2026/04/09/ex-secretario-de-bolsonaro-recebeu-38-milhoes-para-defender-vorcaro/</t>
+        </is>
+      </c>
+      <c r="L93" s="24" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="M93" s="24" t="inlineStr">
+        <is>
+          <t>23/10/2026: perfil novo (base piauí/InterSecLab, rodada de verificação).</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="24" t="inlineStr">
+        <is>
+          <t>mantega</t>
+        </is>
+      </c>
+      <c r="B94" s="24" t="inlineStr">
+        <is>
+          <t>Guido Mantega</t>
+        </is>
+      </c>
+      <c r="C94" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D94" s="24" t="inlineStr">
+        <is>
+          <t>Ex-ministro da Fazenda (PT). Disse à piauí ter sido contratado pelo Master entre 2024 e 2025 para consultoria econômica. Aparece com 323 interações no celular de Vorcaro (jun/2024 a nov/2025); 94% expiraram e as 19 ligações não ficaram registradas. Mensagens divulgadas pelo Estadão mostram Vorcaro e um advogado tentando levá-lo a Lula em 2025.</t>
+        </is>
+      </c>
+      <c r="E94" s="24" t="n"/>
+      <c r="F94" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G94" s="24" t="inlineStr">
+        <is>
+          <t>As fontes lidas não informam se ele é formalmente investigado.</t>
+        </is>
+      </c>
+      <c r="H94" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I94" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J94" s="24" t="inlineStr">
+        <is>
+          <t>O Planalto diz que Lula recebeu Vorcaro uma única vez (04/12/2024), acompanhado de Mantega, e que não houve outro contato. A matéria da Gazeta do Povo não traz manifestação de Mantega sobre as mensagens. Os números de contato são do levantamento piauí/InterSecLab sobre o celular de Vorcaro (base 18/11/2025): medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
+        </is>
+      </c>
+      <c r="K94" s="24" t="inlineStr">
+        <is>
+          <t>Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/ | Vorcaro acionou Mantega e buscou nova reunião com Lula em 2025 (gazetadopovo.com.br) https://www.gazetadopovo.com.br/republica/vorcaro-acionou-mantega-e-buscou-nova-reuniao-com-lula-em-2025/</t>
+        </is>
+      </c>
+      <c r="L94" s="24" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="M94" s="24" t="inlineStr">
+        <is>
+          <t>23/10/2026: perfil novo (base piauí/InterSecLab, rodada de verificação).</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="24" t="inlineStr">
+        <is>
+          <t>doria</t>
+        </is>
+      </c>
+      <c r="B95" s="24" t="inlineStr">
+        <is>
+          <t>João Doria</t>
+        </is>
+      </c>
+      <c r="C95" s="24" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="D95" s="24" t="inlineStr">
+        <is>
+          <t>Ex-governador de São Paulo e fundador do Grupo Lide. Aparece com 2.309 interações no celular de Vorcaro (abr/2022 a nov/2025), o 5º maior volume; 99,7% ainda legíveis. Em mensagem de maio/2025, disse estar “preocupado” com Vorcaro e propôs uma conversa reservada; um print no processo indica que Vorcaro retornou a ligação.</t>
+        </is>
+      </c>
+      <c r="E95" s="24" t="inlineStr">
+        <is>
+          <t>São Paulo (SP)</t>
+        </is>
+      </c>
+      <c r="F95" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G95" s="24" t="inlineStr">
+        <is>
+          <t>As fontes lidas não informam se ele é formalmente investigado.</t>
+        </is>
+      </c>
+      <c r="H95" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I95" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J95" s="24" t="inlineStr">
+        <is>
+          <t>A assessoria dele confirma o diálogo, diz que a mensagem foi enviada em maio/2025, antes de qualquer tema público grave sobre o Master, e que foi “apenas um gesto cordial”. O texto da piauí não comenta o caso dele. Os números de contato são do levantamento piauí/InterSecLab sobre o celular de Vorcaro (base 18/11/2025): medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
+        </is>
+      </c>
+      <c r="K95" s="24" t="inlineStr">
+        <is>
+          <t>Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/ | “Foi apenas um gesto cordial”, diz Doria (poder360.com.br) https://www.poder360.com.br/poder-gente/foi-apenas-um-gesto-cordial-diz-doria-sobre-mensagem-a-vorcaro/ | Em mensagem, Doria se diz preocupado com Vorcaro (cnnbrasil.com.br) https://www.cnnbrasil.com.br/blogs/gustavo-uribe/politica/em-mensagem-doria-se-diz-preocupado-com-vorcaro-e-pede-conversa-reservada/</t>
+        </is>
+      </c>
+      <c r="L95" s="24" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="M95" s="24" t="inlineStr">
+        <is>
+          <t>23/10/2026: perfil novo (base piauí/InterSecLab, rodada de verificação).</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="24" t="inlineStr">
+        <is>
+          <t>bacelar</t>
+        </is>
+      </c>
+      <c r="B96" s="24" t="inlineStr">
+        <is>
+          <t>João Carlos Bacelar</t>
+        </is>
+      </c>
+      <c r="C96" s="24" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="D96" s="24" t="inlineStr">
+        <is>
+          <t>Deputado federal (PL-BA). A PF encontrou, em endereço ligado a Vorcaro, uma pasta com o nome dele e um termo de opção de compra de um terreno de ~892 mil m² em Trancoso (BA), avaliado em ~R$ 250 mi, em nome da empresa dele (Costa Esmeralda). O documento não cita Vorcaro nem o Master; a defesa de Vorcaro pediu a remessa do caso ao STF e Toffoli aceitou em 03/12/2025. Aparece com 597 interações no celular de Vorcaro (jul/2024 a nov/2025); 98% ainda legíveis.</t>
+        </is>
+      </c>
+      <c r="E96" s="24" t="inlineStr">
+        <is>
+          <t>Bahia (BA); mandato em Brasília</t>
+        </is>
+      </c>
+      <c r="F96" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G96" s="24" t="inlineStr">
+        <is>
+          <t>Em 01/12/2025 a PF ainda não havia analisado se há indícios de irregularidade no documento (Estadão). O caso foi enviado ao STF por decisão de Toffoli.</t>
+        </is>
+      </c>
+      <c r="H96" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I96" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J96" s="24" t="inlineStr">
+        <is>
+          <t>Bacelar diz que ajudou a montar um fundo para um empreendimento em Trancoso, que Vorcaro o consultou sobre o imóvel, que o negócio “não se concretizou” e que o documento deu a Vorcaro a opção de compra. Questionado sobre a ausência do nome de Vorcaro no papel, não respondeu. Os números de contato são do levantamento piauí/InterSecLab sobre o celular de Vorcaro (base 18/11/2025): medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
+        </is>
+      </c>
+      <c r="K96" s="24" t="inlineStr">
+        <is>
+          <t>Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/ | PF encontra documentos sobre negócio imobiliário entre Vorcaro e Bacelar (bahianoticias.com.br) https://www.bahianoticias.com.br/noticia/311096-pf-encontra-documentos-sobre-negocio-imobiliario-entre-vorcaro-e-deputado-jonga-bacelar-durante-investigacao-do-banco-master | Documento com Vorcaro previa compra de terreno de R$ 250 milhões por deputado (timesbrasil.com.br) https://timesbrasil.com.br/brasil/documento-com-vorcaro-previa-compra-de-casa-de-r-250-milhoes-por-deputado-e-levou-caso-ao-stf/</t>
+        </is>
+      </c>
+      <c r="L96" s="24" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="M96" s="24" t="inlineStr">
+        <is>
+          <t>23/10/2026: perfil novo (base piauí/InterSecLab, rodada de verificação).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="24" t="inlineStr">
+        <is>
+          <t>feitosa</t>
+        </is>
+      </c>
+      <c r="B97" s="24" t="inlineStr">
+        <is>
+          <t>Chiquinho Feitosa</t>
+        </is>
+      </c>
+      <c r="C97" s="24" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="D97" s="24" t="inlineStr">
+        <is>
+          <t>Ex-senador e presidente do Republicanos no Ceará; à época cunhado do ministro do STF Gilmar Mendes. Mensagens obtidas pela PF indicam que foi apresentado a Vorcaro em abr/2024 e se ofereceu como ponte com Gilmar em temas de interesse do Master, como um processo de precatórios do setor sucroalcooleiro. Aparece com 446 interações no celular de Vorcaro (abr/2024 a mai/2025); 85% ainda legíveis.</t>
+        </is>
+      </c>
+      <c r="E97" s="24" t="inlineStr">
+        <is>
+          <t>Ceará (CE)</t>
+        </is>
+      </c>
+      <c r="F97" s="24" t="inlineStr">
+        <is>
+          <t>Vivo</t>
+        </is>
+      </c>
+      <c r="G97" s="24" t="inlineStr">
+        <is>
+          <t>As fontes lidas não informam se ele é formalmente investigado.</t>
+        </is>
+      </c>
+      <c r="H97" s="24" t="inlineStr">
+        <is>
+          <t>Citado, sem acusação</t>
+        </is>
+      </c>
+      <c r="I97" s="24" t="inlineStr">
+        <is>
+          <t>Nada nas fontes.</t>
+        </is>
+      </c>
+      <c r="J97" s="24" t="inlineStr">
+        <is>
+          <t>Não respondeu à piauí nem aos veículos citados. Gilmar Mendes nega que o jantar citado nas mensagens tenha ocorrido, diz que elas foram trocadas por terceiros e que votou contra pagamentos desse tipo. O advogado citado nas mensagens diz que não houve irregularidade. Os números de contato são do levantamento piauí/InterSecLab sobre o celular de Vorcaro (base 18/11/2025): medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
+        </is>
+      </c>
+      <c r="K97" s="24" t="inlineStr">
+        <is>
+          <t>Piauí: 71% das interações de Vorcaro com políticos eram do governo Bolsonaro (piaui.uol.com.br) https://piaui.uol.com.br/web/mais-de-70-das-interacoes-do-celular-de-vorcaro-com-politicos-eram-com-membros-do-governo-bolsonaro/ | Chiquinho Feitosa teria atuado como ponte entre Vorcaro e Gilmar (mais.opovo.com.br) https://mais.opovo.com.br/jornal/politica/2026/09/19/chiquinho-feitosa-teria-atuado-como-ponte-entre-vorcaro-e-ex-mulher-de-ministro-aponta-pf.html | Mensagens apontam tentativa de aproximar Vorcaro e Gilmar (timesbrasil.com.br) https://timesbrasil.com.br/brasil/mensagens-apontam-tentativa-de-aproximar-vorcaro-e-gilmar/</t>
+        </is>
+      </c>
+      <c r="L97" s="24" t="inlineStr">
+        <is>
+          <t>23/10/2026</t>
+        </is>
+      </c>
+      <c r="M97" s="24" t="inlineStr">
+        <is>
+          <t>23/10/2026: perfil novo (base piauí/InterSecLab, rodada de verificação).</t>
         </is>
       </c>
     </row>
@@ -7894,7 +8284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:J91"/>
+  <dimension ref="A1:J97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="24" min="1" max="1"/>
@@ -7984,7 +8374,7 @@
         </is>
       </c>
       <c r="F2" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A2)+COUNTIF(Edges!$B$2:$B$198,A2)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A2)+COUNTIF(Edges!$B$2:$B$221,A2)</f>
         <v/>
       </c>
       <c r="G2" s="24" t="n"/>
@@ -8019,7 +8409,7 @@
         </is>
       </c>
       <c r="F3" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A3)+COUNTIF(Edges!$B$2:$B$198,A3)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A3)+COUNTIF(Edges!$B$2:$B$221,A3)</f>
         <v/>
       </c>
     </row>
@@ -8050,7 +8440,7 @@
         </is>
       </c>
       <c r="F4" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A4)+COUNTIF(Edges!$B$2:$B$198,A4)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A4)+COUNTIF(Edges!$B$2:$B$221,A4)</f>
         <v/>
       </c>
     </row>
@@ -8081,7 +8471,7 @@
         </is>
       </c>
       <c r="F5" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A5)+COUNTIF(Edges!$B$2:$B$198,A5)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A5)+COUNTIF(Edges!$B$2:$B$221,A5)</f>
         <v/>
       </c>
     </row>
@@ -8112,7 +8502,7 @@
         </is>
       </c>
       <c r="F6" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A6)+COUNTIF(Edges!$B$2:$B$198,A6)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A6)+COUNTIF(Edges!$B$2:$B$221,A6)</f>
         <v/>
       </c>
     </row>
@@ -8143,7 +8533,7 @@
         </is>
       </c>
       <c r="F7" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A7)+COUNTIF(Edges!$B$2:$B$198,A7)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A7)+COUNTIF(Edges!$B$2:$B$221,A7)</f>
         <v/>
       </c>
     </row>
@@ -8174,7 +8564,7 @@
         </is>
       </c>
       <c r="F8" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A8)+COUNTIF(Edges!$B$2:$B$198,A8)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A8)+COUNTIF(Edges!$B$2:$B$221,A8)</f>
         <v/>
       </c>
       <c r="G8" s="24" t="n"/>
@@ -8209,7 +8599,7 @@
         </is>
       </c>
       <c r="F9" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A9)+COUNTIF(Edges!$B$2:$B$198,A9)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A9)+COUNTIF(Edges!$B$2:$B$221,A9)</f>
         <v/>
       </c>
       <c r="G9" s="24" t="n"/>
@@ -8244,7 +8634,7 @@
         </is>
       </c>
       <c r="F10" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A10)+COUNTIF(Edges!$B$2:$B$198,A10)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A10)+COUNTIF(Edges!$B$2:$B$221,A10)</f>
         <v/>
       </c>
     </row>
@@ -8275,7 +8665,7 @@
         </is>
       </c>
       <c r="F11" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A11)+COUNTIF(Edges!$B$2:$B$198,A11)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A11)+COUNTIF(Edges!$B$2:$B$221,A11)</f>
         <v/>
       </c>
       <c r="G11" s="24" t="n"/>
@@ -8310,7 +8700,7 @@
         </is>
       </c>
       <c r="F12" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A12)+COUNTIF(Edges!$B$2:$B$198,A12)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A12)+COUNTIF(Edges!$B$2:$B$221,A12)</f>
         <v/>
       </c>
       <c r="G12" s="24" t="inlineStr">
@@ -8357,7 +8747,7 @@
         </is>
       </c>
       <c r="F13" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A13)+COUNTIF(Edges!$B$2:$B$198,A13)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A13)+COUNTIF(Edges!$B$2:$B$221,A13)</f>
         <v/>
       </c>
     </row>
@@ -8388,7 +8778,7 @@
         </is>
       </c>
       <c r="F14" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A14)+COUNTIF(Edges!$B$2:$B$198,A14)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A14)+COUNTIF(Edges!$B$2:$B$221,A14)</f>
         <v/>
       </c>
       <c r="G14" s="24" t="n"/>
@@ -8423,7 +8813,7 @@
         </is>
       </c>
       <c r="F15" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A15)+COUNTIF(Edges!$B$2:$B$198,A15)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A15)+COUNTIF(Edges!$B$2:$B$221,A15)</f>
         <v/>
       </c>
       <c r="G15" s="24" t="n"/>
@@ -8458,7 +8848,7 @@
         </is>
       </c>
       <c r="F16" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A16)+COUNTIF(Edges!$B$2:$B$198,A16)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A16)+COUNTIF(Edges!$B$2:$B$221,A16)</f>
         <v/>
       </c>
       <c r="G16" s="24" t="inlineStr">
@@ -8505,7 +8895,7 @@
         </is>
       </c>
       <c r="F17" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A17)+COUNTIF(Edges!$B$2:$B$198,A17)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A17)+COUNTIF(Edges!$B$2:$B$221,A17)</f>
         <v/>
       </c>
       <c r="G17" s="24" t="inlineStr">
@@ -8552,7 +8942,7 @@
         </is>
       </c>
       <c r="F18" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A18)+COUNTIF(Edges!$B$2:$B$198,A18)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A18)+COUNTIF(Edges!$B$2:$B$221,A18)</f>
         <v/>
       </c>
     </row>
@@ -8583,7 +8973,7 @@
         </is>
       </c>
       <c r="F19" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A19)+COUNTIF(Edges!$B$2:$B$198,A19)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A19)+COUNTIF(Edges!$B$2:$B$221,A19)</f>
         <v/>
       </c>
     </row>
@@ -8614,7 +9004,7 @@
         </is>
       </c>
       <c r="F20" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A20)+COUNTIF(Edges!$B$2:$B$198,A20)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A20)+COUNTIF(Edges!$B$2:$B$221,A20)</f>
         <v/>
       </c>
     </row>
@@ -8645,7 +9035,7 @@
         </is>
       </c>
       <c r="F21" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A21)+COUNTIF(Edges!$B$2:$B$198,A21)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A21)+COUNTIF(Edges!$B$2:$B$221,A21)</f>
         <v/>
       </c>
     </row>
@@ -8676,7 +9066,7 @@
         </is>
       </c>
       <c r="F22" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A22)+COUNTIF(Edges!$B$2:$B$198,A22)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A22)+COUNTIF(Edges!$B$2:$B$221,A22)</f>
         <v/>
       </c>
       <c r="G22" s="24" t="n"/>
@@ -8711,7 +9101,7 @@
         </is>
       </c>
       <c r="F23" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A23)+COUNTIF(Edges!$B$2:$B$198,A23)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A23)+COUNTIF(Edges!$B$2:$B$221,A23)</f>
         <v/>
       </c>
       <c r="G23" s="24" t="n"/>
@@ -8746,7 +9136,7 @@
         </is>
       </c>
       <c r="F24" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A24)+COUNTIF(Edges!$B$2:$B$198,A24)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A24)+COUNTIF(Edges!$B$2:$B$221,A24)</f>
         <v/>
       </c>
     </row>
@@ -8777,7 +9167,7 @@
         </is>
       </c>
       <c r="F25" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A25)+COUNTIF(Edges!$B$2:$B$198,A25)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A25)+COUNTIF(Edges!$B$2:$B$221,A25)</f>
         <v/>
       </c>
     </row>
@@ -8808,7 +9198,7 @@
         </is>
       </c>
       <c r="F26" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A26)+COUNTIF(Edges!$B$2:$B$198,A26)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A26)+COUNTIF(Edges!$B$2:$B$221,A26)</f>
         <v/>
       </c>
     </row>
@@ -8839,7 +9229,7 @@
         </is>
       </c>
       <c r="F27" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A27)+COUNTIF(Edges!$B$2:$B$198,A27)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A27)+COUNTIF(Edges!$B$2:$B$221,A27)</f>
         <v/>
       </c>
     </row>
@@ -8870,7 +9260,7 @@
         </is>
       </c>
       <c r="F28" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A28)+COUNTIF(Edges!$B$2:$B$198,A28)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A28)+COUNTIF(Edges!$B$2:$B$221,A28)</f>
         <v/>
       </c>
     </row>
@@ -8901,7 +9291,7 @@
         </is>
       </c>
       <c r="F29" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A29)+COUNTIF(Edges!$B$2:$B$198,A29)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A29)+COUNTIF(Edges!$B$2:$B$221,A29)</f>
         <v/>
       </c>
     </row>
@@ -8932,7 +9322,7 @@
         </is>
       </c>
       <c r="F30" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A30)+COUNTIF(Edges!$B$2:$B$198,A30)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A30)+COUNTIF(Edges!$B$2:$B$221,A30)</f>
         <v/>
       </c>
       <c r="G30" s="24" t="inlineStr">
@@ -8979,7 +9369,7 @@
         </is>
       </c>
       <c r="F31" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A31)+COUNTIF(Edges!$B$2:$B$198,A31)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A31)+COUNTIF(Edges!$B$2:$B$221,A31)</f>
         <v/>
       </c>
     </row>
@@ -9010,7 +9400,7 @@
         </is>
       </c>
       <c r="F32" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A32)+COUNTIF(Edges!$B$2:$B$198,A32)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A32)+COUNTIF(Edges!$B$2:$B$221,A32)</f>
         <v/>
       </c>
     </row>
@@ -9041,7 +9431,7 @@
         </is>
       </c>
       <c r="F33" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A33)+COUNTIF(Edges!$B$2:$B$198,A33)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A33)+COUNTIF(Edges!$B$2:$B$221,A33)</f>
         <v/>
       </c>
       <c r="G33" s="24" t="n"/>
@@ -9076,7 +9466,7 @@
         </is>
       </c>
       <c r="F34" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A34)+COUNTIF(Edges!$B$2:$B$198,A34)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A34)+COUNTIF(Edges!$B$2:$B$221,A34)</f>
         <v/>
       </c>
       <c r="G34" s="24" t="n"/>
@@ -9111,7 +9501,7 @@
         </is>
       </c>
       <c r="F35" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A35)+COUNTIF(Edges!$B$2:$B$198,A35)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A35)+COUNTIF(Edges!$B$2:$B$221,A35)</f>
         <v/>
       </c>
     </row>
@@ -9142,7 +9532,7 @@
         </is>
       </c>
       <c r="F36" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A36)+COUNTIF(Edges!$B$2:$B$198,A36)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A36)+COUNTIF(Edges!$B$2:$B$221,A36)</f>
         <v/>
       </c>
     </row>
@@ -9173,7 +9563,7 @@
         </is>
       </c>
       <c r="F37" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A37)+COUNTIF(Edges!$B$2:$B$198,A37)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A37)+COUNTIF(Edges!$B$2:$B$221,A37)</f>
         <v/>
       </c>
     </row>
@@ -9204,7 +9594,7 @@
         </is>
       </c>
       <c r="F38" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A38)+COUNTIF(Edges!$B$2:$B$198,A38)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A38)+COUNTIF(Edges!$B$2:$B$221,A38)</f>
         <v/>
       </c>
       <c r="G38" s="24" t="n"/>
@@ -9239,7 +9629,7 @@
         </is>
       </c>
       <c r="F39" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A39)+COUNTIF(Edges!$B$2:$B$198,A39)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A39)+COUNTIF(Edges!$B$2:$B$221,A39)</f>
         <v/>
       </c>
       <c r="G39" s="24" t="n"/>
@@ -9274,7 +9664,7 @@
         </is>
       </c>
       <c r="F40" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A40)+COUNTIF(Edges!$B$2:$B$198,A40)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A40)+COUNTIF(Edges!$B$2:$B$221,A40)</f>
         <v/>
       </c>
       <c r="G40" s="24" t="n"/>
@@ -9309,7 +9699,7 @@
         </is>
       </c>
       <c r="F41" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A41)+COUNTIF(Edges!$B$2:$B$198,A41)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A41)+COUNTIF(Edges!$B$2:$B$221,A41)</f>
         <v/>
       </c>
       <c r="G41" s="24" t="n"/>
@@ -9344,7 +9734,7 @@
         </is>
       </c>
       <c r="F42" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A42)+COUNTIF(Edges!$B$2:$B$198,A42)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A42)+COUNTIF(Edges!$B$2:$B$221,A42)</f>
         <v/>
       </c>
       <c r="G42" s="24" t="n"/>
@@ -9379,7 +9769,7 @@
         </is>
       </c>
       <c r="F43" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A43)+COUNTIF(Edges!$B$2:$B$198,A43)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A43)+COUNTIF(Edges!$B$2:$B$221,A43)</f>
         <v/>
       </c>
     </row>
@@ -9410,7 +9800,7 @@
         </is>
       </c>
       <c r="F44" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A44)+COUNTIF(Edges!$B$2:$B$198,A44)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A44)+COUNTIF(Edges!$B$2:$B$221,A44)</f>
         <v/>
       </c>
     </row>
@@ -9441,7 +9831,7 @@
         </is>
       </c>
       <c r="F45" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A45)+COUNTIF(Edges!$B$2:$B$198,A45)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A45)+COUNTIF(Edges!$B$2:$B$221,A45)</f>
         <v/>
       </c>
     </row>
@@ -9472,7 +9862,7 @@
         </is>
       </c>
       <c r="F46" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A46)+COUNTIF(Edges!$B$2:$B$198,A46)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A46)+COUNTIF(Edges!$B$2:$B$221,A46)</f>
         <v/>
       </c>
     </row>
@@ -9503,7 +9893,7 @@
         </is>
       </c>
       <c r="F47" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A47)+COUNTIF(Edges!$B$2:$B$198,A47)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A47)+COUNTIF(Edges!$B$2:$B$221,A47)</f>
         <v/>
       </c>
     </row>
@@ -9534,7 +9924,7 @@
         </is>
       </c>
       <c r="F48" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A48)+COUNTIF(Edges!$B$2:$B$198,A48)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A48)+COUNTIF(Edges!$B$2:$B$221,A48)</f>
         <v/>
       </c>
       <c r="G48" s="24" t="n"/>
@@ -9569,7 +9959,7 @@
         </is>
       </c>
       <c r="F49" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A49)+COUNTIF(Edges!$B$2:$B$198,A49)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A49)+COUNTIF(Edges!$B$2:$B$221,A49)</f>
         <v/>
       </c>
     </row>
@@ -9600,7 +9990,7 @@
         </is>
       </c>
       <c r="F50" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A50)+COUNTIF(Edges!$B$2:$B$198,A50)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A50)+COUNTIF(Edges!$B$2:$B$221,A50)</f>
         <v/>
       </c>
     </row>
@@ -9631,7 +10021,7 @@
         </is>
       </c>
       <c r="F51" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A51)+COUNTIF(Edges!$B$2:$B$198,A51)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A51)+COUNTIF(Edges!$B$2:$B$221,A51)</f>
         <v/>
       </c>
     </row>
@@ -9662,7 +10052,7 @@
         </is>
       </c>
       <c r="F52" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A52)+COUNTIF(Edges!$B$2:$B$198,A52)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A52)+COUNTIF(Edges!$B$2:$B$221,A52)</f>
         <v/>
       </c>
       <c r="G52" s="24" t="inlineStr">
@@ -9709,7 +10099,7 @@
         </is>
       </c>
       <c r="F53" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A53)+COUNTIF(Edges!$B$2:$B$198,A53)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A53)+COUNTIF(Edges!$B$2:$B$221,A53)</f>
         <v/>
       </c>
       <c r="G53" s="24" t="inlineStr">
@@ -9756,7 +10146,7 @@
         </is>
       </c>
       <c r="F54" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A54)+COUNTIF(Edges!$B$2:$B$198,A54)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A54)+COUNTIF(Edges!$B$2:$B$221,A54)</f>
         <v/>
       </c>
       <c r="G54" s="24" t="inlineStr">
@@ -9803,7 +10193,7 @@
         </is>
       </c>
       <c r="F55" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A55)+COUNTIF(Edges!$B$2:$B$198,A55)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A55)+COUNTIF(Edges!$B$2:$B$221,A55)</f>
         <v/>
       </c>
       <c r="G55" s="24" t="inlineStr">
@@ -9850,7 +10240,7 @@
         </is>
       </c>
       <c r="F56" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A56)+COUNTIF(Edges!$B$2:$B$198,A56)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A56)+COUNTIF(Edges!$B$2:$B$221,A56)</f>
         <v/>
       </c>
     </row>
@@ -9881,7 +10271,7 @@
         </is>
       </c>
       <c r="F57" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A57)+COUNTIF(Edges!$B$2:$B$198,A57)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A57)+COUNTIF(Edges!$B$2:$B$221,A57)</f>
         <v/>
       </c>
       <c r="G57" s="24" t="inlineStr">
@@ -9928,7 +10318,7 @@
         </is>
       </c>
       <c r="F58" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A58)+COUNTIF(Edges!$B$2:$B$198,A58)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A58)+COUNTIF(Edges!$B$2:$B$221,A58)</f>
         <v/>
       </c>
       <c r="G58" s="24" t="inlineStr">
@@ -9975,7 +10365,7 @@
         </is>
       </c>
       <c r="F59" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A59)+COUNTIF(Edges!$B$2:$B$198,A59)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A59)+COUNTIF(Edges!$B$2:$B$221,A59)</f>
         <v/>
       </c>
       <c r="G59" s="24" t="n"/>
@@ -10010,7 +10400,7 @@
         </is>
       </c>
       <c r="F60" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A60)+COUNTIF(Edges!$B$2:$B$198,A60)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A60)+COUNTIF(Edges!$B$2:$B$221,A60)</f>
         <v/>
       </c>
       <c r="G60" s="24" t="n"/>
@@ -10045,7 +10435,7 @@
         </is>
       </c>
       <c r="F61" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A61)+COUNTIF(Edges!$B$2:$B$198,A61)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A61)+COUNTIF(Edges!$B$2:$B$221,A61)</f>
         <v/>
       </c>
       <c r="G61" s="24" t="n"/>
@@ -10080,7 +10470,7 @@
         </is>
       </c>
       <c r="F62" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A62)+COUNTIF(Edges!$B$2:$B$198,A62)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A62)+COUNTIF(Edges!$B$2:$B$221,A62)</f>
         <v/>
       </c>
       <c r="G62" s="24" t="n"/>
@@ -10115,7 +10505,7 @@
         </is>
       </c>
       <c r="F63" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A63)+COUNTIF(Edges!$B$2:$B$198,A63)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A63)+COUNTIF(Edges!$B$2:$B$221,A63)</f>
         <v/>
       </c>
       <c r="G63" s="24" t="n"/>
@@ -10150,7 +10540,7 @@
         </is>
       </c>
       <c r="F64" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A64)+COUNTIF(Edges!$B$2:$B$198,A64)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A64)+COUNTIF(Edges!$B$2:$B$221,A64)</f>
         <v/>
       </c>
       <c r="G64" s="24" t="n"/>
@@ -10185,7 +10575,7 @@
         </is>
       </c>
       <c r="F65" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A65)+COUNTIF(Edges!$B$2:$B$198,A65)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A65)+COUNTIF(Edges!$B$2:$B$221,A65)</f>
         <v/>
       </c>
       <c r="G65" s="24" t="n"/>
@@ -10220,7 +10610,7 @@
         </is>
       </c>
       <c r="F66" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A66)+COUNTIF(Edges!$B$2:$B$198,A66)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A66)+COUNTIF(Edges!$B$2:$B$221,A66)</f>
         <v/>
       </c>
       <c r="G66" s="24" t="n"/>
@@ -10255,7 +10645,7 @@
         </is>
       </c>
       <c r="F67" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A67)+COUNTIF(Edges!$B$2:$B$198,A67)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A67)+COUNTIF(Edges!$B$2:$B$221,A67)</f>
         <v/>
       </c>
       <c r="G67" s="24" t="n"/>
@@ -10290,7 +10680,7 @@
         </is>
       </c>
       <c r="F68" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A68)+COUNTIF(Edges!$B$2:$B$198,A68)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A68)+COUNTIF(Edges!$B$2:$B$221,A68)</f>
         <v/>
       </c>
       <c r="G68" s="24" t="n"/>
@@ -10325,7 +10715,7 @@
         </is>
       </c>
       <c r="F69" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A69)+COUNTIF(Edges!$B$2:$B$198,A69)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A69)+COUNTIF(Edges!$B$2:$B$221,A69)</f>
         <v/>
       </c>
       <c r="G69" s="24" t="n"/>
@@ -10360,7 +10750,7 @@
         </is>
       </c>
       <c r="F70" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A70)+COUNTIF(Edges!$B$2:$B$198,A70)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A70)+COUNTIF(Edges!$B$2:$B$221,A70)</f>
         <v/>
       </c>
       <c r="G70" s="24" t="n"/>
@@ -10395,7 +10785,7 @@
         </is>
       </c>
       <c r="F71" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A71)+COUNTIF(Edges!$B$2:$B$198,A71)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A71)+COUNTIF(Edges!$B$2:$B$221,A71)</f>
         <v/>
       </c>
       <c r="G71" s="24" t="n"/>
@@ -10430,7 +10820,7 @@
         </is>
       </c>
       <c r="F72" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A72)+COUNTIF(Edges!$B$2:$B$198,A72)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A72)+COUNTIF(Edges!$B$2:$B$221,A72)</f>
         <v/>
       </c>
       <c r="G72" s="24" t="n"/>
@@ -10465,7 +10855,7 @@
         </is>
       </c>
       <c r="F73" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A73)+COUNTIF(Edges!$B$2:$B$198,A73)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A73)+COUNTIF(Edges!$B$2:$B$221,A73)</f>
         <v/>
       </c>
       <c r="G73" s="24" t="n"/>
@@ -10500,7 +10890,7 @@
         </is>
       </c>
       <c r="F74" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A74)+COUNTIF(Edges!$B$2:$B$198,A74)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A74)+COUNTIF(Edges!$B$2:$B$221,A74)</f>
         <v/>
       </c>
       <c r="G74" s="24" t="n"/>
@@ -10535,7 +10925,7 @@
         </is>
       </c>
       <c r="F75" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A75)+COUNTIF(Edges!$B$2:$B$198,A75)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A75)+COUNTIF(Edges!$B$2:$B$221,A75)</f>
         <v/>
       </c>
       <c r="G75" s="24" t="n"/>
@@ -10570,7 +10960,7 @@
         </is>
       </c>
       <c r="F76" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A76)+COUNTIF(Edges!$B$2:$B$198,A76)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A76)+COUNTIF(Edges!$B$2:$B$221,A76)</f>
         <v/>
       </c>
       <c r="G76" s="24" t="n"/>
@@ -10605,7 +10995,7 @@
         </is>
       </c>
       <c r="F77" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A77)+COUNTIF(Edges!$B$2:$B$198,A77)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A77)+COUNTIF(Edges!$B$2:$B$221,A77)</f>
         <v/>
       </c>
       <c r="G77" s="24" t="n"/>
@@ -10640,7 +11030,7 @@
         </is>
       </c>
       <c r="F78" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A78)+COUNTIF(Edges!$B$2:$B$198,A78)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A78)+COUNTIF(Edges!$B$2:$B$221,A78)</f>
         <v/>
       </c>
       <c r="G78" s="24" t="n"/>
@@ -10675,7 +11065,7 @@
         </is>
       </c>
       <c r="F79" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A79)+COUNTIF(Edges!$B$2:$B$198,A79)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A79)+COUNTIF(Edges!$B$2:$B$221,A79)</f>
         <v/>
       </c>
       <c r="G79" s="24" t="n"/>
@@ -10710,7 +11100,7 @@
         </is>
       </c>
       <c r="F80" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A80)+COUNTIF(Edges!$B$2:$B$198,A80)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A80)+COUNTIF(Edges!$B$2:$B$221,A80)</f>
         <v/>
       </c>
       <c r="G80" s="24" t="n"/>
@@ -10745,7 +11135,7 @@
         </is>
       </c>
       <c r="F81" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A81)+COUNTIF(Edges!$B$2:$B$198,A81)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A81)+COUNTIF(Edges!$B$2:$B$221,A81)</f>
         <v/>
       </c>
       <c r="G81" s="24" t="n"/>
@@ -10780,7 +11170,7 @@
         </is>
       </c>
       <c r="F82" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A82)+COUNTIF(Edges!$B$2:$B$198,A82)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A82)+COUNTIF(Edges!$B$2:$B$221,A82)</f>
         <v/>
       </c>
       <c r="G82" s="24" t="n"/>
@@ -10815,7 +11205,7 @@
         </is>
       </c>
       <c r="F83" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A83)+COUNTIF(Edges!$B$2:$B$198,A83)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A83)+COUNTIF(Edges!$B$2:$B$221,A83)</f>
         <v/>
       </c>
       <c r="G83" s="24" t="n"/>
@@ -10850,7 +11240,7 @@
         </is>
       </c>
       <c r="F84" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A84)+COUNTIF(Edges!$B$2:$B$198,A84)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A84)+COUNTIF(Edges!$B$2:$B$221,A84)</f>
         <v/>
       </c>
       <c r="G84" s="24" t="n"/>
@@ -10885,7 +11275,7 @@
         </is>
       </c>
       <c r="F85" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A85)+COUNTIF(Edges!$B$2:$B$198,A85)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A85)+COUNTIF(Edges!$B$2:$B$221,A85)</f>
         <v/>
       </c>
       <c r="G85" s="24" t="n"/>
@@ -10920,7 +11310,7 @@
         </is>
       </c>
       <c r="F86" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A86)+COUNTIF(Edges!$B$2:$B$198,A86)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A86)+COUNTIF(Edges!$B$2:$B$221,A86)</f>
         <v/>
       </c>
       <c r="G86" s="24" t="n"/>
@@ -10955,7 +11345,7 @@
         </is>
       </c>
       <c r="F87" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A87)+COUNTIF(Edges!$B$2:$B$198,A87)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A87)+COUNTIF(Edges!$B$2:$B$221,A87)</f>
         <v/>
       </c>
       <c r="G87" s="24" t="n"/>
@@ -10990,7 +11380,7 @@
         </is>
       </c>
       <c r="F88" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A88)+COUNTIF(Edges!$B$2:$B$198,A88)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A88)+COUNTIF(Edges!$B$2:$B$221,A88)</f>
         <v/>
       </c>
       <c r="G88" s="24" t="n"/>
@@ -11025,7 +11415,7 @@
         </is>
       </c>
       <c r="F89" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A89)+COUNTIF(Edges!$B$2:$B$198,A89)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A89)+COUNTIF(Edges!$B$2:$B$221,A89)</f>
         <v/>
       </c>
       <c r="G89" s="24" t="n"/>
@@ -11060,7 +11450,7 @@
         </is>
       </c>
       <c r="F90" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A90)+COUNTIF(Edges!$B$2:$B$198,A90)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A90)+COUNTIF(Edges!$B$2:$B$221,A90)</f>
         <v/>
       </c>
       <c r="G90" s="24" t="n"/>
@@ -11095,13 +11485,223 @@
         </is>
       </c>
       <c r="F91" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$198,A91)+COUNTIF(Edges!$B$2:$B$198,A91)</f>
+        <f>COUNTIF(Edges!$A$2:$A$221,A91)+COUNTIF(Edges!$B$2:$B$221,A91)</f>
         <v/>
       </c>
       <c r="G91" s="24" t="n"/>
       <c r="H91" s="24" t="n"/>
       <c r="I91" s="24" t="n"/>
       <c r="J91" s="24" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="45" t="inlineStr">
+        <is>
+          <t>rueda</t>
+        </is>
+      </c>
+      <c r="B92" s="45" t="inlineStr">
+        <is>
+          <t>Antonio Rueda</t>
+        </is>
+      </c>
+      <c r="C92" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D92" s="45" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="E92" s="45" t="inlineStr">
+        <is>
+          <t>Presidente do União Brasil; admitiu ter advogado para o Master; 4º maior volume de interações no celular de Vorcaro</t>
+        </is>
+      </c>
+      <c r="F92" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$221,A92)+COUNTIF(Edges!$B$2:$B$221,A92)</f>
+        <v/>
+      </c>
+      <c r="G92" s="24" t="n"/>
+      <c r="H92" s="24" t="n"/>
+      <c r="I92" s="24" t="n"/>
+      <c r="J92" s="24" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="45" t="inlineStr">
+        <is>
+          <t>wajngarten</t>
+        </is>
+      </c>
+      <c r="B93" s="45" t="inlineStr">
+        <is>
+          <t>Fabio Wajngarten</t>
+        </is>
+      </c>
+      <c r="C93" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D93" s="45" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="E93" s="45" t="inlineStr">
+        <is>
+          <t>Ex-secretário de Comunicação de Bolsonaro; integra a defesa de Vorcaro na comunicação; 6º maior volume no celular dele</t>
+        </is>
+      </c>
+      <c r="F93" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$221,A93)+COUNTIF(Edges!$B$2:$B$221,A93)</f>
+        <v/>
+      </c>
+      <c r="G93" s="24" t="n"/>
+      <c r="H93" s="24" t="n"/>
+      <c r="I93" s="24" t="n"/>
+      <c r="J93" s="24" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="45" t="inlineStr">
+        <is>
+          <t>mantega</t>
+        </is>
+      </c>
+      <c r="B94" s="45" t="inlineStr">
+        <is>
+          <t>Guido Mantega</t>
+        </is>
+      </c>
+      <c r="C94" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D94" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E94" s="45" t="inlineStr">
+        <is>
+          <t>Ex-ministro da Fazenda (PT); diz ter feito consultoria para o Master em 2024–25; aparece em mensagens sobre aproximação com Lula</t>
+        </is>
+      </c>
+      <c r="F94" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$221,A94)+COUNTIF(Edges!$B$2:$B$221,A94)</f>
+        <v/>
+      </c>
+      <c r="G94" s="24" t="n"/>
+      <c r="H94" s="24" t="n"/>
+      <c r="I94" s="24" t="n"/>
+      <c r="J94" s="24" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="45" t="inlineStr">
+        <is>
+          <t>doria</t>
+        </is>
+      </c>
+      <c r="B95" s="45" t="inlineStr">
+        <is>
+          <t>João Doria</t>
+        </is>
+      </c>
+      <c r="C95" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D95" s="45" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="E95" s="45" t="inlineStr">
+        <is>
+          <t>Ex-governador de SP; 5º maior volume no celular de Vorcaro; mensagem de maio/2025 sobre “preocupação” com o banco</t>
+        </is>
+      </c>
+      <c r="F95" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$221,A95)+COUNTIF(Edges!$B$2:$B$221,A95)</f>
+        <v/>
+      </c>
+      <c r="G95" s="24" t="n"/>
+      <c r="H95" s="24" t="n"/>
+      <c r="I95" s="24" t="n"/>
+      <c r="J95" s="24" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="45" t="inlineStr">
+        <is>
+          <t>bacelar</t>
+        </is>
+      </c>
+      <c r="B96" s="45" t="inlineStr">
+        <is>
+          <t>João Carlos Bacelar</t>
+        </is>
+      </c>
+      <c r="C96" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D96" s="45" t="inlineStr">
+        <is>
+          <t>Vorcaro e o Banco Master</t>
+        </is>
+      </c>
+      <c r="E96" s="45" t="inlineStr">
+        <is>
+          <t>Deputado federal (PL-BA); PF achou documento com seu nome sobre opção de compra de terreno em Trancoso (BA)</t>
+        </is>
+      </c>
+      <c r="F96" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$221,A96)+COUNTIF(Edges!$B$2:$B$221,A96)</f>
+        <v/>
+      </c>
+      <c r="G96" s="24" t="n"/>
+      <c r="H96" s="24" t="n"/>
+      <c r="I96" s="24" t="n"/>
+      <c r="J96" s="24" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="45" t="inlineStr">
+        <is>
+          <t>feitosa</t>
+        </is>
+      </c>
+      <c r="B97" s="45" t="inlineStr">
+        <is>
+          <t>Chiquinho Feitosa</t>
+        </is>
+      </c>
+      <c r="C97" s="45" t="inlineStr">
+        <is>
+          <t>Pessoa</t>
+        </is>
+      </c>
+      <c r="D97" s="45" t="inlineStr">
+        <is>
+          <t>Poder e Justiça</t>
+        </is>
+      </c>
+      <c r="E97" s="45" t="inlineStr">
+        <is>
+          <t>Ex-senador (Republicanos-CE); mensagens da PF indicam que se ofereceu como ponte entre Vorcaro e o ministro Gilmar Mendes</t>
+        </is>
+      </c>
+      <c r="F97" s="45">
+        <f>COUNTIF(Edges!$A$2:$A$221,A97)+COUNTIF(Edges!$B$2:$B$221,A97)</f>
+        <v/>
+      </c>
+      <c r="G97" s="24" t="n"/>
+      <c r="H97" s="24" t="n"/>
+      <c r="I97" s="24" t="n"/>
+      <c r="J97" s="24" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F58"/>
@@ -11117,7 +11717,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F198"/>
+  <dimension ref="A1:F221"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="24" min="1" max="2"/>
@@ -11180,11 +11780,11 @@
         </is>
       </c>
       <c r="E2" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A2,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A2,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F2" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B2,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B2,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11210,11 +11810,11 @@
         </is>
       </c>
       <c r="E3" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A3,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A3,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F3" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B3,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B3,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11240,11 +11840,11 @@
         </is>
       </c>
       <c r="E4" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A4,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A4,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F4" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B4,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B4,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11270,11 +11870,11 @@
         </is>
       </c>
       <c r="E5" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A5,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A5,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F5" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B5,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B5,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11300,11 +11900,11 @@
         </is>
       </c>
       <c r="E6" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A6,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A6,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F6" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B6,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B6,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11330,11 +11930,11 @@
         </is>
       </c>
       <c r="E7" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A7,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A7,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F7" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B7,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B7,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11360,11 +11960,11 @@
         </is>
       </c>
       <c r="E8" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A8,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A8,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F8" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B8,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B8,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11390,11 +11990,11 @@
         </is>
       </c>
       <c r="E9" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A9,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A9,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F9" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B9,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B9,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11420,11 +12020,11 @@
         </is>
       </c>
       <c r="E10" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A10,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A10,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F10" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B10,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B10,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11450,11 +12050,11 @@
         </is>
       </c>
       <c r="E11" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A11,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A11,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F11" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B11,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B11,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11480,11 +12080,11 @@
         </is>
       </c>
       <c r="E12" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A12,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A12,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F12" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B12,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B12,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11510,11 +12110,11 @@
         </is>
       </c>
       <c r="E13" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A13,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A13,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F13" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B13,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B13,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11540,11 +12140,11 @@
         </is>
       </c>
       <c r="E14" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A14,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A14,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F14" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B14,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B14,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11570,11 +12170,11 @@
         </is>
       </c>
       <c r="E15" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A15,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A15,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F15" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B15,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B15,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11600,11 +12200,11 @@
         </is>
       </c>
       <c r="E16" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A16,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A16,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F16" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B16,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B16,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11630,11 +12230,11 @@
         </is>
       </c>
       <c r="E17" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A17,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A17,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F17" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B17,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B17,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11660,11 +12260,11 @@
         </is>
       </c>
       <c r="E18" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A18,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A18,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F18" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B18,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B18,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11690,11 +12290,11 @@
         </is>
       </c>
       <c r="E19" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A19,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A19,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F19" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B19,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B19,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11720,11 +12320,11 @@
         </is>
       </c>
       <c r="E20" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A20,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A20,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F20" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B20,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B20,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11750,11 +12350,11 @@
         </is>
       </c>
       <c r="E21" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A21,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A21,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F21" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B21,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B21,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11780,11 +12380,11 @@
         </is>
       </c>
       <c r="E22" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A22,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A22,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F22" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B22,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B22,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11810,11 +12410,11 @@
         </is>
       </c>
       <c r="E23" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A23,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A23,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F23" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B23,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B23,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11840,11 +12440,11 @@
         </is>
       </c>
       <c r="E24" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A24,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A24,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F24" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B24,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B24,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11870,11 +12470,11 @@
         </is>
       </c>
       <c r="E25" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A25,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A25,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F25" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B25,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B25,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11900,11 +12500,11 @@
         </is>
       </c>
       <c r="E26" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A26,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A26,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F26" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B26,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B26,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11930,11 +12530,11 @@
         </is>
       </c>
       <c r="E27" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A27,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A27,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F27" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B27,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B27,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11960,11 +12560,11 @@
         </is>
       </c>
       <c r="E28" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A28,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A28,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F28" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B28,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B28,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -11990,11 +12590,11 @@
         </is>
       </c>
       <c r="E29" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A29,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A29,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F29" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B29,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B29,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12020,11 +12620,11 @@
         </is>
       </c>
       <c r="E30" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A30,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A30,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F30" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B30,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B30,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12050,11 +12650,11 @@
         </is>
       </c>
       <c r="E31" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A31,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A31,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F31" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B31,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B31,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12080,11 +12680,11 @@
         </is>
       </c>
       <c r="E32" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A32,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A32,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F32" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B32,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B32,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12110,11 +12710,11 @@
         </is>
       </c>
       <c r="E33" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A33,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A33,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F33" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B33,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B33,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12140,11 +12740,11 @@
         </is>
       </c>
       <c r="E34" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A34,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A34,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F34" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B34,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B34,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12170,11 +12770,11 @@
         </is>
       </c>
       <c r="E35" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A35,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A35,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F35" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B35,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B35,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12200,11 +12800,11 @@
         </is>
       </c>
       <c r="E36" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A36,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A36,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F36" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B36,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B36,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12230,11 +12830,11 @@
         </is>
       </c>
       <c r="E37" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A37,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A37,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F37" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B37,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B37,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12260,11 +12860,11 @@
         </is>
       </c>
       <c r="E38" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A38,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A38,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F38" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B38,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B38,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12290,11 +12890,11 @@
         </is>
       </c>
       <c r="E39" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A39,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A39,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F39" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B39,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B39,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12320,11 +12920,11 @@
         </is>
       </c>
       <c r="E40" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A40,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A40,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F40" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B40,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B40,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12350,11 +12950,11 @@
         </is>
       </c>
       <c r="E41" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A41,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A41,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F41" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B41,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B41,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12380,11 +12980,11 @@
         </is>
       </c>
       <c r="E42" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A42,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A42,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F42" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B42,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B42,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12410,11 +13010,11 @@
         </is>
       </c>
       <c r="E43" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A43,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A43,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F43" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B43,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B43,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12440,11 +13040,11 @@
         </is>
       </c>
       <c r="E44" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A44,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A44,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F44" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B44,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B44,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12470,11 +13070,11 @@
         </is>
       </c>
       <c r="E45" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A45,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A45,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F45" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B45,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B45,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12500,11 +13100,11 @@
         </is>
       </c>
       <c r="E46" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A46,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A46,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F46" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B46,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B46,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12530,11 +13130,11 @@
         </is>
       </c>
       <c r="E47" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A47,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A47,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F47" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B47,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B47,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12560,11 +13160,11 @@
         </is>
       </c>
       <c r="E48" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A48,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A48,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F48" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B48,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B48,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12590,11 +13190,11 @@
         </is>
       </c>
       <c r="E49" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A49,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A49,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F49" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B49,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B49,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12620,11 +13220,11 @@
         </is>
       </c>
       <c r="E50" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A50,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A50,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F50" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B50,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B50,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12650,11 +13250,11 @@
         </is>
       </c>
       <c r="E51" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A51,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A51,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F51" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B51,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B51,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12680,11 +13280,11 @@
         </is>
       </c>
       <c r="E52" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A52,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A52,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F52" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B52,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B52,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12710,11 +13310,11 @@
         </is>
       </c>
       <c r="E53" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A53,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A53,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F53" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B53,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B53,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12740,11 +13340,11 @@
         </is>
       </c>
       <c r="E54" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A54,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A54,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F54" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B54,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B54,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12770,11 +13370,11 @@
         </is>
       </c>
       <c r="E55" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A55,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A55,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F55" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B55,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B55,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12800,11 +13400,11 @@
         </is>
       </c>
       <c r="E56" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A56,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A56,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F56" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B56,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B56,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12830,11 +13430,11 @@
         </is>
       </c>
       <c r="E57" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A57,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A57,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F57" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B57,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B57,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12860,11 +13460,11 @@
         </is>
       </c>
       <c r="E58" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A58,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A58,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F58" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B58,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B58,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12890,11 +13490,11 @@
         </is>
       </c>
       <c r="E59" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A59,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A59,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F59" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B59,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B59,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12920,11 +13520,11 @@
         </is>
       </c>
       <c r="E60" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A60,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A60,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F60" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B60,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B60,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12950,11 +13550,11 @@
         </is>
       </c>
       <c r="E61" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A61,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A61,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F61" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B61,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B61,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -12980,11 +13580,11 @@
         </is>
       </c>
       <c r="E62" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A62,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A62,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F62" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B62,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B62,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13010,11 +13610,11 @@
         </is>
       </c>
       <c r="E63" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A63,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A63,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F63" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B63,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B63,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13040,11 +13640,11 @@
         </is>
       </c>
       <c r="E64" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A64,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A64,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F64" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B64,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B64,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13070,11 +13670,11 @@
         </is>
       </c>
       <c r="E65" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A65,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A65,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F65" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B65,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B65,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13100,11 +13700,11 @@
         </is>
       </c>
       <c r="E66" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A66,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A66,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F66" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B66,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B66,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13130,11 +13730,11 @@
         </is>
       </c>
       <c r="E67" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A67,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A67,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F67" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B67,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B67,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13160,11 +13760,11 @@
         </is>
       </c>
       <c r="E68" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A68,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A68,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F68" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B68,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B68,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13190,11 +13790,11 @@
         </is>
       </c>
       <c r="E69" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A69,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A69,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F69" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B69,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B69,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13220,11 +13820,11 @@
         </is>
       </c>
       <c r="E70" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A70,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A70,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F70" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B70,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B70,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13250,11 +13850,11 @@
         </is>
       </c>
       <c r="E71" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A71,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A71,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F71" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B71,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B71,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13280,11 +13880,11 @@
         </is>
       </c>
       <c r="E72" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A72,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A72,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F72" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B72,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B72,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13310,11 +13910,11 @@
         </is>
       </c>
       <c r="E73" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A73,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A73,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F73" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B73,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B73,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13340,11 +13940,11 @@
         </is>
       </c>
       <c r="E74" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A74,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A74,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F74" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B74,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B74,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13370,11 +13970,11 @@
         </is>
       </c>
       <c r="E75" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A75,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A75,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F75" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B75,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B75,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13400,11 +14000,11 @@
         </is>
       </c>
       <c r="E76" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A76,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A76,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F76" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B76,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B76,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13430,11 +14030,11 @@
         </is>
       </c>
       <c r="E77" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A77,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A77,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F77" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B77,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B77,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13460,11 +14060,11 @@
         </is>
       </c>
       <c r="E78" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A78,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A78,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F78" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B78,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B78,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13490,11 +14090,11 @@
         </is>
       </c>
       <c r="E79" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A79,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A79,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F79" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B79,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B79,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13520,11 +14120,11 @@
         </is>
       </c>
       <c r="E80" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A80,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A80,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F80" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B80,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B80,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13550,11 +14150,11 @@
         </is>
       </c>
       <c r="E81" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A81,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A81,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F81" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B81,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B81,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13580,11 +14180,11 @@
         </is>
       </c>
       <c r="E82" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A82,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A82,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F82" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B82,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B82,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13610,11 +14210,11 @@
         </is>
       </c>
       <c r="E83" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A83,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A83,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F83" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B83,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B83,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13640,11 +14240,11 @@
         </is>
       </c>
       <c r="E84" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A84,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A84,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F84" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B84,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B84,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13670,11 +14270,11 @@
         </is>
       </c>
       <c r="E85" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A85,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A85,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F85" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B85,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B85,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13700,11 +14300,11 @@
         </is>
       </c>
       <c r="E86" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A86,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A86,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F86" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B86,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B86,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13730,11 +14330,11 @@
         </is>
       </c>
       <c r="E87" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A87,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A87,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F87" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B87,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B87,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13760,11 +14360,11 @@
         </is>
       </c>
       <c r="E88" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A88,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A88,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F88" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B88,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B88,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13790,11 +14390,11 @@
         </is>
       </c>
       <c r="E89" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A89,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A89,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F89" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B89,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B89,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13820,11 +14420,11 @@
         </is>
       </c>
       <c r="E90" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A90,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A90,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F90" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B90,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B90,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13850,11 +14450,11 @@
         </is>
       </c>
       <c r="E91" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A91,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A91,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F91" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B91,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B91,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13880,11 +14480,11 @@
         </is>
       </c>
       <c r="E92" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A92,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A92,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F92" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B92,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B92,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13910,11 +14510,11 @@
         </is>
       </c>
       <c r="E93" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A93,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A93,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F93" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B93,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B93,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13940,11 +14540,11 @@
         </is>
       </c>
       <c r="E94" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A94,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A94,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F94" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B94,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B94,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -13970,11 +14570,11 @@
         </is>
       </c>
       <c r="E95" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A95,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A95,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F95" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B95,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B95,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14000,11 +14600,11 @@
         </is>
       </c>
       <c r="E96" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A96,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A96,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F96" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B96,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B96,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14030,11 +14630,11 @@
         </is>
       </c>
       <c r="E97" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A97,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A97,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F97" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B97,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B97,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14060,11 +14660,11 @@
         </is>
       </c>
       <c r="E98" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A98,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A98,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F98" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B98,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B98,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14090,11 +14690,11 @@
         </is>
       </c>
       <c r="E99" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A99,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A99,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F99" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B99,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B99,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14120,11 +14720,11 @@
         </is>
       </c>
       <c r="E100" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A100,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A100,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F100" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B100,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B100,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14150,11 +14750,11 @@
         </is>
       </c>
       <c r="E101" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A101,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A101,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F101" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B101,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B101,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14180,11 +14780,11 @@
         </is>
       </c>
       <c r="E102" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A102,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A102,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F102" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B102,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B102,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14210,11 +14810,11 @@
         </is>
       </c>
       <c r="E103" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A103,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A103,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F103" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B103,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B103,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14240,11 +14840,11 @@
         </is>
       </c>
       <c r="E104" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A104,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A104,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F104" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B104,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B104,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14270,11 +14870,11 @@
         </is>
       </c>
       <c r="E105" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A105,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A105,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F105" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B105,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B105,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14300,11 +14900,11 @@
         </is>
       </c>
       <c r="E106" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A106,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A106,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F106" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B106,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B106,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14330,11 +14930,11 @@
         </is>
       </c>
       <c r="E107" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A107,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A107,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F107" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B107,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B107,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14360,11 +14960,11 @@
         </is>
       </c>
       <c r="E108" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A108,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A108,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F108" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B108,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B108,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14390,11 +14990,11 @@
         </is>
       </c>
       <c r="E109" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A109,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A109,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F109" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B109,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B109,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14420,11 +15020,11 @@
         </is>
       </c>
       <c r="E110" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A110,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A110,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F110" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B110,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B110,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14450,11 +15050,11 @@
         </is>
       </c>
       <c r="E111" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A111,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A111,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F111" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B111,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B111,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14480,11 +15080,11 @@
         </is>
       </c>
       <c r="E112" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A112,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A112,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F112" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B112,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B112,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14510,11 +15110,11 @@
         </is>
       </c>
       <c r="E113" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A113,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A113,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F113" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B113,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B113,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14540,11 +15140,11 @@
         </is>
       </c>
       <c r="E114" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A114,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A114,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F114" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B114,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B114,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14570,11 +15170,11 @@
         </is>
       </c>
       <c r="E115" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A115,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A115,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F115" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B115,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B115,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14600,11 +15200,11 @@
         </is>
       </c>
       <c r="E116" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A116,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A116,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F116" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B116,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B116,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14630,11 +15230,11 @@
         </is>
       </c>
       <c r="E117" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A117,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A117,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F117" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B117,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B117,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14660,11 +15260,11 @@
         </is>
       </c>
       <c r="E118" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A118,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A118,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F118" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B118,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B118,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14690,11 +15290,11 @@
         </is>
       </c>
       <c r="E119" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A119,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A119,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F119" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B119,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B119,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14720,11 +15320,11 @@
         </is>
       </c>
       <c r="E120" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A120,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A120,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F120" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B120,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B120,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14750,11 +15350,11 @@
         </is>
       </c>
       <c r="E121" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A121,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A121,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F121" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B121,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B121,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14780,11 +15380,11 @@
         </is>
       </c>
       <c r="E122" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A122,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A122,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F122" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B122,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B122,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14810,11 +15410,11 @@
         </is>
       </c>
       <c r="E123" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A123,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A123,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F123" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B123,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B123,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14840,11 +15440,11 @@
         </is>
       </c>
       <c r="E124" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A124,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A124,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F124" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B124,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B124,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14870,11 +15470,11 @@
         </is>
       </c>
       <c r="E125" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A125,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A125,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F125" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B125,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B125,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14900,11 +15500,11 @@
         </is>
       </c>
       <c r="E126" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A126,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A126,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F126" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B126,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B126,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14930,11 +15530,11 @@
         </is>
       </c>
       <c r="E127" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A127,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A127,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F127" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B127,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B127,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14960,11 +15560,11 @@
         </is>
       </c>
       <c r="E128" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A128,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A128,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F128" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B128,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B128,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -14990,11 +15590,11 @@
         </is>
       </c>
       <c r="E129" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A129,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A129,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F129" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B129,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B129,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15020,11 +15620,11 @@
         </is>
       </c>
       <c r="E130" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A130,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A130,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F130" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B130,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B130,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15050,11 +15650,11 @@
         </is>
       </c>
       <c r="E131" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A131,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A131,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F131" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B131,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B131,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15080,11 +15680,11 @@
         </is>
       </c>
       <c r="E132" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A132,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A132,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F132" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B132,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B132,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15110,11 +15710,11 @@
         </is>
       </c>
       <c r="E133" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A133,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A133,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F133" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B133,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B133,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15140,11 +15740,11 @@
         </is>
       </c>
       <c r="E134" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A134,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A134,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F134" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B134,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B134,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15170,11 +15770,11 @@
         </is>
       </c>
       <c r="E135" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A135,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A135,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F135" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B135,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B135,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15200,11 +15800,11 @@
         </is>
       </c>
       <c r="E136" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A136,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A136,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F136" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B136,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B136,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15230,11 +15830,11 @@
         </is>
       </c>
       <c r="E137" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A137,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A137,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F137" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B137,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B137,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15260,11 +15860,11 @@
         </is>
       </c>
       <c r="E138" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A138,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A138,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F138" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B138,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B138,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15290,11 +15890,11 @@
         </is>
       </c>
       <c r="E139" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A139,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A139,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F139" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B139,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B139,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15320,11 +15920,11 @@
         </is>
       </c>
       <c r="E140" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A140,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A140,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F140" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B140,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B140,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15350,11 +15950,11 @@
         </is>
       </c>
       <c r="E141" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A141,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A141,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F141" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B141,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B141,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15380,11 +15980,11 @@
         </is>
       </c>
       <c r="E142" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A142,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A142,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F142" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B142,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B142,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15410,11 +16010,11 @@
         </is>
       </c>
       <c r="E143" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A143,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A143,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F143" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B143,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B143,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15440,11 +16040,11 @@
         </is>
       </c>
       <c r="E144" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A144,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A144,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F144" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B144,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B144,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15470,11 +16070,11 @@
         </is>
       </c>
       <c r="E145" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A145,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A145,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F145" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B145,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B145,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15500,11 +16100,11 @@
         </is>
       </c>
       <c r="E146" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A146,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A146,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F146" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B146,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B146,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15530,11 +16130,11 @@
         </is>
       </c>
       <c r="E147" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A147,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A147,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F147" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B147,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B147,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15560,11 +16160,11 @@
         </is>
       </c>
       <c r="E148" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A148,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A148,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F148" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B148,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B148,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15590,11 +16190,11 @@
         </is>
       </c>
       <c r="E149" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A149,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A149,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F149" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B149,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B149,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15620,11 +16220,11 @@
         </is>
       </c>
       <c r="E150" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A150,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A150,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F150" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B150,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B150,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15650,11 +16250,11 @@
         </is>
       </c>
       <c r="E151" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A151,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A151,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F151" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B151,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B151,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15680,11 +16280,11 @@
         </is>
       </c>
       <c r="E152" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A152,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A152,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F152" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B152,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B152,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15701,7 +16301,7 @@
       </c>
       <c r="C153" s="45" t="inlineStr">
         <is>
-          <t>PF: pagamentos mensais de R$ 300 mil a 500 mil e viagens pagas, incluindo Courchevel (~R$ 2 mi); ele nega ilicitude</t>
+          <t>PF: mesadas de ao menos R$ 6 mi (jun/2024 a ago/2025), estimadas por mensagens entre Vorcaro e o primo (R$ 300 mil por mês; relatos falam em R$ 500 mil), e viagens pagas (R$ 468,7 mil em viagens e jantares, R$ 122 mil só em restaurantes em Courchevel; CNN); ele nega ilicitude</t>
         </is>
       </c>
       <c r="D153" s="45" t="inlineStr">
@@ -15710,11 +16310,11 @@
         </is>
       </c>
       <c r="E153" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A153,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A153,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F153" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B153,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B153,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15740,11 +16340,11 @@
         </is>
       </c>
       <c r="E154" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A154,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A154,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F154" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B154,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B154,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15770,11 +16370,11 @@
         </is>
       </c>
       <c r="E155" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A155,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A155,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F155" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B155,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B155,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15800,11 +16400,11 @@
         </is>
       </c>
       <c r="E156" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A156,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A156,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F156" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B156,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B156,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15821,7 +16421,7 @@
       </c>
       <c r="C157" s="45" t="inlineStr">
         <is>
-          <t>PF: articulador dele em Brasília; Vorcaro pagou R$ 67,5 mi por projeto eólico de Faria, que defende o valor</t>
+          <t>PF: articulador dele em Brasília. Vorcaro pagou R$ 67,5 mi por projeto eólico de Faria (piauí); ele defende o valor</t>
         </is>
       </c>
       <c r="D157" s="45" t="inlineStr">
@@ -15830,11 +16430,11 @@
         </is>
       </c>
       <c r="E157" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A157,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A157,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F157" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B157,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B157,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15860,11 +16460,11 @@
         </is>
       </c>
       <c r="E158" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A158,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A158,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F158" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B158,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B158,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15890,11 +16490,11 @@
         </is>
       </c>
       <c r="E159" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A159,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A159,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F159" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B159,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B159,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15920,11 +16520,11 @@
         </is>
       </c>
       <c r="E160" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A160,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A160,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F160" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B160,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B160,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15950,11 +16550,11 @@
         </is>
       </c>
       <c r="E161" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A161,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A161,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F161" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B161,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B161,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -15980,11 +16580,11 @@
         </is>
       </c>
       <c r="E162" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A162,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A162,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F162" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B162,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B162,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16010,11 +16610,11 @@
         </is>
       </c>
       <c r="E163" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A163,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A163,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F163" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B163,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B163,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16040,11 +16640,11 @@
         </is>
       </c>
       <c r="E164" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A164,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A164,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F164" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B164,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B164,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16070,11 +16670,11 @@
         </is>
       </c>
       <c r="E165" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A165,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A165,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F165" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B165,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B165,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16100,11 +16700,11 @@
         </is>
       </c>
       <c r="E166" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A166,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A166,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F166" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B166,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B166,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16130,11 +16730,11 @@
         </is>
       </c>
       <c r="E167" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A167,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A167,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F167" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B167,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B167,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16160,11 +16760,11 @@
         </is>
       </c>
       <c r="E168" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A168,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A168,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F168" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B168,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B168,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16190,11 +16790,11 @@
         </is>
       </c>
       <c r="E169" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A169,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A169,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F169" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B169,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B169,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16220,11 +16820,11 @@
         </is>
       </c>
       <c r="E170" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A170,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A170,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F170" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B170,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B170,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16250,11 +16850,11 @@
         </is>
       </c>
       <c r="E171" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A171,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A171,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F171" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B171,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B171,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16280,11 +16880,11 @@
         </is>
       </c>
       <c r="E172" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A172,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A172,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F172" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B172,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B172,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16310,11 +16910,11 @@
         </is>
       </c>
       <c r="E173" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A173,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A173,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F173" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B173,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B173,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16340,11 +16940,11 @@
         </is>
       </c>
       <c r="E174" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A174,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A174,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F174" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B174,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B174,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16370,11 +16970,11 @@
         </is>
       </c>
       <c r="E175" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A175,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A175,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F175" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B175,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B175,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16400,11 +17000,11 @@
         </is>
       </c>
       <c r="E176" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A176,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A176,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F176" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B176,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B176,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16430,11 +17030,11 @@
         </is>
       </c>
       <c r="E177" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A177,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A177,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F177" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B177,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B177,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16460,11 +17060,11 @@
         </is>
       </c>
       <c r="E178" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A178,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A178,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F178" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B178,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B178,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16490,11 +17090,11 @@
         </is>
       </c>
       <c r="E179" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A179,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A179,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F179" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B179,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B179,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16520,11 +17120,11 @@
         </is>
       </c>
       <c r="E180" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A180,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A180,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F180" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B180,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B180,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16550,11 +17150,11 @@
         </is>
       </c>
       <c r="E181" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A181,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A181,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F181" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B181,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B181,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16580,11 +17180,11 @@
         </is>
       </c>
       <c r="E182" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A182,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A182,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F182" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B182,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B182,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16610,11 +17210,11 @@
         </is>
       </c>
       <c r="E183" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A183,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A183,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F183" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B183,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B183,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16640,11 +17240,11 @@
         </is>
       </c>
       <c r="E184" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A184,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A184,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F184" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B184,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B184,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16670,11 +17270,11 @@
         </is>
       </c>
       <c r="E185" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A185,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A185,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F185" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B185,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B185,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16700,11 +17300,11 @@
         </is>
       </c>
       <c r="E186" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A186,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A186,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F186" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B186,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B186,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16730,11 +17330,11 @@
         </is>
       </c>
       <c r="E187" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A187,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A187,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F187" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B187,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B187,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16760,11 +17360,11 @@
         </is>
       </c>
       <c r="E188" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A188,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A188,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F188" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B188,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B188,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16790,11 +17390,11 @@
         </is>
       </c>
       <c r="E189" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A189,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A189,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F189" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B189,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B189,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16820,11 +17420,11 @@
         </is>
       </c>
       <c r="E190" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A190,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A190,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F190" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B190,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B190,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16850,11 +17450,11 @@
         </is>
       </c>
       <c r="E191" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A191,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A191,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F191" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B191,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B191,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16880,11 +17480,11 @@
         </is>
       </c>
       <c r="E192" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A192,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A192,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F192" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B192,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B192,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16910,11 +17510,11 @@
         </is>
       </c>
       <c r="E193" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A193,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A193,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F193" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B193,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B193,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16940,11 +17540,11 @@
         </is>
       </c>
       <c r="E194" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A194,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A194,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F194" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B194,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B194,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -16970,11 +17570,11 @@
         </is>
       </c>
       <c r="E195" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A195,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A195,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F195" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B195,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B195,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -17000,11 +17600,11 @@
         </is>
       </c>
       <c r="E196" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A196,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A196,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F196" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B196,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B196,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -17030,11 +17630,11 @@
         </is>
       </c>
       <c r="E197" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A197,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A197,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F197" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B197,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B197,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>
@@ -17060,11 +17660,701 @@
         </is>
       </c>
       <c r="E198" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(A198,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A198,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
       <c r="F198" s="45">
-        <f>INDEX(Nodes!$B$2:$B$91,MATCH(B198,Nodes!$A$2:$A$91,0))</f>
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B198,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="45" t="inlineStr">
+        <is>
+          <t>rueda</t>
+        </is>
+      </c>
+      <c r="B199" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C199" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 2.712 interações (nov/2023 a set/2025); 36% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D199" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E199" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A199,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F199" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B199,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="45" t="inlineStr">
+        <is>
+          <t>rueda</t>
+        </is>
+      </c>
+      <c r="B200" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C200" s="45" t="inlineStr">
+        <is>
+          <t>Admitiu à piauí ter advogado para o Master (“dezenas de pareceres e centenas de reuniões”); diz que só teve “contatos sociais eventuais” com Vorcaro</t>
+        </is>
+      </c>
+      <c r="D200" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E200" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A200,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F200" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B200,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="45" t="inlineStr">
+        <is>
+          <t>rueda</t>
+        </is>
+      </c>
+      <c r="B201" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C201" s="45" t="inlineStr">
+        <is>
+          <t>Proposta de delação de Vorcaro, rejeitada pela PF e pela PGR (UOL, set/2026), diz que ele e ACM Neto receberiam 10% dos aportes de previdências; os dois negam</t>
+        </is>
+      </c>
+      <c r="D201" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E201" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A201,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F201" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B201,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="45" t="inlineStr">
+        <is>
+          <t>wajngarten</t>
+        </is>
+      </c>
+      <c r="B202" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C202" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 1.151 interações (mar a nov/2025); 7% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D202" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E202" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A202,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F202" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B202,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="45" t="inlineStr">
+        <is>
+          <t>wajngarten</t>
+        </is>
+      </c>
+      <c r="B203" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C203" s="45" t="inlineStr">
+        <is>
+          <t>Integra a defesa de Vorcaro na comunicação (desde o 1º semestre de 2025); o Master pagou ao menos R$ 3,8 mi à empresa dele em 2025 (Folha, documentos da Receita à CPI)</t>
+        </is>
+      </c>
+      <c r="D203" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E203" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A203,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F203" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B203,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="45" t="inlineStr">
+        <is>
+          <t>mantega</t>
+        </is>
+      </c>
+      <c r="B204" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C204" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 323 interações (jun/2024 a nov/2025); 6% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D204" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E204" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A204,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F204" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B204,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="45" t="inlineStr">
+        <is>
+          <t>mantega</t>
+        </is>
+      </c>
+      <c r="B205" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C205" s="45" t="inlineStr">
+        <is>
+          <t>Diz à piauí ter sido contratado pelo Master em 2024–2025 para consultoria econômica</t>
+        </is>
+      </c>
+      <c r="D205" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E205" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A205,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F205" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B205,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="45" t="inlineStr">
+        <is>
+          <t>mantega</t>
+        </is>
+      </c>
+      <c r="B206" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C206" s="45" t="inlineStr">
+        <is>
+          <t>Mensagens (Estadão) mostram Vorcaro e um advogado tentando levá-lo a Lula em 2025; o Planalto diz que Lula recebeu Vorcaro só uma vez (04/12/2024), com Mantega</t>
+        </is>
+      </c>
+      <c r="D206" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E206" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A206,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F206" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B206,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="45" t="inlineStr">
+        <is>
+          <t>doria</t>
+        </is>
+      </c>
+      <c r="B207" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C207" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 2.309 interações (abr/2022 a nov/2025); 99,7% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D207" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E207" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A207,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F207" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B207,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="45" t="inlineStr">
+        <is>
+          <t>doria</t>
+        </is>
+      </c>
+      <c r="B208" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C208" s="45" t="inlineStr">
+        <is>
+          <t>Mensagem de maio/2025 (confirmada por sua assessoria): disse estar “preocupado” e propôs conversa reservada; ele diz que foi “gesto cordial”</t>
+        </is>
+      </c>
+      <c r="D208" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E208" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A208,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F208" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B208,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="45" t="inlineStr">
+        <is>
+          <t>bacelar</t>
+        </is>
+      </c>
+      <c r="B209" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C209" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 597 interações (jul/2024 a nov/2025); 98% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D209" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E209" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A209,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F209" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B209,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="45" t="inlineStr">
+        <is>
+          <t>bacelar</t>
+        </is>
+      </c>
+      <c r="B210" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C210" s="45" t="inlineStr">
+        <is>
+          <t>PF achou, em endereço ligado a Vorcaro, documento com o nome dele: opção de compra de terreno em Trancoso (BA), ~R$ 250 mi. O papel não cita Vorcaro; Bacelar diz que o negócio não se concretizou</t>
+        </is>
+      </c>
+      <c r="D210" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E210" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A210,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F210" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B210,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="45" t="inlineStr">
+        <is>
+          <t>feitosa</t>
+        </is>
+      </c>
+      <c r="B211" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C211" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 446 interações (abr/2024 a mai/2025); 85% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D211" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E211" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A211,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F211" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B211,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="45" t="inlineStr">
+        <is>
+          <t>feitosa</t>
+        </is>
+      </c>
+      <c r="B212" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C212" s="45" t="inlineStr">
+        <is>
+          <t>Mensagens obtidas pela PF indicam que se ofereceu como ponte entre Vorcaro e Gilmar Mendes, de quem era cunhado; Gilmar nega que o jantar citado tenha ocorrido</t>
+        </is>
+      </c>
+      <c r="D212" s="45" t="inlineStr">
+        <is>
+          <t>Alegado ou contestado</t>
+        </is>
+      </c>
+      <c r="E212" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A212,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F212" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B212,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="45" t="inlineStr">
+        <is>
+          <t>faria</t>
+        </is>
+      </c>
+      <c r="B213" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C213" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 19.293 interações (out/2023 a nov/2025); 59% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D213" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E213" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A213,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F213" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B213,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="45" t="inlineStr">
+        <is>
+          <t>bianco</t>
+        </is>
+      </c>
+      <c r="B214" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C214" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 4.782 interações (jan/2024 a nov/2025); 13% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D214" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E214" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A214,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F214" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B214,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="45" t="inlineStr">
+        <is>
+          <t>ciro</t>
+        </is>
+      </c>
+      <c r="B215" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C215" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 3.967 interações (out/2023 a nov/2025); 3% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D215" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E215" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A215,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F215" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B215,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="45" t="inlineStr">
+        <is>
+          <t>motta</t>
+        </is>
+      </c>
+      <c r="B216" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C216" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 1.068 interações (mar/2024 a out/2025); 99% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D216" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E216" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A216,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F216" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B216,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="45" t="inlineStr">
+        <is>
+          <t>castro</t>
+        </is>
+      </c>
+      <c r="B217" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C217" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 463 interações (mai/2023 a nov/2025); 100% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D217" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E217" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A217,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F217" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B217,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="45" t="inlineStr">
+        <is>
+          <t>marcal</t>
+        </is>
+      </c>
+      <c r="B218" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C218" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 438 interações (ago/2024 a set/2025); 1% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D218" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E218" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A218,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F218" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B218,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="45" t="inlineStr">
+        <is>
+          <t>flavio</t>
+        </is>
+      </c>
+      <c r="B219" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C219" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 246 interações (dez/2024 a nov/2025); 53% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D219" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E219" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A219,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F219" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B219,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="45" t="inlineStr">
+        <is>
+          <t>frias</t>
+        </is>
+      </c>
+      <c r="B220" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C220" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 181 interações (dez/2024 a nov/2025); 60% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D220" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E220" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A220,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F220" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B220,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="45" t="inlineStr">
+        <is>
+          <t>cezinha</t>
+        </is>
+      </c>
+      <c r="B221" s="45" t="inlineStr">
+        <is>
+          <t>vorcaro</t>
+        </is>
+      </c>
+      <c r="C221" s="45" t="inlineStr">
+        <is>
+          <t>Contato no celular de Vorcaro: 34 interações (mar a mai/2025); 100% ainda legíveis. Mede volume, não conteúdo (piauí/InterSecLab)</t>
+        </is>
+      </c>
+      <c r="D221" s="45" t="inlineStr">
+        <is>
+          <t>Documentado</t>
+        </is>
+      </c>
+      <c r="E221" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A221,Nodes!$A$2:$A$97,0))</f>
+        <v/>
+      </c>
+      <c r="F221" s="45">
+        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B221,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
     </row>

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -1380,7 +1380,7 @@
       </c>
       <c r="J3" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K3" s="37" t="inlineStr">
@@ -1395,7 +1395,7 @@
       </c>
       <c r="M3" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site). 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="D4" s="37" t="inlineStr">
         <is>
-          <t>Irmã do contador; administra o escritório de advocacia de Flávio desde 2021. Em entrevista à Agência Pública (2022) disse que chegou ao escritório por indicação de Willer Tomaz.</t>
+          <t>Irmã do contador Alexandre Caetano dos Reis; é a administradora registrada do escritório de advocacia de Flávio na Receita. Em entrevista à Agência Pública (2022) disse que chegou ao escritório por indicação de Willer Tomaz; Willer disse à reportagem que não a conhece.</t>
         </is>
       </c>
       <c r="E4" s="37" t="inlineStr">
@@ -1447,22 +1447,22 @@
       </c>
       <c r="J4" s="37" t="inlineStr">
         <is>
-          <t>Pessoa privada: mantive só o papel público no caso.</t>
+          <t>Pessoa privada: mantive só o papel público no caso. 23/10/2026: retirei "desde 2021" (a Pública não informa quando ela começou) e incluí a negativa de Willer.</t>
         </is>
       </c>
       <c r="K4" s="37" t="inlineStr">
         <is>
-          <t>Bahia Notícias (link acima)</t>
+          <t>Agência Pública (06/2022) https://apublica.org/2022/06/firma-de-advocacia-de-flavio-bolsonaro-tem-contratos-consideraveis-diz-administradora/ | Bahia Notícias (levantamento do ICL) https://www.bahianoticias.com.br/noticia/321055-empresas-de-flavio-bolsonaro-e-do-careca-do-inss-dividem-a-mesma-sala-e-possuem-o-mesmo-contador</t>
         </is>
       </c>
       <c r="L4" s="37" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M4" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23/10/2026: fontes completadas; negativa de Willer incluída.</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D6" s="37" t="inlineStr">
         <is>
-          <t>Lobista/consultora (RL Consultoria e Intermediações), amiga de Lulinha. PF diz que ela recebeu cerca de R$ 1,5 mi em parcelas do Careca via a Brasília Consultoria Empresarial, que a PF chama de empresa de fachada. Defesa: tratativas de um projeto de canabidiol, sem relação com o INSS. Depôs à PF em 20/05/2026 negando ter repassado valores a Lulinha.</t>
+          <t>Lobista/consultora (RL Consultoria e Intermediações), amiga de Lulinha. Segundo o Correio da Manhã, teria recebido R$ 1,5 mi do Careca do INSS para tentar viabilizar um negócio de canabidiol com o Ministério da Saúde (o texto não atribui o valor à PF). Ela diz que os valores são honorários de consultoria e nega irregularidades; a defesa de Lulinha diz que ele não tem relação com os negócios dela. Depôs à PF em 20/05/2026 negando ter repassado valores a Lulinha.</t>
         </is>
       </c>
       <c r="E6" s="37" t="inlineStr">
@@ -1581,22 +1581,22 @@
       </c>
       <c r="J6" s="37" t="inlineStr">
         <is>
-          <t>Planilha diz "~R$ 1 mi"; a PF fala em ordem de R$ 300 mil e ~R$ 1,5 mi no total.</t>
+          <t>Planilha diz "~R$ 1 mi". Os R$ 1,5 mi vêm do Correio da Manhã, sem atribuição à PF; o Estado de Minas cita R$ 150 mil recebidos de Cleber Ribas. A afirmação anterior de que a PF chama a Brasília Consultoria Empresarial de empresa de fachada não foi confirmada nas matérias relidas em 23/10/2026 e foi retirada.</t>
         </is>
       </c>
       <c r="K6" s="37" t="inlineStr">
         <is>
-          <t>Poder360 (link acima) | Brasil Agro (link acima) | Gazeta do Povo (link na linha do Lulinha)</t>
+          <t>Estado de Minas (08/2026) https://www.em.com.br/politica/2026/08/7483581-quem-e-roberta-luchsinger-a-lobista-investigada-pela-pf.html | Correio da Manhã (08/2026) https://www.correiodamanha.com.br/politica/2026/08/312474-pf-investiga-ate-onde-ia-atuacao-de-lobista-em-nome-de-lulinha.html | Poder360: amiga de Lulinha nega repasses à PF https://www.poder360.com.br/poder-justica/amiga-de-lulinha-nega-ter-repassado-valores-do-careca-do-inss-a-pf/ | Brasil Agro https://brasilagro.com.br/conteudo/pf-apura-se-lulinha-foi-socio-oculto-de-careca-do-inss.html | Gazeta do Povo: defesa de Lulinha https://www.gazetadopovo.com.br/republica/defesa-de-lulinha-nega-irregularidades-apos-declaracoes-de-lobista-roberta-luchsinger/</t>
         </is>
       </c>
       <c r="L6" s="37" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M6" s="37" t="inlineStr">
         <is>
-          <t>Agora investigada por tráfico de influência e anuncia delação (17/10/2026).</t>
+          <t>Agora investigada por tráfico de influência e anuncia delação (17/10/2026). 23/10/2026: valores atribuídos à PF revisados; fontes completadas (revisão editorial).</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="D8" s="37" t="inlineStr">
         <is>
-          <t>61 anos. Dirigente formal de 14 empresas ligadas a Willer (WT, Jet Line, Friponor, RioPag, Ícaro Aviation etc.); assinou a escritura da mansão de Angra. Teve vínculo formal com o escritório de Willer entre mar/2019 e set/2020. Ao ser abordada disse ser doméstica; depois afirmou nunca ter sido empregada doméstica e que respondeu assim por medo. A defesa de Willer diz que é administradora de empresas.</t>
+          <t>Apontada pela Agência Pública (20/10/2026) como administradora de empresas de Willer Tomaz; em maio/2024 representava a Jet Line na compra da Direção Táxi Aéreo. Segundo o ICL Notícias (única fonte destes pontos): dirigente formal de 14 empresas ligadas a Willer (WT, Jet Line, Friponor, RioPag, Ícaro Aviation etc.); assinou a escritura da mansão de Angra; teve vínculo formal com o escritório de Willer entre mar/2019 e set/2020. Ao ser abordada disse ser doméstica; depois afirmou nunca ter sido empregada doméstica e que respondeu assim por medo. A defesa de Willer diz que é administradora de empresas.</t>
         </is>
       </c>
       <c r="E8" s="37" t="inlineStr">
@@ -1730,22 +1730,22 @@
       </c>
       <c r="J8" s="37" t="inlineStr">
         <is>
-          <t>Planilha diz "diz ser doméstica": ela depois desmentiu isso. Hipótese de "laranja" é da reportagem, não está comprovada.</t>
+          <t>Planilha diz "diz ser doméstica": ela depois desmentiu isso. Hipótese de "laranja" é da reportagem, não está comprovada. 23/10/2026: a Pública não traz posicionamento dela; os pontos atribuídos ao ICL não foram confirmados por outro veículo (O Povo e Correio da Manhã não a citam). Retirei a idade.</t>
         </is>
       </c>
       <c r="K8" s="37" t="inlineStr">
         <is>
-          <t>ICL Notícias https://iclnoticias.com.br/domestica-preside-empresas-fraude-flavio/</t>
+          <t>ICL Notícias https://iclnoticias.com.br/domestica-preside-empresas-fraude-flavio/ | Empresa ligada a Willer Tomaz foi administrada por diretor da Polícia Civil do DF (Agência Pública, 20/10/2026) https://apublica.org/?p=268402</t>
         </is>
       </c>
       <c r="L8" s="37" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M8" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23/10/2026: segunda fonte (Pública); idade retirada; pontos exclusivos do ICL atribuídos.</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1797,7 @@
       </c>
       <c r="J9" s="37" t="inlineStr">
         <is>
-          <t>Não achei notícia de 2026 sobre os inquéritos; só sobre a eleição.</t>
+          <t>Não achei notícia de 2026 sobre os inquéritos; só sobre a eleição. Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K9" s="37" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="M9" s="37" t="inlineStr">
         <is>
-          <t>Perdeu a reeleição em 04/10/2026.</t>
+          <t>Perdeu a reeleição em 04/10/2026. 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
       <c r="N9" s="24" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="B11" s="38" t="inlineStr">
         <is>
-          <t>Mulher e filhas de Flávio</t>
+          <t>Família de Flávio</t>
         </is>
       </c>
       <c r="C11" s="37" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J12" s="37" t="inlineStr">
         <is>
-          <t>Eleição baseada em página que reproduz dados do TSE; não achei a matéria de apuração.</t>
+          <t>Eleição baseada em página que reproduz dados do TSE; não achei a matéria de apuração. Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K12" s="37" t="inlineStr">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="M12" s="37" t="inlineStr">
         <is>
-          <t>Eleito senador por SC; deixou a Câmara de Vereadores. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
+          <t>Eleito senador por SC; deixou a Câmara de Vereadores. 21/10/2026: importado do acervo a verdade. (bolsomaster.site). 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
       <c r="N12" s="24" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="J15" s="37" t="inlineStr">
         <is>
-          <t>Planilha diz "19 meses sem depor": não consegui verificar. Candidatura em 2026: sem registro de que tenha sido formalizada (conforme a usuária; em mar/2026 ele só cogitava).</t>
+          <t>Planilha diz "19 meses sem depor": não consegui verificar. Candidatura em 2026: sem registro de que tenha sido formalizada (conforme a usuária; em mar/2026 ele só cogitava). Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K15" s="37" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="M15" s="37" t="inlineStr">
         <is>
-          <t>Sem candidatura formalizada em 2026 (confirmado pela usuária); cargo público e encontro com Flávio em set/2026. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
+          <t>Sem candidatura formalizada em 2026 (confirmado pela usuária); cargo público e encontro com Flávio em set/2026. 21/10/2026: importado do acervo a verdade. (bolsomaster.site). 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="J17" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K17" s="37" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="M17" s="37" t="inlineStr">
         <is>
-          <t>Preso na Papudinha desde 25/06/2026; delações rejeitadas; situação das provas no STF. 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
+          <t>Preso na Papudinha desde 25/06/2026; delações rejeitadas; situação das provas no STF. 21/10/2026: importado do acervo a verdade. (bolsomaster.site). 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
       <c r="N17" s="24" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="J18" s="37" t="inlineStr">
         <is>
-          <t>Não achei a venda do apartamento à WT nas fontes que abri.</t>
+          <t>Não achei a venda do apartamento à WT nas fontes que abri. Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K18" s="37" t="inlineStr">
         <is>
-          <t>Congresso em Foco https://www.congressoemfoco.com.br/noticia/116929/pf-prende-cunhado-de-vorcaro-suspeito-de-operar-esquema-do-master | Mateus Oliver (link na linha do Vorcaro) | Doações de Fabiano Zettel nas eleições de 2022 (cnnbrasil.com.br) https://www.cnnbrasil.com.br/politica/alvo-da-pf-doou-r-5-mi-para-campanhas-de-bolsonaro-e-tarcisio-em-2022/ | O apartamento de Fabiano Zettel e Willer Tomaz (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-zettel-tomaz-imovel-vila-nova-conceicao-sao-paulo/</t>
+          <t>Congresso em Foco https://www.congressoemfoco.com.br/noticia/116929/pf-prende-cunhado-de-vorcaro-suspeito-de-operar-esquema-do-master | Mateus Oliver Reporter (20/10/2026) https://www.mateusoliverreporter.com.br/2026/10/20/pgr-defende-manutencao-de-prisoes-no-caso-banco-master-e-permanencia-de-fachin-a-frente-de-decisoes-no-stf/ | Doações de Fabiano Zettel nas eleições de 2022 (cnnbrasil.com.br) https://www.cnnbrasil.com.br/politica/alvo-da-pf-doou-r-5-mi-para-campanhas-de-bolsonaro-e-tarcisio-em-2022/ | O apartamento de Fabiano Zettel e Willer Tomaz (piaui.uol.com.br) https://piaui.uol.com.br/web/flavio-bolsonaro-zettel-tomaz-imovel-vila-nova-conceicao-sao-paulo/</t>
         </is>
       </c>
       <c r="L18" s="37" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="M18" s="37" t="inlineStr">
         <is>
-          <t>Segue preso em 20/10/2026 (PGR contra soltura). 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
+          <t>Segue preso em 20/10/2026 (PGR contra soltura). 21/10/2026: importado do acervo a verdade. (bolsomaster.site). 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
       <c r="N18" s="24" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="D21" s="37" t="inlineStr">
         <is>
-          <t>Não pesquisado: pessoa privada e não nomeada.</t>
+          <t>Não pesquisado: pessoa privada e não nomeada. Funcionário da casa que, segundo a piauí, trocava mensagens com Vorcaro sobre a organização das festas, entre elas a de 28/02/2025.</t>
         </is>
       </c>
       <c r="E21" s="37" t="inlineStr">
@@ -2711,17 +2711,17 @@
       </c>
       <c r="K21" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Festas no triplex de Vorcaro, diz revista (Agenda do Poder, 16/10/2026, reproduz a piauí) https://agendadopoder.com.br/vorcaro-promoveu-festa-com-garotas-de-programa-para-kassio-nunes-marques-diz-revista/</t>
         </is>
       </c>
       <c r="L21" s="37" t="inlineStr">
         <is>
-          <t>20/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M21" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23/10/2026: retirada a ligação com ministro (mensagens não o identificam).</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
       </c>
       <c r="D22" s="37" t="inlineStr">
         <is>
-          <t>Não pesquisado: pessoas privadas, não nomeadas, incluindo uma de 19 anos. Não faz sentido (nem é seguro) montar perfil.</t>
+          <t>Não pesquisado: pessoas privadas e não nomeadas. Não faz sentido (nem é seguro) montar perfil.</t>
         </is>
       </c>
       <c r="E22" s="37" t="inlineStr">
@@ -2949,7 +2949,7 @@
       </c>
       <c r="B25" s="38" t="inlineStr">
         <is>
-          <t>Antônio Marcos da Silva</t>
+          <t>Ex-possuidor da mansão (nome não confirmado)</t>
         </is>
       </c>
       <c r="C25" s="37" t="inlineStr">
@@ -3369,7 +3369,7 @@
       </c>
       <c r="J30" s="37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K30" s="37" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="M30" s="37" t="inlineStr">
         <is>
-          <t>Eleito governador do Paraná no 1º turno (04/10/2026). 21/10/2026: importado do acervo a verdade. (bolsomaster.site).</t>
+          <t>Eleito governador do Paraná no 1º turno (04/10/2026). 21/10/2026: importado do acervo a verdade. (bolsomaster.site). 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
       <c r="N30" s="24" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="J32" s="37" t="inlineStr">
         <is>
-          <t>Dados do acervo a verdade.; fontes não reverificadas uma a uma. Os levantamentos de contratos do ITER (52 contratos e R$ 8,2 mi; 55 contratos e R$ 10,8 mi) são recortes diferentes e não se somam.</t>
+          <t>Dados do acervo a verdade.; fontes não reverificadas uma a uma. Os levantamentos de contratos do ITER (52 contratos e R$ 8,2 mi; 55 contratos e R$ 10,8 mi) são recortes diferentes e não se somam. Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K32" s="37" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="M32" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada.</t>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada. 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
       <c r="N32" s="24" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="J33" s="37" t="inlineStr">
         <is>
-          <t>Dados do acervo a verdade.; fontes não reverificadas uma a uma. Contato no celular de Vorcaro (piauí, 19/10/2026): Respondeu à piauí que deixou o setor público em dez/2022 e conheceu Vorcaro no fim de 2023. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
+          <t>Dados do acervo a verdade.; fontes não reverificadas uma a uma. Contato no celular de Vorcaro (piauí, 19/10/2026): Respondeu à piauí que deixou o setor público em dez/2022 e conheceu Vorcaro no fim de 2023. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis. Resposta do citado: ele defende o valor do projeto eólico (piauí); demais pontos sem resposta localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K33" s="37" t="inlineStr">
@@ -3630,7 +3630,7 @@
       </c>
       <c r="M33" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada. 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem.</t>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada. 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem. 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
       <c r="N33" s="24" t="inlineStr">
@@ -3697,7 +3697,7 @@
       </c>
       <c r="J34" s="37" t="inlineStr">
         <is>
-          <t>Situação de investigado vem do PDF do acervo; não reverificada. Contato no celular de Vorcaro (piauí, 19/10/2026): A reportagem da piauí não reproduz a resposta dele. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
+          <t>Situação de investigado vem do PDF do acervo; não reverificada. Contato no celular de Vorcaro (piauí, 19/10/2026): A reportagem da piauí não reproduz a resposta dele. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis. Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K34" s="37" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="M34" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada. 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem.</t>
+          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada. 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem. 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
       <c r="N34" s="24" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="G35" s="37" t="inlineStr">
         <is>
-          <t>Pedido de investigação por estupro de vulnerável arquivado pelo ministro Gilmar Mendes em out/2026, por falta de indícios suficientes. Ele nega.</t>
+          <t>Sem processo ou investigação em andamento nas fontes consultadas.</t>
         </is>
       </c>
       <c r="H35" s="39" t="inlineStr">
@@ -3779,22 +3779,22 @@
       </c>
       <c r="J35" s="37" t="inlineStr">
         <is>
-          <t>A PGR também pediu o arquivamento; ele diz que a acusação é falsa e move ações contra quem a levou adiante. O PDF original diz que ele “é investigado”; isso está desatualizado desde o arquivamento (Folha e UOL, 06/10/2026).</t>
+          <t>Perfil limitado ao papel na chapa. Em 23/10/2026 retirei a menção a pedido de investigação já arquivado: não é uma conexão com os demais nós.</t>
         </is>
       </c>
       <c r="K35" s="37" t="inlineStr">
         <is>
-          <t>Alfredo Gaspar: pedido de investigação arquivado (metropoles.com) https://www.metropoles.com/colunas/igor-gadelha/denuncia-de-suposto-estupro-contra-vice-de-flavio-deve-avancar-no-stf | Alfredo Gaspar: pedido de investigação arquivado (folha.uol.com.br) https://www1.folha.uol.com.br/poder/2026/10/gilmar-arquiva-pedido-de-investigacao-contra-vice-de-flavio-bolsonaro-por-suspeita-de-estupro.shtml | Alfredo Gaspar: pedido de investigação arquivado (noticias.uol.com.br) https://noticias.uol.com.br/eleicoes/2026/10/06/gilmar-mendes-arquiva-stf-suspeita-estupro-alfredo-gaspar-vice-flavio.ghtm</t>
+          <t>Alfredo Gaspar, vice na chapa de Flávio (folha.uol.com.br) https://www1.folha.uol.com.br/poder/2026/10/gilmar-arquiva-pedido-de-investigacao-contra-vice-de-flavio-bolsonaro-por-suspeita-de-estupro.shtml | Alfredo Gaspar, vice na chapa de Flávio (noticias.uol.com.br) https://noticias.uol.com.br/eleicoes/2026/10/06/gilmar-mendes-arquiva-stf-suspeita-estupro-alfredo-gaspar-vice-flavio.ghtm | Alfredo Gaspar, vice na chapa de Flávio (dgabc.com.br) https://www.dgabc.com.br/Noticia/4351319/gilmar-arquiva-pedido-de-investigacao-por-suspeita-de-estupro-contra-vice-de-flavio</t>
         </is>
       </c>
       <c r="L35" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M35" s="37" t="inlineStr">
         <is>
-          <t>21/10/2026: importado do acervo a verdade. (bolsomaster.site) (perfil novo). 22/10/2026: foto adicionada.</t>
+          <t>23/10/2026: retirada a menção a pedido de investigação arquivado (revisão editorial).</t>
         </is>
       </c>
       <c r="N35" s="24" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="J39" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K39" s="24" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="M39" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
       <c r="N39" s="24" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="D46" s="24" t="inlineStr">
         <is>
-          <t>Apartamento de Daniel Vorcaro no Itaim Bibi, em São Paulo. Segundo a piauí, com base em relatos de promoters e mensagens, recebia às quartas e quintas festas fechadas com garotas de programa. A reportagem cita entre os frequentadores o ministro Nunes Marques e o filho Kevin, e o ex-ministro Fábio Faria.</t>
+          <t>Triplex no Itaim Bibi, em São Paulo, ligado a Daniel Vorcaro; em fev/2025 o imóvel pertencia à Super Empreendimentos e Participações, empresa que teve o pastor Fabiano Zettel entre os diretores (levantamento do ICL em cartório). Segundo a piauí, com base em ~125 mensagens do celular de Vorcaro e relatos de funcionários, recebia festas fechadas com garotas de programa.</t>
         </is>
       </c>
       <c r="E46" s="24" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="G46" s="24" t="inlineStr">
         <is>
-          <t>Não há processo sobre o imóvel nas fontes. As festas aparecem em mensagens obtidas pela PF e em reportagens.</t>
+          <t>Não há processo sobre o imóvel nas fontes. As festas aparecem em mensagens do celular de Vorcaro apreendido pela PF e em reportagens (piauí, UOL, Metrópoles).</t>
         </is>
       </c>
       <c r="H46" s="24" t="inlineStr">
@@ -4576,22 +4576,22 @@
       </c>
       <c r="J46" s="24" t="inlineStr">
         <is>
-          <t>O gabinete de Nunes Marques nega contato com Vorcaro. Os relatos não foram verificados de forma independente pela imprensa que os reproduziu.</t>
+          <t>Os relatos não foram verificados de forma independente pela imprensa que os reproduziu. Em 23/10/2026 foram retiradas as menções a frequentadores nomeados, por falta de confirmação nas mensagens. Link da reportagem original da piauí não localizado; ela é citada via Agenda do Poder.</t>
         </is>
       </c>
       <c r="K46" s="24" t="inlineStr">
         <is>
-          <t>A semana de festas fechadas de Vorcaro (diariodepernambuco.com.br) https://www.diariodepernambuco.com.br/politica/2026/10/11725610-terca-no-bar-quarta-e-quinta-no-triplex-a-semana-de-festas-fechadas-de-vorcaro.html | Vorcaro coordenou noitada para Nunes Marques (diariodepernambuco.com.br) https://www.diariodepernambuco.com.br/politica/2026/10/11726793-vorcaro-coordenou-noitada-em-triplex-para-ministro-kassio-nunes-marques.html</t>
+          <t>A semana de festas fechadas de Vorcaro (diariodepernambuco.com.br) https://www.diariodepernambuco.com.br/politica/2026/10/11725610-terca-no-bar-quarta-e-quinta-no-triplex-a-semana-de-festas-fechadas-de-vorcaro.html | Festas no triplex de Vorcaro, diz revista (Agenda do Poder, 16/10/2026, reproduz a piauí) https://agendadopoder.com.br/vorcaro-promoveu-festa-com-garotas-de-programa-para-kassio-nunes-marques-diz-revista/</t>
         </is>
       </c>
       <c r="L46" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026</t>
+          <t>23/10/2026</t>
         </is>
       </c>
       <c r="M46" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: retiradas menções a frequentadores nomeados.</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="J51" s="24" t="inlineStr">
         <is>
-          <t>As reportagens não trazem resposta dele. Contato no celular de Vorcaro (piauí, 19/10/2026): Não respondeu à piauí. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis.</t>
+          <t>As reportagens não trazem resposta dele. Contato no celular de Vorcaro (piauí, 19/10/2026): Não respondeu à piauí. Os números de contato (piauí/InterSecLab, base 18/11/2025) medem volume de contato individual (WhatsApp e ligações), não conteúdo; mensagens expiradas ou apagadas não são recuperáveis. Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K51" s="24" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="M51" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem.</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: contato no celular de Vorcaro (piauí/InterSecLab) e resposta à reportagem. 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
       <c r="N51" s="24" t="inlineStr">
@@ -5053,7 +5053,7 @@
       </c>
       <c r="J52" s="24" t="inlineStr">
         <is>
-          <t>A indicação dele por Flávio é atribuída à Folha ("teria"). Ele não comentou até a publicação das reportagens.</t>
+          <t>A indicação dele por Flávio é atribuída à Folha ("teria"). Ele não comentou até a publicação das reportagens. Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K52" s="24" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="M52" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
     </row>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="J56" s="24" t="inlineStr">
         <is>
-          <t>As reportagens não trazem resposta dele.</t>
+          <t>As reportagens não trazem resposta dele. Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K56" s="24" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="M56" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
       <c r="N56" s="24" t="inlineStr">
@@ -6007,7 +6007,7 @@
       </c>
       <c r="J64" s="24" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K64" s="24" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="M64" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
       <c r="N64" s="24" t="inlineStr">
@@ -6243,71 +6243,19 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="24" t="inlineStr">
-        <is>
-          <t>orelha</t>
-        </is>
-      </c>
-      <c r="B68" s="24" t="inlineStr">
-        <is>
-          <t>Luís Carlos Felipe Martins (“Orelha”)</t>
-        </is>
-      </c>
-      <c r="C68" s="24" t="inlineStr">
-        <is>
-          <t>Flávio e família</t>
-        </is>
-      </c>
-      <c r="D68" s="24" t="inlineStr">
-        <is>
-          <t>Não consegui confirmar em fonte pública a identidade nem o histórico de "Orelha" como descritos na planilha (ex-PM ligado à milícia de Rio das Pedras, homenageado por Flávio e morto em 2021). O nó fica sem perfil detalhado até haver fonte.</t>
-        </is>
-      </c>
-      <c r="E68" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F68" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G68" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H68" s="24" t="inlineStr">
-        <is>
-          <t>Não pesquisado</t>
-        </is>
-      </c>
-      <c r="I68" s="24" t="inlineStr">
-        <is>
-          <t>Nada nas fontes.</t>
-        </is>
-      </c>
-      <c r="J68" s="24" t="inlineStr">
-        <is>
-          <t>Identidade não confirmada: mais vale faltar do que atribuir algo à pessoa errada.</t>
-        </is>
-      </c>
-      <c r="K68" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L68" s="24" t="inlineStr">
-        <is>
-          <t>22/10/2026</t>
-        </is>
-      </c>
-      <c r="M68" s="24" t="inlineStr">
-        <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
-        </is>
-      </c>
+      <c r="A68" s="24" t="n"/>
+      <c r="B68" s="24" t="n"/>
+      <c r="C68" s="24" t="n"/>
+      <c r="D68" s="24" t="n"/>
+      <c r="E68" s="24" t="n"/>
+      <c r="F68" s="24" t="n"/>
+      <c r="G68" s="24" t="n"/>
+      <c r="H68" s="24" t="n"/>
+      <c r="I68" s="24" t="n"/>
+      <c r="J68" s="24" t="n"/>
+      <c r="K68" s="24" t="n"/>
+      <c r="L68" s="24" t="n"/>
+      <c r="M68" s="24" t="n"/>
     </row>
     <row r="69">
       <c r="A69" s="24" t="inlineStr">
@@ -6424,7 +6372,7 @@
       </c>
       <c r="J70" s="24" t="inlineStr">
         <is>
-          <t>O total de 16 vem do vídeo de origem. A fonte reverificada nomeia seis homenageados denunciados e não confirma o total.</t>
+          <t>O total de 16 vem do vídeo de origem. A fonte reverificada nomeia seis homenageados denunciados e não confirma o total. Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K70" s="24" t="inlineStr">
@@ -6439,7 +6387,7 @@
       </c>
       <c r="M70" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
     </row>
@@ -7295,7 +7243,7 @@
       </c>
       <c r="J83" s="24" t="inlineStr">
         <is>
-          <t>Willer atribui o vínculo a um erro cadastral do banco.</t>
+          <t>Willer atribui o vínculo a um erro cadastral do banco. Resposta do citado: não localizada nas fontes consultadas (checagem de 23/10/2026). Pedidos de correção ou resposta: ver “Sobre este mapa”.</t>
         </is>
       </c>
       <c r="K83" s="24" t="inlineStr">
@@ -7310,7 +7258,7 @@
       </c>
       <c r="M83" s="24" t="inlineStr">
         <is>
-          <t>22/10/2026: rodada contexto e imagens (perfil novo).</t>
+          <t>22/10/2026: rodada contexto e imagens (perfil novo). 23/10/2026: campo de resposta do citado incluído.</t>
         </is>
       </c>
       <c r="N83" s="24" t="inlineStr">
@@ -8467,7 +8415,7 @@
       </c>
       <c r="E5" s="45" t="inlineStr">
         <is>
-          <t>Irmã do contador; administra o escritório de Flávio</t>
+          <t>Irmã do contador; administradora registrada do escritório de Flávio</t>
         </is>
       </c>
       <c r="F5" s="45">
@@ -8529,7 +8477,7 @@
       </c>
       <c r="E7" s="45" t="inlineStr">
         <is>
-          <t>Amiga de Lulinha; recebeu ~R$ 1 mi de empresa de fachada do Careca</t>
+          <t>Amiga de Lulinha; segundo o Correio da Manhã, teria recebido R$ 1,5 mi do Careca; ela nega irregularidades</t>
         </is>
       </c>
       <c r="F7" s="45">
@@ -8743,7 +8691,7 @@
       </c>
       <c r="E13" s="45" t="inlineStr">
         <is>
-          <t>61 anos; diz ser doméstica; figura à frente de 14 empresas</t>
+          <t>Apontada como administradora de empresas de Willer (Agência Pública); diz que respondeu "doméstica" por medo (ICL)</t>
         </is>
       </c>
       <c r="F13" s="45">
@@ -8985,7 +8933,7 @@
       </c>
       <c r="B20" s="45" t="inlineStr">
         <is>
-          <t>Mulher e filhas de Flávio</t>
+          <t>Família de Flávio</t>
         </is>
       </c>
       <c r="C20" s="45" t="inlineStr">
@@ -9000,7 +8948,7 @@
       </c>
       <c r="E20" s="45" t="inlineStr">
         <is>
-          <t>Voaram no jato em jan/2025</t>
+          <t>Passageiros do jato em jan/2025</t>
         </is>
       </c>
       <c r="F20" s="45">
@@ -9559,7 +9507,7 @@
       </c>
       <c r="E37" s="45" t="inlineStr">
         <is>
-          <t>Agenciadas; entre elas uma ucraniana de 19 anos</t>
+          <t>Agenciadas para as festas</t>
         </is>
       </c>
       <c r="F37" s="45">
@@ -9660,7 +9608,7 @@
       </c>
       <c r="E40" s="45" t="inlineStr">
         <is>
-          <t>Palco das festas</t>
+          <t>Palco das festas (segundo a piauí)</t>
         </is>
       </c>
       <c r="F40" s="45">
@@ -9781,7 +9729,7 @@
       </c>
       <c r="B44" s="45" t="inlineStr">
         <is>
-          <t>Antônio Marcos da Silva</t>
+          <t>Ex-possuidor da mansão (nome não confirmado)</t>
         </is>
       </c>
       <c r="C44" s="45" t="inlineStr">
@@ -9796,7 +9744,7 @@
       </c>
       <c r="E44" s="45" t="inlineStr">
         <is>
-          <t>Dono da mansão; ouviu Flávio chamar Willer de sócio</t>
+          <t>Ex-possuidor da mansão; testemunha segundo as fontes</t>
         </is>
       </c>
       <c r="F44" s="45">
@@ -11004,35 +10952,12 @@
       <c r="J77" s="24" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="45" t="inlineStr">
-        <is>
-          <t>orelha</t>
-        </is>
-      </c>
-      <c r="B78" s="45" t="inlineStr">
-        <is>
-          <t>Luís Carlos Felipe Martins (“Orelha”)</t>
-        </is>
-      </c>
-      <c r="C78" s="45" t="inlineStr">
-        <is>
-          <t>Pessoa</t>
-        </is>
-      </c>
-      <c r="D78" s="45" t="inlineStr">
-        <is>
-          <t>Flávio e família</t>
-        </is>
-      </c>
-      <c r="E78" s="45" t="inlineStr">
-        <is>
-          <t>Ex-PM expulso, ligado à milícia de Rio das Pedras; homenageado por Flávio; morto em 2021</t>
-        </is>
-      </c>
-      <c r="F78" s="45">
-        <f>COUNTIF(Edges!$A$2:$A$221,A78)+COUNTIF(Edges!$B$2:$B$221,A78)</f>
-        <v/>
-      </c>
+      <c r="A78" s="45" t="n"/>
+      <c r="B78" s="45" t="n"/>
+      <c r="C78" s="45" t="n"/>
+      <c r="D78" s="45" t="n"/>
+      <c r="E78" s="45" t="n"/>
+      <c r="F78" s="45" t="n"/>
       <c r="G78" s="24" t="n"/>
       <c r="H78" s="24" t="n"/>
       <c r="I78" s="24" t="n"/>
@@ -11166,7 +11091,7 @@
       </c>
       <c r="E82" s="45" t="inlineStr">
         <is>
-          <t>Vice na chapa de Flávio; pedido de investigação arquivado pelo STF (out/2026); nega</t>
+          <t>Vice na chapa de Flávio</t>
         </is>
       </c>
       <c r="F82" s="45">
@@ -11776,7 +11701,7 @@
       </c>
       <c r="D2" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E2" s="45">
@@ -11806,7 +11731,7 @@
       </c>
       <c r="D3" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E3" s="45">
@@ -11836,7 +11761,7 @@
       </c>
       <c r="D4" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E4" s="45">
@@ -11866,7 +11791,7 @@
       </c>
       <c r="D5" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E5" s="45">
@@ -11896,7 +11821,7 @@
       </c>
       <c r="D6" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E6" s="45">
@@ -11921,12 +11846,12 @@
       </c>
       <c r="C7" s="45" t="inlineStr">
         <is>
-          <t>Teria indicado a irmã ao escritório de Flávio</t>
+          <t>Ela diz que veio por indicação dele; Willer diz à Pública que não a conhece</t>
         </is>
       </c>
       <c r="D7" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Alegado ou contestado</t>
         </is>
       </c>
       <c r="E7" s="45">
@@ -11956,7 +11881,7 @@
       </c>
       <c r="D8" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E8" s="45">
@@ -11986,7 +11911,7 @@
       </c>
       <c r="D9" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E9" s="45">
@@ -12016,7 +11941,7 @@
       </c>
       <c r="D10" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E10" s="45">
@@ -12106,7 +12031,7 @@
       </c>
       <c r="D13" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E13" s="45">
@@ -12136,7 +12061,7 @@
       </c>
       <c r="D14" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E14" s="45">
@@ -12166,7 +12091,7 @@
       </c>
       <c r="D15" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E15" s="45">
@@ -12196,7 +12121,7 @@
       </c>
       <c r="D16" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E16" s="45">
@@ -12226,7 +12151,7 @@
       </c>
       <c r="D17" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E17" s="45">
@@ -12256,7 +12181,7 @@
       </c>
       <c r="D18" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E18" s="45">
@@ -12286,7 +12211,7 @@
       </c>
       <c r="D19" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E19" s="45">
@@ -12316,7 +12241,7 @@
       </c>
       <c r="D20" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E20" s="45">
@@ -12346,7 +12271,7 @@
       </c>
       <c r="D21" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E21" s="45">
@@ -12376,7 +12301,7 @@
       </c>
       <c r="D22" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E22" s="45">
@@ -12406,7 +12331,7 @@
       </c>
       <c r="D23" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E23" s="45">
@@ -12436,7 +12361,7 @@
       </c>
       <c r="D24" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E24" s="45">
@@ -12556,7 +12481,7 @@
       </c>
       <c r="D28" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E28" s="45">
@@ -12586,7 +12511,7 @@
       </c>
       <c r="D29" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E29" s="45">
@@ -12616,7 +12541,7 @@
       </c>
       <c r="D30" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E30" s="45">
@@ -12646,7 +12571,7 @@
       </c>
       <c r="D31" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E31" s="45">
@@ -12676,7 +12601,7 @@
       </c>
       <c r="D32" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E32" s="45">
@@ -12796,7 +12721,7 @@
       </c>
       <c r="D36" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E36" s="45">
@@ -12826,7 +12751,7 @@
       </c>
       <c r="D37" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E37" s="45">
@@ -12856,7 +12781,7 @@
       </c>
       <c r="D38" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E38" s="45">
@@ -12886,7 +12811,7 @@
       </c>
       <c r="D39" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E39" s="45">
@@ -12916,7 +12841,7 @@
       </c>
       <c r="D40" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E40" s="45">
@@ -12946,7 +12871,7 @@
       </c>
       <c r="D41" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E41" s="45">
@@ -12976,7 +12901,7 @@
       </c>
       <c r="D42" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E42" s="45">
@@ -13006,7 +12931,7 @@
       </c>
       <c r="D43" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E43" s="45">
@@ -13036,7 +12961,7 @@
       </c>
       <c r="D44" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E44" s="45">
@@ -13066,7 +12991,7 @@
       </c>
       <c r="D45" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E45" s="45">
@@ -13096,7 +13021,7 @@
       </c>
       <c r="D46" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E46" s="45">
@@ -13126,7 +13051,7 @@
       </c>
       <c r="D47" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E47" s="45">
@@ -13156,7 +13081,7 @@
       </c>
       <c r="D48" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E48" s="45">
@@ -13186,7 +13111,7 @@
       </c>
       <c r="D49" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E49" s="45">
@@ -13216,7 +13141,7 @@
       </c>
       <c r="D50" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E50" s="45">
@@ -13246,7 +13171,7 @@
       </c>
       <c r="D51" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E51" s="45">
@@ -13276,7 +13201,7 @@
       </c>
       <c r="D52" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E52" s="45">
@@ -13306,7 +13231,7 @@
       </c>
       <c r="D53" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E53" s="45">
@@ -13336,7 +13261,7 @@
       </c>
       <c r="D54" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E54" s="45">
@@ -13366,7 +13291,7 @@
       </c>
       <c r="D55" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E55" s="45">
@@ -13396,7 +13321,7 @@
       </c>
       <c r="D56" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Alegado ou contestado</t>
         </is>
       </c>
       <c r="E56" s="45">
@@ -13426,7 +13351,7 @@
       </c>
       <c r="D57" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E57" s="45">
@@ -13456,7 +13381,7 @@
       </c>
       <c r="D58" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E58" s="45">
@@ -13486,7 +13411,7 @@
       </c>
       <c r="D59" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E59" s="45">
@@ -13606,7 +13531,7 @@
       </c>
       <c r="D63" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E63" s="45">
@@ -13619,34 +13544,12 @@
       </c>
     </row>
     <row r="64" ht="23.25" customHeight="1" s="25">
-      <c r="A64" s="45" t="inlineStr">
-        <is>
-          <t>triplex</t>
-        </is>
-      </c>
-      <c r="B64" s="45" t="inlineStr">
-        <is>
-          <t>nunes</t>
-        </is>
-      </c>
-      <c r="C64" s="45" t="inlineStr">
-        <is>
-          <t>Segundo a Piauí, frequentava as festas com o filho; ele nega irregularidades</t>
-        </is>
-      </c>
-      <c r="D64" s="45" t="inlineStr">
-        <is>
-          <t>Alegado ou contestado</t>
-        </is>
-      </c>
-      <c r="E64" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A64,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
-      <c r="F64" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B64,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
+      <c r="A64" s="45" t="n"/>
+      <c r="B64" s="45" t="n"/>
+      <c r="C64" s="45" t="n"/>
+      <c r="D64" s="45" t="n"/>
+      <c r="E64" s="45" t="n"/>
+      <c r="F64" s="45" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1" s="25">
       <c r="A65" s="45" t="inlineStr">
@@ -13786,7 +13689,7 @@
       </c>
       <c r="D69" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E69" s="45">
@@ -13829,34 +13732,12 @@
       </c>
     </row>
     <row r="71" ht="15" customHeight="1" s="25">
-      <c r="A71" s="45" t="inlineStr">
-        <is>
-          <t>mordomo</t>
-        </is>
-      </c>
-      <c r="B71" s="45" t="inlineStr">
-        <is>
-          <t>nunes</t>
-        </is>
-      </c>
-      <c r="C71" s="45" t="inlineStr">
-        <is>
-          <t>Relatou “ministro com cinco meninas”</t>
-        </is>
-      </c>
-      <c r="D71" s="45" t="inlineStr">
-        <is>
-          <t>Alegado ou contestado</t>
-        </is>
-      </c>
-      <c r="E71" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A71,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
-      <c r="F71" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B71,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
+      <c r="A71" s="45" t="n"/>
+      <c r="B71" s="45" t="n"/>
+      <c r="C71" s="45" t="n"/>
+      <c r="D71" s="45" t="n"/>
+      <c r="E71" s="45" t="n"/>
+      <c r="F71" s="45" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1" s="25">
       <c r="A72" s="45" t="inlineStr">
@@ -13876,7 +13757,7 @@
       </c>
       <c r="D72" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E72" s="45">
@@ -13966,7 +13847,7 @@
       </c>
       <c r="D75" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E75" s="45">
@@ -13996,7 +13877,7 @@
       </c>
       <c r="D76" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E76" s="45">
@@ -14026,7 +13907,7 @@
       </c>
       <c r="D77" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E77" s="45">
@@ -14056,7 +13937,7 @@
       </c>
       <c r="D78" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E78" s="45">
@@ -14086,7 +13967,7 @@
       </c>
       <c r="D79" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E79" s="45">
@@ -14116,7 +13997,7 @@
       </c>
       <c r="D80" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E80" s="45">
@@ -14146,7 +14027,7 @@
       </c>
       <c r="D81" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E81" s="45">
@@ -14176,7 +14057,7 @@
       </c>
       <c r="D82" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E82" s="45">
@@ -14206,7 +14087,7 @@
       </c>
       <c r="D83" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E83" s="45">
@@ -14236,7 +14117,7 @@
       </c>
       <c r="D84" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E84" s="45">
@@ -14266,7 +14147,7 @@
       </c>
       <c r="D85" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E85" s="45">
@@ -14296,7 +14177,7 @@
       </c>
       <c r="D86" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E86" s="45">
@@ -14326,7 +14207,7 @@
       </c>
       <c r="D87" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E87" s="45">
@@ -14356,7 +14237,7 @@
       </c>
       <c r="D88" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E88" s="45">
@@ -14386,7 +14267,7 @@
       </c>
       <c r="D89" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E89" s="45">
@@ -14416,7 +14297,7 @@
       </c>
       <c r="D90" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E90" s="45">
@@ -14446,7 +14327,7 @@
       </c>
       <c r="D91" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E91" s="45">
@@ -14476,7 +14357,7 @@
       </c>
       <c r="D92" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E92" s="45">
@@ -14506,7 +14387,7 @@
       </c>
       <c r="D93" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E93" s="45">
@@ -14536,7 +14417,7 @@
       </c>
       <c r="D94" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E94" s="45">
@@ -14566,7 +14447,7 @@
       </c>
       <c r="D95" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E95" s="45">
@@ -14596,7 +14477,7 @@
       </c>
       <c r="D96" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E96" s="45">
@@ -14686,7 +14567,7 @@
       </c>
       <c r="D99" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E99" s="45">
@@ -14741,12 +14622,12 @@
       </c>
       <c r="C101" s="45" t="inlineStr">
         <is>
-          <t>Empresa dele, segundo o vídeo</t>
+          <t>Empresa dele</t>
         </is>
       </c>
       <c r="D101" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E101" s="45">
@@ -14776,7 +14657,7 @@
       </c>
       <c r="D102" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E102" s="45">
@@ -14806,7 +14687,7 @@
       </c>
       <c r="D103" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E103" s="45">
@@ -14836,7 +14717,7 @@
       </c>
       <c r="D104" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E104" s="45">
@@ -14969,34 +14850,12 @@
       </c>
     </row>
     <row r="109" ht="15" customHeight="1" s="25">
-      <c r="A109" s="45" t="inlineStr">
-        <is>
-          <t>kevin</t>
-        </is>
-      </c>
-      <c r="B109" s="45" t="inlineStr">
-        <is>
-          <t>triplex</t>
-        </is>
-      </c>
-      <c r="C109" s="45" t="inlineStr">
-        <is>
-          <t>Segundo a Piauí, ia às festas com o pai</t>
-        </is>
-      </c>
-      <c r="D109" s="45" t="inlineStr">
-        <is>
-          <t>Alegado ou contestado</t>
-        </is>
-      </c>
-      <c r="E109" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A109,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
-      <c r="F109" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B109,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
+      <c r="A109" s="45" t="n"/>
+      <c r="B109" s="45" t="n"/>
+      <c r="C109" s="45" t="n"/>
+      <c r="D109" s="45" t="n"/>
+      <c r="E109" s="45" t="n"/>
+      <c r="F109" s="45" t="n"/>
     </row>
     <row r="110" ht="15" customHeight="1" s="25">
       <c r="A110" s="45" t="inlineStr">
@@ -15029,34 +14888,12 @@
       </c>
     </row>
     <row r="111" ht="23.25" customHeight="1" s="25">
-      <c r="A111" s="45" t="inlineStr">
-        <is>
-          <t>vorcaro</t>
-        </is>
-      </c>
-      <c r="B111" s="45" t="inlineStr">
-        <is>
-          <t>nunes</t>
-        </is>
-      </c>
-      <c r="C111" s="45" t="inlineStr">
-        <is>
-          <t>Mensagens apontam presença nas festas; Nunes diz nunca ter trocado mensagens com ele</t>
-        </is>
-      </c>
-      <c r="D111" s="45" t="inlineStr">
-        <is>
-          <t>Alegado ou contestado</t>
-        </is>
-      </c>
-      <c r="E111" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A111,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
-      <c r="F111" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B111,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
+      <c r="A111" s="45" t="n"/>
+      <c r="B111" s="45" t="n"/>
+      <c r="C111" s="45" t="n"/>
+      <c r="D111" s="45" t="n"/>
+      <c r="E111" s="45" t="n"/>
+      <c r="F111" s="45" t="n"/>
     </row>
     <row r="112" ht="15" customHeight="1" s="25">
       <c r="A112" s="45" t="inlineStr">
@@ -15076,7 +14913,7 @@
       </c>
       <c r="D112" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E112" s="45">
@@ -15106,7 +14943,7 @@
       </c>
       <c r="D113" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E113" s="45">
@@ -15196,7 +15033,7 @@
       </c>
       <c r="D116" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E116" s="45">
@@ -15226,7 +15063,7 @@
       </c>
       <c r="D117" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E117" s="45">
@@ -15256,7 +15093,7 @@
       </c>
       <c r="D118" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E118" s="45">
@@ -15286,7 +15123,7 @@
       </c>
       <c r="D119" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E119" s="45">
@@ -15316,7 +15153,7 @@
       </c>
       <c r="D120" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E120" s="45">
@@ -15466,7 +15303,7 @@
       </c>
       <c r="D125" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E125" s="45">
@@ -15496,7 +15333,7 @@
       </c>
       <c r="D126" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E126" s="45">
@@ -15526,7 +15363,7 @@
       </c>
       <c r="D127" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E127" s="45">
@@ -15556,7 +15393,7 @@
       </c>
       <c r="D128" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E128" s="45">
@@ -15629,34 +15466,12 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="45" t="inlineStr">
-        <is>
-          <t>zetel</t>
-        </is>
-      </c>
-      <c r="B131" s="45" t="inlineStr">
-        <is>
-          <t>nunes</t>
-        </is>
-      </c>
-      <c r="C131" s="45" t="inlineStr">
-        <is>
-          <t>Reportagem cita encontro com garota de programa em apartamento de Zettel; ministro nega irregularidades</t>
-        </is>
-      </c>
-      <c r="D131" s="45" t="inlineStr">
-        <is>
-          <t>Alegado ou contestado</t>
-        </is>
-      </c>
-      <c r="E131" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A131,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
-      <c r="F131" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B131,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
+      <c r="A131" s="45" t="n"/>
+      <c r="B131" s="45" t="n"/>
+      <c r="C131" s="45" t="n"/>
+      <c r="D131" s="45" t="n"/>
+      <c r="E131" s="45" t="n"/>
+      <c r="F131" s="45" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="45" t="inlineStr">
@@ -15676,7 +15491,7 @@
       </c>
       <c r="D132" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E132" s="45">
@@ -15706,7 +15521,7 @@
       </c>
       <c r="D133" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E133" s="45">
@@ -15886,7 +15701,7 @@
       </c>
       <c r="D139" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E139" s="45">
@@ -15916,7 +15731,7 @@
       </c>
       <c r="D140" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E140" s="45">
@@ -15976,7 +15791,7 @@
       </c>
       <c r="D142" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E142" s="45">
@@ -16006,7 +15821,7 @@
       </c>
       <c r="D143" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E143" s="45">
@@ -16036,7 +15851,7 @@
       </c>
       <c r="D144" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E144" s="45">
@@ -16156,7 +15971,7 @@
       </c>
       <c r="D148" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E148" s="45">
@@ -16186,7 +16001,7 @@
       </c>
       <c r="D149" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E149" s="45">
@@ -16246,7 +16061,7 @@
       </c>
       <c r="D151" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E151" s="45">
@@ -16336,7 +16151,7 @@
       </c>
       <c r="D154" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E154" s="45">
@@ -16366,7 +16181,7 @@
       </c>
       <c r="D155" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E155" s="45">
@@ -16396,7 +16211,7 @@
       </c>
       <c r="D156" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E156" s="45">
@@ -16516,7 +16331,7 @@
       </c>
       <c r="D160" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E160" s="45">
@@ -16546,7 +16361,7 @@
       </c>
       <c r="D161" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E161" s="45">
@@ -16606,7 +16421,7 @@
       </c>
       <c r="D163" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E163" s="45">
@@ -16666,7 +16481,7 @@
       </c>
       <c r="D165" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E165" s="45">
@@ -16696,7 +16511,7 @@
       </c>
       <c r="D166" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E166" s="45">
@@ -16786,7 +16601,7 @@
       </c>
       <c r="D169" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E169" s="45">
@@ -16876,7 +16691,7 @@
       </c>
       <c r="D172" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E172" s="45">
@@ -16889,64 +16704,20 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="45" t="inlineStr">
-        <is>
-          <t>flavio</t>
-        </is>
-      </c>
-      <c r="B173" s="45" t="inlineStr">
-        <is>
-          <t>orelha</t>
-        </is>
-      </c>
-      <c r="C173" s="45" t="inlineStr">
-        <is>
-          <t>Homenageou</t>
-        </is>
-      </c>
-      <c r="D173" s="45" t="inlineStr">
-        <is>
-          <t>Documentado</t>
-        </is>
-      </c>
-      <c r="E173" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A173,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
-      <c r="F173" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B173,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
+      <c r="A173" s="45" t="n"/>
+      <c r="B173" s="45" t="n"/>
+      <c r="C173" s="45" t="n"/>
+      <c r="D173" s="45" t="n"/>
+      <c r="E173" s="45" t="n"/>
+      <c r="F173" s="45" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="45" t="inlineStr">
-        <is>
-          <t>adriano</t>
-        </is>
-      </c>
-      <c r="B174" s="45" t="inlineStr">
-        <is>
-          <t>orelha</t>
-        </is>
-      </c>
-      <c r="C174" s="45" t="inlineStr">
-        <is>
-          <t>Ligados</t>
-        </is>
-      </c>
-      <c r="D174" s="45" t="inlineStr">
-        <is>
-          <t>Documentado</t>
-        </is>
-      </c>
-      <c r="E174" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(A174,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
-      <c r="F174" s="45">
-        <f>INDEX(Nodes!$B$2:$B$97,MATCH(B174,Nodes!$A$2:$A$97,0))</f>
-        <v/>
-      </c>
+      <c r="A174" s="45" t="n"/>
+      <c r="B174" s="45" t="n"/>
+      <c r="C174" s="45" t="n"/>
+      <c r="D174" s="45" t="n"/>
+      <c r="E174" s="45" t="n"/>
+      <c r="F174" s="45" t="n"/>
     </row>
     <row r="175">
       <c r="A175" s="45" t="inlineStr">
@@ -16966,7 +16737,7 @@
       </c>
       <c r="D175" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E175" s="45">
@@ -16996,7 +16767,7 @@
       </c>
       <c r="D176" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E176" s="45">
@@ -17116,7 +16887,7 @@
       </c>
       <c r="D180" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E180" s="45">
@@ -17146,7 +16917,7 @@
       </c>
       <c r="D181" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E181" s="45">
@@ -17206,7 +16977,7 @@
       </c>
       <c r="D183" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E183" s="45">
@@ -17236,7 +17007,7 @@
       </c>
       <c r="D184" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E184" s="45">
@@ -17326,7 +17097,7 @@
       </c>
       <c r="D187" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E187" s="45">
@@ -17356,7 +17127,7 @@
       </c>
       <c r="D188" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E188" s="45">
@@ -17416,7 +17187,7 @@
       </c>
       <c r="D190" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E190" s="45">
@@ -17476,7 +17247,7 @@
       </c>
       <c r="D192" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E192" s="45">
@@ -17506,7 +17277,7 @@
       </c>
       <c r="D193" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E193" s="45">
@@ -17536,7 +17307,7 @@
       </c>
       <c r="D194" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E194" s="45">
@@ -17596,7 +17367,7 @@
       </c>
       <c r="D196" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E196" s="45">
@@ -17686,7 +17457,7 @@
       </c>
       <c r="D199" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E199" s="45">
@@ -17716,7 +17487,7 @@
       </c>
       <c r="D200" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E200" s="45">
@@ -17776,7 +17547,7 @@
       </c>
       <c r="D202" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E202" s="45">
@@ -17806,7 +17577,7 @@
       </c>
       <c r="D203" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E203" s="45">
@@ -17836,7 +17607,7 @@
       </c>
       <c r="D204" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E204" s="45">
@@ -17866,7 +17637,7 @@
       </c>
       <c r="D205" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E205" s="45">
@@ -17926,7 +17697,7 @@
       </c>
       <c r="D207" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E207" s="45">
@@ -17956,7 +17727,7 @@
       </c>
       <c r="D208" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E208" s="45">
@@ -17986,7 +17757,7 @@
       </c>
       <c r="D209" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E209" s="45">
@@ -18016,7 +17787,7 @@
       </c>
       <c r="D210" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Alegado ou contestado</t>
         </is>
       </c>
       <c r="E210" s="45">
@@ -18046,7 +17817,7 @@
       </c>
       <c r="D211" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E211" s="45">
@@ -18106,7 +17877,7 @@
       </c>
       <c r="D213" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E213" s="45">
@@ -18136,7 +17907,7 @@
       </c>
       <c r="D214" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E214" s="45">
@@ -18166,7 +17937,7 @@
       </c>
       <c r="D215" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E215" s="45">
@@ -18196,7 +17967,7 @@
       </c>
       <c r="D216" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E216" s="45">
@@ -18226,7 +17997,7 @@
       </c>
       <c r="D217" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E217" s="45">
@@ -18256,7 +18027,7 @@
       </c>
       <c r="D218" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E218" s="45">
@@ -18286,7 +18057,7 @@
       </c>
       <c r="D219" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E219" s="45">
@@ -18316,7 +18087,7 @@
       </c>
       <c r="D220" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E220" s="45">
@@ -18346,7 +18117,7 @@
       </c>
       <c r="D221" s="45" t="inlineStr">
         <is>
-          <t>Documentado</t>
+          <t>Reportado</t>
         </is>
       </c>
       <c r="E221" s="45">

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -8913,7 +8913,7 @@
       </c>
       <c r="E19" s="46" t="inlineStr">
         <is>
-          <t>Senador; disputou a Presidência em 2026 e perdeu; nega irregularidades</t>
+          <t>Senador; nega irregularidades; disputou a Presidência em 2026 e perdeu</t>
         </is>
       </c>
       <c r="F19" s="46">

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -11638,13 +11638,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F221"/>
+  <dimension ref="A1:H221"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="14" customWidth="1" style="25" min="1" max="2"/>
     <col width="60" customWidth="1" style="25" min="3" max="3"/>
     <col width="22" customWidth="1" style="25" min="4" max="4"/>
     <col width="30" customWidth="1" style="25" min="5" max="6"/>
+    <col width="60" customWidth="1" style="25" min="7" max="7"/>
+    <col width="26" customWidth="1" style="25" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="26">
@@ -11676,6 +11678,16 @@
       <c r="F1" s="45" t="inlineStr">
         <is>
           <t>Target name</t>
+        </is>
+      </c>
+      <c r="G1" s="45" t="inlineStr">
+        <is>
+          <t>Fontes</t>
+        </is>
+      </c>
+      <c r="H1" s="45" t="inlineStr">
+        <is>
+          <t>Nota da fonte</t>
         </is>
       </c>
     </row>

--- a/data/mapa.xlsx
+++ b/data/mapa.xlsx
@@ -16440,6 +16440,16 @@
         <f>INDEX(Nodes!$B$2:$B$97,MATCH(B163,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
+      <c r="G163" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GP1 02/10/2026 https://www.gp1.com.br/brasil/noticia/2026/10/2/empresa-ligada-a-daniel-vorcaro-pagou-voo-de-r-117-milhao-usado-por-pablo-marcal-633016.html</t>
+        </is>
+      </c>
+      <c r="H163" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GP1 credita o Valor Econômico, que não consegui abrir.</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="23.85" customHeight="1" s="26">
       <c r="A164" s="46" t="inlineStr">
@@ -16679,6 +16689,16 @@
       <c r="F171" s="46">
         <f>INDEX(Nodes!$B$2:$B$97,MATCH(B171,Nodes!$A$2:$A$97,0))</f>
         <v/>
+      </c>
+      <c r="G171" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O Povo 25/04/2020 https://www.opovo.com.br/noticias/brasil/2020/04/25/materia-do-the-intercept-br-acusa-flavio-bolsonaro-de-envolvimento-com-milicia-e-esquema-de-rachadinhas.html</t>
+        </is>
+      </c>
+      <c r="H171" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O Povo resume a reportagem do Intercept Brasil, baseada em documentos do MP-RJ.</t>
+        </is>
       </c>
     </row>
     <row r="172" ht="15" customHeight="1" s="26">
@@ -17040,7 +17060,7 @@
       </c>
       <c r="C185" s="46" t="inlineStr">
         <is>
-          <t>Mesmo dono, administrador e endereço no Funchal; auditor ouvido pela piauí vê possível financiamento</t>
+          <t>Mesmo dono, administrador e endereço no Funchal; auditor ouvido pela piauí vê forte integração financeira entre as duas</t>
         </is>
       </c>
       <c r="D185" s="46" t="inlineStr">
@@ -17056,6 +17076,16 @@
         <f>INDEX(Nodes!$B$2:$B$97,MATCH(B185,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
+      <c r="G185" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O Povo/DW 22/10/2026 https://www.opovo.com.br/noticias/mundo/2026/10/22/o-que-se-sabe-sobre-suposto-elo-de-flavio-bolsonaro-com-esquema-de-bets.html</t>
+        </is>
+      </c>
+      <c r="H185" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credita a piauí. O auditor fala em forte integração financeira, não em financiamento.</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="23.85" customHeight="1" s="26">
       <c r="A186" s="46" t="inlineStr">
@@ -17266,6 +17296,16 @@
         <f>INDEX(Nodes!$B$2:$B$97,MATCH(B192,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
+      <c r="G192" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correio da Manhã 21/10/2026 https://www.correiodamanha.com.br/politica/2026/10/328716-aliado-de-flavio-bolsonaro-admitiu-ser-socio-de-empresa-da-loterj-apos-negar-ligacao-revela-e-mail.html</t>
+        </is>
+      </c>
+      <c r="H192" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credita a coluna de Malu Gaspar, em O Globo, que não consegui abrir.</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="23.85" customHeight="1" s="26">
       <c r="A193" s="46" t="inlineStr">
@@ -17340,7 +17380,7 @@
       </c>
       <c r="C195" s="46" t="inlineStr">
         <is>
-          <t>Busca em ago/2026: sala oculta, máquina de contar e malas vazias, sem dinheiro (Estadão); Willer nega uso irregular</t>
+          <t>Busca em ago/2026: sala-cofre e máquina de contar dinheiro (Metrópoles); a defesa diz que a estrutura atende transporte de valores e que nada foi encontrado</t>
         </is>
       </c>
       <c r="D195" s="46" t="inlineStr">
@@ -17356,6 +17396,16 @@
         <f>INDEX(Nodes!$B$2:$B$97,MATCH(B195,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
+      <c r="G195" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Metrópoles 22/10/2026 https://www.metropoles.com/colunas/mirelle-pinheiro/pf-acha-sala-secreta-e-maquina-de-contar-dinheiro-em-hangar-de-willer-tomaz</t>
+        </is>
+      </c>
+      <c r="H195" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Apuração do Metrópoles; não menciona malas. A ausência de dinheiro é afirmação da defesa, não achado da PF. Não localizei a matéria do Estadão antes citada.</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="15" customHeight="1" s="26">
       <c r="A196" s="46" t="inlineStr">
@@ -17580,7 +17630,7 @@
       </c>
       <c r="C203" s="46" t="inlineStr">
         <is>
-          <t>Integra a defesa de Vorcaro na comunicação (desde o 1º semestre de 2025); o Master pagou ao menos R$ 3,8 mi à empresa dele em 2025 (Folha, documentos da Receita à CPI)</t>
+          <t>Integra a defesa de Vorcaro na comunicação (desde o 1º semestre de 2025); o Master pagou ao menos R$ 3,8 mi à empresa dele (documentos da Receita à CPI do Crime, via CNN Brasil)</t>
         </is>
       </c>
       <c r="D203" s="46" t="inlineStr">
@@ -17596,6 +17646,16 @@
         <f>INDEX(Nodes!$B$2:$B$97,MATCH(B203,Nodes!$A$2:$A$97,0))</f>
         <v/>
       </c>
+      <c r="G203" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CNN Brasil 09/04/2026 https://www.cnnbrasil.com.br/politica/ex-secretario-de-bolsonaro-recebeu-r-38-milhoes-para-defender-vorcaro/</t>
+        </is>
+      </c>
+      <c r="H203" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A CNN cita documentos da Receita à CPI do Crime e não credita a Folha; também não informa o ano dos pagamentos.</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="23.85" customHeight="1" s="26">
       <c r="A204" s="46" t="inlineStr">
@@ -17670,7 +17730,7 @@
       </c>
       <c r="C206" s="46" t="inlineStr">
         <is>
-          <t>Mensagens (Estadão) mostram Vorcaro e um advogado tentando levá-lo a Lula em 2025; o Planalto diz que Lula recebeu Vorcaro só uma vez (04/12/2024), com Mantega</t>
+          <t>Mensagens mostram Vorcaro e seu advogado articulando chegar a Lula entre abr/2024 e jan/2025, com Mantega intercedendo (O Globo); o Planalto diz que Lula recebeu Vorcaro só uma vez (04/12/2024)</t>
         </is>
       </c>
       <c r="D206" s="46" t="inlineStr">
@@ -17685,6 +17745,16 @@
       <c r="F206" s="46">
         <f>INDEX(Nodes!$B$2:$B$97,MATCH(B206,Nodes!$A$2:$A$97,0))</f>
         <v/>
+      </c>
+      <c r="G206" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">InfoMoney/Agência O Globo 23/09/2026 https://www.infomoney.com.br/politica/mensagens-mostram-advogado-articulando-aproximacao-vorcaro-com-governo-lula/ | Gazeta do Povo https://www.gazetadopovo.com.br/republica/vorcaro-acionou-mantega-e-buscou-nova-reuniao-com-lula-em-2025/</t>
+        </is>
+      </c>
+      <c r="H206" s="46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">As duas remetem à apuração de O Globo (coluna Lauro Jardim); não são independentes entre si. Não localizei a matéria do Estadão antes citada.</t>
+        </is>
       </c>
     </row>
     <row r="207" ht="23.85" customHeight="1" s="26">
